--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\特殊用户标记\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3458A81-2EEF-46CA-8B41-F080006ADE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,21 +30,20 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
     <author>C</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -59,7 +52,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -68,13 +60,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">普通场 1
@@ -84,27 +75,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>押分筹码列表</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="K1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -113,7 +102,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -122,13 +110,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="M1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>阶段信息:[准备阶段时间-毫秒，押分阶段时间-毫秒，亮牌阶段时间-毫秒，结算阶段-毫秒]
@@ -137,13 +124,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>每笔投注进入房间水池比例
@@ -153,27 +139,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>净赢分*抽水比例</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="P1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -182,7 +166,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -191,14 +174,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="Q1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -207,7 +189,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -216,14 +197,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="R1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -232,7 +212,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -242,14 +221,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -258,7 +236,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -267,14 +244,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="U1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -283,7 +259,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -292,14 +267,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="V1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -308,7 +282,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -318,14 +291,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="W1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -334,7 +306,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -342,13 +313,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="Y1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最大押分值*10000</t>
@@ -698,11 +668,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -751,45 +725,173 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,54 +900,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7993408001953185"/>
+        <fgColor theme="7" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7993408001953185"/>
+        <fgColor theme="9" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993408001953185"/>
+        <fgColor theme="4" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7993408001953185"/>
+        <fgColor theme="5" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -853,30 +1117,272 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -896,19 +1402,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -932,7 +1438,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -944,14 +1450,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -968,6 +1474,10 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -996,11 +1506,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1015,7 +1525,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1025,6 +1535,10 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1037,43 +1551,87 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="60">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="50"/>
+    <cellStyle name="常规 2 2 2" xfId="51"/>
+    <cellStyle name="常规 3" xfId="52"/>
+    <cellStyle name="常规 3 2" xfId="53"/>
+    <cellStyle name="常规 4" xfId="54"/>
+    <cellStyle name="常规 5" xfId="55"/>
+    <cellStyle name="常规 6" xfId="56"/>
+    <cellStyle name="常规 6 2" xfId="57"/>
+    <cellStyle name="常规 6 2 2" xfId="58"/>
+    <cellStyle name="常规 7" xfId="59"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1331,12 +1889,11 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -1365,7 +1922,7 @@
     <col min="25" max="25" width="20.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="41.1" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="41.1" customHeight="1" spans="1:25">
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1434,7 +1991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="1" customFormat="1">
+    <row r="2" s="1" customFormat="1" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1505,7 +2062,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="1" customFormat="1">
+    <row r="3" s="1" customFormat="1" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -1576,7 +2133,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="1" customFormat="1">
+    <row r="4" s="1" customFormat="1" spans="1:25">
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
@@ -1618,19 +2175,19 @@
       <c r="E5" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H5" s="28">
         <v>1</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <v>1990000</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="J5" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K5" s="2">
@@ -1639,7 +2196,7 @@
       <c r="L5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="M5" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="2">
@@ -1657,13 +2214,13 @@
       <c r="R5" s="2">
         <v>15000</v>
       </c>
-      <c r="S5" s="33">
+      <c r="S5" s="34">
         <v>16008</v>
       </c>
       <c r="T5" s="5">
         <v>48</v>
       </c>
-      <c r="U5" s="34">
+      <c r="U5" s="35">
         <v>0</v>
       </c>
       <c r="V5" t="s">
@@ -1685,31 +2242,31 @@
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="36">
         <v>200100</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="36">
         <v>200100038</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="36">
         <v>2</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="31">
         <v>1990000</v>
       </c>
-      <c r="J6" s="36" t="s">
+      <c r="J6" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="2">
@@ -1718,7 +2275,7 @@
       <c r="L6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="M6" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N6" s="2">
@@ -1736,13 +2293,13 @@
       <c r="R6" s="2">
         <v>15000</v>
       </c>
-      <c r="S6" s="33">
+      <c r="S6" s="34">
         <v>16008</v>
       </c>
       <c r="T6" s="5">
         <v>48</v>
       </c>
-      <c r="U6" s="34">
+      <c r="U6" s="35">
         <v>0</v>
       </c>
       <c r="V6" t="s">
@@ -1759,7 +2316,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="7" spans="1:25" s="2" customFormat="1">
+    <row r="7" s="2" customFormat="1" spans="1:25">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -1776,19 +2333,19 @@
       <c r="E7" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H7" s="28">
         <v>3</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <v>1990000</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K7" s="2">
@@ -1797,7 +2354,7 @@
       <c r="L7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="32" t="s">
+      <c r="M7" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N7" s="2">
@@ -1815,13 +2372,13 @@
       <c r="R7" s="2">
         <v>15000</v>
       </c>
-      <c r="S7" s="33">
+      <c r="S7" s="34">
         <v>16008</v>
       </c>
       <c r="T7" s="5">
         <v>48</v>
       </c>
-      <c r="U7" s="34">
+      <c r="U7" s="35">
         <v>0</v>
       </c>
       <c r="V7" t="s">
@@ -1838,7 +2395,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="2" customFormat="1">
+    <row r="8" s="2" customFormat="1" spans="1:25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -1852,22 +2409,22 @@
       <c r="D8" s="28">
         <v>200101001</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H8" s="28">
         <v>1</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <v>1990000</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K8" s="2">
@@ -1876,7 +2433,7 @@
       <c r="L8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="32" t="s">
+      <c r="M8" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N8" s="2">
@@ -1894,13 +2451,13 @@
       <c r="R8" s="2">
         <v>15000</v>
       </c>
-      <c r="S8" s="33">
+      <c r="S8" s="34">
         <v>16008</v>
       </c>
       <c r="T8" s="5">
         <v>48</v>
       </c>
-      <c r="U8" s="34">
+      <c r="U8" s="35">
         <v>0</v>
       </c>
       <c r="V8" t="s">
@@ -1922,31 +2479,31 @@
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <v>200101</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="36">
         <v>200101001</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="36">
         <v>2</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <v>1990000</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K9" s="2">
@@ -1955,7 +2512,7 @@
       <c r="L9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="M9" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N9" s="2">
@@ -1973,13 +2530,13 @@
       <c r="R9" s="2">
         <v>15000</v>
       </c>
-      <c r="S9" s="33">
+      <c r="S9" s="34">
         <v>16008</v>
       </c>
       <c r="T9" s="5">
         <v>48</v>
       </c>
-      <c r="U9" s="34">
+      <c r="U9" s="35">
         <v>0</v>
       </c>
       <c r="V9" t="s">
@@ -2013,19 +2570,19 @@
       <c r="E10" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H10" s="28">
         <v>3</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="31">
         <v>1990000</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K10" s="2">
@@ -2034,7 +2591,7 @@
       <c r="L10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="32" t="s">
+      <c r="M10" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N10" s="2">
@@ -2052,13 +2609,13 @@
       <c r="R10" s="2">
         <v>15000</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10" s="34">
         <v>16008</v>
       </c>
       <c r="T10" s="5">
         <v>48</v>
       </c>
-      <c r="U10" s="34">
+      <c r="U10" s="35">
         <v>0</v>
       </c>
       <c r="V10" t="s">
@@ -2089,22 +2646,22 @@
       <c r="D11" s="28">
         <v>200300001</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H11" s="28">
         <v>1</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <v>1990000</v>
       </c>
-      <c r="J11" s="31" t="s">
+      <c r="J11" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K11" s="2">
@@ -2113,7 +2670,7 @@
       <c r="L11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="32" t="s">
+      <c r="M11" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N11" s="2">
@@ -2131,13 +2688,13 @@
       <c r="R11" s="2">
         <v>15000</v>
       </c>
-      <c r="S11" s="33">
+      <c r="S11" s="34">
         <v>16008</v>
       </c>
       <c r="T11" s="5">
         <v>50</v>
       </c>
-      <c r="U11" s="34">
+      <c r="U11" s="35">
         <v>0</v>
       </c>
       <c r="V11" t="s">
@@ -2154,36 +2711,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="2" customFormat="1">
+    <row r="12" s="2" customFormat="1" spans="1:25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <v>200300</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="36">
         <v>200300001</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="36">
         <v>2</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <v>1990000</v>
       </c>
-      <c r="J12" s="36" t="s">
+      <c r="J12" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K12" s="2">
@@ -2192,7 +2749,7 @@
       <c r="L12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N12" s="2">
@@ -2210,13 +2767,13 @@
       <c r="R12" s="2">
         <v>15000</v>
       </c>
-      <c r="S12" s="33">
+      <c r="S12" s="34">
         <v>16008</v>
       </c>
       <c r="T12" s="5">
         <v>50</v>
       </c>
-      <c r="U12" s="34">
+      <c r="U12" s="35">
         <v>0</v>
       </c>
       <c r="V12" t="s">
@@ -2250,19 +2807,19 @@
       <c r="E13" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H13" s="28">
         <v>3</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <v>1990000</v>
       </c>
-      <c r="J13" s="31" t="s">
+      <c r="J13" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K13" s="2">
@@ -2271,7 +2828,7 @@
       <c r="L13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="M13" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N13" s="2">
@@ -2289,13 +2846,13 @@
       <c r="R13" s="2">
         <v>15000</v>
       </c>
-      <c r="S13" s="33">
+      <c r="S13" s="34">
         <v>16008</v>
       </c>
       <c r="T13" s="5">
         <v>50</v>
       </c>
-      <c r="U13" s="34">
+      <c r="U13" s="35">
         <v>0</v>
       </c>
       <c r="V13" t="s">
@@ -2326,22 +2883,22 @@
       <c r="D14" s="28">
         <v>200400009</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H14" s="28">
         <v>1</v>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <v>1990000</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="2">
@@ -2350,7 +2907,7 @@
       <c r="L14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="32" t="s">
+      <c r="M14" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N14" s="2">
@@ -2368,13 +2925,13 @@
       <c r="R14" s="2">
         <v>15000</v>
       </c>
-      <c r="S14" s="33">
+      <c r="S14" s="34">
         <v>16008</v>
       </c>
       <c r="T14" s="5">
         <v>50</v>
       </c>
-      <c r="U14" s="34">
+      <c r="U14" s="35">
         <v>0</v>
       </c>
       <c r="V14" t="s">
@@ -2396,31 +2953,31 @@
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <v>200400</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <v>200400009</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="36">
         <v>2</v>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="31">
         <v>1990000</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K15" s="2">
@@ -2429,7 +2986,7 @@
       <c r="L15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="32" t="s">
+      <c r="M15" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N15" s="2">
@@ -2447,13 +3004,13 @@
       <c r="R15" s="2">
         <v>15000</v>
       </c>
-      <c r="S15" s="33">
+      <c r="S15" s="34">
         <v>16008</v>
       </c>
       <c r="T15" s="5">
         <v>50</v>
       </c>
-      <c r="U15" s="34">
+      <c r="U15" s="35">
         <v>0</v>
       </c>
       <c r="V15" t="s">
@@ -2470,7 +3027,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" s="2" customFormat="1">
+    <row r="16" s="2" customFormat="1" spans="1:25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -2487,19 +3044,19 @@
       <c r="E16" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G16" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H16" s="28">
         <v>3</v>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="31">
         <v>1990000</v>
       </c>
-      <c r="J16" s="31" t="s">
+      <c r="J16" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K16" s="2">
@@ -2508,7 +3065,7 @@
       <c r="L16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M16" s="32" t="s">
+      <c r="M16" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N16" s="2">
@@ -2526,13 +3083,13 @@
       <c r="R16" s="2">
         <v>15000</v>
       </c>
-      <c r="S16" s="33">
+      <c r="S16" s="34">
         <v>16008</v>
       </c>
       <c r="T16" s="5">
         <v>50</v>
       </c>
-      <c r="U16" s="34">
+      <c r="U16" s="35">
         <v>0</v>
       </c>
       <c r="V16" t="s">
@@ -2549,7 +3106,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="17" spans="1:25" s="2" customFormat="1">
+    <row r="17" s="2" customFormat="1" spans="1:25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -2566,19 +3123,19 @@
       <c r="E17" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H17" s="28">
         <v>1</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="31">
         <v>1990000</v>
       </c>
-      <c r="J17" s="31" t="s">
+      <c r="J17" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K17" s="2">
@@ -2587,7 +3144,7 @@
       <c r="L17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="32" t="s">
+      <c r="M17" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N17" s="2">
@@ -2605,13 +3162,13 @@
       <c r="R17" s="2">
         <v>15000</v>
       </c>
-      <c r="S17" s="33">
+      <c r="S17" s="34">
         <v>16008</v>
       </c>
       <c r="T17" s="5">
         <v>48</v>
       </c>
-      <c r="U17" s="34">
+      <c r="U17" s="35">
         <v>0</v>
       </c>
       <c r="V17" t="s">
@@ -2633,31 +3190,31 @@
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="36">
         <v>200500</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="36">
         <v>200500025</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="36">
         <v>2</v>
       </c>
-      <c r="I18" s="30">
+      <c r="I18" s="31">
         <v>1990000</v>
       </c>
-      <c r="J18" s="36" t="s">
+      <c r="J18" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K18" s="2">
@@ -2666,7 +3223,7 @@
       <c r="L18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="32" t="s">
+      <c r="M18" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N18" s="2">
@@ -2684,13 +3241,13 @@
       <c r="R18" s="2">
         <v>15000</v>
       </c>
-      <c r="S18" s="33">
+      <c r="S18" s="34">
         <v>16008</v>
       </c>
       <c r="T18" s="5">
         <v>48</v>
       </c>
-      <c r="U18" s="34">
+      <c r="U18" s="35">
         <v>0</v>
       </c>
       <c r="V18" t="s">
@@ -2724,19 +3281,19 @@
       <c r="E19" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="28">
         <v>3</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="31">
         <v>1990000</v>
       </c>
-      <c r="J19" s="31" t="s">
+      <c r="J19" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K19" s="2">
@@ -2745,7 +3302,7 @@
       <c r="L19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="32" t="s">
+      <c r="M19" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N19" s="2">
@@ -2763,13 +3320,13 @@
       <c r="R19" s="2">
         <v>15000</v>
       </c>
-      <c r="S19" s="33">
+      <c r="S19" s="34">
         <v>16008</v>
       </c>
       <c r="T19" s="5">
         <v>48</v>
       </c>
-      <c r="U19" s="34">
+      <c r="U19" s="35">
         <v>0</v>
       </c>
       <c r="V19" t="s">
@@ -2800,22 +3357,22 @@
       <c r="D20" s="28">
         <v>200600001</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H20" s="28">
         <v>1</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="31">
         <v>1990000</v>
       </c>
-      <c r="J20" s="31" t="s">
+      <c r="J20" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K20" s="2">
@@ -2824,7 +3381,7 @@
       <c r="L20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="32" t="s">
+      <c r="M20" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N20" s="2">
@@ -2842,13 +3399,13 @@
       <c r="R20" s="2">
         <v>15000</v>
       </c>
-      <c r="S20" s="33">
+      <c r="S20" s="34">
         <v>16008</v>
       </c>
       <c r="T20" s="5">
         <v>20</v>
       </c>
-      <c r="U20" s="34">
+      <c r="U20" s="35">
         <v>0</v>
       </c>
       <c r="V20" t="s">
@@ -2865,36 +3422,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="21" spans="1:25" s="2" customFormat="1">
+    <row r="21" s="2" customFormat="1" spans="1:25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="36">
         <v>200600</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="36">
         <v>200600001</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="36">
         <v>2</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>1990000</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K21" s="2">
@@ -2903,7 +3460,7 @@
       <c r="L21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="32" t="s">
+      <c r="M21" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N21" s="2">
@@ -2921,13 +3478,13 @@
       <c r="R21" s="2">
         <v>15000</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="34">
         <v>16008</v>
       </c>
       <c r="T21" s="5">
         <v>20</v>
       </c>
-      <c r="U21" s="34">
+      <c r="U21" s="35">
         <v>0</v>
       </c>
       <c r="V21" t="s">
@@ -2961,19 +3518,19 @@
       <c r="E22" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G22" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H22" s="28">
         <v>3</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>1990000</v>
       </c>
-      <c r="J22" s="31" t="s">
+      <c r="J22" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K22" s="2">
@@ -2982,7 +3539,7 @@
       <c r="L22" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M22" s="32" t="s">
+      <c r="M22" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N22" s="2">
@@ -3000,13 +3557,13 @@
       <c r="R22" s="2">
         <v>15000</v>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="34">
         <v>16008</v>
       </c>
       <c r="T22" s="5">
         <v>20</v>
       </c>
-      <c r="U22" s="34">
+      <c r="U22" s="35">
         <v>0</v>
       </c>
       <c r="V22" t="s">
@@ -3040,19 +3597,19 @@
       <c r="E23" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H23" s="28">
         <v>1</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="31">
         <v>1990000</v>
       </c>
-      <c r="J23" s="31" t="s">
+      <c r="J23" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K23" s="2">
@@ -3061,7 +3618,7 @@
       <c r="L23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="32" t="s">
+      <c r="M23" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N23" s="2">
@@ -3079,13 +3636,13 @@
       <c r="R23" s="2">
         <v>15000</v>
       </c>
-      <c r="S23" s="33">
+      <c r="S23" s="34">
         <v>16008</v>
       </c>
       <c r="T23" s="5">
         <v>30</v>
       </c>
-      <c r="U23" s="34">
+      <c r="U23" s="35">
         <v>1</v>
       </c>
       <c r="V23" t="s">
@@ -3107,31 +3664,31 @@
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="36">
         <v>200700</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="36">
         <v>200700001</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="36">
         <v>2</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>1990000</v>
       </c>
-      <c r="J24" s="36" t="s">
+      <c r="J24" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K24" s="2">
@@ -3140,7 +3697,7 @@
       <c r="L24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N24" s="2">
@@ -3158,13 +3715,13 @@
       <c r="R24" s="2">
         <v>15000</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="34">
         <v>16008</v>
       </c>
       <c r="T24" s="5">
         <v>30</v>
       </c>
-      <c r="U24" s="34">
+      <c r="U24" s="35">
         <v>1</v>
       </c>
       <c r="V24" t="s">
@@ -3181,7 +3738,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="25" spans="1:25" s="2" customFormat="1">
+    <row r="25" s="2" customFormat="1" spans="1:25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -3198,19 +3755,19 @@
       <c r="E25" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="29" t="s">
+      <c r="G25" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H25" s="28">
         <v>3</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>1990000</v>
       </c>
-      <c r="J25" s="31" t="s">
+      <c r="J25" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K25" s="2">
@@ -3219,7 +3776,7 @@
       <c r="L25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M25" s="32" t="s">
+      <c r="M25" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N25" s="2">
@@ -3237,13 +3794,13 @@
       <c r="R25" s="2">
         <v>15000</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="34">
         <v>16008</v>
       </c>
       <c r="T25" s="5">
         <v>30</v>
       </c>
-      <c r="U25" s="34">
+      <c r="U25" s="35">
         <v>1</v>
       </c>
       <c r="V25" t="s">
@@ -3260,7 +3817,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="26" spans="1:25" s="2" customFormat="1">
+    <row r="26" s="2" customFormat="1" spans="1:25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -3274,22 +3831,22 @@
       <c r="D26" s="28">
         <v>200800001</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="29" t="s">
+      <c r="G26" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H26" s="28">
         <v>1</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="31">
         <v>1990000</v>
       </c>
-      <c r="J26" s="31" t="s">
+      <c r="J26" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K26" s="2">
@@ -3298,7 +3855,7 @@
       <c r="L26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="32" t="s">
+      <c r="M26" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N26" s="2">
@@ -3316,13 +3873,13 @@
       <c r="R26" s="2">
         <v>15000</v>
       </c>
-      <c r="S26" s="33">
+      <c r="S26" s="34">
         <v>16008</v>
       </c>
       <c r="T26" s="5">
         <v>20</v>
       </c>
-      <c r="U26" s="34">
+      <c r="U26" s="35">
         <v>0</v>
       </c>
       <c r="V26" t="s">
@@ -3339,7 +3896,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="27" spans="1:25" s="2" customFormat="1">
+    <row r="27" s="2" customFormat="1" spans="1:25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -3353,22 +3910,22 @@
       <c r="D27" s="28">
         <v>200800001</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="36">
         <v>2</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="31">
         <v>1990000</v>
       </c>
-      <c r="J27" s="36" t="s">
+      <c r="J27" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K27" s="2">
@@ -3377,7 +3934,7 @@
       <c r="L27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="32" t="s">
+      <c r="M27" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N27" s="2">
@@ -3395,13 +3952,13 @@
       <c r="R27" s="2">
         <v>15000</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>16008</v>
       </c>
       <c r="T27" s="5">
         <v>20</v>
       </c>
-      <c r="U27" s="34">
+      <c r="U27" s="35">
         <v>0</v>
       </c>
       <c r="V27" t="s">
@@ -3418,7 +3975,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="28" spans="1:25" s="2" customFormat="1">
+    <row r="28" s="2" customFormat="1" spans="1:25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -3435,19 +3992,19 @@
       <c r="E28" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G28" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H28" s="28">
         <v>3</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="31">
         <v>1990000</v>
       </c>
-      <c r="J28" s="31" t="s">
+      <c r="J28" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K28" s="2">
@@ -3456,7 +4013,7 @@
       <c r="L28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M28" s="32" t="s">
+      <c r="M28" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N28" s="2">
@@ -3474,13 +4031,13 @@
       <c r="R28" s="2">
         <v>15000</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="34">
         <v>16008</v>
       </c>
       <c r="T28" s="5">
         <v>20</v>
       </c>
-      <c r="U28" s="34">
+      <c r="U28" s="35">
         <v>0</v>
       </c>
       <c r="V28" t="s">
@@ -3497,12 +4054,12 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="29" spans="1:25" s="2" customFormat="1">
+    <row r="29" s="2" customFormat="1" spans="1:25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="39">
+      <c r="B29" s="40">
         <v>200900</v>
       </c>
       <c r="C29" s="28" t="s">
@@ -3511,31 +4068,31 @@
       <c r="D29" s="28">
         <v>200900001</v>
       </c>
-      <c r="E29" s="37" t="s">
+      <c r="E29" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="29" t="s">
+      <c r="G29" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H29" s="28">
         <v>1</v>
       </c>
-      <c r="I29" s="30">
+      <c r="I29" s="31">
         <v>1990000</v>
       </c>
-      <c r="J29" s="31" t="s">
+      <c r="J29" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="40">
+      <c r="K29" s="41">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M29" s="32" t="s">
+      <c r="M29" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N29" s="2">
@@ -3553,13 +4110,13 @@
       <c r="R29" s="2">
         <v>15000</v>
       </c>
-      <c r="S29" s="33">
+      <c r="S29" s="34">
         <v>16008</v>
       </c>
       <c r="T29" s="5">
         <v>20</v>
       </c>
-      <c r="U29" s="34">
+      <c r="U29" s="35">
         <v>0</v>
       </c>
       <c r="V29" t="s">
@@ -3581,40 +4138,40 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="42">
         <v>200900</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>200900001</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="29" t="s">
+      <c r="G30" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>2</v>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="31">
         <v>1990000</v>
       </c>
-      <c r="J30" s="36" t="s">
+      <c r="J30" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="40">
+      <c r="K30" s="41">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M30" s="32" t="s">
+      <c r="M30" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N30" s="2">
@@ -3632,13 +4189,13 @@
       <c r="R30" s="2">
         <v>15000</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="34">
         <v>16008</v>
       </c>
       <c r="T30" s="5">
         <v>20</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="35">
         <v>0</v>
       </c>
       <c r="V30" t="s">
@@ -3660,7 +4217,7 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="39">
+      <c r="B31" s="40">
         <v>200900</v>
       </c>
       <c r="C31" s="28" t="s">
@@ -3672,28 +4229,28 @@
       <c r="E31" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="G31" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H31" s="28">
         <v>3</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="31">
         <v>1990000</v>
       </c>
-      <c r="J31" s="31" t="s">
+      <c r="J31" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="40">
+      <c r="K31" s="41">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M31" s="32" t="s">
+      <c r="M31" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N31" s="2">
@@ -3711,13 +4268,13 @@
       <c r="R31" s="2">
         <v>15000</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="34">
         <v>16008</v>
       </c>
       <c r="T31" s="5">
         <v>20</v>
       </c>
-      <c r="U31" s="34">
+      <c r="U31" s="35">
         <v>0</v>
       </c>
       <c r="V31" t="s">
@@ -3734,45 +4291,45 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="32" spans="1:25" s="2" customFormat="1">
+    <row r="32" s="2" customFormat="1" spans="1:25">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>2012001</v>
       </c>
-      <c r="B32" s="42">
+      <c r="B32" s="43">
         <v>201200</v>
       </c>
       <c r="C32" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="36">
         <v>201200001</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="E32" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="G32" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H32" s="28">
         <v>1</v>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="31">
         <v>1990000</v>
       </c>
-      <c r="J32" s="31" t="s">
+      <c r="J32" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="40">
+      <c r="K32" s="41">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M32" s="32" t="s">
+      <c r="M32" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N32" s="2">
@@ -3790,13 +4347,13 @@
       <c r="R32" s="2">
         <v>15000</v>
       </c>
-      <c r="S32" s="33">
+      <c r="S32" s="34">
         <v>16008</v>
       </c>
       <c r="T32" s="5">
         <v>12</v>
       </c>
-      <c r="U32" s="34">
+      <c r="U32" s="35">
         <v>0</v>
       </c>
       <c r="V32" t="s">
@@ -3818,40 +4375,40 @@
         <f t="shared" si="0"/>
         <v>2012002</v>
       </c>
-      <c r="B33" s="42">
+      <c r="B33" s="43">
         <v>201200</v>
       </c>
       <c r="C33" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>201200001</v>
       </c>
-      <c r="E33" s="35" t="s">
+      <c r="E33" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="50" t="s">
+      <c r="F33" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="29" t="s">
+      <c r="G33" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>2</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="31">
         <v>1990000</v>
       </c>
-      <c r="J33" s="36" t="s">
+      <c r="J33" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="40">
+      <c r="K33" s="41">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="32" t="s">
+      <c r="M33" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N33" s="2">
@@ -3869,13 +4426,13 @@
       <c r="R33" s="2">
         <v>15000</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="34">
         <v>16008</v>
       </c>
       <c r="T33" s="5">
         <v>12</v>
       </c>
-      <c r="U33" s="34">
+      <c r="U33" s="35">
         <v>0</v>
       </c>
       <c r="V33" t="s">
@@ -3897,40 +4454,40 @@
         <f t="shared" si="0"/>
         <v>2012003</v>
       </c>
-      <c r="B34" s="42">
+      <c r="B34" s="43">
         <v>201200</v>
       </c>
       <c r="C34" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>201200001</v>
       </c>
       <c r="E34" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H34" s="28">
         <v>3</v>
       </c>
-      <c r="I34" s="30">
+      <c r="I34" s="31">
         <v>1990000</v>
       </c>
-      <c r="J34" s="31" t="s">
+      <c r="J34" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="40">
+      <c r="K34" s="41">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M34" s="32" t="s">
+      <c r="M34" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N34" s="2">
@@ -3948,13 +4505,13 @@
       <c r="R34" s="2">
         <v>15000</v>
       </c>
-      <c r="S34" s="33">
+      <c r="S34" s="34">
         <v>16008</v>
       </c>
       <c r="T34" s="5">
         <v>12</v>
       </c>
-      <c r="U34" s="34">
+      <c r="U34" s="35">
         <v>0</v>
       </c>
       <c r="V34" t="s">
@@ -3971,35 +4528,35 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="35" spans="1:25" s="3" customFormat="1">
-      <c r="A35" s="43">
+    <row r="35" s="3" customFormat="1" spans="1:25">
+      <c r="A35" s="44">
         <v>20010010</v>
       </c>
       <c r="B35" s="3">
         <v>200100</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="C35" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="45">
         <v>200100038</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="45" t="s">
+      <c r="G35" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="44">
+      <c r="H35" s="45">
         <v>1</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="45">
         <v>1980000</v>
       </c>
-      <c r="J35" s="31" t="s">
+      <c r="J35" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K35" s="3">
@@ -4008,7 +4565,7 @@
       <c r="L35" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M35" s="46" t="s">
+      <c r="M35" s="48" t="s">
         <v>56</v>
       </c>
       <c r="N35" s="2">
@@ -4026,13 +4583,13 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="47">
+      <c r="S35" s="49">
         <v>16008</v>
       </c>
-      <c r="T35" s="43">
+      <c r="T35" s="44">
         <v>48</v>
       </c>
-      <c r="U35" s="48">
+      <c r="U35" s="50">
         <v>0</v>
       </c>
       <c r="V35" t="s">
@@ -4044,37 +4601,37 @@
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="49"/>
-    </row>
-    <row r="36" spans="1:25" s="3" customFormat="1">
-      <c r="A36" s="43">
+      <c r="Y35" s="51"/>
+    </row>
+    <row r="36" s="3" customFormat="1" spans="1:25">
+      <c r="A36" s="44">
         <v>20010011</v>
       </c>
       <c r="B36" s="3">
         <v>200100</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="C36" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="45">
         <v>200100038</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="51" t="s">
+      <c r="F36" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="45" t="s">
+      <c r="G36" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H36" s="44">
+      <c r="H36" s="45">
         <v>2</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="45">
         <v>1980000</v>
       </c>
-      <c r="J36" s="36" t="s">
+      <c r="J36" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K36" s="3">
@@ -4083,7 +4640,7 @@
       <c r="L36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M36" s="46" t="s">
+      <c r="M36" s="48" t="s">
         <v>56</v>
       </c>
       <c r="N36" s="2">
@@ -4101,13 +4658,13 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="47">
+      <c r="S36" s="49">
         <v>16008</v>
       </c>
-      <c r="T36" s="43">
+      <c r="T36" s="44">
         <v>48</v>
       </c>
-      <c r="U36" s="48">
+      <c r="U36" s="50">
         <v>0</v>
       </c>
       <c r="V36" t="s">
@@ -4119,37 +4676,37 @@
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="49"/>
-    </row>
-    <row r="37" spans="1:25" s="3" customFormat="1">
-      <c r="A37" s="43">
+      <c r="Y36" s="51"/>
+    </row>
+    <row r="37" s="3" customFormat="1" spans="1:25">
+      <c r="A37" s="44">
         <v>20010012</v>
       </c>
       <c r="B37" s="3">
         <v>200100</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="C37" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="45">
         <v>200100038</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E37" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="51" t="s">
+      <c r="F37" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="45" t="s">
+      <c r="G37" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H37" s="44">
+      <c r="H37" s="45">
         <v>3</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="45">
         <v>1980000</v>
       </c>
-      <c r="J37" s="31" t="s">
+      <c r="J37" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K37" s="3">
@@ -4158,7 +4715,7 @@
       <c r="L37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M37" s="46" t="s">
+      <c r="M37" s="48" t="s">
         <v>56</v>
       </c>
       <c r="N37" s="2">
@@ -4176,13 +4733,13 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="47">
+      <c r="S37" s="49">
         <v>16008</v>
       </c>
-      <c r="T37" s="43">
+      <c r="T37" s="44">
         <v>48</v>
       </c>
-      <c r="U37" s="48">
+      <c r="U37" s="50">
         <v>0</v>
       </c>
       <c r="V37" t="s">
@@ -4194,10 +4751,10 @@
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="49"/>
-    </row>
-    <row r="38" spans="1:25" s="3" customFormat="1">
-      <c r="A38" s="43">
+      <c r="Y37" s="51"/>
+    </row>
+    <row r="38" s="3" customFormat="1" spans="1:25">
+      <c r="A38" s="44">
         <v>20010110</v>
       </c>
       <c r="B38" s="3">
@@ -4212,19 +4769,19 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="52" t="s">
+      <c r="F38" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G38" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="45">
         <v>1980000</v>
       </c>
-      <c r="J38" s="31" t="s">
+      <c r="J38" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K38" s="3">
@@ -4233,7 +4790,7 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="46" t="s">
+      <c r="M38" s="48" t="s">
         <v>69</v>
       </c>
       <c r="N38" s="2">
@@ -4254,10 +4811,10 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="43">
+      <c r="T38" s="44">
         <v>48</v>
       </c>
-      <c r="U38" s="48">
+      <c r="U38" s="50">
         <v>0</v>
       </c>
       <c r="V38" t="s">
@@ -4269,10 +4826,10 @@
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="49"/>
-    </row>
-    <row r="39" spans="1:25" s="3" customFormat="1">
-      <c r="A39" s="43">
+      <c r="Y38" s="51"/>
+    </row>
+    <row r="39" s="3" customFormat="1" spans="1:25">
+      <c r="A39" s="44">
         <v>20010111</v>
       </c>
       <c r="B39" s="3">
@@ -4287,19 +4844,19 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="52" t="s">
+      <c r="F39" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="45" t="s">
+      <c r="G39" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="45">
         <v>1980000</v>
       </c>
-      <c r="J39" s="36" t="s">
+      <c r="J39" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K39" s="3">
@@ -4308,7 +4865,7 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="46" t="s">
+      <c r="M39" s="48" t="s">
         <v>69</v>
       </c>
       <c r="N39" s="2">
@@ -4329,10 +4886,10 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="43">
+      <c r="T39" s="44">
         <v>48</v>
       </c>
-      <c r="U39" s="48">
+      <c r="U39" s="50">
         <v>0</v>
       </c>
       <c r="V39" t="s">
@@ -4344,10 +4901,10 @@
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="49"/>
-    </row>
-    <row r="40" spans="1:25" s="3" customFormat="1">
-      <c r="A40" s="43">
+      <c r="Y39" s="51"/>
+    </row>
+    <row r="40" s="3" customFormat="1" spans="1:25">
+      <c r="A40" s="44">
         <v>20010112</v>
       </c>
       <c r="B40" s="3">
@@ -4362,19 +4919,19 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="52" t="s">
+      <c r="F40" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="45" t="s">
+      <c r="G40" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="45">
         <v>1980000</v>
       </c>
-      <c r="J40" s="31" t="s">
+      <c r="J40" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K40" s="3">
@@ -4383,7 +4940,7 @@
       <c r="L40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="46" t="s">
+      <c r="M40" s="48" t="s">
         <v>69</v>
       </c>
       <c r="N40" s="2">
@@ -4404,10 +4961,10 @@
       <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="43">
+      <c r="T40" s="44">
         <v>48</v>
       </c>
-      <c r="U40" s="48">
+      <c r="U40" s="50">
         <v>0</v>
       </c>
       <c r="V40" t="s">
@@ -4419,10 +4976,10 @@
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="49"/>
-    </row>
-    <row r="41" spans="1:25" s="3" customFormat="1">
-      <c r="A41" s="43">
+      <c r="Y40" s="51"/>
+    </row>
+    <row r="41" s="3" customFormat="1" spans="1:25">
+      <c r="A41" s="44">
         <v>20030010</v>
       </c>
       <c r="B41" s="3">
@@ -4437,19 +4994,19 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="52" t="s">
+      <c r="F41" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="45" t="s">
+      <c r="G41" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="45">
         <v>1980000</v>
       </c>
-      <c r="J41" s="31" t="s">
+      <c r="J41" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K41" s="3">
@@ -4458,7 +5015,7 @@
       <c r="L41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="46" t="s">
+      <c r="M41" s="48" t="s">
         <v>71</v>
       </c>
       <c r="N41" s="2">
@@ -4479,10 +5036,10 @@
       <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="43">
+      <c r="T41" s="44">
         <v>50</v>
       </c>
-      <c r="U41" s="48">
+      <c r="U41" s="50">
         <v>0</v>
       </c>
       <c r="V41" t="s">
@@ -4494,10 +5051,10 @@
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="49"/>
-    </row>
-    <row r="42" spans="1:25" s="3" customFormat="1">
-      <c r="A42" s="43">
+      <c r="Y41" s="51"/>
+    </row>
+    <row r="42" s="3" customFormat="1" spans="1:25">
+      <c r="A42" s="44">
         <v>20030011</v>
       </c>
       <c r="B42" s="3">
@@ -4512,19 +5069,19 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="52" t="s">
+      <c r="F42" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="45" t="s">
+      <c r="G42" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="44">
+      <c r="I42" s="45">
         <v>1980000</v>
       </c>
-      <c r="J42" s="36" t="s">
+      <c r="J42" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K42" s="3">
@@ -4533,7 +5090,7 @@
       <c r="L42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="46" t="s">
+      <c r="M42" s="48" t="s">
         <v>71</v>
       </c>
       <c r="N42" s="2">
@@ -4554,10 +5111,10 @@
       <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="43">
+      <c r="T42" s="44">
         <v>50</v>
       </c>
-      <c r="U42" s="48">
+      <c r="U42" s="50">
         <v>0</v>
       </c>
       <c r="V42" t="s">
@@ -4569,10 +5126,10 @@
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="49"/>
-    </row>
-    <row r="43" spans="1:25" s="3" customFormat="1">
-      <c r="A43" s="43">
+      <c r="Y42" s="51"/>
+    </row>
+    <row r="43" s="3" customFormat="1" spans="1:25">
+      <c r="A43" s="44">
         <v>20030012</v>
       </c>
       <c r="B43" s="3">
@@ -4587,19 +5144,19 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="52" t="s">
+      <c r="F43" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="45" t="s">
+      <c r="G43" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="45">
         <v>1980000</v>
       </c>
-      <c r="J43" s="31" t="s">
+      <c r="J43" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K43" s="3">
@@ -4608,7 +5165,7 @@
       <c r="L43" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="46" t="s">
+      <c r="M43" s="48" t="s">
         <v>71</v>
       </c>
       <c r="N43" s="2">
@@ -4629,10 +5186,10 @@
       <c r="S43" s="3">
         <v>16008</v>
       </c>
-      <c r="T43" s="43">
+      <c r="T43" s="44">
         <v>50</v>
       </c>
-      <c r="U43" s="48">
+      <c r="U43" s="50">
         <v>0</v>
       </c>
       <c r="V43" t="s">
@@ -4644,10 +5201,10 @@
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="49"/>
-    </row>
-    <row r="44" spans="1:25" s="3" customFormat="1">
-      <c r="A44" s="43">
+      <c r="Y43" s="51"/>
+    </row>
+    <row r="44" s="3" customFormat="1" spans="1:25">
+      <c r="A44" s="44">
         <v>20040010</v>
       </c>
       <c r="B44" s="3">
@@ -4662,19 +5219,19 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="52" t="s">
+      <c r="F44" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="45">
         <v>1980000</v>
       </c>
-      <c r="J44" s="31" t="s">
+      <c r="J44" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K44" s="3">
@@ -4683,7 +5240,7 @@
       <c r="L44" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M44" s="46" t="s">
+      <c r="M44" s="48" t="s">
         <v>73</v>
       </c>
       <c r="N44" s="2">
@@ -4704,10 +5261,10 @@
       <c r="S44" s="3">
         <v>16008</v>
       </c>
-      <c r="T44" s="43">
+      <c r="T44" s="44">
         <v>50</v>
       </c>
-      <c r="U44" s="48">
+      <c r="U44" s="50">
         <v>0</v>
       </c>
       <c r="V44" t="s">
@@ -4719,10 +5276,10 @@
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="49"/>
-    </row>
-    <row r="45" spans="1:25" s="3" customFormat="1">
-      <c r="A45" s="43">
+      <c r="Y44" s="51"/>
+    </row>
+    <row r="45" s="3" customFormat="1" spans="1:25">
+      <c r="A45" s="44">
         <v>20040011</v>
       </c>
       <c r="B45" s="3">
@@ -4737,19 +5294,19 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="52" t="s">
+      <c r="F45" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="45" t="s">
+      <c r="G45" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="45">
         <v>1980000</v>
       </c>
-      <c r="J45" s="36" t="s">
+      <c r="J45" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K45" s="3">
@@ -4758,7 +5315,7 @@
       <c r="L45" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M45" s="46" t="s">
+      <c r="M45" s="48" t="s">
         <v>73</v>
       </c>
       <c r="N45" s="2">
@@ -4779,10 +5336,10 @@
       <c r="S45" s="3">
         <v>16008</v>
       </c>
-      <c r="T45" s="43">
+      <c r="T45" s="44">
         <v>50</v>
       </c>
-      <c r="U45" s="48">
+      <c r="U45" s="50">
         <v>0</v>
       </c>
       <c r="V45" t="s">
@@ -4794,10 +5351,10 @@
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="49"/>
-    </row>
-    <row r="46" spans="1:25" s="3" customFormat="1">
-      <c r="A46" s="43">
+      <c r="Y45" s="51"/>
+    </row>
+    <row r="46" s="3" customFormat="1" spans="1:25">
+      <c r="A46" s="44">
         <v>20040012</v>
       </c>
       <c r="B46" s="3">
@@ -4812,19 +5369,19 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="52" t="s">
+      <c r="F46" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="45" t="s">
+      <c r="G46" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="45">
         <v>1980000</v>
       </c>
-      <c r="J46" s="31" t="s">
+      <c r="J46" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K46" s="3">
@@ -4833,7 +5390,7 @@
       <c r="L46" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M46" s="46" t="s">
+      <c r="M46" s="48" t="s">
         <v>73</v>
       </c>
       <c r="N46" s="2">
@@ -4854,10 +5411,10 @@
       <c r="S46" s="3">
         <v>16008</v>
       </c>
-      <c r="T46" s="43">
+      <c r="T46" s="44">
         <v>50</v>
       </c>
-      <c r="U46" s="48">
+      <c r="U46" s="50">
         <v>0</v>
       </c>
       <c r="V46" t="s">
@@ -4869,10 +5426,10 @@
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="49"/>
-    </row>
-    <row r="47" spans="1:25" s="3" customFormat="1">
-      <c r="A47" s="43">
+      <c r="Y46" s="51"/>
+    </row>
+    <row r="47" s="3" customFormat="1" spans="1:25">
+      <c r="A47" s="44">
         <v>20050010</v>
       </c>
       <c r="B47" s="3">
@@ -4887,19 +5444,19 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="52" t="s">
+      <c r="F47" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="45" t="s">
+      <c r="G47" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="45">
         <v>1980000</v>
       </c>
-      <c r="J47" s="31" t="s">
+      <c r="J47" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K47" s="3">
@@ -4908,7 +5465,7 @@
       <c r="L47" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M47" s="46" t="s">
+      <c r="M47" s="48" t="s">
         <v>75</v>
       </c>
       <c r="N47" s="2">
@@ -4929,10 +5486,10 @@
       <c r="S47" s="3">
         <v>16008</v>
       </c>
-      <c r="T47" s="43">
+      <c r="T47" s="44">
         <v>48</v>
       </c>
-      <c r="U47" s="43">
+      <c r="U47" s="44">
         <v>0</v>
       </c>
       <c r="V47" t="s">
@@ -4944,10 +5501,10 @@
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="49"/>
-    </row>
-    <row r="48" spans="1:25" s="3" customFormat="1">
-      <c r="A48" s="43">
+      <c r="Y47" s="51"/>
+    </row>
+    <row r="48" s="3" customFormat="1" spans="1:25">
+      <c r="A48" s="44">
         <v>20050011</v>
       </c>
       <c r="B48" s="3">
@@ -4962,19 +5519,19 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="52" t="s">
+      <c r="F48" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="45" t="s">
+      <c r="G48" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="44">
+      <c r="I48" s="45">
         <v>1980000</v>
       </c>
-      <c r="J48" s="36" t="s">
+      <c r="J48" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K48" s="3">
@@ -4983,7 +5540,7 @@
       <c r="L48" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M48" s="46" t="s">
+      <c r="M48" s="48" t="s">
         <v>75</v>
       </c>
       <c r="N48" s="2">
@@ -5004,10 +5561,10 @@
       <c r="S48" s="3">
         <v>16008</v>
       </c>
-      <c r="T48" s="43">
+      <c r="T48" s="44">
         <v>48</v>
       </c>
-      <c r="U48" s="43">
+      <c r="U48" s="44">
         <v>0</v>
       </c>
       <c r="V48" t="s">
@@ -5019,10 +5576,10 @@
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="49"/>
-    </row>
-    <row r="49" spans="1:25" s="3" customFormat="1">
-      <c r="A49" s="43">
+      <c r="Y48" s="51"/>
+    </row>
+    <row r="49" s="3" customFormat="1" spans="1:25">
+      <c r="A49" s="44">
         <v>20050012</v>
       </c>
       <c r="B49" s="3">
@@ -5037,19 +5594,19 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="52" t="s">
+      <c r="F49" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="45" t="s">
+      <c r="G49" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="44">
+      <c r="I49" s="45">
         <v>1980000</v>
       </c>
-      <c r="J49" s="31" t="s">
+      <c r="J49" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K49" s="3">
@@ -5058,7 +5615,7 @@
       <c r="L49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M49" s="46" t="s">
+      <c r="M49" s="48" t="s">
         <v>75</v>
       </c>
       <c r="N49" s="2">
@@ -5079,10 +5636,10 @@
       <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="43">
+      <c r="T49" s="44">
         <v>48</v>
       </c>
-      <c r="U49" s="43">
+      <c r="U49" s="44">
         <v>0</v>
       </c>
       <c r="V49" t="s">
@@ -5094,10 +5651,10 @@
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="49"/>
-    </row>
-    <row r="50" spans="1:25" s="3" customFormat="1">
-      <c r="A50" s="43">
+      <c r="Y49" s="51"/>
+    </row>
+    <row r="50" s="3" customFormat="1" spans="1:25">
+      <c r="A50" s="44">
         <v>20060010</v>
       </c>
       <c r="B50" s="3">
@@ -5112,19 +5669,19 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="52" t="s">
+      <c r="F50" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="45" t="s">
+      <c r="G50" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="45">
         <v>1980000</v>
       </c>
-      <c r="J50" s="31" t="s">
+      <c r="J50" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K50" s="3">
@@ -5133,7 +5690,7 @@
       <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="46" t="s">
+      <c r="M50" s="48" t="s">
         <v>77</v>
       </c>
       <c r="N50" s="2">
@@ -5154,10 +5711,10 @@
       <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="43">
+      <c r="T50" s="44">
         <v>20</v>
       </c>
-      <c r="U50" s="43">
+      <c r="U50" s="44">
         <v>0</v>
       </c>
       <c r="V50" t="s">
@@ -5169,10 +5726,10 @@
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="49"/>
-    </row>
-    <row r="51" spans="1:25" s="3" customFormat="1">
-      <c r="A51" s="43">
+      <c r="Y50" s="51"/>
+    </row>
+    <row r="51" s="3" customFormat="1" spans="1:25">
+      <c r="A51" s="44">
         <v>20060011</v>
       </c>
       <c r="B51" s="3">
@@ -5187,19 +5744,19 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="52" t="s">
+      <c r="F51" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="45" t="s">
+      <c r="G51" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="44">
+      <c r="I51" s="45">
         <v>1980000</v>
       </c>
-      <c r="J51" s="36" t="s">
+      <c r="J51" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K51" s="3">
@@ -5208,7 +5765,7 @@
       <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="46" t="s">
+      <c r="M51" s="48" t="s">
         <v>77</v>
       </c>
       <c r="N51" s="2">
@@ -5229,10 +5786,10 @@
       <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="43">
+      <c r="T51" s="44">
         <v>20</v>
       </c>
-      <c r="U51" s="43">
+      <c r="U51" s="44">
         <v>0</v>
       </c>
       <c r="V51" t="s">
@@ -5244,10 +5801,10 @@
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="49"/>
-    </row>
-    <row r="52" spans="1:25" s="3" customFormat="1">
-      <c r="A52" s="43">
+      <c r="Y51" s="51"/>
+    </row>
+    <row r="52" s="3" customFormat="1" spans="1:25">
+      <c r="A52" s="44">
         <v>20060012</v>
       </c>
       <c r="B52" s="3">
@@ -5262,19 +5819,19 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="52" t="s">
+      <c r="F52" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="45" t="s">
+      <c r="G52" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="45">
         <v>1980000</v>
       </c>
-      <c r="J52" s="31" t="s">
+      <c r="J52" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K52" s="3">
@@ -5283,7 +5840,7 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="46" t="s">
+      <c r="M52" s="48" t="s">
         <v>77</v>
       </c>
       <c r="N52" s="2">
@@ -5304,10 +5861,10 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="43">
+      <c r="T52" s="44">
         <v>20</v>
       </c>
-      <c r="U52" s="43">
+      <c r="U52" s="44">
         <v>0</v>
       </c>
       <c r="V52" t="s">
@@ -5319,10 +5876,10 @@
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="49"/>
-    </row>
-    <row r="53" spans="1:25" s="3" customFormat="1">
-      <c r="A53" s="43">
+      <c r="Y52" s="51"/>
+    </row>
+    <row r="53" s="3" customFormat="1" spans="1:25">
+      <c r="A53" s="44">
         <v>20070010</v>
       </c>
       <c r="B53" s="3">
@@ -5337,19 +5894,19 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="52" t="s">
+      <c r="F53" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="45" t="s">
+      <c r="G53" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="45">
         <v>1980000</v>
       </c>
-      <c r="J53" s="31" t="s">
+      <c r="J53" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K53" s="3">
@@ -5358,7 +5915,7 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="46" t="s">
+      <c r="M53" s="48" t="s">
         <v>79</v>
       </c>
       <c r="N53" s="2">
@@ -5379,10 +5936,10 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="43">
+      <c r="T53" s="44">
         <v>30</v>
       </c>
-      <c r="U53" s="43">
+      <c r="U53" s="44">
         <v>1</v>
       </c>
       <c r="V53" t="s">
@@ -5394,10 +5951,10 @@
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="49"/>
-    </row>
-    <row r="54" spans="1:25" s="3" customFormat="1">
-      <c r="A54" s="43">
+      <c r="Y53" s="51"/>
+    </row>
+    <row r="54" s="3" customFormat="1" spans="1:25">
+      <c r="A54" s="44">
         <v>20070011</v>
       </c>
       <c r="B54" s="3">
@@ -5412,19 +5969,19 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="52" t="s">
+      <c r="F54" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="45" t="s">
+      <c r="G54" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="45">
         <v>1980000</v>
       </c>
-      <c r="J54" s="36" t="s">
+      <c r="J54" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K54" s="3">
@@ -5433,7 +5990,7 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="46" t="s">
+      <c r="M54" s="48" t="s">
         <v>79</v>
       </c>
       <c r="N54" s="2">
@@ -5454,10 +6011,10 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="43">
+      <c r="T54" s="44">
         <v>30</v>
       </c>
-      <c r="U54" s="43">
+      <c r="U54" s="44">
         <v>1</v>
       </c>
       <c r="V54" t="s">
@@ -5469,10 +6026,10 @@
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="49"/>
-    </row>
-    <row r="55" spans="1:25" s="3" customFormat="1">
-      <c r="A55" s="43">
+      <c r="Y54" s="51"/>
+    </row>
+    <row r="55" s="3" customFormat="1" spans="1:25">
+      <c r="A55" s="44">
         <v>20070012</v>
       </c>
       <c r="B55" s="3">
@@ -5487,19 +6044,19 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="52" t="s">
+      <c r="F55" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="45" t="s">
+      <c r="G55" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="45">
         <v>1980000</v>
       </c>
-      <c r="J55" s="31" t="s">
+      <c r="J55" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K55" s="3">
@@ -5508,7 +6065,7 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="46" t="s">
+      <c r="M55" s="48" t="s">
         <v>79</v>
       </c>
       <c r="N55" s="2">
@@ -5529,10 +6086,10 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="43">
+      <c r="T55" s="44">
         <v>30</v>
       </c>
-      <c r="U55" s="43">
+      <c r="U55" s="44">
         <v>1</v>
       </c>
       <c r="V55" t="s">
@@ -5544,10 +6101,10 @@
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="49"/>
-    </row>
-    <row r="56" spans="1:25" s="3" customFormat="1">
-      <c r="A56" s="43">
+      <c r="Y55" s="51"/>
+    </row>
+    <row r="56" s="3" customFormat="1" spans="1:25">
+      <c r="A56" s="44">
         <v>20080010</v>
       </c>
       <c r="B56" s="3">
@@ -5562,19 +6119,19 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="52" t="s">
+      <c r="F56" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="45" t="s">
+      <c r="G56" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="44">
+      <c r="I56" s="45">
         <v>1980000</v>
       </c>
-      <c r="J56" s="31" t="s">
+      <c r="J56" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K56" s="3">
@@ -5583,7 +6140,7 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="46" t="s">
+      <c r="M56" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N56" s="2">
@@ -5604,10 +6161,10 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="43">
+      <c r="T56" s="44">
         <v>20</v>
       </c>
-      <c r="U56" s="43">
+      <c r="U56" s="44">
         <v>0</v>
       </c>
       <c r="V56" t="s">
@@ -5619,10 +6176,10 @@
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="49"/>
-    </row>
-    <row r="57" spans="1:25" s="3" customFormat="1">
-      <c r="A57" s="43">
+      <c r="Y56" s="51"/>
+    </row>
+    <row r="57" s="3" customFormat="1" spans="1:25">
+      <c r="A57" s="44">
         <v>20080011</v>
       </c>
       <c r="B57" s="3">
@@ -5637,19 +6194,19 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="52" t="s">
+      <c r="F57" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="45" t="s">
+      <c r="G57" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="45">
         <v>1980000</v>
       </c>
-      <c r="J57" s="36" t="s">
+      <c r="J57" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K57" s="3">
@@ -5658,7 +6215,7 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="46" t="s">
+      <c r="M57" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="2">
@@ -5679,10 +6236,10 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="43">
+      <c r="T57" s="44">
         <v>20</v>
       </c>
-      <c r="U57" s="43">
+      <c r="U57" s="44">
         <v>0</v>
       </c>
       <c r="V57" t="s">
@@ -5694,10 +6251,10 @@
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="49"/>
-    </row>
-    <row r="58" spans="1:25" s="3" customFormat="1">
-      <c r="A58" s="43">
+      <c r="Y57" s="51"/>
+    </row>
+    <row r="58" s="3" customFormat="1" spans="1:25">
+      <c r="A58" s="44">
         <v>20080012</v>
       </c>
       <c r="B58" s="3">
@@ -5712,19 +6269,19 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="52" t="s">
+      <c r="F58" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="45" t="s">
+      <c r="G58" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="45">
         <v>1980000</v>
       </c>
-      <c r="J58" s="31" t="s">
+      <c r="J58" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K58" s="3">
@@ -5733,7 +6290,7 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="46" t="s">
+      <c r="M58" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N58" s="2">
@@ -5754,10 +6311,10 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="43">
+      <c r="T58" s="44">
         <v>20</v>
       </c>
-      <c r="U58" s="43">
+      <c r="U58" s="44">
         <v>0</v>
       </c>
       <c r="V58" t="s">
@@ -5769,10 +6326,10 @@
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="49"/>
-    </row>
-    <row r="59" spans="1:25" s="3" customFormat="1">
-      <c r="A59" s="43">
+      <c r="Y58" s="51"/>
+    </row>
+    <row r="59" s="3" customFormat="1" spans="1:25">
+      <c r="A59" s="44">
         <v>20090010</v>
       </c>
       <c r="B59" s="3">
@@ -5787,19 +6344,19 @@
       <c r="E59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="52" t="s">
+      <c r="F59" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G59" s="45" t="s">
+      <c r="G59" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H59" s="3">
         <v>1</v>
       </c>
-      <c r="I59" s="44">
+      <c r="I59" s="45">
         <v>1980000</v>
       </c>
-      <c r="J59" s="31" t="s">
+      <c r="J59" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K59" s="3">
@@ -5808,7 +6365,7 @@
       <c r="L59" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M59" s="46" t="s">
+      <c r="M59" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N59" s="2">
@@ -5829,10 +6386,10 @@
       <c r="S59" s="3">
         <v>16008</v>
       </c>
-      <c r="T59" s="43">
+      <c r="T59" s="44">
         <v>20</v>
       </c>
-      <c r="U59" s="43">
+      <c r="U59" s="44">
         <v>0</v>
       </c>
       <c r="V59" t="s">
@@ -5844,10 +6401,10 @@
       <c r="X59" s="3">
         <v>1</v>
       </c>
-      <c r="Y59" s="49"/>
-    </row>
-    <row r="60" spans="1:25" s="3" customFormat="1">
-      <c r="A60" s="43">
+      <c r="Y59" s="51"/>
+    </row>
+    <row r="60" s="3" customFormat="1" spans="1:25">
+      <c r="A60" s="44">
         <v>20090011</v>
       </c>
       <c r="B60" s="3">
@@ -5862,19 +6419,19 @@
       <c r="E60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F60" s="52" t="s">
+      <c r="F60" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G60" s="45" t="s">
+      <c r="G60" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H60" s="3">
         <v>2</v>
       </c>
-      <c r="I60" s="44">
+      <c r="I60" s="45">
         <v>1980000</v>
       </c>
-      <c r="J60" s="36" t="s">
+      <c r="J60" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K60" s="3">
@@ -5883,7 +6440,7 @@
       <c r="L60" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M60" s="46" t="s">
+      <c r="M60" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N60" s="2">
@@ -5904,10 +6461,10 @@
       <c r="S60" s="3">
         <v>16008</v>
       </c>
-      <c r="T60" s="43">
+      <c r="T60" s="44">
         <v>20</v>
       </c>
-      <c r="U60" s="43">
+      <c r="U60" s="44">
         <v>0</v>
       </c>
       <c r="V60" t="s">
@@ -5919,10 +6476,10 @@
       <c r="X60" s="3">
         <v>1</v>
       </c>
-      <c r="Y60" s="49"/>
-    </row>
-    <row r="61" spans="1:25" s="3" customFormat="1">
-      <c r="A61" s="43">
+      <c r="Y60" s="51"/>
+    </row>
+    <row r="61" s="3" customFormat="1" spans="1:25">
+      <c r="A61" s="44">
         <v>20090012</v>
       </c>
       <c r="B61" s="3">
@@ -5937,19 +6494,19 @@
       <c r="E61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G61" s="45" t="s">
+      <c r="G61" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H61" s="3">
         <v>3</v>
       </c>
-      <c r="I61" s="44">
+      <c r="I61" s="45">
         <v>1980000</v>
       </c>
-      <c r="J61" s="31" t="s">
+      <c r="J61" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K61" s="3">
@@ -5958,7 +6515,7 @@
       <c r="L61" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M61" s="46" t="s">
+      <c r="M61" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N61" s="2">
@@ -5979,10 +6536,10 @@
       <c r="S61" s="3">
         <v>16008</v>
       </c>
-      <c r="T61" s="43">
+      <c r="T61" s="44">
         <v>20</v>
       </c>
-      <c r="U61" s="43">
+      <c r="U61" s="44">
         <v>0</v>
       </c>
       <c r="V61" t="s">
@@ -5994,13 +6551,13 @@
       <c r="X61" s="3">
         <v>1</v>
       </c>
-      <c r="Y61" s="49"/>
-    </row>
-    <row r="62" spans="1:25" s="3" customFormat="1">
-      <c r="A62" s="43">
+      <c r="Y61" s="51"/>
+    </row>
+    <row r="62" s="3" customFormat="1" spans="1:25">
+      <c r="A62" s="44">
         <v>20120010</v>
       </c>
-      <c r="B62" s="42">
+      <c r="B62" s="43">
         <v>201200</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -6012,19 +6569,19 @@
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="52" t="s">
+      <c r="F62" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G62" s="45" t="s">
+      <c r="G62" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H62" s="3">
         <v>1</v>
       </c>
-      <c r="I62" s="44">
+      <c r="I62" s="45">
         <v>1980000</v>
       </c>
-      <c r="J62" s="31" t="s">
+      <c r="J62" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K62" s="3">
@@ -6033,7 +6590,7 @@
       <c r="L62" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M62" s="46" t="s">
+      <c r="M62" s="48" t="s">
         <v>84</v>
       </c>
       <c r="N62" s="2">
@@ -6054,10 +6611,10 @@
       <c r="S62" s="3">
         <v>16008</v>
       </c>
-      <c r="T62" s="43">
+      <c r="T62" s="44">
         <v>12</v>
       </c>
-      <c r="U62" s="43">
+      <c r="U62" s="44">
         <v>0</v>
       </c>
       <c r="V62" t="s">
@@ -6069,13 +6626,13 @@
       <c r="X62" s="3">
         <v>1</v>
       </c>
-      <c r="Y62" s="49"/>
-    </row>
-    <row r="63" spans="1:25" s="3" customFormat="1">
-      <c r="A63" s="43">
+      <c r="Y62" s="51"/>
+    </row>
+    <row r="63" s="3" customFormat="1" spans="1:25">
+      <c r="A63" s="44">
         <v>20120011</v>
       </c>
-      <c r="B63" s="42">
+      <c r="B63" s="43">
         <v>201200</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -6087,19 +6644,19 @@
       <c r="E63" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="52" t="s">
+      <c r="F63" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G63" s="45" t="s">
+      <c r="G63" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H63" s="3">
         <v>2</v>
       </c>
-      <c r="I63" s="44">
+      <c r="I63" s="45">
         <v>1980000</v>
       </c>
-      <c r="J63" s="36" t="s">
+      <c r="J63" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K63" s="3">
@@ -6108,7 +6665,7 @@
       <c r="L63" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M63" s="46" t="s">
+      <c r="M63" s="48" t="s">
         <v>84</v>
       </c>
       <c r="N63" s="2">
@@ -6129,10 +6686,10 @@
       <c r="S63" s="3">
         <v>16008</v>
       </c>
-      <c r="T63" s="43">
+      <c r="T63" s="44">
         <v>12</v>
       </c>
-      <c r="U63" s="43">
+      <c r="U63" s="44">
         <v>0</v>
       </c>
       <c r="V63" t="s">
@@ -6144,13 +6701,13 @@
       <c r="X63" s="3">
         <v>1</v>
       </c>
-      <c r="Y63" s="49"/>
-    </row>
-    <row r="64" spans="1:25" s="3" customFormat="1">
-      <c r="A64" s="43">
+      <c r="Y63" s="51"/>
+    </row>
+    <row r="64" s="3" customFormat="1" spans="1:25">
+      <c r="A64" s="44">
         <v>20120012</v>
       </c>
-      <c r="B64" s="42">
+      <c r="B64" s="43">
         <v>201200</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -6162,19 +6719,19 @@
       <c r="E64" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G64" s="45" t="s">
+      <c r="G64" s="47" t="s">
         <v>85</v>
       </c>
       <c r="H64" s="3">
         <v>3</v>
       </c>
-      <c r="I64" s="44">
+      <c r="I64" s="45">
         <v>1980000</v>
       </c>
-      <c r="J64" s="31" t="s">
+      <c r="J64" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K64" s="3">
@@ -6183,7 +6740,7 @@
       <c r="L64" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M64" s="46" t="s">
+      <c r="M64" s="48" t="s">
         <v>84</v>
       </c>
       <c r="N64" s="2">
@@ -6204,10 +6761,10 @@
       <c r="S64" s="3">
         <v>16008</v>
       </c>
-      <c r="T64" s="43">
+      <c r="T64" s="44">
         <v>12</v>
       </c>
-      <c r="U64" s="43">
+      <c r="U64" s="44">
         <v>0</v>
       </c>
       <c r="V64" t="s">
@@ -6219,7 +6776,7 @@
       <c r="X64" s="3">
         <v>1</v>
       </c>
-      <c r="Y64" s="49"/>
+      <c r="Y64" s="51"/>
     </row>
     <row r="65" spans="1:25">
       <c r="A65" s="2">
@@ -6238,19 +6795,19 @@
       <c r="E65" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F65" s="50" t="s">
+      <c r="F65" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G65" s="29" t="s">
+      <c r="G65" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H65" s="28">
         <v>21</v>
       </c>
-      <c r="I65" s="30">
+      <c r="I65" s="31">
         <v>1990000</v>
       </c>
-      <c r="J65" s="31" t="s">
+      <c r="J65" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K65" s="2">
@@ -6259,7 +6816,7 @@
       <c r="L65" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M65" s="32" t="s">
+      <c r="M65" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N65" s="2">
@@ -6277,13 +6834,13 @@
       <c r="R65" s="2">
         <v>15000</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>16008</v>
       </c>
       <c r="T65" s="5">
         <v>48</v>
       </c>
-      <c r="U65" s="34">
+      <c r="U65" s="35">
         <v>0</v>
       </c>
       <c r="V65" t="s">
@@ -6305,31 +6862,31 @@
         <f t="shared" ref="A65:A94" si="6">B66*10+H66</f>
         <v>2001022</v>
       </c>
-      <c r="B66" s="35">
+      <c r="B66" s="36">
         <v>200100</v>
       </c>
-      <c r="C66" s="35" t="s">
+      <c r="C66" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D66" s="35">
+      <c r="D66" s="36">
         <v>200100038</v>
       </c>
-      <c r="E66" s="35" t="s">
+      <c r="E66" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F66" s="50" t="s">
+      <c r="F66" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G66" s="29" t="s">
+      <c r="G66" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H66" s="28">
         <v>22</v>
       </c>
-      <c r="I66" s="30">
+      <c r="I66" s="31">
         <v>1990000</v>
       </c>
-      <c r="J66" s="36" t="s">
+      <c r="J66" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K66" s="2">
@@ -6338,7 +6895,7 @@
       <c r="L66" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M66" s="32" t="s">
+      <c r="M66" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N66" s="2">
@@ -6356,13 +6913,13 @@
       <c r="R66" s="2">
         <v>15000</v>
       </c>
-      <c r="S66" s="33">
+      <c r="S66" s="34">
         <v>16008</v>
       </c>
       <c r="T66" s="5">
         <v>48</v>
       </c>
-      <c r="U66" s="34">
+      <c r="U66" s="35">
         <v>0</v>
       </c>
       <c r="V66" t="s">
@@ -6379,7 +6936,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="67" spans="1:25" s="2" customFormat="1">
+    <row r="67" s="2" customFormat="1" spans="1:25">
       <c r="A67" s="2">
         <f t="shared" si="6"/>
         <v>2001023</v>
@@ -6396,19 +6953,19 @@
       <c r="E67" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F67" s="50" t="s">
+      <c r="F67" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G67" s="29" t="s">
+      <c r="G67" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H67" s="28">
         <v>23</v>
       </c>
-      <c r="I67" s="30">
+      <c r="I67" s="31">
         <v>1990000</v>
       </c>
-      <c r="J67" s="31" t="s">
+      <c r="J67" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K67" s="2">
@@ -6417,7 +6974,7 @@
       <c r="L67" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M67" s="32" t="s">
+      <c r="M67" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N67" s="2">
@@ -6435,13 +6992,13 @@
       <c r="R67" s="2">
         <v>15000</v>
       </c>
-      <c r="S67" s="33">
+      <c r="S67" s="34">
         <v>16008</v>
       </c>
       <c r="T67" s="5">
         <v>48</v>
       </c>
-      <c r="U67" s="34">
+      <c r="U67" s="35">
         <v>0</v>
       </c>
       <c r="V67" t="s">
@@ -6458,7 +7015,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="68" spans="1:25" s="2" customFormat="1">
+    <row r="68" s="2" customFormat="1" spans="1:25">
       <c r="A68" s="2">
         <f t="shared" si="6"/>
         <v>2001031</v>
@@ -6472,22 +7029,22 @@
       <c r="D68" s="28">
         <v>200101001</v>
       </c>
-      <c r="E68" s="37" t="s">
+      <c r="E68" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F68" s="50" t="s">
+      <c r="F68" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G68" s="29" t="s">
+      <c r="G68" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H68" s="28">
         <v>21</v>
       </c>
-      <c r="I68" s="30">
+      <c r="I68" s="31">
         <v>1990000</v>
       </c>
-      <c r="J68" s="31" t="s">
+      <c r="J68" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K68" s="2">
@@ -6496,7 +7053,7 @@
       <c r="L68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M68" s="32" t="s">
+      <c r="M68" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N68" s="2">
@@ -6514,13 +7071,13 @@
       <c r="R68" s="2">
         <v>15000</v>
       </c>
-      <c r="S68" s="33">
+      <c r="S68" s="34">
         <v>16008</v>
       </c>
       <c r="T68" s="5">
         <v>48</v>
       </c>
-      <c r="U68" s="34">
+      <c r="U68" s="35">
         <v>0</v>
       </c>
       <c r="V68" t="s">
@@ -6542,31 +7099,31 @@
         <f t="shared" si="6"/>
         <v>2001032</v>
       </c>
-      <c r="B69" s="35">
+      <c r="B69" s="36">
         <v>200101</v>
       </c>
-      <c r="C69" s="35" t="s">
+      <c r="C69" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D69" s="35">
+      <c r="D69" s="36">
         <v>200101001</v>
       </c>
-      <c r="E69" s="35" t="s">
+      <c r="E69" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F69" s="50" t="s">
+      <c r="F69" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G69" s="29" t="s">
+      <c r="G69" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H69" s="28">
         <v>22</v>
       </c>
-      <c r="I69" s="30">
+      <c r="I69" s="31">
         <v>1990000</v>
       </c>
-      <c r="J69" s="36" t="s">
+      <c r="J69" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K69" s="2">
@@ -6575,7 +7132,7 @@
       <c r="L69" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M69" s="32" t="s">
+      <c r="M69" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N69" s="2">
@@ -6593,13 +7150,13 @@
       <c r="R69" s="2">
         <v>15000</v>
       </c>
-      <c r="S69" s="33">
+      <c r="S69" s="34">
         <v>16008</v>
       </c>
       <c r="T69" s="5">
         <v>48</v>
       </c>
-      <c r="U69" s="34">
+      <c r="U69" s="35">
         <v>0</v>
       </c>
       <c r="V69" t="s">
@@ -6633,19 +7190,19 @@
       <c r="E70" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F70" s="50" t="s">
+      <c r="F70" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G70" s="29" t="s">
+      <c r="G70" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H70" s="28">
         <v>23</v>
       </c>
-      <c r="I70" s="30">
+      <c r="I70" s="31">
         <v>1990000</v>
       </c>
-      <c r="J70" s="31" t="s">
+      <c r="J70" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K70" s="2">
@@ -6654,7 +7211,7 @@
       <c r="L70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M70" s="32" t="s">
+      <c r="M70" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N70" s="2">
@@ -6672,13 +7229,13 @@
       <c r="R70" s="2">
         <v>15000</v>
       </c>
-      <c r="S70" s="33">
+      <c r="S70" s="34">
         <v>16008</v>
       </c>
       <c r="T70" s="5">
         <v>48</v>
       </c>
-      <c r="U70" s="34">
+      <c r="U70" s="35">
         <v>0</v>
       </c>
       <c r="V70" t="s">
@@ -6709,22 +7266,22 @@
       <c r="D71" s="28">
         <v>200300001</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="E71" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F71" s="50" t="s">
+      <c r="F71" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G71" s="29" t="s">
+      <c r="G71" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H71" s="28">
         <v>21</v>
       </c>
-      <c r="I71" s="30">
+      <c r="I71" s="31">
         <v>1990000</v>
       </c>
-      <c r="J71" s="31" t="s">
+      <c r="J71" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K71" s="2">
@@ -6733,7 +7290,7 @@
       <c r="L71" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M71" s="32" t="s">
+      <c r="M71" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N71" s="2">
@@ -6751,13 +7308,13 @@
       <c r="R71" s="2">
         <v>15000</v>
       </c>
-      <c r="S71" s="33">
+      <c r="S71" s="34">
         <v>16008</v>
       </c>
       <c r="T71" s="5">
         <v>50</v>
       </c>
-      <c r="U71" s="34">
+      <c r="U71" s="35">
         <v>0</v>
       </c>
       <c r="V71" t="s">
@@ -6774,36 +7331,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="72" spans="1:25" s="2" customFormat="1">
+    <row r="72" s="2" customFormat="1" spans="1:25">
       <c r="A72" s="2">
         <f t="shared" si="6"/>
         <v>2003022</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B72" s="36">
         <v>200300</v>
       </c>
-      <c r="C72" s="35" t="s">
+      <c r="C72" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D72" s="35">
+      <c r="D72" s="36">
         <v>200300001</v>
       </c>
-      <c r="E72" s="35" t="s">
+      <c r="E72" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F72" s="50" t="s">
+      <c r="F72" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G72" s="29" t="s">
+      <c r="G72" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H72" s="28">
         <v>22</v>
       </c>
-      <c r="I72" s="30">
+      <c r="I72" s="31">
         <v>1990000</v>
       </c>
-      <c r="J72" s="36" t="s">
+      <c r="J72" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K72" s="2">
@@ -6812,7 +7369,7 @@
       <c r="L72" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M72" s="32" t="s">
+      <c r="M72" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N72" s="2">
@@ -6830,13 +7387,13 @@
       <c r="R72" s="2">
         <v>15000</v>
       </c>
-      <c r="S72" s="33">
+      <c r="S72" s="34">
         <v>16008</v>
       </c>
       <c r="T72" s="5">
         <v>50</v>
       </c>
-      <c r="U72" s="34">
+      <c r="U72" s="35">
         <v>0</v>
       </c>
       <c r="V72" t="s">
@@ -6870,19 +7427,19 @@
       <c r="E73" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F73" s="50" t="s">
+      <c r="F73" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G73" s="29" t="s">
+      <c r="G73" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H73" s="28">
         <v>23</v>
       </c>
-      <c r="I73" s="30">
+      <c r="I73" s="31">
         <v>1990000</v>
       </c>
-      <c r="J73" s="31" t="s">
+      <c r="J73" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K73" s="2">
@@ -6891,7 +7448,7 @@
       <c r="L73" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M73" s="32" t="s">
+      <c r="M73" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N73" s="2">
@@ -6909,13 +7466,13 @@
       <c r="R73" s="2">
         <v>15000</v>
       </c>
-      <c r="S73" s="33">
+      <c r="S73" s="34">
         <v>16008</v>
       </c>
       <c r="T73" s="5">
         <v>50</v>
       </c>
-      <c r="U73" s="34">
+      <c r="U73" s="35">
         <v>0</v>
       </c>
       <c r="V73" t="s">
@@ -6946,22 +7503,22 @@
       <c r="D74" s="28">
         <v>200400009</v>
       </c>
-      <c r="E74" s="37" t="s">
+      <c r="E74" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F74" s="50" t="s">
+      <c r="F74" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G74" s="29" t="s">
+      <c r="G74" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H74" s="28">
         <v>21</v>
       </c>
-      <c r="I74" s="30">
+      <c r="I74" s="31">
         <v>1990000</v>
       </c>
-      <c r="J74" s="31" t="s">
+      <c r="J74" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K74" s="2">
@@ -6970,7 +7527,7 @@
       <c r="L74" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M74" s="32" t="s">
+      <c r="M74" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N74" s="2">
@@ -6988,13 +7545,13 @@
       <c r="R74" s="2">
         <v>15000</v>
       </c>
-      <c r="S74" s="33">
+      <c r="S74" s="34">
         <v>16008</v>
       </c>
       <c r="T74" s="5">
         <v>50</v>
       </c>
-      <c r="U74" s="34">
+      <c r="U74" s="35">
         <v>0</v>
       </c>
       <c r="V74" t="s">
@@ -7016,31 +7573,31 @@
         <f t="shared" si="6"/>
         <v>2004022</v>
       </c>
-      <c r="B75" s="35">
+      <c r="B75" s="36">
         <v>200400</v>
       </c>
-      <c r="C75" s="35" t="s">
+      <c r="C75" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D75" s="35">
+      <c r="D75" s="36">
         <v>200400009</v>
       </c>
-      <c r="E75" s="35" t="s">
+      <c r="E75" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F75" s="50" t="s">
+      <c r="F75" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G75" s="29" t="s">
+      <c r="G75" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H75" s="28">
         <v>22</v>
       </c>
-      <c r="I75" s="30">
+      <c r="I75" s="31">
         <v>1990000</v>
       </c>
-      <c r="J75" s="36" t="s">
+      <c r="J75" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K75" s="2">
@@ -7049,7 +7606,7 @@
       <c r="L75" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M75" s="32" t="s">
+      <c r="M75" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N75" s="2">
@@ -7067,13 +7624,13 @@
       <c r="R75" s="2">
         <v>15000</v>
       </c>
-      <c r="S75" s="33">
+      <c r="S75" s="34">
         <v>16008</v>
       </c>
       <c r="T75" s="5">
         <v>50</v>
       </c>
-      <c r="U75" s="34">
+      <c r="U75" s="35">
         <v>0</v>
       </c>
       <c r="V75" t="s">
@@ -7090,7 +7647,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="76" spans="1:25" s="2" customFormat="1">
+    <row r="76" s="2" customFormat="1" spans="1:25">
       <c r="A76" s="2">
         <f t="shared" si="6"/>
         <v>2004023</v>
@@ -7107,19 +7664,19 @@
       <c r="E76" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F76" s="50" t="s">
+      <c r="F76" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G76" s="29" t="s">
+      <c r="G76" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H76" s="28">
         <v>23</v>
       </c>
-      <c r="I76" s="30">
+      <c r="I76" s="31">
         <v>1990000</v>
       </c>
-      <c r="J76" s="31" t="s">
+      <c r="J76" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K76" s="2">
@@ -7128,7 +7685,7 @@
       <c r="L76" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M76" s="32" t="s">
+      <c r="M76" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N76" s="2">
@@ -7146,13 +7703,13 @@
       <c r="R76" s="2">
         <v>15000</v>
       </c>
-      <c r="S76" s="33">
+      <c r="S76" s="34">
         <v>16008</v>
       </c>
       <c r="T76" s="5">
         <v>50</v>
       </c>
-      <c r="U76" s="34">
+      <c r="U76" s="35">
         <v>0</v>
       </c>
       <c r="V76" t="s">
@@ -7169,10 +7726,9 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="77" spans="1:25" s="2" customFormat="1">
-      <c r="A77" s="2">
-        <f t="shared" si="6"/>
-        <v>2005021</v>
+    <row r="77" s="2" customFormat="1" spans="1:25">
+      <c r="A77" s="44">
+        <v>20050021</v>
       </c>
       <c r="B77" s="28">
         <v>200500</v>
@@ -7186,19 +7742,19 @@
       <c r="E77" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F77" s="50" t="s">
+      <c r="F77" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G77" s="29" t="s">
+      <c r="G77" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H77" s="28">
         <v>21</v>
       </c>
-      <c r="I77" s="30">
+      <c r="I77" s="31">
         <v>1990000</v>
       </c>
-      <c r="J77" s="31" t="s">
+      <c r="J77" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K77" s="2">
@@ -7207,7 +7763,7 @@
       <c r="L77" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M77" s="32" t="s">
+      <c r="M77" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N77" s="2">
@@ -7225,13 +7781,13 @@
       <c r="R77" s="2">
         <v>15000</v>
       </c>
-      <c r="S77" s="33">
+      <c r="S77" s="34">
         <v>16008</v>
       </c>
       <c r="T77" s="5">
         <v>48</v>
       </c>
-      <c r="U77" s="34">
+      <c r="U77" s="35">
         <v>0</v>
       </c>
       <c r="V77" t="s">
@@ -7249,35 +7805,34 @@
       </c>
     </row>
     <row r="78" spans="1:25">
-      <c r="A78" s="2">
-        <f t="shared" si="6"/>
-        <v>2005022</v>
-      </c>
-      <c r="B78" s="35">
+      <c r="A78" s="44">
+        <v>20050022</v>
+      </c>
+      <c r="B78" s="36">
         <v>200500</v>
       </c>
-      <c r="C78" s="35" t="s">
+      <c r="C78" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D78" s="35">
+      <c r="D78" s="36">
         <v>200500025</v>
       </c>
-      <c r="E78" s="35" t="s">
+      <c r="E78" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F78" s="50" t="s">
+      <c r="F78" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G78" s="29" t="s">
+      <c r="G78" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H78" s="28">
         <v>22</v>
       </c>
-      <c r="I78" s="30">
+      <c r="I78" s="31">
         <v>1990000</v>
       </c>
-      <c r="J78" s="36" t="s">
+      <c r="J78" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K78" s="2">
@@ -7286,7 +7841,7 @@
       <c r="L78" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M78" s="32" t="s">
+      <c r="M78" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N78" s="2">
@@ -7304,13 +7859,13 @@
       <c r="R78" s="2">
         <v>15000</v>
       </c>
-      <c r="S78" s="33">
+      <c r="S78" s="34">
         <v>16008</v>
       </c>
       <c r="T78" s="5">
         <v>48</v>
       </c>
-      <c r="U78" s="34">
+      <c r="U78" s="35">
         <v>0</v>
       </c>
       <c r="V78" t="s">
@@ -7328,9 +7883,8 @@
       </c>
     </row>
     <row r="79" spans="1:25">
-      <c r="A79" s="2">
-        <f t="shared" si="6"/>
-        <v>2005023</v>
+      <c r="A79" s="44">
+        <v>20050023</v>
       </c>
       <c r="B79" s="28">
         <v>200500</v>
@@ -7344,19 +7898,19 @@
       <c r="E79" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F79" s="50" t="s">
+      <c r="F79" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G79" s="29" t="s">
+      <c r="G79" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H79" s="28">
         <v>23</v>
       </c>
-      <c r="I79" s="30">
+      <c r="I79" s="31">
         <v>1990000</v>
       </c>
-      <c r="J79" s="31" t="s">
+      <c r="J79" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K79" s="2">
@@ -7365,7 +7919,7 @@
       <c r="L79" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M79" s="32" t="s">
+      <c r="M79" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N79" s="2">
@@ -7383,13 +7937,13 @@
       <c r="R79" s="2">
         <v>15000</v>
       </c>
-      <c r="S79" s="33">
+      <c r="S79" s="34">
         <v>16008</v>
       </c>
       <c r="T79" s="5">
         <v>48</v>
       </c>
-      <c r="U79" s="34">
+      <c r="U79" s="35">
         <v>0</v>
       </c>
       <c r="V79" t="s">
@@ -7420,22 +7974,22 @@
       <c r="D80" s="28">
         <v>200600001</v>
       </c>
-      <c r="E80" s="38" t="s">
+      <c r="E80" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F80" s="50" t="s">
+      <c r="F80" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G80" s="29" t="s">
+      <c r="G80" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H80" s="28">
         <v>21</v>
       </c>
-      <c r="I80" s="30">
+      <c r="I80" s="31">
         <v>1990000</v>
       </c>
-      <c r="J80" s="31" t="s">
+      <c r="J80" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K80" s="2">
@@ -7444,7 +7998,7 @@
       <c r="L80" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M80" s="32" t="s">
+      <c r="M80" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N80" s="2">
@@ -7462,13 +8016,13 @@
       <c r="R80" s="2">
         <v>15000</v>
       </c>
-      <c r="S80" s="33">
+      <c r="S80" s="34">
         <v>16008</v>
       </c>
       <c r="T80" s="5">
         <v>20</v>
       </c>
-      <c r="U80" s="34">
+      <c r="U80" s="35">
         <v>0</v>
       </c>
       <c r="V80" t="s">
@@ -7485,36 +8039,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="81" spans="1:25" s="2" customFormat="1">
+    <row r="81" s="2" customFormat="1" spans="1:25">
       <c r="A81" s="2">
         <f t="shared" si="6"/>
         <v>2006022</v>
       </c>
-      <c r="B81" s="35">
+      <c r="B81" s="36">
         <v>200600</v>
       </c>
-      <c r="C81" s="35" t="s">
+      <c r="C81" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D81" s="35">
+      <c r="D81" s="36">
         <v>200600001</v>
       </c>
-      <c r="E81" s="35" t="s">
+      <c r="E81" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F81" s="50" t="s">
+      <c r="F81" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G81" s="29" t="s">
+      <c r="G81" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H81" s="28">
         <v>22</v>
       </c>
-      <c r="I81" s="30">
+      <c r="I81" s="31">
         <v>1990000</v>
       </c>
-      <c r="J81" s="36" t="s">
+      <c r="J81" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K81" s="2">
@@ -7523,7 +8077,7 @@
       <c r="L81" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M81" s="32" t="s">
+      <c r="M81" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N81" s="2">
@@ -7541,13 +8095,13 @@
       <c r="R81" s="2">
         <v>15000</v>
       </c>
-      <c r="S81" s="33">
+      <c r="S81" s="34">
         <v>16008</v>
       </c>
       <c r="T81" s="5">
         <v>20</v>
       </c>
-      <c r="U81" s="34">
+      <c r="U81" s="35">
         <v>0</v>
       </c>
       <c r="V81" t="s">
@@ -7581,19 +8135,19 @@
       <c r="E82" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F82" s="50" t="s">
+      <c r="F82" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G82" s="29" t="s">
+      <c r="G82" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H82" s="28">
         <v>23</v>
       </c>
-      <c r="I82" s="30">
+      <c r="I82" s="31">
         <v>1990000</v>
       </c>
-      <c r="J82" s="31" t="s">
+      <c r="J82" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K82" s="2">
@@ -7602,7 +8156,7 @@
       <c r="L82" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M82" s="32" t="s">
+      <c r="M82" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N82" s="2">
@@ -7620,13 +8174,13 @@
       <c r="R82" s="2">
         <v>15000</v>
       </c>
-      <c r="S82" s="33">
+      <c r="S82" s="34">
         <v>16008</v>
       </c>
       <c r="T82" s="5">
         <v>20</v>
       </c>
-      <c r="U82" s="34">
+      <c r="U82" s="35">
         <v>0</v>
       </c>
       <c r="V82" t="s">
@@ -7660,19 +8214,19 @@
       <c r="E83" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F83" s="50" t="s">
+      <c r="F83" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G83" s="29" t="s">
+      <c r="G83" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H83" s="28">
         <v>21</v>
       </c>
-      <c r="I83" s="30">
+      <c r="I83" s="31">
         <v>1990000</v>
       </c>
-      <c r="J83" s="31" t="s">
+      <c r="J83" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K83" s="2">
@@ -7681,7 +8235,7 @@
       <c r="L83" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M83" s="32" t="s">
+      <c r="M83" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N83" s="2">
@@ -7699,13 +8253,13 @@
       <c r="R83" s="2">
         <v>15000</v>
       </c>
-      <c r="S83" s="33">
+      <c r="S83" s="34">
         <v>16008</v>
       </c>
       <c r="T83" s="5">
         <v>30</v>
       </c>
-      <c r="U83" s="34">
+      <c r="U83" s="35">
         <v>1</v>
       </c>
       <c r="V83" t="s">
@@ -7727,31 +8281,31 @@
         <f t="shared" si="6"/>
         <v>2007022</v>
       </c>
-      <c r="B84" s="35">
+      <c r="B84" s="36">
         <v>200700</v>
       </c>
-      <c r="C84" s="35" t="s">
+      <c r="C84" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D84" s="35">
+      <c r="D84" s="36">
         <v>200700001</v>
       </c>
-      <c r="E84" s="35" t="s">
+      <c r="E84" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F84" s="50" t="s">
+      <c r="F84" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G84" s="29" t="s">
+      <c r="G84" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H84" s="28">
         <v>22</v>
       </c>
-      <c r="I84" s="30">
+      <c r="I84" s="31">
         <v>1990000</v>
       </c>
-      <c r="J84" s="36" t="s">
+      <c r="J84" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K84" s="2">
@@ -7760,7 +8314,7 @@
       <c r="L84" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M84" s="32" t="s">
+      <c r="M84" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N84" s="2">
@@ -7778,13 +8332,13 @@
       <c r="R84" s="2">
         <v>15000</v>
       </c>
-      <c r="S84" s="33">
+      <c r="S84" s="34">
         <v>16008</v>
       </c>
       <c r="T84" s="5">
         <v>30</v>
       </c>
-      <c r="U84" s="34">
+      <c r="U84" s="35">
         <v>1</v>
       </c>
       <c r="V84" t="s">
@@ -7801,7 +8355,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="85" spans="1:25" s="2" customFormat="1">
+    <row r="85" s="2" customFormat="1" spans="1:25">
       <c r="A85" s="2">
         <f t="shared" si="6"/>
         <v>2007023</v>
@@ -7818,19 +8372,19 @@
       <c r="E85" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="50" t="s">
+      <c r="F85" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G85" s="29" t="s">
+      <c r="G85" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H85" s="28">
         <v>23</v>
       </c>
-      <c r="I85" s="30">
+      <c r="I85" s="31">
         <v>1990000</v>
       </c>
-      <c r="J85" s="31" t="s">
+      <c r="J85" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K85" s="2">
@@ -7839,7 +8393,7 @@
       <c r="L85" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M85" s="32" t="s">
+      <c r="M85" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N85" s="2">
@@ -7857,13 +8411,13 @@
       <c r="R85" s="2">
         <v>15000</v>
       </c>
-      <c r="S85" s="33">
+      <c r="S85" s="34">
         <v>16008</v>
       </c>
       <c r="T85" s="5">
         <v>30</v>
       </c>
-      <c r="U85" s="34">
+      <c r="U85" s="35">
         <v>1</v>
       </c>
       <c r="V85" t="s">
@@ -7880,7 +8434,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="86" spans="1:25" s="2" customFormat="1">
+    <row r="86" s="2" customFormat="1" spans="1:25">
       <c r="A86" s="2">
         <f t="shared" si="6"/>
         <v>2008021</v>
@@ -7894,22 +8448,22 @@
       <c r="D86" s="28">
         <v>200800001</v>
       </c>
-      <c r="E86" s="38" t="s">
+      <c r="E86" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F86" s="50" t="s">
+      <c r="F86" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G86" s="29" t="s">
+      <c r="G86" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H86" s="28">
         <v>21</v>
       </c>
-      <c r="I86" s="30">
+      <c r="I86" s="31">
         <v>1990000</v>
       </c>
-      <c r="J86" s="31" t="s">
+      <c r="J86" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K86" s="2">
@@ -7918,7 +8472,7 @@
       <c r="L86" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M86" s="32" t="s">
+      <c r="M86" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N86" s="2">
@@ -7936,13 +8490,13 @@
       <c r="R86" s="2">
         <v>15000</v>
       </c>
-      <c r="S86" s="33">
+      <c r="S86" s="34">
         <v>16008</v>
       </c>
       <c r="T86" s="5">
         <v>20</v>
       </c>
-      <c r="U86" s="34">
+      <c r="U86" s="35">
         <v>0</v>
       </c>
       <c r="V86" t="s">
@@ -7959,7 +8513,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="87" spans="1:25" s="2" customFormat="1">
+    <row r="87" s="2" customFormat="1" spans="1:25">
       <c r="A87" s="2">
         <f t="shared" si="6"/>
         <v>2008022</v>
@@ -7973,22 +8527,22 @@
       <c r="D87" s="28">
         <v>200800001</v>
       </c>
-      <c r="E87" s="35" t="s">
+      <c r="E87" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F87" s="50" t="s">
+      <c r="F87" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G87" s="29" t="s">
+      <c r="G87" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H87" s="28">
         <v>22</v>
       </c>
-      <c r="I87" s="30">
+      <c r="I87" s="31">
         <v>1990000</v>
       </c>
-      <c r="J87" s="36" t="s">
+      <c r="J87" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K87" s="2">
@@ -7997,7 +8551,7 @@
       <c r="L87" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M87" s="32" t="s">
+      <c r="M87" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N87" s="2">
@@ -8015,13 +8569,13 @@
       <c r="R87" s="2">
         <v>15000</v>
       </c>
-      <c r="S87" s="33">
+      <c r="S87" s="34">
         <v>16008</v>
       </c>
       <c r="T87" s="5">
         <v>20</v>
       </c>
-      <c r="U87" s="34">
+      <c r="U87" s="35">
         <v>0</v>
       </c>
       <c r="V87" t="s">
@@ -8038,7 +8592,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="88" spans="1:25" s="2" customFormat="1">
+    <row r="88" s="2" customFormat="1" spans="1:25">
       <c r="A88" s="2">
         <f t="shared" si="6"/>
         <v>2008023</v>
@@ -8055,19 +8609,19 @@
       <c r="E88" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F88" s="50" t="s">
+      <c r="F88" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G88" s="29" t="s">
+      <c r="G88" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H88" s="28">
         <v>23</v>
       </c>
-      <c r="I88" s="30">
+      <c r="I88" s="31">
         <v>1990000</v>
       </c>
-      <c r="J88" s="31" t="s">
+      <c r="J88" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K88" s="2">
@@ -8076,7 +8630,7 @@
       <c r="L88" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M88" s="32" t="s">
+      <c r="M88" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N88" s="2">
@@ -8094,13 +8648,13 @@
       <c r="R88" s="2">
         <v>15000</v>
       </c>
-      <c r="S88" s="33">
+      <c r="S88" s="34">
         <v>16008</v>
       </c>
       <c r="T88" s="5">
         <v>20</v>
       </c>
-      <c r="U88" s="34">
+      <c r="U88" s="35">
         <v>0</v>
       </c>
       <c r="V88" t="s">
@@ -8117,12 +8671,12 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="89" spans="1:25" s="2" customFormat="1">
+    <row r="89" s="2" customFormat="1" spans="1:25">
       <c r="A89" s="2">
         <f t="shared" si="6"/>
         <v>2009021</v>
       </c>
-      <c r="B89" s="39">
+      <c r="B89" s="40">
         <v>200900</v>
       </c>
       <c r="C89" s="28" t="s">
@@ -8131,31 +8685,31 @@
       <c r="D89" s="28">
         <v>200900001</v>
       </c>
-      <c r="E89" s="37" t="s">
+      <c r="E89" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F89" s="50" t="s">
+      <c r="F89" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G89" s="29" t="s">
+      <c r="G89" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H89" s="28">
         <v>21</v>
       </c>
-      <c r="I89" s="30">
+      <c r="I89" s="31">
         <v>1990000</v>
       </c>
-      <c r="J89" s="31" t="s">
+      <c r="J89" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K89" s="40">
+      <c r="K89" s="41">
         <v>0</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M89" s="32" t="s">
+      <c r="M89" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N89" s="2">
@@ -8173,13 +8727,13 @@
       <c r="R89" s="2">
         <v>15000</v>
       </c>
-      <c r="S89" s="33">
+      <c r="S89" s="34">
         <v>16008</v>
       </c>
       <c r="T89" s="5">
         <v>20</v>
       </c>
-      <c r="U89" s="34">
+      <c r="U89" s="35">
         <v>0</v>
       </c>
       <c r="V89" t="s">
@@ -8201,40 +8755,40 @@
         <f t="shared" si="6"/>
         <v>2009022</v>
       </c>
-      <c r="B90" s="41">
+      <c r="B90" s="42">
         <v>200900</v>
       </c>
-      <c r="C90" s="35" t="s">
+      <c r="C90" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="D90" s="35">
+      <c r="D90" s="36">
         <v>200900001</v>
       </c>
-      <c r="E90" s="35" t="s">
+      <c r="E90" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F90" s="50" t="s">
+      <c r="F90" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G90" s="29" t="s">
+      <c r="G90" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H90" s="28">
         <v>22</v>
       </c>
-      <c r="I90" s="30">
+      <c r="I90" s="31">
         <v>1990000</v>
       </c>
-      <c r="J90" s="36" t="s">
+      <c r="J90" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K90" s="40">
+      <c r="K90" s="41">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M90" s="32" t="s">
+      <c r="M90" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N90" s="2">
@@ -8252,13 +8806,13 @@
       <c r="R90" s="2">
         <v>15000</v>
       </c>
-      <c r="S90" s="33">
+      <c r="S90" s="34">
         <v>16008</v>
       </c>
       <c r="T90" s="5">
         <v>20</v>
       </c>
-      <c r="U90" s="34">
+      <c r="U90" s="35">
         <v>0</v>
       </c>
       <c r="V90" t="s">
@@ -8280,7 +8834,7 @@
         <f t="shared" si="6"/>
         <v>2009023</v>
       </c>
-      <c r="B91" s="39">
+      <c r="B91" s="40">
         <v>200900</v>
       </c>
       <c r="C91" s="28" t="s">
@@ -8292,28 +8846,28 @@
       <c r="E91" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F91" s="50" t="s">
+      <c r="F91" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G91" s="29" t="s">
+      <c r="G91" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H91" s="28">
         <v>23</v>
       </c>
-      <c r="I91" s="30">
+      <c r="I91" s="31">
         <v>1990000</v>
       </c>
-      <c r="J91" s="31" t="s">
+      <c r="J91" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K91" s="40">
+      <c r="K91" s="41">
         <v>0</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M91" s="32" t="s">
+      <c r="M91" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N91" s="2">
@@ -8331,13 +8885,13 @@
       <c r="R91" s="2">
         <v>15000</v>
       </c>
-      <c r="S91" s="33">
+      <c r="S91" s="34">
         <v>16008</v>
       </c>
       <c r="T91" s="5">
         <v>20</v>
       </c>
-      <c r="U91" s="34">
+      <c r="U91" s="35">
         <v>0</v>
       </c>
       <c r="V91" t="s">
@@ -8354,45 +8908,45 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="92" spans="1:25" s="2" customFormat="1">
+    <row r="92" s="2" customFormat="1" spans="1:25">
       <c r="A92" s="2">
         <f t="shared" si="6"/>
         <v>2012021</v>
       </c>
-      <c r="B92" s="42">
+      <c r="B92" s="43">
         <v>201200</v>
       </c>
       <c r="C92" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D92" s="35">
+      <c r="D92" s="36">
         <v>201200001</v>
       </c>
-      <c r="E92" s="37" t="s">
+      <c r="E92" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F92" s="50" t="s">
+      <c r="F92" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G92" s="29" t="s">
+      <c r="G92" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H92" s="28">
         <v>21</v>
       </c>
-      <c r="I92" s="30">
+      <c r="I92" s="31">
         <v>1990000</v>
       </c>
-      <c r="J92" s="31" t="s">
+      <c r="J92" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K92" s="40">
+      <c r="K92" s="41">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M92" s="32" t="s">
+      <c r="M92" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N92" s="2">
@@ -8410,13 +8964,13 @@
       <c r="R92" s="2">
         <v>15000</v>
       </c>
-      <c r="S92" s="33">
+      <c r="S92" s="34">
         <v>16008</v>
       </c>
       <c r="T92" s="5">
         <v>12</v>
       </c>
-      <c r="U92" s="34">
+      <c r="U92" s="35">
         <v>0</v>
       </c>
       <c r="V92" t="s">
@@ -8438,40 +8992,40 @@
         <f t="shared" si="6"/>
         <v>2012022</v>
       </c>
-      <c r="B93" s="42">
+      <c r="B93" s="43">
         <v>201200</v>
       </c>
       <c r="C93" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D93" s="35">
+      <c r="D93" s="36">
         <v>201200001</v>
       </c>
-      <c r="E93" s="35" t="s">
+      <c r="E93" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F93" s="50" t="s">
+      <c r="F93" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G93" s="29" t="s">
+      <c r="G93" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H93" s="28">
         <v>22</v>
       </c>
-      <c r="I93" s="30">
+      <c r="I93" s="31">
         <v>1990000</v>
       </c>
-      <c r="J93" s="36" t="s">
+      <c r="J93" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K93" s="40">
+      <c r="K93" s="41">
         <v>0</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M93" s="32" t="s">
+      <c r="M93" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N93" s="2">
@@ -8489,13 +9043,13 @@
       <c r="R93" s="2">
         <v>15000</v>
       </c>
-      <c r="S93" s="33">
+      <c r="S93" s="34">
         <v>16008</v>
       </c>
       <c r="T93" s="5">
         <v>12</v>
       </c>
-      <c r="U93" s="34">
+      <c r="U93" s="35">
         <v>0</v>
       </c>
       <c r="V93" t="s">
@@ -8517,40 +9071,40 @@
         <f t="shared" si="6"/>
         <v>2012023</v>
       </c>
-      <c r="B94" s="42">
+      <c r="B94" s="43">
         <v>201200</v>
       </c>
       <c r="C94" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="35">
+      <c r="D94" s="36">
         <v>201200001</v>
       </c>
       <c r="E94" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F94" s="50" t="s">
+      <c r="F94" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G94" s="29" t="s">
+      <c r="G94" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H94" s="28">
         <v>23</v>
       </c>
-      <c r="I94" s="30">
+      <c r="I94" s="31">
         <v>1990000</v>
       </c>
-      <c r="J94" s="31" t="s">
+      <c r="J94" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K94" s="40">
+      <c r="K94" s="41">
         <v>0</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M94" s="32" t="s">
+      <c r="M94" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N94" s="2">
@@ -8568,13 +9122,13 @@
       <c r="R94" s="2">
         <v>15000</v>
       </c>
-      <c r="S94" s="33">
+      <c r="S94" s="34">
         <v>16008</v>
       </c>
       <c r="T94" s="5">
         <v>12</v>
       </c>
-      <c r="U94" s="34">
+      <c r="U94" s="35">
         <v>0</v>
       </c>
       <c r="V94" t="s">
@@ -8592,10 +9146,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S94" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\特殊用户标记相关配置表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE37467-CAA5-4650-81E5-0D9A000FE32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="794"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,20 +36,21 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
     <author>C</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -52,6 +59,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -60,12 +68,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">普通场 1
@@ -75,25 +84,27 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>押分筹码列表</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2">
+    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -102,6 +113,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -110,12 +122,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1">
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>阶段信息:[准备阶段时间-毫秒，押分阶段时间-毫秒，亮牌阶段时间-毫秒，结算阶段-毫秒]
@@ -124,12 +137,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1">
+    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>每笔投注进入房间水池比例
@@ -139,25 +153,27 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>净赢分*抽水比例</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2">
+    <comment ref="P1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -166,6 +182,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -174,13 +191,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="2">
+    <comment ref="Q1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -189,6 +207,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -197,13 +216,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="2">
+    <comment ref="R1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -212,6 +232,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -221,13 +242,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -236,6 +258,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -244,13 +267,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="2">
+    <comment ref="U1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -259,6 +283,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -267,13 +292,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0">
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -282,6 +308,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -291,13 +318,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0">
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -306,6 +334,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -313,12 +342,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最大押分值*10000</t>
@@ -668,15 +698,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -725,173 +751,45 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -900,216 +798,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799340800195319"/>
+        <fgColor theme="7" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799340800195319"/>
+        <fgColor theme="9" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799340800195319"/>
+        <fgColor theme="4" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799340800195319"/>
+        <fgColor theme="5" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1117,272 +853,30 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="60">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1402,19 +896,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1453,11 +947,11 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1471,10 +965,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1506,11 +996,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1525,17 +1015,13 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1554,84 +1040,40 @@
     <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="60">
+  <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 2 2" xfId="50"/>
-    <cellStyle name="常规 2 2 2" xfId="51"/>
-    <cellStyle name="常规 3" xfId="52"/>
-    <cellStyle name="常规 3 2" xfId="53"/>
-    <cellStyle name="常规 4" xfId="54"/>
-    <cellStyle name="常规 5" xfId="55"/>
-    <cellStyle name="常规 6" xfId="56"/>
-    <cellStyle name="常规 6 2" xfId="57"/>
-    <cellStyle name="常规 6 2 2" xfId="58"/>
-    <cellStyle name="常规 7" xfId="59"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1889,18 +1331,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.375" style="2"/>
+    <col min="1" max="1" width="10.75" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="4" width="20.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
@@ -1922,7 +1365,7 @@
     <col min="25" max="25" width="20.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41.1" customHeight="1" spans="1:25">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="41.1" customHeight="1">
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1991,7 +1434,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:25">
+    <row r="2" spans="1:25" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -2062,7 +1505,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:25">
+    <row r="3" spans="1:25" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -2133,7 +1576,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:25">
+    <row r="4" spans="1:25" s="1" customFormat="1">
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
@@ -2175,19 +1618,19 @@
       <c r="E5" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="30" t="s">
+      <c r="F5" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H5" s="28">
         <v>1</v>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="30">
         <v>1990000</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="J5" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K5" s="2">
@@ -2196,7 +1639,7 @@
       <c r="L5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="33" t="s">
+      <c r="M5" s="32" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="2">
@@ -2214,13 +1657,13 @@
       <c r="R5" s="2">
         <v>15000</v>
       </c>
-      <c r="S5" s="34">
+      <c r="S5" s="33">
         <v>16008</v>
       </c>
       <c r="T5" s="5">
         <v>48</v>
       </c>
-      <c r="U5" s="35">
+      <c r="U5" s="34">
         <v>0</v>
       </c>
       <c r="V5" t="s">
@@ -2242,31 +1685,31 @@
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="35">
         <v>200100</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="35">
         <v>200100038</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="30" t="s">
+      <c r="F6" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="35">
         <v>2</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="30">
         <v>1990000</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="2">
@@ -2275,7 +1718,7 @@
       <c r="L6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="33" t="s">
+      <c r="M6" s="32" t="s">
         <v>56</v>
       </c>
       <c r="N6" s="2">
@@ -2293,13 +1736,13 @@
       <c r="R6" s="2">
         <v>15000</v>
       </c>
-      <c r="S6" s="34">
+      <c r="S6" s="33">
         <v>16008</v>
       </c>
       <c r="T6" s="5">
         <v>48</v>
       </c>
-      <c r="U6" s="35">
+      <c r="U6" s="34">
         <v>0</v>
       </c>
       <c r="V6" t="s">
@@ -2316,7 +1759,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:25">
+    <row r="7" spans="1:25" s="2" customFormat="1">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -2333,19 +1776,19 @@
       <c r="E7" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="F7" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H7" s="28">
         <v>3</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="30">
         <v>1990000</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="J7" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K7" s="2">
@@ -2354,7 +1797,7 @@
       <c r="L7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="33" t="s">
+      <c r="M7" s="32" t="s">
         <v>56</v>
       </c>
       <c r="N7" s="2">
@@ -2372,13 +1815,13 @@
       <c r="R7" s="2">
         <v>15000</v>
       </c>
-      <c r="S7" s="34">
+      <c r="S7" s="33">
         <v>16008</v>
       </c>
       <c r="T7" s="5">
         <v>48</v>
       </c>
-      <c r="U7" s="35">
+      <c r="U7" s="34">
         <v>0</v>
       </c>
       <c r="V7" t="s">
@@ -2395,7 +1838,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:25">
+    <row r="8" spans="1:25" s="2" customFormat="1">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -2409,22 +1852,22 @@
       <c r="D8" s="28">
         <v>200101001</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="F8" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H8" s="28">
         <v>1</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="30">
         <v>1990000</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K8" s="2">
@@ -2433,7 +1876,7 @@
       <c r="L8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="33" t="s">
+      <c r="M8" s="32" t="s">
         <v>69</v>
       </c>
       <c r="N8" s="2">
@@ -2451,13 +1894,13 @@
       <c r="R8" s="2">
         <v>15000</v>
       </c>
-      <c r="S8" s="34">
+      <c r="S8" s="33">
         <v>16008</v>
       </c>
       <c r="T8" s="5">
         <v>48</v>
       </c>
-      <c r="U8" s="35">
+      <c r="U8" s="34">
         <v>0</v>
       </c>
       <c r="V8" t="s">
@@ -2479,31 +1922,31 @@
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="35">
         <v>200101</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="35">
         <v>200101001</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="30" t="s">
+      <c r="F9" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="35">
         <v>2</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="30">
         <v>1990000</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K9" s="2">
@@ -2512,7 +1955,7 @@
       <c r="L9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="32" t="s">
         <v>69</v>
       </c>
       <c r="N9" s="2">
@@ -2530,13 +1973,13 @@
       <c r="R9" s="2">
         <v>15000</v>
       </c>
-      <c r="S9" s="34">
+      <c r="S9" s="33">
         <v>16008</v>
       </c>
       <c r="T9" s="5">
         <v>48</v>
       </c>
-      <c r="U9" s="35">
+      <c r="U9" s="34">
         <v>0</v>
       </c>
       <c r="V9" t="s">
@@ -2570,19 +2013,19 @@
       <c r="E10" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="30" t="s">
+      <c r="F10" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H10" s="28">
         <v>3</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="30">
         <v>1990000</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K10" s="2">
@@ -2591,7 +2034,7 @@
       <c r="L10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="33" t="s">
+      <c r="M10" s="32" t="s">
         <v>69</v>
       </c>
       <c r="N10" s="2">
@@ -2609,13 +2052,13 @@
       <c r="R10" s="2">
         <v>15000</v>
       </c>
-      <c r="S10" s="34">
+      <c r="S10" s="33">
         <v>16008</v>
       </c>
       <c r="T10" s="5">
         <v>48</v>
       </c>
-      <c r="U10" s="35">
+      <c r="U10" s="34">
         <v>0</v>
       </c>
       <c r="V10" t="s">
@@ -2646,22 +2089,22 @@
       <c r="D11" s="28">
         <v>200300001</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="30" t="s">
+      <c r="F11" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H11" s="28">
         <v>1</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="30">
         <v>1990000</v>
       </c>
-      <c r="J11" s="32" t="s">
+      <c r="J11" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K11" s="2">
@@ -2670,7 +2113,7 @@
       <c r="L11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="33" t="s">
+      <c r="M11" s="32" t="s">
         <v>71</v>
       </c>
       <c r="N11" s="2">
@@ -2688,13 +2131,13 @@
       <c r="R11" s="2">
         <v>15000</v>
       </c>
-      <c r="S11" s="34">
+      <c r="S11" s="33">
         <v>16008</v>
       </c>
       <c r="T11" s="5">
         <v>50</v>
       </c>
-      <c r="U11" s="35">
+      <c r="U11" s="34">
         <v>0</v>
       </c>
       <c r="V11" t="s">
@@ -2711,36 +2154,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:25">
+    <row r="12" spans="1:25" s="2" customFormat="1">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="35">
         <v>200300</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="35">
         <v>200300001</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="30" t="s">
+      <c r="F12" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="35">
         <v>2</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="30">
         <v>1990000</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="J12" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K12" s="2">
@@ -2749,7 +2192,7 @@
       <c r="L12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="33" t="s">
+      <c r="M12" s="32" t="s">
         <v>71</v>
       </c>
       <c r="N12" s="2">
@@ -2767,13 +2210,13 @@
       <c r="R12" s="2">
         <v>15000</v>
       </c>
-      <c r="S12" s="34">
+      <c r="S12" s="33">
         <v>16008</v>
       </c>
       <c r="T12" s="5">
         <v>50</v>
       </c>
-      <c r="U12" s="35">
+      <c r="U12" s="34">
         <v>0</v>
       </c>
       <c r="V12" t="s">
@@ -2807,19 +2250,19 @@
       <c r="E13" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="30" t="s">
+      <c r="F13" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H13" s="28">
         <v>3</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="30">
         <v>1990000</v>
       </c>
-      <c r="J13" s="32" t="s">
+      <c r="J13" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K13" s="2">
@@ -2828,7 +2271,7 @@
       <c r="L13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="33" t="s">
+      <c r="M13" s="32" t="s">
         <v>71</v>
       </c>
       <c r="N13" s="2">
@@ -2846,13 +2289,13 @@
       <c r="R13" s="2">
         <v>15000</v>
       </c>
-      <c r="S13" s="34">
+      <c r="S13" s="33">
         <v>16008</v>
       </c>
       <c r="T13" s="5">
         <v>50</v>
       </c>
-      <c r="U13" s="35">
+      <c r="U13" s="34">
         <v>0</v>
       </c>
       <c r="V13" t="s">
@@ -2883,22 +2326,22 @@
       <c r="D14" s="28">
         <v>200400009</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="30" t="s">
+      <c r="F14" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H14" s="28">
         <v>1</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="30">
         <v>1990000</v>
       </c>
-      <c r="J14" s="32" t="s">
+      <c r="J14" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="2">
@@ -2907,7 +2350,7 @@
       <c r="L14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="33" t="s">
+      <c r="M14" s="32" t="s">
         <v>73</v>
       </c>
       <c r="N14" s="2">
@@ -2925,13 +2368,13 @@
       <c r="R14" s="2">
         <v>15000</v>
       </c>
-      <c r="S14" s="34">
+      <c r="S14" s="33">
         <v>16008</v>
       </c>
       <c r="T14" s="5">
         <v>50</v>
       </c>
-      <c r="U14" s="35">
+      <c r="U14" s="34">
         <v>0</v>
       </c>
       <c r="V14" t="s">
@@ -2953,31 +2396,31 @@
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="35">
         <v>200400</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="35">
         <v>200400009</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="30" t="s">
+      <c r="F15" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="35">
         <v>2</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="30">
         <v>1990000</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K15" s="2">
@@ -2986,7 +2429,7 @@
       <c r="L15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="33" t="s">
+      <c r="M15" s="32" t="s">
         <v>73</v>
       </c>
       <c r="N15" s="2">
@@ -3004,13 +2447,13 @@
       <c r="R15" s="2">
         <v>15000</v>
       </c>
-      <c r="S15" s="34">
+      <c r="S15" s="33">
         <v>16008</v>
       </c>
       <c r="T15" s="5">
         <v>50</v>
       </c>
-      <c r="U15" s="35">
+      <c r="U15" s="34">
         <v>0</v>
       </c>
       <c r="V15" t="s">
@@ -3027,7 +2470,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:25">
+    <row r="16" spans="1:25" s="2" customFormat="1">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -3044,19 +2487,19 @@
       <c r="E16" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="30" t="s">
+      <c r="F16" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H16" s="28">
         <v>3</v>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="30">
         <v>1990000</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="J16" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K16" s="2">
@@ -3065,7 +2508,7 @@
       <c r="L16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M16" s="33" t="s">
+      <c r="M16" s="32" t="s">
         <v>73</v>
       </c>
       <c r="N16" s="2">
@@ -3083,13 +2526,13 @@
       <c r="R16" s="2">
         <v>15000</v>
       </c>
-      <c r="S16" s="34">
+      <c r="S16" s="33">
         <v>16008</v>
       </c>
       <c r="T16" s="5">
         <v>50</v>
       </c>
-      <c r="U16" s="35">
+      <c r="U16" s="34">
         <v>0</v>
       </c>
       <c r="V16" t="s">
@@ -3106,7 +2549,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:25">
+    <row r="17" spans="1:25" s="2" customFormat="1">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -3123,19 +2566,19 @@
       <c r="E17" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="30" t="s">
+      <c r="F17" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H17" s="28">
         <v>1</v>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="30">
         <v>1990000</v>
       </c>
-      <c r="J17" s="32" t="s">
+      <c r="J17" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K17" s="2">
@@ -3144,7 +2587,7 @@
       <c r="L17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="33" t="s">
+      <c r="M17" s="32" t="s">
         <v>75</v>
       </c>
       <c r="N17" s="2">
@@ -3162,13 +2605,13 @@
       <c r="R17" s="2">
         <v>15000</v>
       </c>
-      <c r="S17" s="34">
+      <c r="S17" s="33">
         <v>16008</v>
       </c>
       <c r="T17" s="5">
         <v>48</v>
       </c>
-      <c r="U17" s="35">
+      <c r="U17" s="34">
         <v>0</v>
       </c>
       <c r="V17" t="s">
@@ -3190,31 +2633,31 @@
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="35">
         <v>200500</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="35">
         <v>200500025</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="30" t="s">
+      <c r="F18" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="35">
         <v>2</v>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="30">
         <v>1990000</v>
       </c>
-      <c r="J18" s="37" t="s">
+      <c r="J18" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K18" s="2">
@@ -3223,7 +2666,7 @@
       <c r="L18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="33" t="s">
+      <c r="M18" s="32" t="s">
         <v>75</v>
       </c>
       <c r="N18" s="2">
@@ -3241,13 +2684,13 @@
       <c r="R18" s="2">
         <v>15000</v>
       </c>
-      <c r="S18" s="34">
+      <c r="S18" s="33">
         <v>16008</v>
       </c>
       <c r="T18" s="5">
         <v>48</v>
       </c>
-      <c r="U18" s="35">
+      <c r="U18" s="34">
         <v>0</v>
       </c>
       <c r="V18" t="s">
@@ -3281,19 +2724,19 @@
       <c r="E19" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="30" t="s">
+      <c r="F19" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="28">
         <v>3</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="30">
         <v>1990000</v>
       </c>
-      <c r="J19" s="32" t="s">
+      <c r="J19" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K19" s="2">
@@ -3302,7 +2745,7 @@
       <c r="L19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="33" t="s">
+      <c r="M19" s="32" t="s">
         <v>75</v>
       </c>
       <c r="N19" s="2">
@@ -3320,13 +2763,13 @@
       <c r="R19" s="2">
         <v>15000</v>
       </c>
-      <c r="S19" s="34">
+      <c r="S19" s="33">
         <v>16008</v>
       </c>
       <c r="T19" s="5">
         <v>48</v>
       </c>
-      <c r="U19" s="35">
+      <c r="U19" s="34">
         <v>0</v>
       </c>
       <c r="V19" t="s">
@@ -3357,22 +2800,22 @@
       <c r="D20" s="28">
         <v>200600001</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" s="30" t="s">
+      <c r="F20" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H20" s="28">
         <v>1</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="30">
         <v>1990000</v>
       </c>
-      <c r="J20" s="32" t="s">
+      <c r="J20" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K20" s="2">
@@ -3381,7 +2824,7 @@
       <c r="L20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="33" t="s">
+      <c r="M20" s="32" t="s">
         <v>77</v>
       </c>
       <c r="N20" s="2">
@@ -3399,13 +2842,13 @@
       <c r="R20" s="2">
         <v>15000</v>
       </c>
-      <c r="S20" s="34">
+      <c r="S20" s="33">
         <v>16008</v>
       </c>
       <c r="T20" s="5">
         <v>20</v>
       </c>
-      <c r="U20" s="35">
+      <c r="U20" s="34">
         <v>0</v>
       </c>
       <c r="V20" t="s">
@@ -3422,36 +2865,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:25">
+    <row r="21" spans="1:25" s="2" customFormat="1">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="36">
+      <c r="B21" s="35">
         <v>200600</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="35">
         <v>200600001</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21" s="30" t="s">
+      <c r="F21" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="35">
         <v>2</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="30">
         <v>1990000</v>
       </c>
-      <c r="J21" s="37" t="s">
+      <c r="J21" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K21" s="2">
@@ -3460,7 +2903,7 @@
       <c r="L21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="33" t="s">
+      <c r="M21" s="32" t="s">
         <v>77</v>
       </c>
       <c r="N21" s="2">
@@ -3478,13 +2921,13 @@
       <c r="R21" s="2">
         <v>15000</v>
       </c>
-      <c r="S21" s="34">
+      <c r="S21" s="33">
         <v>16008</v>
       </c>
       <c r="T21" s="5">
         <v>20</v>
       </c>
-      <c r="U21" s="35">
+      <c r="U21" s="34">
         <v>0</v>
       </c>
       <c r="V21" t="s">
@@ -3518,19 +2961,19 @@
       <c r="E22" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" s="30" t="s">
+      <c r="F22" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H22" s="28">
         <v>3</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="30">
         <v>1990000</v>
       </c>
-      <c r="J22" s="32" t="s">
+      <c r="J22" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K22" s="2">
@@ -3539,7 +2982,7 @@
       <c r="L22" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M22" s="33" t="s">
+      <c r="M22" s="32" t="s">
         <v>77</v>
       </c>
       <c r="N22" s="2">
@@ -3557,13 +3000,13 @@
       <c r="R22" s="2">
         <v>15000</v>
       </c>
-      <c r="S22" s="34">
+      <c r="S22" s="33">
         <v>16008</v>
       </c>
       <c r="T22" s="5">
         <v>20</v>
       </c>
-      <c r="U22" s="35">
+      <c r="U22" s="34">
         <v>0</v>
       </c>
       <c r="V22" t="s">
@@ -3597,19 +3040,19 @@
       <c r="E23" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" s="30" t="s">
+      <c r="F23" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H23" s="28">
         <v>1</v>
       </c>
-      <c r="I23" s="31">
+      <c r="I23" s="30">
         <v>1990000</v>
       </c>
-      <c r="J23" s="32" t="s">
+      <c r="J23" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K23" s="2">
@@ -3618,7 +3061,7 @@
       <c r="L23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="33" t="s">
+      <c r="M23" s="32" t="s">
         <v>79</v>
       </c>
       <c r="N23" s="2">
@@ -3636,13 +3079,13 @@
       <c r="R23" s="2">
         <v>15000</v>
       </c>
-      <c r="S23" s="34">
+      <c r="S23" s="33">
         <v>16008</v>
       </c>
       <c r="T23" s="5">
         <v>30</v>
       </c>
-      <c r="U23" s="35">
+      <c r="U23" s="34">
         <v>1</v>
       </c>
       <c r="V23" t="s">
@@ -3664,31 +3107,31 @@
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="36">
+      <c r="B24" s="35">
         <v>200700</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="35">
         <v>200700001</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" s="30" t="s">
+      <c r="F24" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="35">
         <v>2</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="30">
         <v>1990000</v>
       </c>
-      <c r="J24" s="37" t="s">
+      <c r="J24" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K24" s="2">
@@ -3697,7 +3140,7 @@
       <c r="L24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="32" t="s">
         <v>79</v>
       </c>
       <c r="N24" s="2">
@@ -3715,13 +3158,13 @@
       <c r="R24" s="2">
         <v>15000</v>
       </c>
-      <c r="S24" s="34">
+      <c r="S24" s="33">
         <v>16008</v>
       </c>
       <c r="T24" s="5">
         <v>30</v>
       </c>
-      <c r="U24" s="35">
+      <c r="U24" s="34">
         <v>1</v>
       </c>
       <c r="V24" t="s">
@@ -3738,7 +3181,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:25">
+    <row r="25" spans="1:25" s="2" customFormat="1">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -3755,19 +3198,19 @@
       <c r="E25" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="30" t="s">
+      <c r="F25" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H25" s="28">
         <v>3</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="30">
         <v>1990000</v>
       </c>
-      <c r="J25" s="32" t="s">
+      <c r="J25" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K25" s="2">
@@ -3776,7 +3219,7 @@
       <c r="L25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M25" s="33" t="s">
+      <c r="M25" s="32" t="s">
         <v>79</v>
       </c>
       <c r="N25" s="2">
@@ -3794,13 +3237,13 @@
       <c r="R25" s="2">
         <v>15000</v>
       </c>
-      <c r="S25" s="34">
+      <c r="S25" s="33">
         <v>16008</v>
       </c>
       <c r="T25" s="5">
         <v>30</v>
       </c>
-      <c r="U25" s="35">
+      <c r="U25" s="34">
         <v>1</v>
       </c>
       <c r="V25" t="s">
@@ -3817,7 +3260,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:25">
+    <row r="26" spans="1:25" s="2" customFormat="1">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -3831,22 +3274,22 @@
       <c r="D26" s="28">
         <v>200800001</v>
       </c>
-      <c r="E26" s="39" t="s">
+      <c r="E26" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" s="30" t="s">
+      <c r="F26" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H26" s="28">
         <v>1</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="30">
         <v>1990000</v>
       </c>
-      <c r="J26" s="32" t="s">
+      <c r="J26" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K26" s="2">
@@ -3855,7 +3298,7 @@
       <c r="L26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="33" t="s">
+      <c r="M26" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N26" s="2">
@@ -3873,13 +3316,13 @@
       <c r="R26" s="2">
         <v>15000</v>
       </c>
-      <c r="S26" s="34">
+      <c r="S26" s="33">
         <v>16008</v>
       </c>
       <c r="T26" s="5">
         <v>20</v>
       </c>
-      <c r="U26" s="35">
+      <c r="U26" s="34">
         <v>0</v>
       </c>
       <c r="V26" t="s">
@@ -3896,7 +3339,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:25">
+    <row r="27" spans="1:25" s="2" customFormat="1">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -3910,22 +3353,22 @@
       <c r="D27" s="28">
         <v>200800001</v>
       </c>
-      <c r="E27" s="36" t="s">
+      <c r="E27" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" s="30" t="s">
+      <c r="F27" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="36">
+      <c r="H27" s="35">
         <v>2</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="30">
         <v>1990000</v>
       </c>
-      <c r="J27" s="37" t="s">
+      <c r="J27" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K27" s="2">
@@ -3934,7 +3377,7 @@
       <c r="L27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="33" t="s">
+      <c r="M27" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N27" s="2">
@@ -3952,13 +3395,13 @@
       <c r="R27" s="2">
         <v>15000</v>
       </c>
-      <c r="S27" s="34">
+      <c r="S27" s="33">
         <v>16008</v>
       </c>
       <c r="T27" s="5">
         <v>20</v>
       </c>
-      <c r="U27" s="35">
+      <c r="U27" s="34">
         <v>0</v>
       </c>
       <c r="V27" t="s">
@@ -3975,7 +3418,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:25">
+    <row r="28" spans="1:25" s="2" customFormat="1">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -3992,19 +3435,19 @@
       <c r="E28" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" s="30" t="s">
+      <c r="F28" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H28" s="28">
         <v>3</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="30">
         <v>1990000</v>
       </c>
-      <c r="J28" s="32" t="s">
+      <c r="J28" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K28" s="2">
@@ -4013,7 +3456,7 @@
       <c r="L28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M28" s="33" t="s">
+      <c r="M28" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N28" s="2">
@@ -4031,13 +3474,13 @@
       <c r="R28" s="2">
         <v>15000</v>
       </c>
-      <c r="S28" s="34">
+      <c r="S28" s="33">
         <v>16008</v>
       </c>
       <c r="T28" s="5">
         <v>20</v>
       </c>
-      <c r="U28" s="35">
+      <c r="U28" s="34">
         <v>0</v>
       </c>
       <c r="V28" t="s">
@@ -4054,12 +3497,12 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:25">
+    <row r="29" spans="1:25" s="2" customFormat="1">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="39">
         <v>200900</v>
       </c>
       <c r="C29" s="28" t="s">
@@ -4068,31 +3511,31 @@
       <c r="D29" s="28">
         <v>200900001</v>
       </c>
-      <c r="E29" s="38" t="s">
+      <c r="E29" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" s="30" t="s">
+      <c r="F29" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H29" s="28">
         <v>1</v>
       </c>
-      <c r="I29" s="31">
+      <c r="I29" s="30">
         <v>1990000</v>
       </c>
-      <c r="J29" s="32" t="s">
+      <c r="J29" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="41">
+      <c r="K29" s="40">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M29" s="33" t="s">
+      <c r="M29" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N29" s="2">
@@ -4110,13 +3553,13 @@
       <c r="R29" s="2">
         <v>15000</v>
       </c>
-      <c r="S29" s="34">
+      <c r="S29" s="33">
         <v>16008</v>
       </c>
       <c r="T29" s="5">
         <v>20</v>
       </c>
-      <c r="U29" s="35">
+      <c r="U29" s="34">
         <v>0</v>
       </c>
       <c r="V29" t="s">
@@ -4138,40 +3581,40 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="42">
+      <c r="B30" s="41">
         <v>200900</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="35">
         <v>200900001</v>
       </c>
-      <c r="E30" s="36" t="s">
+      <c r="E30" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" s="30" t="s">
+      <c r="F30" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="35">
         <v>2</v>
       </c>
-      <c r="I30" s="31">
+      <c r="I30" s="30">
         <v>1990000</v>
       </c>
-      <c r="J30" s="37" t="s">
+      <c r="J30" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="41">
+      <c r="K30" s="40">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M30" s="33" t="s">
+      <c r="M30" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N30" s="2">
@@ -4189,13 +3632,13 @@
       <c r="R30" s="2">
         <v>15000</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="33">
         <v>16008</v>
       </c>
       <c r="T30" s="5">
         <v>20</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="34">
         <v>0</v>
       </c>
       <c r="V30" t="s">
@@ -4217,7 +3660,7 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="40">
+      <c r="B31" s="39">
         <v>200900</v>
       </c>
       <c r="C31" s="28" t="s">
@@ -4229,28 +3672,28 @@
       <c r="E31" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G31" s="30" t="s">
+      <c r="F31" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H31" s="28">
         <v>3</v>
       </c>
-      <c r="I31" s="31">
+      <c r="I31" s="30">
         <v>1990000</v>
       </c>
-      <c r="J31" s="32" t="s">
+      <c r="J31" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="41">
+      <c r="K31" s="40">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M31" s="33" t="s">
+      <c r="M31" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N31" s="2">
@@ -4268,13 +3711,13 @@
       <c r="R31" s="2">
         <v>15000</v>
       </c>
-      <c r="S31" s="34">
+      <c r="S31" s="33">
         <v>16008</v>
       </c>
       <c r="T31" s="5">
         <v>20</v>
       </c>
-      <c r="U31" s="35">
+      <c r="U31" s="34">
         <v>0</v>
       </c>
       <c r="V31" t="s">
@@ -4291,45 +3734,45 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:25">
+    <row r="32" spans="1:25" s="2" customFormat="1">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>2012001</v>
       </c>
-      <c r="B32" s="43">
+      <c r="B32" s="42">
         <v>201200</v>
       </c>
       <c r="C32" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="36">
+      <c r="D32" s="35">
         <v>201200001</v>
       </c>
-      <c r="E32" s="38" t="s">
+      <c r="E32" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32" s="30" t="s">
+      <c r="F32" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H32" s="28">
         <v>1</v>
       </c>
-      <c r="I32" s="31">
+      <c r="I32" s="30">
         <v>1990000</v>
       </c>
-      <c r="J32" s="32" t="s">
+      <c r="J32" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="41">
+      <c r="K32" s="40">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M32" s="33" t="s">
+      <c r="M32" s="32" t="s">
         <v>84</v>
       </c>
       <c r="N32" s="2">
@@ -4347,13 +3790,13 @@
       <c r="R32" s="2">
         <v>15000</v>
       </c>
-      <c r="S32" s="34">
+      <c r="S32" s="33">
         <v>16008</v>
       </c>
       <c r="T32" s="5">
         <v>12</v>
       </c>
-      <c r="U32" s="35">
+      <c r="U32" s="34">
         <v>0</v>
       </c>
       <c r="V32" t="s">
@@ -4375,40 +3818,40 @@
         <f t="shared" si="0"/>
         <v>2012002</v>
       </c>
-      <c r="B33" s="43">
+      <c r="B33" s="42">
         <v>201200</v>
       </c>
       <c r="C33" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="35">
         <v>201200001</v>
       </c>
-      <c r="E33" s="36" t="s">
+      <c r="E33" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" s="30" t="s">
+      <c r="F33" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="35">
         <v>2</v>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="30">
         <v>1990000</v>
       </c>
-      <c r="J33" s="37" t="s">
+      <c r="J33" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="41">
+      <c r="K33" s="40">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="33" t="s">
+      <c r="M33" s="32" t="s">
         <v>84</v>
       </c>
       <c r="N33" s="2">
@@ -4426,13 +3869,13 @@
       <c r="R33" s="2">
         <v>15000</v>
       </c>
-      <c r="S33" s="34">
+      <c r="S33" s="33">
         <v>16008</v>
       </c>
       <c r="T33" s="5">
         <v>12</v>
       </c>
-      <c r="U33" s="35">
+      <c r="U33" s="34">
         <v>0</v>
       </c>
       <c r="V33" t="s">
@@ -4454,40 +3897,40 @@
         <f t="shared" si="0"/>
         <v>2012003</v>
       </c>
-      <c r="B34" s="43">
+      <c r="B34" s="42">
         <v>201200</v>
       </c>
       <c r="C34" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="35">
         <v>201200001</v>
       </c>
       <c r="E34" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G34" s="30" t="s">
+      <c r="F34" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H34" s="28">
         <v>3</v>
       </c>
-      <c r="I34" s="31">
+      <c r="I34" s="30">
         <v>1990000</v>
       </c>
-      <c r="J34" s="32" t="s">
+      <c r="J34" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="41">
+      <c r="K34" s="40">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M34" s="33" t="s">
+      <c r="M34" s="32" t="s">
         <v>84</v>
       </c>
       <c r="N34" s="2">
@@ -4505,13 +3948,13 @@
       <c r="R34" s="2">
         <v>15000</v>
       </c>
-      <c r="S34" s="34">
+      <c r="S34" s="33">
         <v>16008</v>
       </c>
       <c r="T34" s="5">
         <v>12</v>
       </c>
-      <c r="U34" s="35">
+      <c r="U34" s="34">
         <v>0</v>
       </c>
       <c r="V34" t="s">
@@ -4528,35 +3971,35 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="44">
+    <row r="35" spans="1:25" s="3" customFormat="1">
+      <c r="A35" s="43">
         <v>20010010</v>
       </c>
       <c r="B35" s="3">
         <v>200100</v>
       </c>
-      <c r="C35" s="45" t="s">
+      <c r="C35" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="45">
+      <c r="D35" s="44">
         <v>200100038</v>
       </c>
-      <c r="E35" s="45" t="s">
+      <c r="E35" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="G35" s="47" t="s">
+      <c r="F35" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="45">
-        <v>1</v>
-      </c>
-      <c r="I35" s="45">
+      <c r="H35" s="44">
+        <v>10</v>
+      </c>
+      <c r="I35" s="44">
         <v>1980000</v>
       </c>
-      <c r="J35" s="32" t="s">
+      <c r="J35" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K35" s="3">
@@ -4565,7 +4008,7 @@
       <c r="L35" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M35" s="48" t="s">
+      <c r="M35" s="46" t="s">
         <v>56</v>
       </c>
       <c r="N35" s="2">
@@ -4583,13 +4026,13 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="49">
-        <v>16008</v>
-      </c>
-      <c r="T35" s="44">
+      <c r="S35" s="47">
+        <v>16008</v>
+      </c>
+      <c r="T35" s="43">
         <v>48</v>
       </c>
-      <c r="U35" s="50">
+      <c r="U35" s="48">
         <v>0</v>
       </c>
       <c r="V35" t="s">
@@ -4601,37 +4044,37 @@
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="51"/>
-    </row>
-    <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="44">
+      <c r="Y35" s="49"/>
+    </row>
+    <row r="36" spans="1:25" s="3" customFormat="1">
+      <c r="A36" s="43">
         <v>20010011</v>
       </c>
       <c r="B36" s="3">
         <v>200100</v>
       </c>
-      <c r="C36" s="45" t="s">
+      <c r="C36" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="44">
         <v>200100038</v>
       </c>
-      <c r="E36" s="45" t="s">
+      <c r="E36" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="G36" s="47" t="s">
+      <c r="F36" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H36" s="45">
-        <v>2</v>
-      </c>
-      <c r="I36" s="45">
+      <c r="H36" s="44">
+        <v>11</v>
+      </c>
+      <c r="I36" s="44">
         <v>1980000</v>
       </c>
-      <c r="J36" s="37" t="s">
+      <c r="J36" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K36" s="3">
@@ -4640,7 +4083,7 @@
       <c r="L36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M36" s="48" t="s">
+      <c r="M36" s="46" t="s">
         <v>56</v>
       </c>
       <c r="N36" s="2">
@@ -4658,13 +4101,13 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="49">
-        <v>16008</v>
-      </c>
-      <c r="T36" s="44">
+      <c r="S36" s="47">
+        <v>16008</v>
+      </c>
+      <c r="T36" s="43">
         <v>48</v>
       </c>
-      <c r="U36" s="50">
+      <c r="U36" s="48">
         <v>0</v>
       </c>
       <c r="V36" t="s">
@@ -4676,37 +4119,37 @@
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="51"/>
-    </row>
-    <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="44">
+      <c r="Y36" s="49"/>
+    </row>
+    <row r="37" spans="1:25" s="3" customFormat="1">
+      <c r="A37" s="43">
         <v>20010012</v>
       </c>
       <c r="B37" s="3">
         <v>200100</v>
       </c>
-      <c r="C37" s="45" t="s">
+      <c r="C37" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="45">
+      <c r="D37" s="44">
         <v>200100038</v>
       </c>
-      <c r="E37" s="45" t="s">
+      <c r="E37" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="G37" s="47" t="s">
+      <c r="F37" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H37" s="45">
-        <v>3</v>
-      </c>
-      <c r="I37" s="45">
+      <c r="H37" s="44">
+        <v>12</v>
+      </c>
+      <c r="I37" s="44">
         <v>1980000</v>
       </c>
-      <c r="J37" s="32" t="s">
+      <c r="J37" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K37" s="3">
@@ -4715,7 +4158,7 @@
       <c r="L37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M37" s="48" t="s">
+      <c r="M37" s="46" t="s">
         <v>56</v>
       </c>
       <c r="N37" s="2">
@@ -4733,13 +4176,13 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="49">
-        <v>16008</v>
-      </c>
-      <c r="T37" s="44">
+      <c r="S37" s="47">
+        <v>16008</v>
+      </c>
+      <c r="T37" s="43">
         <v>48</v>
       </c>
-      <c r="U37" s="50">
+      <c r="U37" s="48">
         <v>0</v>
       </c>
       <c r="V37" t="s">
@@ -4751,10 +4194,10 @@
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="51"/>
-    </row>
-    <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="44">
+      <c r="Y37" s="49"/>
+    </row>
+    <row r="38" spans="1:25" s="3" customFormat="1">
+      <c r="A38" s="43">
         <v>20010110</v>
       </c>
       <c r="B38" s="3">
@@ -4769,19 +4212,19 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G38" s="47" t="s">
+      <c r="F38" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H38" s="3">
-        <v>1</v>
-      </c>
-      <c r="I38" s="45">
+      <c r="H38" s="44">
+        <v>10</v>
+      </c>
+      <c r="I38" s="44">
         <v>1980000</v>
       </c>
-      <c r="J38" s="32" t="s">
+      <c r="J38" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K38" s="3">
@@ -4790,7 +4233,7 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="48" t="s">
+      <c r="M38" s="46" t="s">
         <v>69</v>
       </c>
       <c r="N38" s="2">
@@ -4811,10 +4254,10 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="44">
+      <c r="T38" s="43">
         <v>48</v>
       </c>
-      <c r="U38" s="50">
+      <c r="U38" s="48">
         <v>0</v>
       </c>
       <c r="V38" t="s">
@@ -4826,10 +4269,10 @@
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="51"/>
-    </row>
-    <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="44">
+      <c r="Y38" s="49"/>
+    </row>
+    <row r="39" spans="1:25" s="3" customFormat="1">
+      <c r="A39" s="43">
         <v>20010111</v>
       </c>
       <c r="B39" s="3">
@@ -4844,19 +4287,19 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G39" s="47" t="s">
+      <c r="F39" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H39" s="3">
-        <v>2</v>
-      </c>
-      <c r="I39" s="45">
+      <c r="H39" s="44">
+        <v>11</v>
+      </c>
+      <c r="I39" s="44">
         <v>1980000</v>
       </c>
-      <c r="J39" s="37" t="s">
+      <c r="J39" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K39" s="3">
@@ -4865,7 +4308,7 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="48" t="s">
+      <c r="M39" s="46" t="s">
         <v>69</v>
       </c>
       <c r="N39" s="2">
@@ -4886,10 +4329,10 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="44">
+      <c r="T39" s="43">
         <v>48</v>
       </c>
-      <c r="U39" s="50">
+      <c r="U39" s="48">
         <v>0</v>
       </c>
       <c r="V39" t="s">
@@ -4901,10 +4344,10 @@
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="51"/>
-    </row>
-    <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="44">
+      <c r="Y39" s="49"/>
+    </row>
+    <row r="40" spans="1:25" s="3" customFormat="1">
+      <c r="A40" s="43">
         <v>20010112</v>
       </c>
       <c r="B40" s="3">
@@ -4919,19 +4362,19 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G40" s="47" t="s">
+      <c r="F40" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H40" s="3">
-        <v>3</v>
-      </c>
-      <c r="I40" s="45">
+      <c r="H40" s="44">
+        <v>12</v>
+      </c>
+      <c r="I40" s="44">
         <v>1980000</v>
       </c>
-      <c r="J40" s="32" t="s">
+      <c r="J40" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K40" s="3">
@@ -4940,7 +4383,7 @@
       <c r="L40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="48" t="s">
+      <c r="M40" s="46" t="s">
         <v>69</v>
       </c>
       <c r="N40" s="2">
@@ -4961,10 +4404,10 @@
       <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="44">
+      <c r="T40" s="43">
         <v>48</v>
       </c>
-      <c r="U40" s="50">
+      <c r="U40" s="48">
         <v>0</v>
       </c>
       <c r="V40" t="s">
@@ -4976,10 +4419,10 @@
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="51"/>
-    </row>
-    <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="44">
+      <c r="Y40" s="49"/>
+    </row>
+    <row r="41" spans="1:25" s="3" customFormat="1">
+      <c r="A41" s="43">
         <v>20030010</v>
       </c>
       <c r="B41" s="3">
@@ -4994,19 +4437,19 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G41" s="47" t="s">
+      <c r="F41" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H41" s="3">
-        <v>1</v>
-      </c>
-      <c r="I41" s="45">
+      <c r="H41" s="44">
+        <v>10</v>
+      </c>
+      <c r="I41" s="44">
         <v>1980000</v>
       </c>
-      <c r="J41" s="32" t="s">
+      <c r="J41" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K41" s="3">
@@ -5015,7 +4458,7 @@
       <c r="L41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="48" t="s">
+      <c r="M41" s="46" t="s">
         <v>71</v>
       </c>
       <c r="N41" s="2">
@@ -5036,10 +4479,10 @@
       <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="44">
+      <c r="T41" s="43">
         <v>50</v>
       </c>
-      <c r="U41" s="50">
+      <c r="U41" s="48">
         <v>0</v>
       </c>
       <c r="V41" t="s">
@@ -5051,10 +4494,10 @@
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="51"/>
-    </row>
-    <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="44">
+      <c r="Y41" s="49"/>
+    </row>
+    <row r="42" spans="1:25" s="3" customFormat="1">
+      <c r="A42" s="43">
         <v>20030011</v>
       </c>
       <c r="B42" s="3">
@@ -5069,19 +4512,19 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G42" s="47" t="s">
+      <c r="F42" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H42" s="3">
-        <v>2</v>
-      </c>
-      <c r="I42" s="45">
+      <c r="H42" s="44">
+        <v>11</v>
+      </c>
+      <c r="I42" s="44">
         <v>1980000</v>
       </c>
-      <c r="J42" s="37" t="s">
+      <c r="J42" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K42" s="3">
@@ -5090,7 +4533,7 @@
       <c r="L42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="48" t="s">
+      <c r="M42" s="46" t="s">
         <v>71</v>
       </c>
       <c r="N42" s="2">
@@ -5111,10 +4554,10 @@
       <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="44">
+      <c r="T42" s="43">
         <v>50</v>
       </c>
-      <c r="U42" s="50">
+      <c r="U42" s="48">
         <v>0</v>
       </c>
       <c r="V42" t="s">
@@ -5126,10 +4569,10 @@
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="51"/>
-    </row>
-    <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="44">
+      <c r="Y42" s="49"/>
+    </row>
+    <row r="43" spans="1:25" s="3" customFormat="1">
+      <c r="A43" s="43">
         <v>20030012</v>
       </c>
       <c r="B43" s="3">
@@ -5144,19 +4587,19 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G43" s="47" t="s">
+      <c r="F43" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H43" s="3">
-        <v>3</v>
-      </c>
-      <c r="I43" s="45">
+      <c r="H43" s="44">
+        <v>12</v>
+      </c>
+      <c r="I43" s="44">
         <v>1980000</v>
       </c>
-      <c r="J43" s="32" t="s">
+      <c r="J43" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K43" s="3">
@@ -5165,7 +4608,7 @@
       <c r="L43" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="48" t="s">
+      <c r="M43" s="46" t="s">
         <v>71</v>
       </c>
       <c r="N43" s="2">
@@ -5186,10 +4629,10 @@
       <c r="S43" s="3">
         <v>16008</v>
       </c>
-      <c r="T43" s="44">
+      <c r="T43" s="43">
         <v>50</v>
       </c>
-      <c r="U43" s="50">
+      <c r="U43" s="48">
         <v>0</v>
       </c>
       <c r="V43" t="s">
@@ -5201,10 +4644,10 @@
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="51"/>
-    </row>
-    <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="44">
+      <c r="Y43" s="49"/>
+    </row>
+    <row r="44" spans="1:25" s="3" customFormat="1">
+      <c r="A44" s="43">
         <v>20040010</v>
       </c>
       <c r="B44" s="3">
@@ -5219,19 +4662,19 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G44" s="47" t="s">
+      <c r="F44" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G44" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H44" s="3">
-        <v>1</v>
-      </c>
-      <c r="I44" s="45">
+      <c r="H44" s="44">
+        <v>10</v>
+      </c>
+      <c r="I44" s="44">
         <v>1980000</v>
       </c>
-      <c r="J44" s="32" t="s">
+      <c r="J44" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K44" s="3">
@@ -5240,7 +4683,7 @@
       <c r="L44" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M44" s="48" t="s">
+      <c r="M44" s="46" t="s">
         <v>73</v>
       </c>
       <c r="N44" s="2">
@@ -5261,10 +4704,10 @@
       <c r="S44" s="3">
         <v>16008</v>
       </c>
-      <c r="T44" s="44">
+      <c r="T44" s="43">
         <v>50</v>
       </c>
-      <c r="U44" s="50">
+      <c r="U44" s="48">
         <v>0</v>
       </c>
       <c r="V44" t="s">
@@ -5276,10 +4719,10 @@
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="51"/>
-    </row>
-    <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="44">
+      <c r="Y44" s="49"/>
+    </row>
+    <row r="45" spans="1:25" s="3" customFormat="1">
+      <c r="A45" s="43">
         <v>20040011</v>
       </c>
       <c r="B45" s="3">
@@ -5294,19 +4737,19 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G45" s="47" t="s">
+      <c r="F45" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H45" s="3">
-        <v>2</v>
-      </c>
-      <c r="I45" s="45">
+      <c r="H45" s="44">
+        <v>11</v>
+      </c>
+      <c r="I45" s="44">
         <v>1980000</v>
       </c>
-      <c r="J45" s="37" t="s">
+      <c r="J45" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K45" s="3">
@@ -5315,7 +4758,7 @@
       <c r="L45" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M45" s="48" t="s">
+      <c r="M45" s="46" t="s">
         <v>73</v>
       </c>
       <c r="N45" s="2">
@@ -5336,10 +4779,10 @@
       <c r="S45" s="3">
         <v>16008</v>
       </c>
-      <c r="T45" s="44">
+      <c r="T45" s="43">
         <v>50</v>
       </c>
-      <c r="U45" s="50">
+      <c r="U45" s="48">
         <v>0</v>
       </c>
       <c r="V45" t="s">
@@ -5351,10 +4794,10 @@
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="51"/>
-    </row>
-    <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="44">
+      <c r="Y45" s="49"/>
+    </row>
+    <row r="46" spans="1:25" s="3" customFormat="1">
+      <c r="A46" s="43">
         <v>20040012</v>
       </c>
       <c r="B46" s="3">
@@ -5369,19 +4812,19 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G46" s="47" t="s">
+      <c r="F46" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H46" s="3">
-        <v>3</v>
-      </c>
-      <c r="I46" s="45">
+      <c r="H46" s="44">
+        <v>12</v>
+      </c>
+      <c r="I46" s="44">
         <v>1980000</v>
       </c>
-      <c r="J46" s="32" t="s">
+      <c r="J46" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K46" s="3">
@@ -5390,7 +4833,7 @@
       <c r="L46" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M46" s="48" t="s">
+      <c r="M46" s="46" t="s">
         <v>73</v>
       </c>
       <c r="N46" s="2">
@@ -5411,10 +4854,10 @@
       <c r="S46" s="3">
         <v>16008</v>
       </c>
-      <c r="T46" s="44">
+      <c r="T46" s="43">
         <v>50</v>
       </c>
-      <c r="U46" s="50">
+      <c r="U46" s="48">
         <v>0</v>
       </c>
       <c r="V46" t="s">
@@ -5426,10 +4869,10 @@
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="51"/>
-    </row>
-    <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="44">
+      <c r="Y46" s="49"/>
+    </row>
+    <row r="47" spans="1:25" s="3" customFormat="1">
+      <c r="A47" s="43">
         <v>20050010</v>
       </c>
       <c r="B47" s="3">
@@ -5444,19 +4887,19 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G47" s="47" t="s">
+      <c r="F47" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G47" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H47" s="3">
-        <v>1</v>
-      </c>
-      <c r="I47" s="45">
+      <c r="H47" s="44">
+        <v>10</v>
+      </c>
+      <c r="I47" s="44">
         <v>1980000</v>
       </c>
-      <c r="J47" s="32" t="s">
+      <c r="J47" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K47" s="3">
@@ -5465,7 +4908,7 @@
       <c r="L47" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M47" s="48" t="s">
+      <c r="M47" s="46" t="s">
         <v>75</v>
       </c>
       <c r="N47" s="2">
@@ -5486,10 +4929,10 @@
       <c r="S47" s="3">
         <v>16008</v>
       </c>
-      <c r="T47" s="44">
+      <c r="T47" s="43">
         <v>48</v>
       </c>
-      <c r="U47" s="44">
+      <c r="U47" s="43">
         <v>0</v>
       </c>
       <c r="V47" t="s">
@@ -5501,10 +4944,10 @@
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="51"/>
-    </row>
-    <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="44">
+      <c r="Y47" s="49"/>
+    </row>
+    <row r="48" spans="1:25" s="3" customFormat="1">
+      <c r="A48" s="43">
         <v>20050011</v>
       </c>
       <c r="B48" s="3">
@@ -5519,19 +4962,19 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G48" s="47" t="s">
+      <c r="F48" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H48" s="3">
-        <v>2</v>
-      </c>
-      <c r="I48" s="45">
+      <c r="H48" s="44">
+        <v>11</v>
+      </c>
+      <c r="I48" s="44">
         <v>1980000</v>
       </c>
-      <c r="J48" s="37" t="s">
+      <c r="J48" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K48" s="3">
@@ -5540,7 +4983,7 @@
       <c r="L48" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M48" s="48" t="s">
+      <c r="M48" s="46" t="s">
         <v>75</v>
       </c>
       <c r="N48" s="2">
@@ -5561,10 +5004,10 @@
       <c r="S48" s="3">
         <v>16008</v>
       </c>
-      <c r="T48" s="44">
+      <c r="T48" s="43">
         <v>48</v>
       </c>
-      <c r="U48" s="44">
+      <c r="U48" s="43">
         <v>0</v>
       </c>
       <c r="V48" t="s">
@@ -5576,10 +5019,10 @@
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="51"/>
-    </row>
-    <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="44">
+      <c r="Y48" s="49"/>
+    </row>
+    <row r="49" spans="1:25" s="3" customFormat="1">
+      <c r="A49" s="43">
         <v>20050012</v>
       </c>
       <c r="B49" s="3">
@@ -5594,19 +5037,19 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G49" s="47" t="s">
+      <c r="F49" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H49" s="3">
-        <v>3</v>
-      </c>
-      <c r="I49" s="45">
+      <c r="H49" s="44">
+        <v>12</v>
+      </c>
+      <c r="I49" s="44">
         <v>1980000</v>
       </c>
-      <c r="J49" s="32" t="s">
+      <c r="J49" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K49" s="3">
@@ -5615,7 +5058,7 @@
       <c r="L49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M49" s="48" t="s">
+      <c r="M49" s="46" t="s">
         <v>75</v>
       </c>
       <c r="N49" s="2">
@@ -5636,10 +5079,10 @@
       <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="44">
+      <c r="T49" s="43">
         <v>48</v>
       </c>
-      <c r="U49" s="44">
+      <c r="U49" s="43">
         <v>0</v>
       </c>
       <c r="V49" t="s">
@@ -5651,10 +5094,10 @@
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="51"/>
-    </row>
-    <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="44">
+      <c r="Y49" s="49"/>
+    </row>
+    <row r="50" spans="1:25" s="3" customFormat="1">
+      <c r="A50" s="43">
         <v>20060010</v>
       </c>
       <c r="B50" s="3">
@@ -5669,19 +5112,19 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G50" s="47" t="s">
+      <c r="F50" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G50" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H50" s="3">
-        <v>1</v>
-      </c>
-      <c r="I50" s="45">
+      <c r="H50" s="44">
+        <v>10</v>
+      </c>
+      <c r="I50" s="44">
         <v>1980000</v>
       </c>
-      <c r="J50" s="32" t="s">
+      <c r="J50" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K50" s="3">
@@ -5690,7 +5133,7 @@
       <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="48" t="s">
+      <c r="M50" s="46" t="s">
         <v>77</v>
       </c>
       <c r="N50" s="2">
@@ -5711,10 +5154,10 @@
       <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="44">
+      <c r="T50" s="43">
         <v>20</v>
       </c>
-      <c r="U50" s="44">
+      <c r="U50" s="43">
         <v>0</v>
       </c>
       <c r="V50" t="s">
@@ -5726,10 +5169,10 @@
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="51"/>
-    </row>
-    <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="44">
+      <c r="Y50" s="49"/>
+    </row>
+    <row r="51" spans="1:25" s="3" customFormat="1">
+      <c r="A51" s="43">
         <v>20060011</v>
       </c>
       <c r="B51" s="3">
@@ -5744,19 +5187,19 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G51" s="47" t="s">
+      <c r="F51" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H51" s="3">
-        <v>2</v>
-      </c>
-      <c r="I51" s="45">
+      <c r="H51" s="44">
+        <v>11</v>
+      </c>
+      <c r="I51" s="44">
         <v>1980000</v>
       </c>
-      <c r="J51" s="37" t="s">
+      <c r="J51" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K51" s="3">
@@ -5765,7 +5208,7 @@
       <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="48" t="s">
+      <c r="M51" s="46" t="s">
         <v>77</v>
       </c>
       <c r="N51" s="2">
@@ -5786,10 +5229,10 @@
       <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="44">
+      <c r="T51" s="43">
         <v>20</v>
       </c>
-      <c r="U51" s="44">
+      <c r="U51" s="43">
         <v>0</v>
       </c>
       <c r="V51" t="s">
@@ -5801,10 +5244,10 @@
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="51"/>
-    </row>
-    <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="44">
+      <c r="Y51" s="49"/>
+    </row>
+    <row r="52" spans="1:25" s="3" customFormat="1">
+      <c r="A52" s="43">
         <v>20060012</v>
       </c>
       <c r="B52" s="3">
@@ -5819,19 +5262,19 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G52" s="47" t="s">
+      <c r="F52" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H52" s="3">
-        <v>3</v>
-      </c>
-      <c r="I52" s="45">
+      <c r="H52" s="44">
+        <v>12</v>
+      </c>
+      <c r="I52" s="44">
         <v>1980000</v>
       </c>
-      <c r="J52" s="32" t="s">
+      <c r="J52" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K52" s="3">
@@ -5840,7 +5283,7 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="48" t="s">
+      <c r="M52" s="46" t="s">
         <v>77</v>
       </c>
       <c r="N52" s="2">
@@ -5861,10 +5304,10 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="44">
+      <c r="T52" s="43">
         <v>20</v>
       </c>
-      <c r="U52" s="44">
+      <c r="U52" s="43">
         <v>0</v>
       </c>
       <c r="V52" t="s">
@@ -5876,10 +5319,10 @@
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="51"/>
-    </row>
-    <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="44">
+      <c r="Y52" s="49"/>
+    </row>
+    <row r="53" spans="1:25" s="3" customFormat="1">
+      <c r="A53" s="43">
         <v>20070010</v>
       </c>
       <c r="B53" s="3">
@@ -5894,19 +5337,19 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G53" s="47" t="s">
+      <c r="F53" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H53" s="3">
-        <v>1</v>
-      </c>
-      <c r="I53" s="45">
+      <c r="H53" s="44">
+        <v>10</v>
+      </c>
+      <c r="I53" s="44">
         <v>1980000</v>
       </c>
-      <c r="J53" s="32" t="s">
+      <c r="J53" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K53" s="3">
@@ -5915,7 +5358,7 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="48" t="s">
+      <c r="M53" s="46" t="s">
         <v>79</v>
       </c>
       <c r="N53" s="2">
@@ -5936,10 +5379,10 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="44">
+      <c r="T53" s="43">
         <v>30</v>
       </c>
-      <c r="U53" s="44">
+      <c r="U53" s="43">
         <v>1</v>
       </c>
       <c r="V53" t="s">
@@ -5951,10 +5394,10 @@
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="51"/>
-    </row>
-    <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="44">
+      <c r="Y53" s="49"/>
+    </row>
+    <row r="54" spans="1:25" s="3" customFormat="1">
+      <c r="A54" s="43">
         <v>20070011</v>
       </c>
       <c r="B54" s="3">
@@ -5969,19 +5412,19 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G54" s="47" t="s">
+      <c r="F54" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G54" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H54" s="3">
-        <v>2</v>
-      </c>
-      <c r="I54" s="45">
+      <c r="H54" s="44">
+        <v>11</v>
+      </c>
+      <c r="I54" s="44">
         <v>1980000</v>
       </c>
-      <c r="J54" s="37" t="s">
+      <c r="J54" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K54" s="3">
@@ -5990,7 +5433,7 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="48" t="s">
+      <c r="M54" s="46" t="s">
         <v>79</v>
       </c>
       <c r="N54" s="2">
@@ -6011,10 +5454,10 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="44">
+      <c r="T54" s="43">
         <v>30</v>
       </c>
-      <c r="U54" s="44">
+      <c r="U54" s="43">
         <v>1</v>
       </c>
       <c r="V54" t="s">
@@ -6026,10 +5469,10 @@
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="51"/>
-    </row>
-    <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="44">
+      <c r="Y54" s="49"/>
+    </row>
+    <row r="55" spans="1:25" s="3" customFormat="1">
+      <c r="A55" s="43">
         <v>20070012</v>
       </c>
       <c r="B55" s="3">
@@ -6044,19 +5487,19 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G55" s="47" t="s">
+      <c r="F55" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H55" s="3">
-        <v>3</v>
-      </c>
-      <c r="I55" s="45">
+      <c r="H55" s="44">
+        <v>12</v>
+      </c>
+      <c r="I55" s="44">
         <v>1980000</v>
       </c>
-      <c r="J55" s="32" t="s">
+      <c r="J55" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K55" s="3">
@@ -6065,7 +5508,7 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="48" t="s">
+      <c r="M55" s="46" t="s">
         <v>79</v>
       </c>
       <c r="N55" s="2">
@@ -6086,10 +5529,10 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="44">
+      <c r="T55" s="43">
         <v>30</v>
       </c>
-      <c r="U55" s="44">
+      <c r="U55" s="43">
         <v>1</v>
       </c>
       <c r="V55" t="s">
@@ -6101,10 +5544,10 @@
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="51"/>
-    </row>
-    <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="44">
+      <c r="Y55" s="49"/>
+    </row>
+    <row r="56" spans="1:25" s="3" customFormat="1">
+      <c r="A56" s="43">
         <v>20080010</v>
       </c>
       <c r="B56" s="3">
@@ -6119,19 +5562,19 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G56" s="47" t="s">
+      <c r="F56" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G56" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H56" s="3">
-        <v>1</v>
-      </c>
-      <c r="I56" s="45">
+      <c r="H56" s="44">
+        <v>10</v>
+      </c>
+      <c r="I56" s="44">
         <v>1980000</v>
       </c>
-      <c r="J56" s="32" t="s">
+      <c r="J56" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K56" s="3">
@@ -6140,7 +5583,7 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="48" t="s">
+      <c r="M56" s="46" t="s">
         <v>81</v>
       </c>
       <c r="N56" s="2">
@@ -6161,10 +5604,10 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="44">
+      <c r="T56" s="43">
         <v>20</v>
       </c>
-      <c r="U56" s="44">
+      <c r="U56" s="43">
         <v>0</v>
       </c>
       <c r="V56" t="s">
@@ -6176,10 +5619,10 @@
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="51"/>
-    </row>
-    <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="44">
+      <c r="Y56" s="49"/>
+    </row>
+    <row r="57" spans="1:25" s="3" customFormat="1">
+      <c r="A57" s="43">
         <v>20080011</v>
       </c>
       <c r="B57" s="3">
@@ -6194,19 +5637,19 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G57" s="47" t="s">
+      <c r="F57" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H57" s="3">
-        <v>2</v>
-      </c>
-      <c r="I57" s="45">
+      <c r="H57" s="44">
+        <v>11</v>
+      </c>
+      <c r="I57" s="44">
         <v>1980000</v>
       </c>
-      <c r="J57" s="37" t="s">
+      <c r="J57" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K57" s="3">
@@ -6215,7 +5658,7 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="48" t="s">
+      <c r="M57" s="46" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="2">
@@ -6236,10 +5679,10 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="44">
+      <c r="T57" s="43">
         <v>20</v>
       </c>
-      <c r="U57" s="44">
+      <c r="U57" s="43">
         <v>0</v>
       </c>
       <c r="V57" t="s">
@@ -6251,10 +5694,10 @@
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="51"/>
-    </row>
-    <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="44">
+      <c r="Y57" s="49"/>
+    </row>
+    <row r="58" spans="1:25" s="3" customFormat="1">
+      <c r="A58" s="43">
         <v>20080012</v>
       </c>
       <c r="B58" s="3">
@@ -6269,19 +5712,19 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G58" s="47" t="s">
+      <c r="F58" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G58" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H58" s="3">
-        <v>3</v>
-      </c>
-      <c r="I58" s="45">
+      <c r="H58" s="44">
+        <v>12</v>
+      </c>
+      <c r="I58" s="44">
         <v>1980000</v>
       </c>
-      <c r="J58" s="32" t="s">
+      <c r="J58" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K58" s="3">
@@ -6290,7 +5733,7 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="48" t="s">
+      <c r="M58" s="46" t="s">
         <v>81</v>
       </c>
       <c r="N58" s="2">
@@ -6311,10 +5754,10 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="44">
+      <c r="T58" s="43">
         <v>20</v>
       </c>
-      <c r="U58" s="44">
+      <c r="U58" s="43">
         <v>0</v>
       </c>
       <c r="V58" t="s">
@@ -6326,10 +5769,10 @@
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="51"/>
-    </row>
-    <row r="59" s="3" customFormat="1" spans="1:25">
-      <c r="A59" s="44">
+      <c r="Y58" s="49"/>
+    </row>
+    <row r="59" spans="1:25" s="3" customFormat="1">
+      <c r="A59" s="43">
         <v>20090010</v>
       </c>
       <c r="B59" s="3">
@@ -6344,19 +5787,19 @@
       <c r="E59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G59" s="47" t="s">
+      <c r="F59" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H59" s="3">
-        <v>1</v>
-      </c>
-      <c r="I59" s="45">
+      <c r="H59" s="44">
+        <v>10</v>
+      </c>
+      <c r="I59" s="44">
         <v>1980000</v>
       </c>
-      <c r="J59" s="32" t="s">
+      <c r="J59" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K59" s="3">
@@ -6365,7 +5808,7 @@
       <c r="L59" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M59" s="48" t="s">
+      <c r="M59" s="46" t="s">
         <v>81</v>
       </c>
       <c r="N59" s="2">
@@ -6386,10 +5829,10 @@
       <c r="S59" s="3">
         <v>16008</v>
       </c>
-      <c r="T59" s="44">
+      <c r="T59" s="43">
         <v>20</v>
       </c>
-      <c r="U59" s="44">
+      <c r="U59" s="43">
         <v>0</v>
       </c>
       <c r="V59" t="s">
@@ -6401,10 +5844,10 @@
       <c r="X59" s="3">
         <v>1</v>
       </c>
-      <c r="Y59" s="51"/>
-    </row>
-    <row r="60" s="3" customFormat="1" spans="1:25">
-      <c r="A60" s="44">
+      <c r="Y59" s="49"/>
+    </row>
+    <row r="60" spans="1:25" s="3" customFormat="1">
+      <c r="A60" s="43">
         <v>20090011</v>
       </c>
       <c r="B60" s="3">
@@ -6419,19 +5862,19 @@
       <c r="E60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F60" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G60" s="47" t="s">
+      <c r="F60" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H60" s="3">
-        <v>2</v>
-      </c>
-      <c r="I60" s="45">
+      <c r="H60" s="44">
+        <v>11</v>
+      </c>
+      <c r="I60" s="44">
         <v>1980000</v>
       </c>
-      <c r="J60" s="37" t="s">
+      <c r="J60" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K60" s="3">
@@ -6440,7 +5883,7 @@
       <c r="L60" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M60" s="48" t="s">
+      <c r="M60" s="46" t="s">
         <v>81</v>
       </c>
       <c r="N60" s="2">
@@ -6461,10 +5904,10 @@
       <c r="S60" s="3">
         <v>16008</v>
       </c>
-      <c r="T60" s="44">
+      <c r="T60" s="43">
         <v>20</v>
       </c>
-      <c r="U60" s="44">
+      <c r="U60" s="43">
         <v>0</v>
       </c>
       <c r="V60" t="s">
@@ -6476,10 +5919,10 @@
       <c r="X60" s="3">
         <v>1</v>
       </c>
-      <c r="Y60" s="51"/>
-    </row>
-    <row r="61" s="3" customFormat="1" spans="1:25">
-      <c r="A61" s="44">
+      <c r="Y60" s="49"/>
+    </row>
+    <row r="61" spans="1:25" s="3" customFormat="1">
+      <c r="A61" s="43">
         <v>20090012</v>
       </c>
       <c r="B61" s="3">
@@ -6494,19 +5937,19 @@
       <c r="E61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G61" s="47" t="s">
+      <c r="F61" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G61" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H61" s="3">
-        <v>3</v>
-      </c>
-      <c r="I61" s="45">
+      <c r="H61" s="44">
+        <v>12</v>
+      </c>
+      <c r="I61" s="44">
         <v>1980000</v>
       </c>
-      <c r="J61" s="32" t="s">
+      <c r="J61" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K61" s="3">
@@ -6515,7 +5958,7 @@
       <c r="L61" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M61" s="48" t="s">
+      <c r="M61" s="46" t="s">
         <v>81</v>
       </c>
       <c r="N61" s="2">
@@ -6536,10 +5979,10 @@
       <c r="S61" s="3">
         <v>16008</v>
       </c>
-      <c r="T61" s="44">
+      <c r="T61" s="43">
         <v>20</v>
       </c>
-      <c r="U61" s="44">
+      <c r="U61" s="43">
         <v>0</v>
       </c>
       <c r="V61" t="s">
@@ -6551,13 +5994,13 @@
       <c r="X61" s="3">
         <v>1</v>
       </c>
-      <c r="Y61" s="51"/>
-    </row>
-    <row r="62" s="3" customFormat="1" spans="1:25">
-      <c r="A62" s="44">
+      <c r="Y61" s="49"/>
+    </row>
+    <row r="62" spans="1:25" s="3" customFormat="1">
+      <c r="A62" s="43">
         <v>20120010</v>
       </c>
-      <c r="B62" s="43">
+      <c r="B62" s="42">
         <v>201200</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -6569,19 +6012,19 @@
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G62" s="47" t="s">
+      <c r="F62" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G62" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H62" s="3">
-        <v>1</v>
-      </c>
-      <c r="I62" s="45">
+      <c r="H62" s="44">
+        <v>10</v>
+      </c>
+      <c r="I62" s="44">
         <v>1980000</v>
       </c>
-      <c r="J62" s="32" t="s">
+      <c r="J62" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K62" s="3">
@@ -6590,7 +6033,7 @@
       <c r="L62" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M62" s="48" t="s">
+      <c r="M62" s="46" t="s">
         <v>84</v>
       </c>
       <c r="N62" s="2">
@@ -6611,10 +6054,10 @@
       <c r="S62" s="3">
         <v>16008</v>
       </c>
-      <c r="T62" s="44">
+      <c r="T62" s="43">
         <v>12</v>
       </c>
-      <c r="U62" s="44">
+      <c r="U62" s="43">
         <v>0</v>
       </c>
       <c r="V62" t="s">
@@ -6626,13 +6069,13 @@
       <c r="X62" s="3">
         <v>1</v>
       </c>
-      <c r="Y62" s="51"/>
-    </row>
-    <row r="63" s="3" customFormat="1" spans="1:25">
-      <c r="A63" s="44">
+      <c r="Y62" s="49"/>
+    </row>
+    <row r="63" spans="1:25" s="3" customFormat="1">
+      <c r="A63" s="43">
         <v>20120011</v>
       </c>
-      <c r="B63" s="43">
+      <c r="B63" s="42">
         <v>201200</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -6644,19 +6087,19 @@
       <c r="E63" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G63" s="47" t="s">
+      <c r="F63" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G63" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H63" s="3">
-        <v>2</v>
-      </c>
-      <c r="I63" s="45">
+      <c r="H63" s="44">
+        <v>11</v>
+      </c>
+      <c r="I63" s="44">
         <v>1980000</v>
       </c>
-      <c r="J63" s="37" t="s">
+      <c r="J63" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K63" s="3">
@@ -6665,7 +6108,7 @@
       <c r="L63" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M63" s="48" t="s">
+      <c r="M63" s="46" t="s">
         <v>84</v>
       </c>
       <c r="N63" s="2">
@@ -6686,10 +6129,10 @@
       <c r="S63" s="3">
         <v>16008</v>
       </c>
-      <c r="T63" s="44">
+      <c r="T63" s="43">
         <v>12</v>
       </c>
-      <c r="U63" s="44">
+      <c r="U63" s="43">
         <v>0</v>
       </c>
       <c r="V63" t="s">
@@ -6701,13 +6144,13 @@
       <c r="X63" s="3">
         <v>1</v>
       </c>
-      <c r="Y63" s="51"/>
-    </row>
-    <row r="64" s="3" customFormat="1" spans="1:25">
-      <c r="A64" s="44">
+      <c r="Y63" s="49"/>
+    </row>
+    <row r="64" spans="1:25" s="3" customFormat="1">
+      <c r="A64" s="43">
         <v>20120012</v>
       </c>
-      <c r="B64" s="43">
+      <c r="B64" s="42">
         <v>201200</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -6719,19 +6162,19 @@
       <c r="E64" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F64" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G64" s="47" t="s">
+      <c r="F64" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G64" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="H64" s="3">
-        <v>3</v>
-      </c>
-      <c r="I64" s="45">
+      <c r="H64" s="44">
+        <v>12</v>
+      </c>
+      <c r="I64" s="44">
         <v>1980000</v>
       </c>
-      <c r="J64" s="32" t="s">
+      <c r="J64" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K64" s="3">
@@ -6740,7 +6183,7 @@
       <c r="L64" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M64" s="48" t="s">
+      <c r="M64" s="46" t="s">
         <v>84</v>
       </c>
       <c r="N64" s="2">
@@ -6761,10 +6204,10 @@
       <c r="S64" s="3">
         <v>16008</v>
       </c>
-      <c r="T64" s="44">
+      <c r="T64" s="43">
         <v>12</v>
       </c>
-      <c r="U64" s="44">
+      <c r="U64" s="43">
         <v>0</v>
       </c>
       <c r="V64" t="s">
@@ -6776,12 +6219,12 @@
       <c r="X64" s="3">
         <v>1</v>
       </c>
-      <c r="Y64" s="51"/>
+      <c r="Y64" s="49"/>
     </row>
     <row r="65" spans="1:25">
       <c r="A65" s="2">
-        <f>B65*10+H65</f>
-        <v>2001021</v>
+        <f>B65*100+H65</f>
+        <v>20010021</v>
       </c>
       <c r="B65" s="28">
         <v>200100</v>
@@ -6795,19 +6238,19 @@
       <c r="E65" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F65" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G65" s="30" t="s">
+      <c r="F65" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G65" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H65" s="28">
         <v>21</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="30">
         <v>1990000</v>
       </c>
-      <c r="J65" s="32" t="s">
+      <c r="J65" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K65" s="2">
@@ -6816,7 +6259,7 @@
       <c r="L65" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M65" s="33" t="s">
+      <c r="M65" s="32" t="s">
         <v>56</v>
       </c>
       <c r="N65" s="2">
@@ -6834,13 +6277,13 @@
       <c r="R65" s="2">
         <v>15000</v>
       </c>
-      <c r="S65" s="34">
+      <c r="S65" s="33">
         <v>16008</v>
       </c>
       <c r="T65" s="5">
         <v>48</v>
       </c>
-      <c r="U65" s="35">
+      <c r="U65" s="34">
         <v>0</v>
       </c>
       <c r="V65" t="s">
@@ -6859,34 +6302,34 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="2">
-        <f t="shared" ref="A65:A94" si="6">B66*10+H66</f>
-        <v>2001022</v>
-      </c>
-      <c r="B66" s="36">
+        <f t="shared" ref="A66:A94" si="6">B66*100+H66</f>
+        <v>20010022</v>
+      </c>
+      <c r="B66" s="35">
         <v>200100</v>
       </c>
-      <c r="C66" s="36" t="s">
+      <c r="C66" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="D66" s="36">
+      <c r="D66" s="35">
         <v>200100038</v>
       </c>
-      <c r="E66" s="36" t="s">
+      <c r="E66" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F66" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G66" s="30" t="s">
+      <c r="F66" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G66" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H66" s="28">
         <v>22</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="30">
         <v>1990000</v>
       </c>
-      <c r="J66" s="37" t="s">
+      <c r="J66" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K66" s="2">
@@ -6895,7 +6338,7 @@
       <c r="L66" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M66" s="33" t="s">
+      <c r="M66" s="32" t="s">
         <v>56</v>
       </c>
       <c r="N66" s="2">
@@ -6913,13 +6356,13 @@
       <c r="R66" s="2">
         <v>15000</v>
       </c>
-      <c r="S66" s="34">
+      <c r="S66" s="33">
         <v>16008</v>
       </c>
       <c r="T66" s="5">
         <v>48</v>
       </c>
-      <c r="U66" s="35">
+      <c r="U66" s="34">
         <v>0</v>
       </c>
       <c r="V66" t="s">
@@ -6936,10 +6379,10 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" spans="1:25">
+    <row r="67" spans="1:25" s="2" customFormat="1">
       <c r="A67" s="2">
         <f t="shared" si="6"/>
-        <v>2001023</v>
+        <v>20010023</v>
       </c>
       <c r="B67" s="28">
         <v>200100</v>
@@ -6953,19 +6396,19 @@
       <c r="E67" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F67" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G67" s="30" t="s">
+      <c r="F67" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G67" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H67" s="28">
         <v>23</v>
       </c>
-      <c r="I67" s="31">
+      <c r="I67" s="30">
         <v>1990000</v>
       </c>
-      <c r="J67" s="32" t="s">
+      <c r="J67" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K67" s="2">
@@ -6974,7 +6417,7 @@
       <c r="L67" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M67" s="33" t="s">
+      <c r="M67" s="32" t="s">
         <v>56</v>
       </c>
       <c r="N67" s="2">
@@ -6992,13 +6435,13 @@
       <c r="R67" s="2">
         <v>15000</v>
       </c>
-      <c r="S67" s="34">
+      <c r="S67" s="33">
         <v>16008</v>
       </c>
       <c r="T67" s="5">
         <v>48</v>
       </c>
-      <c r="U67" s="35">
+      <c r="U67" s="34">
         <v>0</v>
       </c>
       <c r="V67" t="s">
@@ -7015,10 +6458,10 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" spans="1:25">
+    <row r="68" spans="1:25" s="2" customFormat="1">
       <c r="A68" s="2">
         <f t="shared" si="6"/>
-        <v>2001031</v>
+        <v>20010121</v>
       </c>
       <c r="B68" s="28">
         <v>200101</v>
@@ -7029,22 +6472,22 @@
       <c r="D68" s="28">
         <v>200101001</v>
       </c>
-      <c r="E68" s="38" t="s">
+      <c r="E68" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F68" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G68" s="30" t="s">
+      <c r="F68" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G68" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H68" s="28">
         <v>21</v>
       </c>
-      <c r="I68" s="31">
+      <c r="I68" s="30">
         <v>1990000</v>
       </c>
-      <c r="J68" s="32" t="s">
+      <c r="J68" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K68" s="2">
@@ -7053,7 +6496,7 @@
       <c r="L68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M68" s="33" t="s">
+      <c r="M68" s="32" t="s">
         <v>69</v>
       </c>
       <c r="N68" s="2">
@@ -7071,13 +6514,13 @@
       <c r="R68" s="2">
         <v>15000</v>
       </c>
-      <c r="S68" s="34">
+      <c r="S68" s="33">
         <v>16008</v>
       </c>
       <c r="T68" s="5">
         <v>48</v>
       </c>
-      <c r="U68" s="35">
+      <c r="U68" s="34">
         <v>0</v>
       </c>
       <c r="V68" t="s">
@@ -7097,33 +6540,33 @@
     <row r="69" spans="1:25">
       <c r="A69" s="2">
         <f t="shared" si="6"/>
-        <v>2001032</v>
-      </c>
-      <c r="B69" s="36">
+        <v>20010122</v>
+      </c>
+      <c r="B69" s="35">
         <v>200101</v>
       </c>
-      <c r="C69" s="36" t="s">
+      <c r="C69" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D69" s="36">
+      <c r="D69" s="35">
         <v>200101001</v>
       </c>
-      <c r="E69" s="36" t="s">
+      <c r="E69" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F69" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G69" s="30" t="s">
+      <c r="F69" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H69" s="28">
         <v>22</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="30">
         <v>1990000</v>
       </c>
-      <c r="J69" s="37" t="s">
+      <c r="J69" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K69" s="2">
@@ -7132,7 +6575,7 @@
       <c r="L69" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M69" s="33" t="s">
+      <c r="M69" s="32" t="s">
         <v>69</v>
       </c>
       <c r="N69" s="2">
@@ -7150,13 +6593,13 @@
       <c r="R69" s="2">
         <v>15000</v>
       </c>
-      <c r="S69" s="34">
+      <c r="S69" s="33">
         <v>16008</v>
       </c>
       <c r="T69" s="5">
         <v>48</v>
       </c>
-      <c r="U69" s="35">
+      <c r="U69" s="34">
         <v>0</v>
       </c>
       <c r="V69" t="s">
@@ -7176,7 +6619,7 @@
     <row r="70" spans="1:25">
       <c r="A70" s="2">
         <f t="shared" si="6"/>
-        <v>2001033</v>
+        <v>20010123</v>
       </c>
       <c r="B70" s="28">
         <v>200101</v>
@@ -7190,19 +6633,19 @@
       <c r="E70" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F70" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G70" s="30" t="s">
+      <c r="F70" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G70" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H70" s="28">
         <v>23</v>
       </c>
-      <c r="I70" s="31">
+      <c r="I70" s="30">
         <v>1990000</v>
       </c>
-      <c r="J70" s="32" t="s">
+      <c r="J70" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K70" s="2">
@@ -7211,7 +6654,7 @@
       <c r="L70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M70" s="33" t="s">
+      <c r="M70" s="32" t="s">
         <v>69</v>
       </c>
       <c r="N70" s="2">
@@ -7229,13 +6672,13 @@
       <c r="R70" s="2">
         <v>15000</v>
       </c>
-      <c r="S70" s="34">
+      <c r="S70" s="33">
         <v>16008</v>
       </c>
       <c r="T70" s="5">
         <v>48</v>
       </c>
-      <c r="U70" s="35">
+      <c r="U70" s="34">
         <v>0</v>
       </c>
       <c r="V70" t="s">
@@ -7255,7 +6698,7 @@
     <row r="71" spans="1:25">
       <c r="A71" s="2">
         <f t="shared" si="6"/>
-        <v>2003021</v>
+        <v>20030021</v>
       </c>
       <c r="B71" s="28">
         <v>200300</v>
@@ -7266,22 +6709,22 @@
       <c r="D71" s="28">
         <v>200300001</v>
       </c>
-      <c r="E71" s="39" t="s">
+      <c r="E71" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F71" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G71" s="30" t="s">
+      <c r="F71" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G71" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H71" s="28">
         <v>21</v>
       </c>
-      <c r="I71" s="31">
+      <c r="I71" s="30">
         <v>1990000</v>
       </c>
-      <c r="J71" s="32" t="s">
+      <c r="J71" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K71" s="2">
@@ -7290,7 +6733,7 @@
       <c r="L71" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M71" s="33" t="s">
+      <c r="M71" s="32" t="s">
         <v>71</v>
       </c>
       <c r="N71" s="2">
@@ -7308,13 +6751,13 @@
       <c r="R71" s="2">
         <v>15000</v>
       </c>
-      <c r="S71" s="34">
+      <c r="S71" s="33">
         <v>16008</v>
       </c>
       <c r="T71" s="5">
         <v>50</v>
       </c>
-      <c r="U71" s="35">
+      <c r="U71" s="34">
         <v>0</v>
       </c>
       <c r="V71" t="s">
@@ -7331,36 +6774,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" spans="1:25">
+    <row r="72" spans="1:25" s="2" customFormat="1">
       <c r="A72" s="2">
         <f t="shared" si="6"/>
-        <v>2003022</v>
-      </c>
-      <c r="B72" s="36">
+        <v>20030022</v>
+      </c>
+      <c r="B72" s="35">
         <v>200300</v>
       </c>
-      <c r="C72" s="36" t="s">
+      <c r="C72" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="D72" s="36">
+      <c r="D72" s="35">
         <v>200300001</v>
       </c>
-      <c r="E72" s="36" t="s">
+      <c r="E72" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F72" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G72" s="30" t="s">
+      <c r="F72" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G72" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H72" s="28">
         <v>22</v>
       </c>
-      <c r="I72" s="31">
+      <c r="I72" s="30">
         <v>1990000</v>
       </c>
-      <c r="J72" s="37" t="s">
+      <c r="J72" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K72" s="2">
@@ -7369,7 +6812,7 @@
       <c r="L72" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M72" s="33" t="s">
+      <c r="M72" s="32" t="s">
         <v>71</v>
       </c>
       <c r="N72" s="2">
@@ -7387,13 +6830,13 @@
       <c r="R72" s="2">
         <v>15000</v>
       </c>
-      <c r="S72" s="34">
+      <c r="S72" s="33">
         <v>16008</v>
       </c>
       <c r="T72" s="5">
         <v>50</v>
       </c>
-      <c r="U72" s="35">
+      <c r="U72" s="34">
         <v>0</v>
       </c>
       <c r="V72" t="s">
@@ -7413,7 +6856,7 @@
     <row r="73" spans="1:25">
       <c r="A73" s="2">
         <f t="shared" si="6"/>
-        <v>2003023</v>
+        <v>20030023</v>
       </c>
       <c r="B73" s="28">
         <v>200300</v>
@@ -7427,19 +6870,19 @@
       <c r="E73" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F73" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G73" s="30" t="s">
+      <c r="F73" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G73" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H73" s="28">
         <v>23</v>
       </c>
-      <c r="I73" s="31">
+      <c r="I73" s="30">
         <v>1990000</v>
       </c>
-      <c r="J73" s="32" t="s">
+      <c r="J73" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K73" s="2">
@@ -7448,7 +6891,7 @@
       <c r="L73" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M73" s="33" t="s">
+      <c r="M73" s="32" t="s">
         <v>71</v>
       </c>
       <c r="N73" s="2">
@@ -7466,13 +6909,13 @@
       <c r="R73" s="2">
         <v>15000</v>
       </c>
-      <c r="S73" s="34">
+      <c r="S73" s="33">
         <v>16008</v>
       </c>
       <c r="T73" s="5">
         <v>50</v>
       </c>
-      <c r="U73" s="35">
+      <c r="U73" s="34">
         <v>0</v>
       </c>
       <c r="V73" t="s">
@@ -7492,7 +6935,7 @@
     <row r="74" spans="1:25">
       <c r="A74" s="2">
         <f t="shared" si="6"/>
-        <v>2004021</v>
+        <v>20040021</v>
       </c>
       <c r="B74" s="28">
         <v>200400</v>
@@ -7503,22 +6946,22 @@
       <c r="D74" s="28">
         <v>200400009</v>
       </c>
-      <c r="E74" s="38" t="s">
+      <c r="E74" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F74" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G74" s="30" t="s">
+      <c r="F74" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G74" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H74" s="28">
         <v>21</v>
       </c>
-      <c r="I74" s="31">
+      <c r="I74" s="30">
         <v>1990000</v>
       </c>
-      <c r="J74" s="32" t="s">
+      <c r="J74" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K74" s="2">
@@ -7527,7 +6970,7 @@
       <c r="L74" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M74" s="33" t="s">
+      <c r="M74" s="32" t="s">
         <v>73</v>
       </c>
       <c r="N74" s="2">
@@ -7545,13 +6988,13 @@
       <c r="R74" s="2">
         <v>15000</v>
       </c>
-      <c r="S74" s="34">
+      <c r="S74" s="33">
         <v>16008</v>
       </c>
       <c r="T74" s="5">
         <v>50</v>
       </c>
-      <c r="U74" s="35">
+      <c r="U74" s="34">
         <v>0</v>
       </c>
       <c r="V74" t="s">
@@ -7571,33 +7014,33 @@
     <row r="75" spans="1:25">
       <c r="A75" s="2">
         <f t="shared" si="6"/>
-        <v>2004022</v>
-      </c>
-      <c r="B75" s="36">
+        <v>20040022</v>
+      </c>
+      <c r="B75" s="35">
         <v>200400</v>
       </c>
-      <c r="C75" s="36" t="s">
+      <c r="C75" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D75" s="36">
+      <c r="D75" s="35">
         <v>200400009</v>
       </c>
-      <c r="E75" s="36" t="s">
+      <c r="E75" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F75" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G75" s="30" t="s">
+      <c r="F75" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G75" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H75" s="28">
         <v>22</v>
       </c>
-      <c r="I75" s="31">
+      <c r="I75" s="30">
         <v>1990000</v>
       </c>
-      <c r="J75" s="37" t="s">
+      <c r="J75" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K75" s="2">
@@ -7606,7 +7049,7 @@
       <c r="L75" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M75" s="33" t="s">
+      <c r="M75" s="32" t="s">
         <v>73</v>
       </c>
       <c r="N75" s="2">
@@ -7624,13 +7067,13 @@
       <c r="R75" s="2">
         <v>15000</v>
       </c>
-      <c r="S75" s="34">
+      <c r="S75" s="33">
         <v>16008</v>
       </c>
       <c r="T75" s="5">
         <v>50</v>
       </c>
-      <c r="U75" s="35">
+      <c r="U75" s="34">
         <v>0</v>
       </c>
       <c r="V75" t="s">
@@ -7647,10 +7090,10 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="76" s="2" customFormat="1" spans="1:25">
+    <row r="76" spans="1:25" s="2" customFormat="1">
       <c r="A76" s="2">
         <f t="shared" si="6"/>
-        <v>2004023</v>
+        <v>20040023</v>
       </c>
       <c r="B76" s="28">
         <v>200400</v>
@@ -7664,19 +7107,19 @@
       <c r="E76" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F76" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G76" s="30" t="s">
+      <c r="F76" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G76" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H76" s="28">
         <v>23</v>
       </c>
-      <c r="I76" s="31">
+      <c r="I76" s="30">
         <v>1990000</v>
       </c>
-      <c r="J76" s="32" t="s">
+      <c r="J76" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K76" s="2">
@@ -7685,7 +7128,7 @@
       <c r="L76" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M76" s="33" t="s">
+      <c r="M76" s="32" t="s">
         <v>73</v>
       </c>
       <c r="N76" s="2">
@@ -7703,13 +7146,13 @@
       <c r="R76" s="2">
         <v>15000</v>
       </c>
-      <c r="S76" s="34">
+      <c r="S76" s="33">
         <v>16008</v>
       </c>
       <c r="T76" s="5">
         <v>50</v>
       </c>
-      <c r="U76" s="35">
+      <c r="U76" s="34">
         <v>0</v>
       </c>
       <c r="V76" t="s">
@@ -7726,8 +7169,9 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="77" s="2" customFormat="1" spans="1:25">
-      <c r="A77" s="44">
+    <row r="77" spans="1:25" s="2" customFormat="1">
+      <c r="A77" s="2">
+        <f t="shared" si="6"/>
         <v>20050021</v>
       </c>
       <c r="B77" s="28">
@@ -7742,19 +7186,19 @@
       <c r="E77" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F77" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G77" s="30" t="s">
+      <c r="F77" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G77" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H77" s="28">
         <v>21</v>
       </c>
-      <c r="I77" s="31">
+      <c r="I77" s="30">
         <v>1990000</v>
       </c>
-      <c r="J77" s="32" t="s">
+      <c r="J77" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K77" s="2">
@@ -7763,7 +7207,7 @@
       <c r="L77" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M77" s="33" t="s">
+      <c r="M77" s="32" t="s">
         <v>75</v>
       </c>
       <c r="N77" s="2">
@@ -7781,13 +7225,13 @@
       <c r="R77" s="2">
         <v>15000</v>
       </c>
-      <c r="S77" s="34">
+      <c r="S77" s="33">
         <v>16008</v>
       </c>
       <c r="T77" s="5">
         <v>48</v>
       </c>
-      <c r="U77" s="35">
+      <c r="U77" s="34">
         <v>0</v>
       </c>
       <c r="V77" t="s">
@@ -7805,34 +7249,35 @@
       </c>
     </row>
     <row r="78" spans="1:25">
-      <c r="A78" s="44">
+      <c r="A78" s="2">
+        <f t="shared" si="6"/>
         <v>20050022</v>
       </c>
-      <c r="B78" s="36">
+      <c r="B78" s="35">
         <v>200500</v>
       </c>
-      <c r="C78" s="36" t="s">
+      <c r="C78" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="D78" s="36">
+      <c r="D78" s="35">
         <v>200500025</v>
       </c>
-      <c r="E78" s="36" t="s">
+      <c r="E78" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F78" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G78" s="30" t="s">
+      <c r="F78" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G78" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H78" s="28">
         <v>22</v>
       </c>
-      <c r="I78" s="31">
+      <c r="I78" s="30">
         <v>1990000</v>
       </c>
-      <c r="J78" s="37" t="s">
+      <c r="J78" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K78" s="2">
@@ -7841,7 +7286,7 @@
       <c r="L78" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M78" s="33" t="s">
+      <c r="M78" s="32" t="s">
         <v>75</v>
       </c>
       <c r="N78" s="2">
@@ -7859,13 +7304,13 @@
       <c r="R78" s="2">
         <v>15000</v>
       </c>
-      <c r="S78" s="34">
+      <c r="S78" s="33">
         <v>16008</v>
       </c>
       <c r="T78" s="5">
         <v>48</v>
       </c>
-      <c r="U78" s="35">
+      <c r="U78" s="34">
         <v>0</v>
       </c>
       <c r="V78" t="s">
@@ -7883,7 +7328,8 @@
       </c>
     </row>
     <row r="79" spans="1:25">
-      <c r="A79" s="44">
+      <c r="A79" s="2">
+        <f t="shared" si="6"/>
         <v>20050023</v>
       </c>
       <c r="B79" s="28">
@@ -7898,19 +7344,19 @@
       <c r="E79" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F79" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G79" s="30" t="s">
+      <c r="F79" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G79" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H79" s="28">
         <v>23</v>
       </c>
-      <c r="I79" s="31">
+      <c r="I79" s="30">
         <v>1990000</v>
       </c>
-      <c r="J79" s="32" t="s">
+      <c r="J79" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K79" s="2">
@@ -7919,7 +7365,7 @@
       <c r="L79" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M79" s="33" t="s">
+      <c r="M79" s="32" t="s">
         <v>75</v>
       </c>
       <c r="N79" s="2">
@@ -7937,13 +7383,13 @@
       <c r="R79" s="2">
         <v>15000</v>
       </c>
-      <c r="S79" s="34">
+      <c r="S79" s="33">
         <v>16008</v>
       </c>
       <c r="T79" s="5">
         <v>48</v>
       </c>
-      <c r="U79" s="35">
+      <c r="U79" s="34">
         <v>0</v>
       </c>
       <c r="V79" t="s">
@@ -7963,7 +7409,7 @@
     <row r="80" spans="1:25">
       <c r="A80" s="2">
         <f t="shared" si="6"/>
-        <v>2006021</v>
+        <v>20060021</v>
       </c>
       <c r="B80" s="28">
         <v>200600</v>
@@ -7974,22 +7420,22 @@
       <c r="D80" s="28">
         <v>200600001</v>
       </c>
-      <c r="E80" s="39" t="s">
+      <c r="E80" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F80" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G80" s="30" t="s">
+      <c r="F80" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G80" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H80" s="28">
         <v>21</v>
       </c>
-      <c r="I80" s="31">
+      <c r="I80" s="30">
         <v>1990000</v>
       </c>
-      <c r="J80" s="32" t="s">
+      <c r="J80" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K80" s="2">
@@ -7998,7 +7444,7 @@
       <c r="L80" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M80" s="33" t="s">
+      <c r="M80" s="32" t="s">
         <v>77</v>
       </c>
       <c r="N80" s="2">
@@ -8016,13 +7462,13 @@
       <c r="R80" s="2">
         <v>15000</v>
       </c>
-      <c r="S80" s="34">
+      <c r="S80" s="33">
         <v>16008</v>
       </c>
       <c r="T80" s="5">
         <v>20</v>
       </c>
-      <c r="U80" s="35">
+      <c r="U80" s="34">
         <v>0</v>
       </c>
       <c r="V80" t="s">
@@ -8039,36 +7485,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="81" s="2" customFormat="1" spans="1:25">
+    <row r="81" spans="1:25" s="2" customFormat="1">
       <c r="A81" s="2">
         <f t="shared" si="6"/>
-        <v>2006022</v>
-      </c>
-      <c r="B81" s="36">
+        <v>20060022</v>
+      </c>
+      <c r="B81" s="35">
         <v>200600</v>
       </c>
-      <c r="C81" s="36" t="s">
+      <c r="C81" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="D81" s="36">
+      <c r="D81" s="35">
         <v>200600001</v>
       </c>
-      <c r="E81" s="36" t="s">
+      <c r="E81" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F81" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G81" s="30" t="s">
+      <c r="F81" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G81" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H81" s="28">
         <v>22</v>
       </c>
-      <c r="I81" s="31">
+      <c r="I81" s="30">
         <v>1990000</v>
       </c>
-      <c r="J81" s="37" t="s">
+      <c r="J81" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K81" s="2">
@@ -8077,7 +7523,7 @@
       <c r="L81" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M81" s="33" t="s">
+      <c r="M81" s="32" t="s">
         <v>77</v>
       </c>
       <c r="N81" s="2">
@@ -8095,13 +7541,13 @@
       <c r="R81" s="2">
         <v>15000</v>
       </c>
-      <c r="S81" s="34">
+      <c r="S81" s="33">
         <v>16008</v>
       </c>
       <c r="T81" s="5">
         <v>20</v>
       </c>
-      <c r="U81" s="35">
+      <c r="U81" s="34">
         <v>0</v>
       </c>
       <c r="V81" t="s">
@@ -8121,7 +7567,7 @@
     <row r="82" spans="1:25">
       <c r="A82" s="2">
         <f t="shared" si="6"/>
-        <v>2006023</v>
+        <v>20060023</v>
       </c>
       <c r="B82" s="28">
         <v>200600</v>
@@ -8135,19 +7581,19 @@
       <c r="E82" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F82" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G82" s="30" t="s">
+      <c r="F82" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G82" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H82" s="28">
         <v>23</v>
       </c>
-      <c r="I82" s="31">
+      <c r="I82" s="30">
         <v>1990000</v>
       </c>
-      <c r="J82" s="32" t="s">
+      <c r="J82" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K82" s="2">
@@ -8156,7 +7602,7 @@
       <c r="L82" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M82" s="33" t="s">
+      <c r="M82" s="32" t="s">
         <v>77</v>
       </c>
       <c r="N82" s="2">
@@ -8174,13 +7620,13 @@
       <c r="R82" s="2">
         <v>15000</v>
       </c>
-      <c r="S82" s="34">
+      <c r="S82" s="33">
         <v>16008</v>
       </c>
       <c r="T82" s="5">
         <v>20</v>
       </c>
-      <c r="U82" s="35">
+      <c r="U82" s="34">
         <v>0</v>
       </c>
       <c r="V82" t="s">
@@ -8200,7 +7646,7 @@
     <row r="83" spans="1:25">
       <c r="A83" s="2">
         <f t="shared" si="6"/>
-        <v>2007021</v>
+        <v>20070021</v>
       </c>
       <c r="B83" s="28">
         <v>200700</v>
@@ -8214,19 +7660,19 @@
       <c r="E83" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F83" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G83" s="30" t="s">
+      <c r="F83" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G83" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H83" s="28">
         <v>21</v>
       </c>
-      <c r="I83" s="31">
+      <c r="I83" s="30">
         <v>1990000</v>
       </c>
-      <c r="J83" s="32" t="s">
+      <c r="J83" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K83" s="2">
@@ -8235,7 +7681,7 @@
       <c r="L83" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M83" s="33" t="s">
+      <c r="M83" s="32" t="s">
         <v>79</v>
       </c>
       <c r="N83" s="2">
@@ -8253,13 +7699,13 @@
       <c r="R83" s="2">
         <v>15000</v>
       </c>
-      <c r="S83" s="34">
+      <c r="S83" s="33">
         <v>16008</v>
       </c>
       <c r="T83" s="5">
         <v>30</v>
       </c>
-      <c r="U83" s="35">
+      <c r="U83" s="34">
         <v>1</v>
       </c>
       <c r="V83" t="s">
@@ -8279,33 +7725,33 @@
     <row r="84" spans="1:25">
       <c r="A84" s="2">
         <f t="shared" si="6"/>
-        <v>2007022</v>
-      </c>
-      <c r="B84" s="36">
+        <v>20070022</v>
+      </c>
+      <c r="B84" s="35">
         <v>200700</v>
       </c>
-      <c r="C84" s="36" t="s">
+      <c r="C84" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="D84" s="36">
+      <c r="D84" s="35">
         <v>200700001</v>
       </c>
-      <c r="E84" s="36" t="s">
+      <c r="E84" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F84" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G84" s="30" t="s">
+      <c r="F84" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G84" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H84" s="28">
         <v>22</v>
       </c>
-      <c r="I84" s="31">
+      <c r="I84" s="30">
         <v>1990000</v>
       </c>
-      <c r="J84" s="37" t="s">
+      <c r="J84" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K84" s="2">
@@ -8314,7 +7760,7 @@
       <c r="L84" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M84" s="33" t="s">
+      <c r="M84" s="32" t="s">
         <v>79</v>
       </c>
       <c r="N84" s="2">
@@ -8332,13 +7778,13 @@
       <c r="R84" s="2">
         <v>15000</v>
       </c>
-      <c r="S84" s="34">
+      <c r="S84" s="33">
         <v>16008</v>
       </c>
       <c r="T84" s="5">
         <v>30</v>
       </c>
-      <c r="U84" s="35">
+      <c r="U84" s="34">
         <v>1</v>
       </c>
       <c r="V84" t="s">
@@ -8355,10 +7801,10 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="85" s="2" customFormat="1" spans="1:25">
+    <row r="85" spans="1:25" s="2" customFormat="1">
       <c r="A85" s="2">
         <f t="shared" si="6"/>
-        <v>2007023</v>
+        <v>20070023</v>
       </c>
       <c r="B85" s="28">
         <v>200700</v>
@@ -8372,19 +7818,19 @@
       <c r="E85" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G85" s="30" t="s">
+      <c r="F85" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G85" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H85" s="28">
         <v>23</v>
       </c>
-      <c r="I85" s="31">
+      <c r="I85" s="30">
         <v>1990000</v>
       </c>
-      <c r="J85" s="32" t="s">
+      <c r="J85" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K85" s="2">
@@ -8393,7 +7839,7 @@
       <c r="L85" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M85" s="33" t="s">
+      <c r="M85" s="32" t="s">
         <v>79</v>
       </c>
       <c r="N85" s="2">
@@ -8411,13 +7857,13 @@
       <c r="R85" s="2">
         <v>15000</v>
       </c>
-      <c r="S85" s="34">
+      <c r="S85" s="33">
         <v>16008</v>
       </c>
       <c r="T85" s="5">
         <v>30</v>
       </c>
-      <c r="U85" s="35">
+      <c r="U85" s="34">
         <v>1</v>
       </c>
       <c r="V85" t="s">
@@ -8434,10 +7880,10 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="86" s="2" customFormat="1" spans="1:25">
+    <row r="86" spans="1:25" s="2" customFormat="1">
       <c r="A86" s="2">
         <f t="shared" si="6"/>
-        <v>2008021</v>
+        <v>20080021</v>
       </c>
       <c r="B86" s="28">
         <v>200800</v>
@@ -8448,22 +7894,22 @@
       <c r="D86" s="28">
         <v>200800001</v>
       </c>
-      <c r="E86" s="39" t="s">
+      <c r="E86" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F86" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G86" s="30" t="s">
+      <c r="F86" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G86" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H86" s="28">
         <v>21</v>
       </c>
-      <c r="I86" s="31">
+      <c r="I86" s="30">
         <v>1990000</v>
       </c>
-      <c r="J86" s="32" t="s">
+      <c r="J86" s="31" t="s">
         <v>54</v>
       </c>
       <c r="K86" s="2">
@@ -8472,7 +7918,7 @@
       <c r="L86" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M86" s="33" t="s">
+      <c r="M86" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N86" s="2">
@@ -8490,13 +7936,13 @@
       <c r="R86" s="2">
         <v>15000</v>
       </c>
-      <c r="S86" s="34">
+      <c r="S86" s="33">
         <v>16008</v>
       </c>
       <c r="T86" s="5">
         <v>20</v>
       </c>
-      <c r="U86" s="35">
+      <c r="U86" s="34">
         <v>0</v>
       </c>
       <c r="V86" t="s">
@@ -8513,10 +7959,10 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="87" s="2" customFormat="1" spans="1:25">
+    <row r="87" spans="1:25" s="2" customFormat="1">
       <c r="A87" s="2">
         <f t="shared" si="6"/>
-        <v>2008022</v>
+        <v>20080022</v>
       </c>
       <c r="B87" s="28">
         <v>200800</v>
@@ -8527,22 +7973,22 @@
       <c r="D87" s="28">
         <v>200800001</v>
       </c>
-      <c r="E87" s="36" t="s">
+      <c r="E87" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F87" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G87" s="30" t="s">
+      <c r="F87" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G87" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H87" s="28">
         <v>22</v>
       </c>
-      <c r="I87" s="31">
+      <c r="I87" s="30">
         <v>1990000</v>
       </c>
-      <c r="J87" s="37" t="s">
+      <c r="J87" s="36" t="s">
         <v>60</v>
       </c>
       <c r="K87" s="2">
@@ -8551,7 +7997,7 @@
       <c r="L87" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M87" s="33" t="s">
+      <c r="M87" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N87" s="2">
@@ -8569,13 +8015,13 @@
       <c r="R87" s="2">
         <v>15000</v>
       </c>
-      <c r="S87" s="34">
+      <c r="S87" s="33">
         <v>16008</v>
       </c>
       <c r="T87" s="5">
         <v>20</v>
       </c>
-      <c r="U87" s="35">
+      <c r="U87" s="34">
         <v>0</v>
       </c>
       <c r="V87" t="s">
@@ -8592,10 +8038,10 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="88" s="2" customFormat="1" spans="1:25">
+    <row r="88" spans="1:25" s="2" customFormat="1">
       <c r="A88" s="2">
         <f t="shared" si="6"/>
-        <v>2008023</v>
+        <v>20080023</v>
       </c>
       <c r="B88" s="28">
         <v>200800</v>
@@ -8609,19 +8055,19 @@
       <c r="E88" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F88" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G88" s="30" t="s">
+      <c r="F88" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G88" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H88" s="28">
         <v>23</v>
       </c>
-      <c r="I88" s="31">
+      <c r="I88" s="30">
         <v>1990000</v>
       </c>
-      <c r="J88" s="32" t="s">
+      <c r="J88" s="31" t="s">
         <v>64</v>
       </c>
       <c r="K88" s="2">
@@ -8630,7 +8076,7 @@
       <c r="L88" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M88" s="33" t="s">
+      <c r="M88" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N88" s="2">
@@ -8648,13 +8094,13 @@
       <c r="R88" s="2">
         <v>15000</v>
       </c>
-      <c r="S88" s="34">
+      <c r="S88" s="33">
         <v>16008</v>
       </c>
       <c r="T88" s="5">
         <v>20</v>
       </c>
-      <c r="U88" s="35">
+      <c r="U88" s="34">
         <v>0</v>
       </c>
       <c r="V88" t="s">
@@ -8671,12 +8117,12 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="89" s="2" customFormat="1" spans="1:25">
+    <row r="89" spans="1:25" s="2" customFormat="1">
       <c r="A89" s="2">
         <f t="shared" si="6"/>
-        <v>2009021</v>
-      </c>
-      <c r="B89" s="40">
+        <v>20090021</v>
+      </c>
+      <c r="B89" s="39">
         <v>200900</v>
       </c>
       <c r="C89" s="28" t="s">
@@ -8685,31 +8131,31 @@
       <c r="D89" s="28">
         <v>200900001</v>
       </c>
-      <c r="E89" s="38" t="s">
+      <c r="E89" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F89" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G89" s="30" t="s">
+      <c r="F89" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G89" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H89" s="28">
         <v>21</v>
       </c>
-      <c r="I89" s="31">
+      <c r="I89" s="30">
         <v>1990000</v>
       </c>
-      <c r="J89" s="32" t="s">
+      <c r="J89" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K89" s="41">
+      <c r="K89" s="40">
         <v>0</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M89" s="33" t="s">
+      <c r="M89" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N89" s="2">
@@ -8727,13 +8173,13 @@
       <c r="R89" s="2">
         <v>15000</v>
       </c>
-      <c r="S89" s="34">
+      <c r="S89" s="33">
         <v>16008</v>
       </c>
       <c r="T89" s="5">
         <v>20</v>
       </c>
-      <c r="U89" s="35">
+      <c r="U89" s="34">
         <v>0</v>
       </c>
       <c r="V89" t="s">
@@ -8753,42 +8199,42 @@
     <row r="90" spans="1:25">
       <c r="A90" s="2">
         <f t="shared" si="6"/>
-        <v>2009022</v>
-      </c>
-      <c r="B90" s="42">
+        <v>20090022</v>
+      </c>
+      <c r="B90" s="41">
         <v>200900</v>
       </c>
-      <c r="C90" s="36" t="s">
+      <c r="C90" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="D90" s="36">
+      <c r="D90" s="35">
         <v>200900001</v>
       </c>
-      <c r="E90" s="36" t="s">
+      <c r="E90" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F90" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G90" s="30" t="s">
+      <c r="F90" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G90" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H90" s="28">
         <v>22</v>
       </c>
-      <c r="I90" s="31">
+      <c r="I90" s="30">
         <v>1990000</v>
       </c>
-      <c r="J90" s="37" t="s">
+      <c r="J90" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="K90" s="41">
+      <c r="K90" s="40">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M90" s="33" t="s">
+      <c r="M90" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N90" s="2">
@@ -8806,13 +8252,13 @@
       <c r="R90" s="2">
         <v>15000</v>
       </c>
-      <c r="S90" s="34">
+      <c r="S90" s="33">
         <v>16008</v>
       </c>
       <c r="T90" s="5">
         <v>20</v>
       </c>
-      <c r="U90" s="35">
+      <c r="U90" s="34">
         <v>0</v>
       </c>
       <c r="V90" t="s">
@@ -8832,9 +8278,9 @@
     <row r="91" spans="1:25">
       <c r="A91" s="2">
         <f t="shared" si="6"/>
-        <v>2009023</v>
-      </c>
-      <c r="B91" s="40">
+        <v>20090023</v>
+      </c>
+      <c r="B91" s="39">
         <v>200900</v>
       </c>
       <c r="C91" s="28" t="s">
@@ -8846,28 +8292,28 @@
       <c r="E91" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F91" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G91" s="30" t="s">
+      <c r="F91" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G91" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H91" s="28">
         <v>23</v>
       </c>
-      <c r="I91" s="31">
+      <c r="I91" s="30">
         <v>1990000</v>
       </c>
-      <c r="J91" s="32" t="s">
+      <c r="J91" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K91" s="41">
+      <c r="K91" s="40">
         <v>0</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M91" s="33" t="s">
+      <c r="M91" s="32" t="s">
         <v>81</v>
       </c>
       <c r="N91" s="2">
@@ -8885,13 +8331,13 @@
       <c r="R91" s="2">
         <v>15000</v>
       </c>
-      <c r="S91" s="34">
+      <c r="S91" s="33">
         <v>16008</v>
       </c>
       <c r="T91" s="5">
         <v>20</v>
       </c>
-      <c r="U91" s="35">
+      <c r="U91" s="34">
         <v>0</v>
       </c>
       <c r="V91" t="s">
@@ -8908,45 +8354,45 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="92" s="2" customFormat="1" spans="1:25">
+    <row r="92" spans="1:25" s="2" customFormat="1">
       <c r="A92" s="2">
         <f t="shared" si="6"/>
-        <v>2012021</v>
-      </c>
-      <c r="B92" s="43">
+        <v>20120021</v>
+      </c>
+      <c r="B92" s="42">
         <v>201200</v>
       </c>
       <c r="C92" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D92" s="36">
+      <c r="D92" s="35">
         <v>201200001</v>
       </c>
-      <c r="E92" s="38" t="s">
+      <c r="E92" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F92" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G92" s="30" t="s">
+      <c r="F92" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G92" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H92" s="28">
         <v>21</v>
       </c>
-      <c r="I92" s="31">
+      <c r="I92" s="30">
         <v>1990000</v>
       </c>
-      <c r="J92" s="32" t="s">
+      <c r="J92" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K92" s="41">
+      <c r="K92" s="40">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M92" s="33" t="s">
+      <c r="M92" s="32" t="s">
         <v>84</v>
       </c>
       <c r="N92" s="2">
@@ -8964,13 +8410,13 @@
       <c r="R92" s="2">
         <v>15000</v>
       </c>
-      <c r="S92" s="34">
+      <c r="S92" s="33">
         <v>16008</v>
       </c>
       <c r="T92" s="5">
         <v>12</v>
       </c>
-      <c r="U92" s="35">
+      <c r="U92" s="34">
         <v>0</v>
       </c>
       <c r="V92" t="s">
@@ -8990,42 +8436,42 @@
     <row r="93" spans="1:25">
       <c r="A93" s="2">
         <f t="shared" si="6"/>
-        <v>2012022</v>
-      </c>
-      <c r="B93" s="43">
+        <v>20120022</v>
+      </c>
+      <c r="B93" s="42">
         <v>201200</v>
       </c>
       <c r="C93" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D93" s="36">
+      <c r="D93" s="35">
         <v>201200001</v>
       </c>
-      <c r="E93" s="36" t="s">
+      <c r="E93" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F93" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G93" s="30" t="s">
+      <c r="F93" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G93" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H93" s="28">
         <v>22</v>
       </c>
-      <c r="I93" s="31">
+      <c r="I93" s="30">
         <v>1990000</v>
       </c>
-      <c r="J93" s="37" t="s">
+      <c r="J93" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="K93" s="41">
+      <c r="K93" s="40">
         <v>0</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M93" s="33" t="s">
+      <c r="M93" s="32" t="s">
         <v>84</v>
       </c>
       <c r="N93" s="2">
@@ -9043,13 +8489,13 @@
       <c r="R93" s="2">
         <v>15000</v>
       </c>
-      <c r="S93" s="34">
+      <c r="S93" s="33">
         <v>16008</v>
       </c>
       <c r="T93" s="5">
         <v>12</v>
       </c>
-      <c r="U93" s="35">
+      <c r="U93" s="34">
         <v>0</v>
       </c>
       <c r="V93" t="s">
@@ -9069,42 +8515,42 @@
     <row r="94" spans="1:25">
       <c r="A94" s="2">
         <f t="shared" si="6"/>
-        <v>2012023</v>
-      </c>
-      <c r="B94" s="43">
+        <v>20120023</v>
+      </c>
+      <c r="B94" s="42">
         <v>201200</v>
       </c>
       <c r="C94" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="36">
+      <c r="D94" s="35">
         <v>201200001</v>
       </c>
       <c r="E94" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F94" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G94" s="30" t="s">
+      <c r="F94" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G94" s="29" t="s">
         <v>53</v>
       </c>
       <c r="H94" s="28">
         <v>23</v>
       </c>
-      <c r="I94" s="31">
+      <c r="I94" s="30">
         <v>1990000</v>
       </c>
-      <c r="J94" s="32" t="s">
+      <c r="J94" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K94" s="41">
+      <c r="K94" s="40">
         <v>0</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M94" s="33" t="s">
+      <c r="M94" s="32" t="s">
         <v>84</v>
       </c>
       <c r="N94" s="2">
@@ -9122,13 +8568,13 @@
       <c r="R94" s="2">
         <v>15000</v>
       </c>
-      <c r="S94" s="34">
+      <c r="S94" s="33">
         <v>16008</v>
       </c>
       <c r="T94" s="5">
         <v>12</v>
       </c>
-      <c r="U94" s="35">
+      <c r="U94" s="34">
         <v>0</v>
       </c>
       <c r="V94" t="s">
@@ -9146,12 +8592,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S94" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:S64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\特殊用户标记相关配置表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE37467-CAA5-4650-81E5-0D9A000FE32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -36,21 +30,20 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
     <author>C</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -59,7 +52,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -68,13 +60,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">普通场 1
@@ -84,27 +75,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>押分筹码列表</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="K1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -113,7 +102,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -122,13 +110,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="M1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>阶段信息:[准备阶段时间-毫秒，押分阶段时间-毫秒，亮牌阶段时间-毫秒，结算阶段-毫秒]
@@ -137,13 +124,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>每笔投注进入房间水池比例
@@ -153,27 +139,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>净赢分*抽水比例</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="P1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -182,7 +166,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -191,14 +174,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="Q1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -207,7 +189,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -216,14 +197,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="R1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -232,7 +212,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -242,14 +221,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -258,7 +236,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -267,14 +244,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="U1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -283,7 +259,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -292,14 +267,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="V1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -308,7 +282,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -318,14 +291,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="W1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -334,7 +306,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -342,13 +313,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="Y1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最大押分值*10000</t>
@@ -360,7 +330,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="111">
   <si>
     <t>游戏ID</t>
   </si>
@@ -698,11 +668,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -751,45 +725,173 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,54 +900,240 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7993408001953185"/>
+        <fgColor theme="7" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7993408001953185"/>
+        <fgColor theme="9" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993408001953185"/>
+        <fgColor theme="4" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7993408001953185"/>
+        <fgColor theme="5" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -853,62 +1141,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -929,151 +1468,218 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="60">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="50"/>
+    <cellStyle name="常规 2 2 2" xfId="51"/>
+    <cellStyle name="常规 3" xfId="52"/>
+    <cellStyle name="常规 3 2" xfId="53"/>
+    <cellStyle name="常规 4" xfId="54"/>
+    <cellStyle name="常规 5" xfId="55"/>
+    <cellStyle name="常规 6" xfId="56"/>
+    <cellStyle name="常规 6 2" xfId="57"/>
+    <cellStyle name="常规 6 2 2" xfId="58"/>
+    <cellStyle name="常规 7" xfId="59"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1331,2675 +1937,2676 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y94"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="4" width="20.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21" style="2" customWidth="1"/>
-    <col min="10" max="10" width="65" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="24.75" style="4" customWidth="1"/>
-    <col min="14" max="14" width="19.25" style="2" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="2" customWidth="1"/>
-    <col min="16" max="19" width="9.875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="17.25" style="5" customWidth="1"/>
-    <col min="21" max="22" width="19.5" style="6" customWidth="1"/>
-    <col min="23" max="23" width="19.125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="4"/>
+    <col min="2" max="2" width="12" style="4" customWidth="1"/>
+    <col min="3" max="4" width="20.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.1416666666667" style="4" customWidth="1"/>
+    <col min="7" max="7" width="28.2333333333333" style="4" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="21.025" style="4" customWidth="1"/>
+    <col min="10" max="10" width="65" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="24.75" style="5" customWidth="1"/>
+    <col min="14" max="14" width="19.2833333333333" style="4" customWidth="1"/>
+    <col min="15" max="15" width="18.75" style="4" customWidth="1"/>
+    <col min="16" max="19" width="9.81666666666667" style="4" customWidth="1"/>
+    <col min="20" max="20" width="17.2166666666667" style="6" customWidth="1"/>
+    <col min="21" max="22" width="19.5" style="7" customWidth="1"/>
+    <col min="23" max="23" width="19.125" style="8" customWidth="1"/>
     <col min="24" max="24" width="12.875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="20.125" style="4" customWidth="1"/>
+    <col min="25" max="25" width="20.125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="41.1" customHeight="1">
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:25">
+      <c r="A1" s="9"/>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11" t="s">
+      <c r="L1" s="13"/>
+      <c r="M1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="S1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="17" t="s">
+      <c r="W1" s="20" t="s">
         <v>19</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="18" t="s">
+      <c r="Y1" s="21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="1" customFormat="1">
+    <row r="2" s="1" customFormat="1" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="19" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="4" t="s">
+      <c r="L2" s="4"/>
+      <c r="M2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="V2" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="21" t="s">
+      <c r="W2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Y2" s="25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="1" customFormat="1">
+    <row r="3" s="1" customFormat="1" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="4" t="s">
+      <c r="L3" s="4"/>
+      <c r="M3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="T3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="6" t="s">
         <v>45</v>
       </c>
       <c r="V3" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="W3" s="20" t="s">
         <v>47</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Y3" s="22" t="s">
+      <c r="Y3" s="25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="1" customFormat="1">
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="17"/>
-      <c r="Y4" s="17"/>
+    <row r="4" s="1" customFormat="1" spans="1:25">
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="20"/>
+      <c r="Y4" s="20"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="2">
+      <c r="A5" s="4">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="32">
         <v>200100</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="32">
         <v>200100038</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="28">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30">
+      <c r="H5" s="32">
+        <v>1</v>
+      </c>
+      <c r="I5" s="35">
         <v>1990000</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="J5" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="s">
+      <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="M5" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="4">
         <v>9500</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="4">
         <v>300</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="4">
         <v>180000</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="4">
         <v>16000</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="4">
         <v>15000</v>
       </c>
-      <c r="S5" s="33">
+      <c r="S5" s="38">
         <v>16008</v>
       </c>
-      <c r="T5" s="5">
+      <c r="T5" s="6">
         <v>48</v>
       </c>
-      <c r="U5" s="34">
+      <c r="U5" s="39">
         <v>0</v>
       </c>
       <c r="V5" t="s">
         <v>57</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X5" s="2">
         <v>0</v>
       </c>
-      <c r="Y5" s="4">
+      <c r="Y5" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="2">
+      <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="40">
         <v>200100</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="40">
         <v>200100038</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="40">
         <v>2</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="35">
         <v>1990000</v>
       </c>
-      <c r="J6" s="36" t="s">
+      <c r="J6" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="M6" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="4">
         <v>9500</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6" s="4">
         <v>300</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="4">
         <v>180000</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="4">
         <v>16000</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="4">
         <v>15000</v>
       </c>
-      <c r="S6" s="33">
+      <c r="S6" s="38">
         <v>16008</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6" s="6">
         <v>48</v>
       </c>
-      <c r="U6" s="34">
+      <c r="U6" s="39">
         <v>0</v>
       </c>
       <c r="V6" t="s">
         <v>61</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="W6" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X6" s="2">
         <v>0</v>
       </c>
-      <c r="Y6" s="4">
+      <c r="Y6" s="8">
         <f t="shared" ref="Y6:Y10" si="1">Y5*10</f>
         <v>100000000</v>
       </c>
     </row>
-    <row r="7" spans="1:25" s="2" customFormat="1">
-      <c r="A7" s="2">
+    <row r="7" s="2" customFormat="1" spans="1:25">
+      <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>2001003</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="32">
         <v>200100</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="32">
         <v>200100038</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="32">
         <v>3</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="35">
         <v>1990000</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="s">
+      <c r="K7" s="4">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="32" t="s">
+      <c r="M7" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="4">
         <v>9500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="4">
         <v>300</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="4">
         <v>180000</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="4">
         <v>16000</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="4">
         <v>15000</v>
       </c>
-      <c r="S7" s="33">
+      <c r="S7" s="38">
         <v>16008</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="6">
         <v>48</v>
       </c>
-      <c r="U7" s="34">
+      <c r="U7" s="39">
         <v>0</v>
       </c>
       <c r="V7" t="s">
         <v>65</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="4">
+      <c r="Y7" s="8">
         <f t="shared" si="1"/>
         <v>1000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="2" customFormat="1">
-      <c r="A8" s="2">
+    <row r="8" s="2" customFormat="1" spans="1:25">
+      <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>2001011</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="32">
         <v>200101</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="32">
         <v>200101001</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="28">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30">
+      <c r="H8" s="32">
+        <v>1</v>
+      </c>
+      <c r="I8" s="35">
         <v>1990000</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="32" t="s">
+      <c r="M8" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="4">
         <v>9500</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="4">
         <v>300</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="4">
         <v>180000</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="4">
         <v>16000</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="4">
         <v>15000</v>
       </c>
-      <c r="S8" s="33">
+      <c r="S8" s="38">
         <v>16008</v>
       </c>
-      <c r="T8" s="5">
+      <c r="T8" s="6">
         <v>48</v>
       </c>
-      <c r="U8" s="34">
+      <c r="U8" s="39">
         <v>0</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X8" s="2">
         <v>0</v>
       </c>
-      <c r="Y8" s="4">
+      <c r="Y8" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="2">
+      <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="40">
         <v>200101</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="40">
         <v>200101001</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="40">
         <v>2</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="35">
         <v>1990000</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="M9" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="4">
         <v>9500</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" s="4">
         <v>300</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="4">
         <v>180000</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="4">
         <v>16000</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="4">
         <v>15000</v>
       </c>
-      <c r="S9" s="33">
+      <c r="S9" s="38">
         <v>16008</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="6">
         <v>48</v>
       </c>
-      <c r="U9" s="34">
+      <c r="U9" s="39">
         <v>0</v>
       </c>
       <c r="V9" t="s">
         <v>61</v>
       </c>
-      <c r="W9" s="4" t="s">
+      <c r="W9" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X9" s="2">
         <v>0</v>
       </c>
-      <c r="Y9" s="4">
+      <c r="Y9" s="8">
         <f t="shared" si="1"/>
         <v>100000000</v>
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="2">
+      <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>2001013</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="32">
         <v>200101</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="32">
         <v>200101001</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="32">
         <v>3</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="35">
         <v>1990000</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="32" t="s">
+      <c r="M10" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="4">
         <v>9500</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="4">
         <v>300</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="4">
         <v>180000</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="4">
         <v>16000</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="4">
         <v>15000</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10" s="38">
         <v>16008</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="6">
         <v>48</v>
       </c>
-      <c r="U10" s="34">
+      <c r="U10" s="39">
         <v>0</v>
       </c>
       <c r="V10" t="s">
         <v>65</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="W10" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X10" s="2">
         <v>0</v>
       </c>
-      <c r="Y10" s="4">
+      <c r="Y10" s="8">
         <f t="shared" si="1"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="2">
+      <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>2003001</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="32">
         <v>200300</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="32">
         <v>200300001</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="28">
-        <v>1</v>
-      </c>
-      <c r="I11" s="30">
+      <c r="H11" s="32">
+        <v>1</v>
+      </c>
+      <c r="I11" s="35">
         <v>1990000</v>
       </c>
-      <c r="J11" s="31" t="s">
+      <c r="J11" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="s">
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="32" t="s">
+      <c r="M11" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="4">
         <v>9500</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="4">
         <v>300</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="4">
         <v>180000</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="4">
         <v>16000</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="4">
         <v>15000</v>
       </c>
-      <c r="S11" s="33">
+      <c r="S11" s="38">
         <v>16008</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T11" s="6">
         <v>50</v>
       </c>
-      <c r="U11" s="34">
+      <c r="U11" s="39">
         <v>0</v>
       </c>
       <c r="V11" t="s">
         <v>57</v>
       </c>
-      <c r="W11" s="4" t="s">
+      <c r="W11" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X11" s="2">
         <v>0</v>
       </c>
-      <c r="Y11" s="4">
+      <c r="Y11" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="2" customFormat="1">
-      <c r="A12" s="2">
+    <row r="12" s="2" customFormat="1" spans="1:25">
+      <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="40">
         <v>200300</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="40">
         <v>200300001</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="40">
         <v>2</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="35">
         <v>1990000</v>
       </c>
-      <c r="J12" s="36" t="s">
+      <c r="J12" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="2">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="4">
         <v>9500</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="4">
         <v>300</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="4">
         <v>180000</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="4">
         <v>16000</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="4">
         <v>15000</v>
       </c>
-      <c r="S12" s="33">
+      <c r="S12" s="38">
         <v>16008</v>
       </c>
-      <c r="T12" s="5">
+      <c r="T12" s="6">
         <v>50</v>
       </c>
-      <c r="U12" s="34">
+      <c r="U12" s="39">
         <v>0</v>
       </c>
       <c r="V12" t="s">
         <v>61</v>
       </c>
-      <c r="W12" s="4" t="s">
+      <c r="W12" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X12" s="2">
         <v>0</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="Y12" s="8">
         <f t="shared" ref="Y12:Y16" si="2">Y11*10</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="2">
+      <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>2003003</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="32">
         <v>200300</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="32">
         <v>200300001</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="32">
         <v>3</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="35">
         <v>1990000</v>
       </c>
-      <c r="J13" s="31" t="s">
+      <c r="J13" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="M13" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="4">
         <v>9500</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13" s="4">
         <v>300</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="4">
         <v>180000</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="4">
         <v>16000</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="4">
         <v>15000</v>
       </c>
-      <c r="S13" s="33">
+      <c r="S13" s="38">
         <v>16008</v>
       </c>
-      <c r="T13" s="5">
+      <c r="T13" s="6">
         <v>50</v>
       </c>
-      <c r="U13" s="34">
+      <c r="U13" s="39">
         <v>0</v>
       </c>
       <c r="V13" t="s">
         <v>65</v>
       </c>
-      <c r="W13" s="4" t="s">
+      <c r="W13" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X13" s="2">
         <v>0</v>
       </c>
-      <c r="Y13" s="4">
+      <c r="Y13" s="8">
         <f t="shared" si="2"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="2">
+      <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>2004001</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="32">
         <v>200400</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="32">
         <v>200400009</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="28">
-        <v>1</v>
-      </c>
-      <c r="I14" s="30">
+      <c r="H14" s="32">
+        <v>1</v>
+      </c>
+      <c r="I14" s="35">
         <v>1990000</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="s">
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="32" t="s">
+      <c r="M14" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="4">
         <v>9500</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O14" s="4">
         <v>300</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="4">
         <v>180000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="4">
         <v>16000</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="4">
         <v>15000</v>
       </c>
-      <c r="S14" s="33">
+      <c r="S14" s="38">
         <v>16008</v>
       </c>
-      <c r="T14" s="5">
+      <c r="T14" s="6">
         <v>50</v>
       </c>
-      <c r="U14" s="34">
+      <c r="U14" s="39">
         <v>0</v>
       </c>
       <c r="V14" t="s">
         <v>57</v>
       </c>
-      <c r="W14" s="4" t="s">
+      <c r="W14" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X14" s="2">
         <v>0</v>
       </c>
-      <c r="Y14" s="4">
+      <c r="Y14" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="2">
+      <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="40">
         <v>200400</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="40">
         <v>200400009</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="40">
         <v>2</v>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="35">
         <v>1990000</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="32" t="s">
+      <c r="M15" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15" s="4">
         <v>9500</v>
       </c>
-      <c r="O15" s="2">
+      <c r="O15" s="4">
         <v>300</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="4">
         <v>180000</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="4">
         <v>16000</v>
       </c>
-      <c r="R15" s="2">
+      <c r="R15" s="4">
         <v>15000</v>
       </c>
-      <c r="S15" s="33">
+      <c r="S15" s="38">
         <v>16008</v>
       </c>
-      <c r="T15" s="5">
+      <c r="T15" s="6">
         <v>50</v>
       </c>
-      <c r="U15" s="34">
+      <c r="U15" s="39">
         <v>0</v>
       </c>
       <c r="V15" t="s">
         <v>61</v>
       </c>
-      <c r="W15" s="4" t="s">
+      <c r="W15" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X15" s="2">
         <v>0</v>
       </c>
-      <c r="Y15" s="4">
+      <c r="Y15" s="8">
         <f t="shared" si="2"/>
         <v>100000000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" s="2" customFormat="1">
-      <c r="A16" s="2">
+    <row r="16" s="2" customFormat="1" spans="1:25">
+      <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>2004003</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="32">
         <v>200400</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="32">
         <v>200400009</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G16" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="32">
         <v>3</v>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="35">
         <v>1990000</v>
       </c>
-      <c r="J16" s="31" t="s">
+      <c r="J16" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="2">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M16" s="32" t="s">
+      <c r="M16" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="4">
         <v>9500</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16" s="4">
         <v>300</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="4">
         <v>180000</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="4">
         <v>16000</v>
       </c>
-      <c r="R16" s="2">
+      <c r="R16" s="4">
         <v>15000</v>
       </c>
-      <c r="S16" s="33">
+      <c r="S16" s="38">
         <v>16008</v>
       </c>
-      <c r="T16" s="5">
+      <c r="T16" s="6">
         <v>50</v>
       </c>
-      <c r="U16" s="34">
+      <c r="U16" s="39">
         <v>0</v>
       </c>
       <c r="V16" t="s">
         <v>65</v>
       </c>
-      <c r="W16" s="4" t="s">
+      <c r="W16" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X16" s="2">
         <v>0</v>
       </c>
-      <c r="Y16" s="4">
+      <c r="Y16" s="8">
         <f t="shared" si="2"/>
         <v>1000000000</v>
       </c>
     </row>
-    <row r="17" spans="1:25" s="2" customFormat="1">
-      <c r="A17" s="2">
+    <row r="17" s="2" customFormat="1" spans="1:25">
+      <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>2005001</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="32">
         <v>200500</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="32">
         <v>200500025</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="28">
-        <v>1</v>
-      </c>
-      <c r="I17" s="30">
+      <c r="H17" s="32">
+        <v>1</v>
+      </c>
+      <c r="I17" s="35">
         <v>1990000</v>
       </c>
-      <c r="J17" s="31" t="s">
+      <c r="J17" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K17" s="2">
-        <v>1</v>
-      </c>
-      <c r="L17" s="2" t="s">
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="32" t="s">
+      <c r="M17" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="4">
         <v>9500</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17" s="4">
         <v>300</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="4">
         <v>180000</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="4">
         <v>16000</v>
       </c>
-      <c r="R17" s="2">
+      <c r="R17" s="4">
         <v>15000</v>
       </c>
-      <c r="S17" s="33">
+      <c r="S17" s="38">
         <v>16008</v>
       </c>
-      <c r="T17" s="5">
+      <c r="T17" s="6">
         <v>48</v>
       </c>
-      <c r="U17" s="34">
+      <c r="U17" s="39">
         <v>0</v>
       </c>
       <c r="V17" t="s">
         <v>57</v>
       </c>
-      <c r="W17" s="4" t="s">
+      <c r="W17" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
       </c>
-      <c r="Y17" s="4">
+      <c r="Y17" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="2">
+      <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="40">
         <v>200500</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="40">
         <v>200500025</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="40">
         <v>2</v>
       </c>
-      <c r="I18" s="30">
+      <c r="I18" s="35">
         <v>1990000</v>
       </c>
-      <c r="J18" s="36" t="s">
+      <c r="J18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
-      <c r="L18" s="2" t="s">
+      <c r="K18" s="4">
+        <v>1</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="32" t="s">
+      <c r="M18" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="4">
         <v>9500</v>
       </c>
-      <c r="O18" s="2">
+      <c r="O18" s="4">
         <v>300</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="4">
         <v>180000</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="4">
         <v>16000</v>
       </c>
-      <c r="R18" s="2">
+      <c r="R18" s="4">
         <v>15000</v>
       </c>
-      <c r="S18" s="33">
+      <c r="S18" s="38">
         <v>16008</v>
       </c>
-      <c r="T18" s="5">
+      <c r="T18" s="6">
         <v>48</v>
       </c>
-      <c r="U18" s="34">
+      <c r="U18" s="39">
         <v>0</v>
       </c>
       <c r="V18" t="s">
         <v>61</v>
       </c>
-      <c r="W18" s="4" t="s">
+      <c r="W18" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X18" s="2">
         <v>0</v>
       </c>
-      <c r="Y18" s="4">
+      <c r="Y18" s="8">
         <f t="shared" ref="Y18:Y22" si="3">Y17*10</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="2">
+      <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>2005003</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="32">
         <v>200500</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="32">
         <v>200500025</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="32">
         <v>3</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="35">
         <v>1990000</v>
       </c>
-      <c r="J19" s="31" t="s">
+      <c r="J19" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="s">
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="32" t="s">
+      <c r="M19" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="N19" s="2">
+      <c r="N19" s="4">
         <v>9500</v>
       </c>
-      <c r="O19" s="2">
+      <c r="O19" s="4">
         <v>300</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="4">
         <v>180000</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="4">
         <v>16000</v>
       </c>
-      <c r="R19" s="2">
+      <c r="R19" s="4">
         <v>15000</v>
       </c>
-      <c r="S19" s="33">
+      <c r="S19" s="38">
         <v>16008</v>
       </c>
-      <c r="T19" s="5">
+      <c r="T19" s="6">
         <v>48</v>
       </c>
-      <c r="U19" s="34">
+      <c r="U19" s="39">
         <v>0</v>
       </c>
       <c r="V19" t="s">
         <v>65</v>
       </c>
-      <c r="W19" s="4" t="s">
+      <c r="W19" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X19" s="2">
         <v>0</v>
       </c>
-      <c r="Y19" s="4">
+      <c r="Y19" s="8">
         <f t="shared" si="3"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="2">
+      <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>2006001</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="32">
         <v>200600</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="32">
         <v>200600001</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="28">
-        <v>1</v>
-      </c>
-      <c r="I20" s="30">
+      <c r="H20" s="32">
+        <v>1</v>
+      </c>
+      <c r="I20" s="35">
         <v>1990000</v>
       </c>
-      <c r="J20" s="31" t="s">
+      <c r="J20" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K20" s="2">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="s">
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="32" t="s">
+      <c r="M20" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="4">
         <v>9500</v>
       </c>
-      <c r="O20" s="2">
+      <c r="O20" s="4">
         <v>300</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="4">
         <v>180000</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="4">
         <v>16000</v>
       </c>
-      <c r="R20" s="2">
+      <c r="R20" s="4">
         <v>15000</v>
       </c>
-      <c r="S20" s="33">
+      <c r="S20" s="38">
         <v>16008</v>
       </c>
-      <c r="T20" s="5">
+      <c r="T20" s="6">
         <v>20</v>
       </c>
-      <c r="U20" s="34">
+      <c r="U20" s="39">
         <v>0</v>
       </c>
       <c r="V20" t="s">
         <v>57</v>
       </c>
-      <c r="W20" s="4" t="s">
+      <c r="W20" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X20" s="2">
         <v>0</v>
       </c>
-      <c r="Y20" s="4">
+      <c r="Y20" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="21" spans="1:25" s="2" customFormat="1">
-      <c r="A21" s="2">
+    <row r="21" s="2" customFormat="1" spans="1:25">
+      <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="40">
         <v>200600</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="40">
         <v>200600001</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="40">
         <v>2</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="35">
         <v>1990000</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K21" s="2">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="s">
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="32" t="s">
+      <c r="M21" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N21" s="4">
         <v>9500</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="4">
         <v>300</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="4">
         <v>180000</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="4">
         <v>16000</v>
       </c>
-      <c r="R21" s="2">
+      <c r="R21" s="4">
         <v>15000</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="38">
         <v>16008</v>
       </c>
-      <c r="T21" s="5">
+      <c r="T21" s="6">
         <v>20</v>
       </c>
-      <c r="U21" s="34">
+      <c r="U21" s="39">
         <v>0</v>
       </c>
       <c r="V21" t="s">
         <v>61</v>
       </c>
-      <c r="W21" s="4" t="s">
+      <c r="W21" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X21" s="2">
         <v>0</v>
       </c>
-      <c r="Y21" s="4">
+      <c r="Y21" s="8">
         <f t="shared" si="3"/>
         <v>100000000</v>
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="2">
+      <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>2006003</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="32">
         <v>200600</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="32">
         <v>200600001</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G22" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="32">
         <v>3</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="35">
         <v>1990000</v>
       </c>
-      <c r="J22" s="31" t="s">
+      <c r="J22" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K22" s="2">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="s">
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M22" s="32" t="s">
+      <c r="M22" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N22" s="4">
         <v>9500</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22" s="4">
         <v>300</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="4">
         <v>180000</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="4">
         <v>16000</v>
       </c>
-      <c r="R22" s="2">
+      <c r="R22" s="4">
         <v>15000</v>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="38">
         <v>16008</v>
       </c>
-      <c r="T22" s="5">
+      <c r="T22" s="6">
         <v>20</v>
       </c>
-      <c r="U22" s="34">
+      <c r="U22" s="39">
         <v>0</v>
       </c>
       <c r="V22" t="s">
         <v>65</v>
       </c>
-      <c r="W22" s="4" t="s">
+      <c r="W22" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X22" s="2">
         <v>0</v>
       </c>
-      <c r="Y22" s="4">
+      <c r="Y22" s="8">
         <f t="shared" si="3"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="2">
+      <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>2007001</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="32">
         <v>200700</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="32">
         <v>200700001</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H23" s="28">
-        <v>1</v>
-      </c>
-      <c r="I23" s="30">
+      <c r="H23" s="32">
+        <v>1</v>
+      </c>
+      <c r="I23" s="35">
         <v>1990000</v>
       </c>
-      <c r="J23" s="31" t="s">
+      <c r="J23" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="2" t="s">
+      <c r="K23" s="4">
+        <v>1</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="32" t="s">
+      <c r="M23" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="4">
         <v>9500</v>
       </c>
-      <c r="O23" s="2">
+      <c r="O23" s="4">
         <v>300</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="4">
         <v>180000</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="4">
         <v>16000</v>
       </c>
-      <c r="R23" s="2">
+      <c r="R23" s="4">
         <v>15000</v>
       </c>
-      <c r="S23" s="33">
+      <c r="S23" s="38">
         <v>16008</v>
       </c>
-      <c r="T23" s="5">
+      <c r="T23" s="6">
         <v>30</v>
       </c>
-      <c r="U23" s="34">
+      <c r="U23" s="39">
         <v>1</v>
       </c>
       <c r="V23" t="s">
         <v>57</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="W23" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X23" s="2">
         <v>0</v>
       </c>
-      <c r="Y23" s="4">
+      <c r="Y23" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="2">
+      <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="40">
         <v>200700</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="40">
         <v>200700001</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="40">
         <v>2</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="35">
         <v>1990000</v>
       </c>
-      <c r="J24" s="36" t="s">
+      <c r="J24" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K24" s="2">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="s">
+      <c r="K24" s="4">
+        <v>1</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24" s="4">
         <v>9500</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24" s="4">
         <v>300</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="4">
         <v>180000</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="4">
         <v>16000</v>
       </c>
-      <c r="R24" s="2">
+      <c r="R24" s="4">
         <v>15000</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="38">
         <v>16008</v>
       </c>
-      <c r="T24" s="5">
+      <c r="T24" s="6">
         <v>30</v>
       </c>
-      <c r="U24" s="34">
+      <c r="U24" s="39">
         <v>1</v>
       </c>
       <c r="V24" t="s">
         <v>61</v>
       </c>
-      <c r="W24" s="4" t="s">
+      <c r="W24" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X24" s="2">
         <v>0</v>
       </c>
-      <c r="Y24" s="4">
+      <c r="Y24" s="8">
         <f t="shared" ref="Y24:Y28" si="4">Y23*10</f>
         <v>100000000</v>
       </c>
     </row>
-    <row r="25" spans="1:25" s="2" customFormat="1">
-      <c r="A25" s="2">
+    <row r="25" s="2" customFormat="1" spans="1:25">
+      <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>2007003</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="32">
         <v>200700</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="32">
         <v>200700001</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="29" t="s">
+      <c r="G25" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="32">
         <v>3</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="35">
         <v>1990000</v>
       </c>
-      <c r="J25" s="31" t="s">
+      <c r="J25" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K25" s="2">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2" t="s">
+      <c r="K25" s="4">
+        <v>1</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M25" s="32" t="s">
+      <c r="M25" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25" s="4">
         <v>9500</v>
       </c>
-      <c r="O25" s="2">
+      <c r="O25" s="4">
         <v>300</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="4">
         <v>180000</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="4">
         <v>16000</v>
       </c>
-      <c r="R25" s="2">
+      <c r="R25" s="4">
         <v>15000</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="38">
         <v>16008</v>
       </c>
-      <c r="T25" s="5">
+      <c r="T25" s="6">
         <v>30</v>
       </c>
-      <c r="U25" s="34">
+      <c r="U25" s="39">
         <v>1</v>
       </c>
       <c r="V25" t="s">
         <v>65</v>
       </c>
-      <c r="W25" s="4" t="s">
+      <c r="W25" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X25" s="2">
         <v>0</v>
       </c>
-      <c r="Y25" s="4">
+      <c r="Y25" s="8">
         <f t="shared" si="4"/>
         <v>1000000000</v>
       </c>
     </row>
-    <row r="26" spans="1:25" s="2" customFormat="1">
-      <c r="A26" s="2">
+    <row r="26" s="2" customFormat="1" spans="1:25">
+      <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>2008001</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="32">
         <v>200800</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="32">
         <v>200800001</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="29" t="s">
+      <c r="G26" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="28">
-        <v>1</v>
-      </c>
-      <c r="I26" s="30">
+      <c r="H26" s="32">
+        <v>1</v>
+      </c>
+      <c r="I26" s="35">
         <v>1990000</v>
       </c>
-      <c r="J26" s="31" t="s">
+      <c r="J26" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K26" s="2">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2" t="s">
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="32" t="s">
+      <c r="M26" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="4">
         <v>9500</v>
       </c>
-      <c r="O26" s="2">
+      <c r="O26" s="4">
         <v>300</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="4">
         <v>180000</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="4">
         <v>16000</v>
       </c>
-      <c r="R26" s="2">
+      <c r="R26" s="4">
         <v>15000</v>
       </c>
-      <c r="S26" s="33">
+      <c r="S26" s="38">
         <v>16008</v>
       </c>
-      <c r="T26" s="5">
+      <c r="T26" s="6">
         <v>20</v>
       </c>
-      <c r="U26" s="34">
+      <c r="U26" s="39">
         <v>0</v>
       </c>
       <c r="V26" t="s">
         <v>57</v>
       </c>
-      <c r="W26" s="4" t="s">
+      <c r="W26" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X26" s="2">
         <v>0</v>
       </c>
-      <c r="Y26" s="4">
+      <c r="Y26" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="27" spans="1:25" s="2" customFormat="1">
-      <c r="A27" s="2">
+    <row r="27" s="2" customFormat="1" spans="1:25">
+      <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>2008002</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="32">
         <v>200800</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="32">
         <v>200800001</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="40">
         <v>2</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="35">
         <v>1990000</v>
       </c>
-      <c r="J27" s="36" t="s">
+      <c r="J27" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K27" s="2">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2" t="s">
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="32" t="s">
+      <c r="M27" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="N27" s="2">
+      <c r="N27" s="4">
         <v>9500</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O27" s="4">
         <v>300</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="4">
         <v>180000</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="4">
         <v>16000</v>
       </c>
-      <c r="R27" s="2">
+      <c r="R27" s="4">
         <v>15000</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="38">
         <v>16008</v>
       </c>
-      <c r="T27" s="5">
+      <c r="T27" s="6">
         <v>20</v>
       </c>
-      <c r="U27" s="34">
+      <c r="U27" s="39">
         <v>0</v>
       </c>
       <c r="V27" t="s">
         <v>61</v>
       </c>
-      <c r="W27" s="4" t="s">
+      <c r="W27" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X27" s="2">
         <v>0</v>
       </c>
-      <c r="Y27" s="4">
+      <c r="Y27" s="8">
         <f t="shared" si="4"/>
         <v>100000000</v>
       </c>
     </row>
-    <row r="28" spans="1:25" s="2" customFormat="1">
-      <c r="A28" s="2">
+    <row r="28" s="2" customFormat="1" spans="1:25">
+      <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>2008003</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="32">
         <v>200800</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="32">
         <v>200800001</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="E28" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G28" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="32">
         <v>3</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="35">
         <v>1990000</v>
       </c>
-      <c r="J28" s="31" t="s">
+      <c r="J28" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K28" s="2">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2" t="s">
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M28" s="32" t="s">
+      <c r="M28" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28" s="4">
         <v>9500</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O28" s="4">
         <v>300</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="4">
         <v>180000</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="4">
         <v>16000</v>
       </c>
-      <c r="R28" s="2">
+      <c r="R28" s="4">
         <v>15000</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="38">
         <v>16008</v>
       </c>
-      <c r="T28" s="5">
+      <c r="T28" s="6">
         <v>20</v>
       </c>
-      <c r="U28" s="34">
+      <c r="U28" s="39">
         <v>0</v>
       </c>
       <c r="V28" t="s">
         <v>65</v>
       </c>
-      <c r="W28" s="4" t="s">
+      <c r="W28" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X28" s="2">
         <v>0</v>
       </c>
-      <c r="Y28" s="4">
+      <c r="Y28" s="8">
         <f t="shared" si="4"/>
         <v>1000000000</v>
       </c>
     </row>
-    <row r="29" spans="1:25" s="2" customFormat="1">
-      <c r="A29" s="2">
+    <row r="29" s="2" customFormat="1" spans="1:25">
+      <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="39">
+      <c r="B29" s="44">
         <v>200900</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="32">
         <v>200900001</v>
       </c>
-      <c r="E29" s="37" t="s">
+      <c r="E29" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="29" t="s">
+      <c r="G29" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H29" s="28">
-        <v>1</v>
-      </c>
-      <c r="I29" s="30">
+      <c r="H29" s="32">
+        <v>1</v>
+      </c>
+      <c r="I29" s="35">
         <v>1990000</v>
       </c>
-      <c r="J29" s="31" t="s">
+      <c r="J29" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="40">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="s">
+      <c r="K29" s="45">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M29" s="32" t="s">
+      <c r="M29" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="N29" s="2">
+      <c r="N29" s="4">
         <v>9500</v>
       </c>
-      <c r="O29" s="2">
+      <c r="O29" s="4">
         <v>300</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="4">
         <v>180000</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="4">
         <v>16000</v>
       </c>
-      <c r="R29" s="2">
+      <c r="R29" s="4">
         <v>15000</v>
       </c>
-      <c r="S29" s="33">
+      <c r="S29" s="38">
         <v>16008</v>
       </c>
-      <c r="T29" s="5">
+      <c r="T29" s="6">
         <v>20</v>
       </c>
-      <c r="U29" s="34">
+      <c r="U29" s="39">
         <v>0</v>
       </c>
       <c r="V29" t="s">
         <v>57</v>
       </c>
-      <c r="W29" s="4" t="s">
+      <c r="W29" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X29" s="2">
         <v>0</v>
       </c>
-      <c r="Y29" s="4">
+      <c r="Y29" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="2">
+      <c r="A30" s="4">
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="46">
         <v>200900</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="40">
         <v>200900001</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="29" t="s">
+      <c r="G30" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="40">
         <v>2</v>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="35">
         <v>1990000</v>
       </c>
-      <c r="J30" s="36" t="s">
+      <c r="J30" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="40">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="s">
+      <c r="K30" s="45">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M30" s="32" t="s">
+      <c r="M30" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="4">
         <v>9500</v>
       </c>
-      <c r="O30" s="2">
+      <c r="O30" s="4">
         <v>300</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="4">
         <v>180000</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="4">
         <v>16000</v>
       </c>
-      <c r="R30" s="2">
+      <c r="R30" s="4">
         <v>15000</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="38">
         <v>16008</v>
       </c>
-      <c r="T30" s="5">
+      <c r="T30" s="6">
         <v>20</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="39">
         <v>0</v>
       </c>
       <c r="V30" t="s">
         <v>61</v>
       </c>
-      <c r="W30" s="4" t="s">
+      <c r="W30" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X30" s="2">
         <v>0</v>
       </c>
-      <c r="Y30" s="4">
+      <c r="Y30" s="8">
         <f t="shared" ref="Y30:Y34" si="5">Y29*10</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="2">
+      <c r="A31" s="4">
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="39">
+      <c r="B31" s="47">
         <v>200900</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="48">
         <v>200900001</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="G31" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="32">
         <v>3</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="35">
         <v>1990000</v>
       </c>
-      <c r="J31" s="31" t="s">
+      <c r="J31" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="40">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="s">
+      <c r="K31" s="45">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M31" s="32" t="s">
+      <c r="M31" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31" s="4">
         <v>9500</v>
       </c>
-      <c r="O31" s="2">
+      <c r="O31" s="4">
         <v>300</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="4">
         <v>180000</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="4">
         <v>16000</v>
       </c>
-      <c r="R31" s="2">
+      <c r="R31" s="4">
         <v>15000</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="38">
         <v>16008</v>
       </c>
-      <c r="T31" s="5">
+      <c r="T31" s="6">
         <v>20</v>
       </c>
-      <c r="U31" s="34">
+      <c r="U31" s="39">
         <v>0</v>
       </c>
       <c r="V31" t="s">
         <v>65</v>
       </c>
-      <c r="W31" s="4" t="s">
+      <c r="W31" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X31" s="2">
         <v>0</v>
       </c>
-      <c r="Y31" s="4">
+      <c r="Y31" s="8">
         <f t="shared" si="5"/>
         <v>1000000000</v>
       </c>
     </row>
-    <row r="32" spans="1:25" s="2" customFormat="1">
-      <c r="A32" s="2">
+    <row r="32" s="2" customFormat="1" spans="1:25">
+      <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>2012001</v>
       </c>
-      <c r="B32" s="42">
+      <c r="B32" s="49">
         <v>201200</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="40">
         <v>201200001</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="E32" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="G32" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H32" s="28">
-        <v>1</v>
-      </c>
-      <c r="I32" s="30">
+      <c r="H32" s="32">
+        <v>1</v>
+      </c>
+      <c r="I32" s="35">
         <v>1990000</v>
       </c>
-      <c r="J32" s="31" t="s">
+      <c r="J32" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="40">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="s">
+      <c r="K32" s="45">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M32" s="32" t="s">
+      <c r="M32" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="N32" s="2">
+      <c r="N32" s="4">
         <v>9500</v>
       </c>
-      <c r="O32" s="2">
+      <c r="O32" s="4">
         <v>300</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="4">
         <v>180000</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="4">
         <v>16000</v>
       </c>
-      <c r="R32" s="2">
+      <c r="R32" s="4">
         <v>15000</v>
       </c>
-      <c r="S32" s="33">
+      <c r="S32" s="38">
         <v>16008</v>
       </c>
-      <c r="T32" s="5">
+      <c r="T32" s="6">
         <v>12</v>
       </c>
-      <c r="U32" s="34">
+      <c r="U32" s="39">
         <v>0</v>
       </c>
       <c r="V32" t="s">
         <v>57</v>
       </c>
-      <c r="W32" s="4" t="s">
+      <c r="W32" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X32" s="2">
         <v>0</v>
       </c>
-      <c r="Y32" s="4">
+      <c r="Y32" s="8">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
-      <c r="A33" s="2">
+    <row r="33" customFormat="1" spans="1:25">
+      <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>2012002</v>
       </c>
-      <c r="B33" s="42">
+      <c r="B33" s="49">
         <v>201200</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="40">
         <v>201200001</v>
       </c>
-      <c r="E33" s="35" t="s">
+      <c r="E33" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="50" t="s">
+      <c r="F33" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="29" t="s">
+      <c r="G33" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="40">
         <v>2</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="35">
         <v>1990000</v>
       </c>
-      <c r="J33" s="36" t="s">
+      <c r="J33" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="40">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2" t="s">
+      <c r="K33" s="45">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="32" t="s">
+      <c r="M33" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="N33" s="2">
+      <c r="N33" s="4">
         <v>9500</v>
       </c>
-      <c r="O33" s="2">
+      <c r="O33" s="4">
         <v>300</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="4">
         <v>180000</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="4">
         <v>16000</v>
       </c>
-      <c r="R33" s="2">
+      <c r="R33" s="4">
         <v>15000</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="38">
         <v>16008</v>
       </c>
-      <c r="T33" s="5">
+      <c r="T33" s="6">
         <v>12</v>
       </c>
-      <c r="U33" s="34">
+      <c r="U33" s="39">
         <v>0</v>
       </c>
       <c r="V33" t="s">
         <v>61</v>
       </c>
-      <c r="W33" s="4" t="s">
+      <c r="W33" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X33" s="2">
         <v>0</v>
       </c>
-      <c r="Y33" s="4">
+      <c r="Y33" s="8">
         <f t="shared" si="5"/>
         <v>100000000</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="2">
+    <row r="34" customFormat="1" spans="1:25">
+      <c r="A34" s="4">
         <f t="shared" si="0"/>
         <v>2012003</v>
       </c>
-      <c r="B34" s="42">
+      <c r="B34" s="49">
         <v>201200</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="40">
         <v>201200001</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H34" s="28">
+      <c r="H34" s="32">
         <v>3</v>
       </c>
-      <c r="I34" s="30">
+      <c r="I34" s="35">
         <v>1990000</v>
       </c>
-      <c r="J34" s="31" t="s">
+      <c r="J34" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="40">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2" t="s">
+      <c r="K34" s="45">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M34" s="32" t="s">
+      <c r="M34" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="N34" s="2">
+      <c r="N34" s="4">
         <v>9500</v>
       </c>
-      <c r="O34" s="2">
+      <c r="O34" s="4">
         <v>300</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="4">
         <v>180000</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="4">
         <v>16000</v>
       </c>
-      <c r="R34" s="2">
+      <c r="R34" s="4">
         <v>15000</v>
       </c>
-      <c r="S34" s="33">
+      <c r="S34" s="38">
         <v>16008</v>
       </c>
-      <c r="T34" s="5">
+      <c r="T34" s="6">
         <v>12</v>
       </c>
-      <c r="U34" s="34">
+      <c r="U34" s="39">
         <v>0</v>
       </c>
       <c r="V34" t="s">
         <v>65</v>
       </c>
-      <c r="W34" s="4" t="s">
+      <c r="W34" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X34" s="2">
         <v>0</v>
       </c>
-      <c r="Y34" s="4">
+      <c r="Y34" s="8">
         <f t="shared" si="5"/>
         <v>1000000000</v>
       </c>
     </row>
-    <row r="35" spans="1:25" s="3" customFormat="1">
-      <c r="A35" s="43">
+    <row r="35" s="3" customFormat="1" spans="1:25">
+      <c r="A35" s="50">
         <v>20010010</v>
       </c>
       <c r="B35" s="3">
         <v>200100</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="C35" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="51">
         <v>200100038</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="45" t="s">
+      <c r="G35" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="44">
-        <v>10</v>
-      </c>
-      <c r="I35" s="44">
+      <c r="H35" s="51">
+        <v>1</v>
+      </c>
+      <c r="I35" s="51">
         <v>1980000</v>
       </c>
-      <c r="J35" s="31" t="s">
+      <c r="J35" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K35" s="3">
@@ -4008,10 +4615,10 @@
       <c r="L35" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M35" s="46" t="s">
+      <c r="M35" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="N35" s="2">
+      <c r="N35" s="4">
         <v>9500</v>
       </c>
       <c r="O35" s="3">
@@ -4026,55 +4633,55 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="47">
+      <c r="S35" s="55">
         <v>16008</v>
       </c>
-      <c r="T35" s="43">
+      <c r="T35" s="50">
         <v>48</v>
       </c>
-      <c r="U35" s="48">
+      <c r="U35" s="56">
         <v>0</v>
       </c>
       <c r="V35" t="s">
         <v>57</v>
       </c>
-      <c r="W35" s="4" t="s">
+      <c r="W35" s="8" t="s">
         <v>86</v>
       </c>
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="49"/>
+      <c r="Y35" s="57"/>
     </row>
-    <row r="36" spans="1:25" s="3" customFormat="1">
-      <c r="A36" s="43">
+    <row r="36" s="3" customFormat="1" spans="1:25">
+      <c r="A36" s="50">
         <v>20010011</v>
       </c>
       <c r="B36" s="3">
         <v>200100</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="C36" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="51">
         <v>200100038</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="51" t="s">
+      <c r="F36" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="45" t="s">
+      <c r="G36" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H36" s="44">
-        <v>11</v>
-      </c>
-      <c r="I36" s="44">
+      <c r="H36" s="51">
+        <v>2</v>
+      </c>
+      <c r="I36" s="51">
         <v>1980000</v>
       </c>
-      <c r="J36" s="36" t="s">
+      <c r="J36" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K36" s="3">
@@ -4083,10 +4690,10 @@
       <c r="L36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M36" s="46" t="s">
+      <c r="M36" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="N36" s="2">
+      <c r="N36" s="4">
         <v>9500</v>
       </c>
       <c r="O36" s="3">
@@ -4101,55 +4708,55 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="47">
+      <c r="S36" s="55">
         <v>16008</v>
       </c>
-      <c r="T36" s="43">
+      <c r="T36" s="50">
         <v>48</v>
       </c>
-      <c r="U36" s="48">
+      <c r="U36" s="56">
         <v>0</v>
       </c>
       <c r="V36" t="s">
         <v>61</v>
       </c>
-      <c r="W36" s="4" t="s">
+      <c r="W36" s="8" t="s">
         <v>87</v>
       </c>
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="49"/>
+      <c r="Y36" s="57"/>
     </row>
-    <row r="37" spans="1:25" s="3" customFormat="1">
-      <c r="A37" s="43">
+    <row r="37" s="3" customFormat="1" spans="1:25">
+      <c r="A37" s="50">
         <v>20010012</v>
       </c>
       <c r="B37" s="3">
         <v>200100</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="C37" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="51">
         <v>200100038</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E37" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="51" t="s">
+      <c r="F37" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="45" t="s">
+      <c r="G37" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H37" s="44">
-        <v>12</v>
-      </c>
-      <c r="I37" s="44">
+      <c r="H37" s="51">
+        <v>3</v>
+      </c>
+      <c r="I37" s="51">
         <v>1980000</v>
       </c>
-      <c r="J37" s="31" t="s">
+      <c r="J37" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K37" s="3">
@@ -4158,10 +4765,10 @@
       <c r="L37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M37" s="46" t="s">
+      <c r="M37" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="N37" s="2">
+      <c r="N37" s="4">
         <v>9500</v>
       </c>
       <c r="O37" s="3">
@@ -4176,28 +4783,28 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="47">
+      <c r="S37" s="55">
         <v>16008</v>
       </c>
-      <c r="T37" s="43">
+      <c r="T37" s="50">
         <v>48</v>
       </c>
-      <c r="U37" s="48">
+      <c r="U37" s="56">
         <v>0</v>
       </c>
       <c r="V37" t="s">
         <v>65</v>
       </c>
-      <c r="W37" s="4" t="s">
+      <c r="W37" s="8" t="s">
         <v>88</v>
       </c>
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="49"/>
+      <c r="Y37" s="57"/>
     </row>
-    <row r="38" spans="1:25" s="3" customFormat="1">
-      <c r="A38" s="43">
+    <row r="38" s="3" customFormat="1" spans="1:25">
+      <c r="A38" s="50">
         <v>20010110</v>
       </c>
       <c r="B38" s="3">
@@ -4212,19 +4819,19 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="52" t="s">
+      <c r="F38" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G38" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H38" s="44">
-        <v>10</v>
-      </c>
-      <c r="I38" s="44">
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="51">
         <v>1980000</v>
       </c>
-      <c r="J38" s="31" t="s">
+      <c r="J38" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K38" s="3">
@@ -4233,10 +4840,10 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="46" t="s">
+      <c r="M38" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="N38" s="2">
+      <c r="N38" s="4">
         <v>9500</v>
       </c>
       <c r="O38" s="3">
@@ -4254,25 +4861,25 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="43">
+      <c r="T38" s="50">
         <v>48</v>
       </c>
-      <c r="U38" s="48">
+      <c r="U38" s="56">
         <v>0</v>
       </c>
       <c r="V38" t="s">
         <v>57</v>
       </c>
-      <c r="W38" s="4" t="s">
+      <c r="W38" s="8" t="s">
         <v>89</v>
       </c>
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="49"/>
+      <c r="Y38" s="57"/>
     </row>
-    <row r="39" spans="1:25" s="3" customFormat="1">
-      <c r="A39" s="43">
+    <row r="39" s="3" customFormat="1" spans="1:25">
+      <c r="A39" s="50">
         <v>20010111</v>
       </c>
       <c r="B39" s="3">
@@ -4287,19 +4894,19 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="52" t="s">
+      <c r="F39" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="45" t="s">
+      <c r="G39" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H39" s="44">
-        <v>11</v>
-      </c>
-      <c r="I39" s="44">
+      <c r="H39" s="3">
+        <v>2</v>
+      </c>
+      <c r="I39" s="51">
         <v>1980000</v>
       </c>
-      <c r="J39" s="36" t="s">
+      <c r="J39" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K39" s="3">
@@ -4308,10 +4915,10 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="46" t="s">
+      <c r="M39" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="N39" s="2">
+      <c r="N39" s="4">
         <v>9500</v>
       </c>
       <c r="O39" s="3">
@@ -4329,25 +4936,25 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="43">
+      <c r="T39" s="50">
         <v>48</v>
       </c>
-      <c r="U39" s="48">
+      <c r="U39" s="56">
         <v>0</v>
       </c>
       <c r="V39" t="s">
         <v>61</v>
       </c>
-      <c r="W39" s="4" t="s">
+      <c r="W39" s="8" t="s">
         <v>90</v>
       </c>
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="49"/>
+      <c r="Y39" s="57"/>
     </row>
-    <row r="40" spans="1:25" s="3" customFormat="1">
-      <c r="A40" s="43">
+    <row r="40" s="3" customFormat="1" spans="1:25">
+      <c r="A40" s="50">
         <v>20010112</v>
       </c>
       <c r="B40" s="3">
@@ -4362,19 +4969,19 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="52" t="s">
+      <c r="F40" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="45" t="s">
+      <c r="G40" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H40" s="44">
-        <v>12</v>
-      </c>
-      <c r="I40" s="44">
+      <c r="H40" s="3">
+        <v>3</v>
+      </c>
+      <c r="I40" s="51">
         <v>1980000</v>
       </c>
-      <c r="J40" s="31" t="s">
+      <c r="J40" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K40" s="3">
@@ -4383,10 +4990,10 @@
       <c r="L40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="46" t="s">
+      <c r="M40" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="N40" s="2">
+      <c r="N40" s="4">
         <v>9500</v>
       </c>
       <c r="O40" s="3">
@@ -4404,25 +5011,25 @@
       <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="43">
+      <c r="T40" s="50">
         <v>48</v>
       </c>
-      <c r="U40" s="48">
+      <c r="U40" s="56">
         <v>0</v>
       </c>
       <c r="V40" t="s">
         <v>65</v>
       </c>
-      <c r="W40" s="4" t="s">
+      <c r="W40" s="8" t="s">
         <v>91</v>
       </c>
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="49"/>
+      <c r="Y40" s="57"/>
     </row>
-    <row r="41" spans="1:25" s="3" customFormat="1">
-      <c r="A41" s="43">
+    <row r="41" s="3" customFormat="1" spans="1:25">
+      <c r="A41" s="50">
         <v>20030010</v>
       </c>
       <c r="B41" s="3">
@@ -4437,19 +5044,19 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="52" t="s">
+      <c r="F41" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="45" t="s">
+      <c r="G41" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H41" s="44">
-        <v>10</v>
-      </c>
-      <c r="I41" s="44">
+      <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="I41" s="51">
         <v>1980000</v>
       </c>
-      <c r="J41" s="31" t="s">
+      <c r="J41" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K41" s="3">
@@ -4458,10 +5065,10 @@
       <c r="L41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="46" t="s">
+      <c r="M41" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="N41" s="2">
+      <c r="N41" s="4">
         <v>9500</v>
       </c>
       <c r="O41" s="3">
@@ -4479,25 +5086,25 @@
       <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="43">
+      <c r="T41" s="50">
         <v>50</v>
       </c>
-      <c r="U41" s="48">
+      <c r="U41" s="56">
         <v>0</v>
       </c>
       <c r="V41" t="s">
         <v>57</v>
       </c>
-      <c r="W41" s="4" t="s">
+      <c r="W41" s="8" t="s">
         <v>92</v>
       </c>
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="49"/>
+      <c r="Y41" s="57"/>
     </row>
-    <row r="42" spans="1:25" s="3" customFormat="1">
-      <c r="A42" s="43">
+    <row r="42" s="3" customFormat="1" spans="1:25">
+      <c r="A42" s="50">
         <v>20030011</v>
       </c>
       <c r="B42" s="3">
@@ -4512,19 +5119,19 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="52" t="s">
+      <c r="F42" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="45" t="s">
+      <c r="G42" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H42" s="44">
-        <v>11</v>
-      </c>
-      <c r="I42" s="44">
+      <c r="H42" s="3">
+        <v>2</v>
+      </c>
+      <c r="I42" s="51">
         <v>1980000</v>
       </c>
-      <c r="J42" s="36" t="s">
+      <c r="J42" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K42" s="3">
@@ -4533,10 +5140,10 @@
       <c r="L42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="46" t="s">
+      <c r="M42" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="N42" s="2">
+      <c r="N42" s="4">
         <v>9500</v>
       </c>
       <c r="O42" s="3">
@@ -4554,25 +5161,25 @@
       <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="43">
+      <c r="T42" s="50">
         <v>50</v>
       </c>
-      <c r="U42" s="48">
+      <c r="U42" s="56">
         <v>0</v>
       </c>
       <c r="V42" t="s">
         <v>61</v>
       </c>
-      <c r="W42" s="4" t="s">
+      <c r="W42" s="8" t="s">
         <v>93</v>
       </c>
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="49"/>
+      <c r="Y42" s="57"/>
     </row>
-    <row r="43" spans="1:25" s="3" customFormat="1">
-      <c r="A43" s="43">
+    <row r="43" s="3" customFormat="1" spans="1:25">
+      <c r="A43" s="50">
         <v>20030012</v>
       </c>
       <c r="B43" s="3">
@@ -4587,67 +5194,67 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="52" t="s">
+      <c r="F43" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="45" t="s">
+      <c r="G43" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H43" s="44">
-        <v>12</v>
-      </c>
-      <c r="I43" s="44">
+      <c r="H43" s="3">
+        <v>3</v>
+      </c>
+      <c r="I43" s="51">
         <v>1980000</v>
       </c>
-      <c r="J43" s="31" t="s">
+      <c r="J43" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="s">
+      <c r="K43" s="58">
+        <v>0</v>
+      </c>
+      <c r="L43" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="46" t="s">
+      <c r="M43" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="N43" s="2">
+      <c r="N43" s="4">
         <v>9500</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="58">
         <v>180000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="58">
         <v>16000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="58">
         <v>15000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="S43" s="58">
         <v>16008</v>
       </c>
-      <c r="T43" s="43">
+      <c r="T43" s="50">
         <v>50</v>
       </c>
-      <c r="U43" s="48">
+      <c r="U43" s="56">
         <v>0</v>
       </c>
       <c r="V43" t="s">
         <v>65</v>
       </c>
-      <c r="W43" s="4" t="s">
+      <c r="W43" s="8" t="s">
         <v>94</v>
       </c>
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="49"/>
+      <c r="Y43" s="57"/>
     </row>
-    <row r="44" spans="1:25" s="3" customFormat="1">
-      <c r="A44" s="43">
+    <row r="44" s="3" customFormat="1" spans="1:25">
+      <c r="A44" s="50">
         <v>20040010</v>
       </c>
       <c r="B44" s="3">
@@ -4662,67 +5269,67 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="52" t="s">
+      <c r="F44" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H44" s="44">
-        <v>10</v>
-      </c>
-      <c r="I44" s="44">
+      <c r="H44" s="3">
+        <v>1</v>
+      </c>
+      <c r="I44" s="51">
         <v>1980000</v>
       </c>
-      <c r="J44" s="31" t="s">
+      <c r="J44" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
+      <c r="K44" s="58">
+        <v>0</v>
+      </c>
+      <c r="L44" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M44" s="46" t="s">
+      <c r="M44" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="4">
         <v>9500</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="58">
         <v>180000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="58">
         <v>16000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="58">
         <v>15000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="S44" s="58">
         <v>16008</v>
       </c>
-      <c r="T44" s="43">
+      <c r="T44" s="50">
         <v>50</v>
       </c>
-      <c r="U44" s="48">
+      <c r="U44" s="56">
         <v>0</v>
       </c>
       <c r="V44" t="s">
         <v>57</v>
       </c>
-      <c r="W44" s="4" t="s">
+      <c r="W44" s="8" t="s">
         <v>95</v>
       </c>
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="49"/>
+      <c r="Y44" s="57"/>
     </row>
-    <row r="45" spans="1:25" s="3" customFormat="1">
-      <c r="A45" s="43">
+    <row r="45" s="3" customFormat="1" spans="1:25">
+      <c r="A45" s="50">
         <v>20040011</v>
       </c>
       <c r="B45" s="3">
@@ -4737,67 +5344,67 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="52" t="s">
+      <c r="F45" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="45" t="s">
+      <c r="G45" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H45" s="44">
-        <v>11</v>
-      </c>
-      <c r="I45" s="44">
+      <c r="H45" s="3">
+        <v>2</v>
+      </c>
+      <c r="I45" s="51">
         <v>1980000</v>
       </c>
-      <c r="J45" s="36" t="s">
+      <c r="J45" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="s">
+      <c r="K45" s="58">
+        <v>0</v>
+      </c>
+      <c r="L45" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M45" s="46" t="s">
+      <c r="M45" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="N45" s="2">
+      <c r="N45" s="4">
         <v>9500</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="58">
         <v>180000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="58">
         <v>16000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="58">
         <v>15000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="58">
         <v>16008</v>
       </c>
-      <c r="T45" s="43">
+      <c r="T45" s="50">
         <v>50</v>
       </c>
-      <c r="U45" s="48">
+      <c r="U45" s="56">
         <v>0</v>
       </c>
       <c r="V45" t="s">
         <v>61</v>
       </c>
-      <c r="W45" s="4" t="s">
+      <c r="W45" s="8" t="s">
         <v>96</v>
       </c>
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="49"/>
+      <c r="Y45" s="57"/>
     </row>
-    <row r="46" spans="1:25" s="3" customFormat="1">
-      <c r="A46" s="43">
+    <row r="46" s="3" customFormat="1" spans="1:25">
+      <c r="A46" s="50">
         <v>20040012</v>
       </c>
       <c r="B46" s="3">
@@ -4812,67 +5419,67 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="52" t="s">
+      <c r="F46" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="45" t="s">
+      <c r="G46" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H46" s="44">
-        <v>12</v>
-      </c>
-      <c r="I46" s="44">
+      <c r="H46" s="3">
+        <v>3</v>
+      </c>
+      <c r="I46" s="51">
         <v>1980000</v>
       </c>
-      <c r="J46" s="31" t="s">
+      <c r="J46" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="s">
+      <c r="K46" s="58">
+        <v>0</v>
+      </c>
+      <c r="L46" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M46" s="46" t="s">
+      <c r="M46" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="N46" s="2">
+      <c r="N46" s="4">
         <v>9500</v>
       </c>
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="58">
         <v>180000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="58">
         <v>16000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="58">
         <v>15000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="58">
         <v>16008</v>
       </c>
-      <c r="T46" s="43">
+      <c r="T46" s="50">
         <v>50</v>
       </c>
-      <c r="U46" s="48">
+      <c r="U46" s="56">
         <v>0</v>
       </c>
       <c r="V46" t="s">
         <v>65</v>
       </c>
-      <c r="W46" s="4" t="s">
+      <c r="W46" s="8" t="s">
         <v>97</v>
       </c>
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="49"/>
+      <c r="Y46" s="57"/>
     </row>
-    <row r="47" spans="1:25" s="3" customFormat="1">
-      <c r="A47" s="43">
+    <row r="47" s="3" customFormat="1" spans="1:25">
+      <c r="A47" s="50">
         <v>20050010</v>
       </c>
       <c r="B47" s="3">
@@ -4887,67 +5494,67 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="52" t="s">
+      <c r="F47" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="45" t="s">
+      <c r="G47" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H47" s="44">
-        <v>10</v>
-      </c>
-      <c r="I47" s="44">
+      <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="I47" s="51">
         <v>1980000</v>
       </c>
-      <c r="J47" s="31" t="s">
+      <c r="J47" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K47" s="3">
-        <v>1</v>
-      </c>
-      <c r="L47" s="3" t="s">
+      <c r="K47" s="58">
+        <v>1</v>
+      </c>
+      <c r="L47" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M47" s="46" t="s">
+      <c r="M47" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="N47" s="2">
+      <c r="N47" s="4">
         <v>9500</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="58">
         <v>180000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="58">
         <v>16000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="58">
         <v>15000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="58">
         <v>16008</v>
       </c>
-      <c r="T47" s="43">
+      <c r="T47" s="50">
         <v>48</v>
       </c>
-      <c r="U47" s="43">
+      <c r="U47" s="50">
         <v>0</v>
       </c>
       <c r="V47" t="s">
         <v>57</v>
       </c>
-      <c r="W47" s="4" t="s">
+      <c r="W47" s="8" t="s">
         <v>98</v>
       </c>
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="49"/>
+      <c r="Y47" s="57"/>
     </row>
-    <row r="48" spans="1:25" s="3" customFormat="1">
-      <c r="A48" s="43">
+    <row r="48" s="3" customFormat="1" spans="1:25">
+      <c r="A48" s="50">
         <v>20050011</v>
       </c>
       <c r="B48" s="3">
@@ -4962,67 +5569,67 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="52" t="s">
+      <c r="F48" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="45" t="s">
+      <c r="G48" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H48" s="44">
-        <v>11</v>
-      </c>
-      <c r="I48" s="44">
+      <c r="H48" s="3">
+        <v>2</v>
+      </c>
+      <c r="I48" s="51">
         <v>1980000</v>
       </c>
-      <c r="J48" s="36" t="s">
+      <c r="J48" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K48" s="3">
-        <v>1</v>
-      </c>
-      <c r="L48" s="3" t="s">
+      <c r="K48" s="58">
+        <v>1</v>
+      </c>
+      <c r="L48" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M48" s="46" t="s">
+      <c r="M48" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="N48" s="2">
+      <c r="N48" s="4">
         <v>9500</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="58">
         <v>180000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="58">
         <v>16000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="58">
         <v>15000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="58">
         <v>16008</v>
       </c>
-      <c r="T48" s="43">
+      <c r="T48" s="50">
         <v>48</v>
       </c>
-      <c r="U48" s="43">
+      <c r="U48" s="50">
         <v>0</v>
       </c>
       <c r="V48" t="s">
         <v>61</v>
       </c>
-      <c r="W48" s="4" t="s">
+      <c r="W48" s="8" t="s">
         <v>99</v>
       </c>
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="49"/>
+      <c r="Y48" s="57"/>
     </row>
-    <row r="49" spans="1:25" s="3" customFormat="1">
-      <c r="A49" s="43">
+    <row r="49" s="3" customFormat="1" spans="1:25">
+      <c r="A49" s="50">
         <v>20050012</v>
       </c>
       <c r="B49" s="3">
@@ -5037,67 +5644,67 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="52" t="s">
+      <c r="F49" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="45" t="s">
+      <c r="G49" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H49" s="44">
-        <v>12</v>
-      </c>
-      <c r="I49" s="44">
+      <c r="H49" s="3">
+        <v>3</v>
+      </c>
+      <c r="I49" s="51">
         <v>1980000</v>
       </c>
-      <c r="J49" s="31" t="s">
+      <c r="J49" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K49" s="3">
-        <v>1</v>
-      </c>
-      <c r="L49" s="3" t="s">
+      <c r="K49" s="58">
+        <v>1</v>
+      </c>
+      <c r="L49" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M49" s="46" t="s">
+      <c r="M49" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="N49" s="2">
+      <c r="N49" s="4">
         <v>9500</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="P49" s="58">
         <v>180000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="Q49" s="58">
         <v>16000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49" s="58">
         <v>15000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="S49" s="58">
         <v>16008</v>
       </c>
-      <c r="T49" s="43">
+      <c r="T49" s="50">
         <v>48</v>
       </c>
-      <c r="U49" s="43">
+      <c r="U49" s="50">
         <v>0</v>
       </c>
       <c r="V49" t="s">
         <v>65</v>
       </c>
-      <c r="W49" s="4" t="s">
+      <c r="W49" s="8" t="s">
         <v>100</v>
       </c>
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="49"/>
+      <c r="Y49" s="57"/>
     </row>
-    <row r="50" spans="1:25" s="3" customFormat="1">
-      <c r="A50" s="43">
+    <row r="50" s="3" customFormat="1" spans="1:25">
+      <c r="A50" s="50">
         <v>20060010</v>
       </c>
       <c r="B50" s="3">
@@ -5112,67 +5719,67 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="52" t="s">
+      <c r="F50" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="45" t="s">
+      <c r="G50" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H50" s="44">
-        <v>10</v>
-      </c>
-      <c r="I50" s="44">
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" s="51">
         <v>1980000</v>
       </c>
-      <c r="J50" s="31" t="s">
+      <c r="J50" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K50" s="3">
-        <v>0</v>
-      </c>
-      <c r="L50" s="3" t="s">
+      <c r="K50" s="58">
+        <v>0</v>
+      </c>
+      <c r="L50" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="46" t="s">
+      <c r="M50" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="N50" s="2">
+      <c r="N50" s="4">
         <v>9500</v>
       </c>
       <c r="O50" s="3">
         <v>300</v>
       </c>
-      <c r="P50" s="3">
+      <c r="P50" s="58">
         <v>180000</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="Q50" s="58">
         <v>16000</v>
       </c>
-      <c r="R50" s="3">
+      <c r="R50" s="58">
         <v>15000</v>
       </c>
-      <c r="S50" s="3">
+      <c r="S50" s="58">
         <v>16008</v>
       </c>
-      <c r="T50" s="43">
+      <c r="T50" s="50">
         <v>20</v>
       </c>
-      <c r="U50" s="43">
+      <c r="U50" s="50">
         <v>0</v>
       </c>
       <c r="V50" t="s">
         <v>57</v>
       </c>
-      <c r="W50" s="4" t="s">
+      <c r="W50" s="8" t="s">
         <v>101</v>
       </c>
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="49"/>
+      <c r="Y50" s="57"/>
     </row>
-    <row r="51" spans="1:25" s="3" customFormat="1">
-      <c r="A51" s="43">
+    <row r="51" s="3" customFormat="1" spans="1:25">
+      <c r="A51" s="50">
         <v>20060011</v>
       </c>
       <c r="B51" s="3">
@@ -5187,67 +5794,67 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="52" t="s">
+      <c r="F51" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="45" t="s">
+      <c r="G51" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H51" s="44">
-        <v>11</v>
-      </c>
-      <c r="I51" s="44">
+      <c r="H51" s="3">
+        <v>2</v>
+      </c>
+      <c r="I51" s="51">
         <v>1980000</v>
       </c>
-      <c r="J51" s="36" t="s">
+      <c r="J51" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K51" s="3">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3" t="s">
+      <c r="K51" s="58">
+        <v>0</v>
+      </c>
+      <c r="L51" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="46" t="s">
+      <c r="M51" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="N51" s="2">
+      <c r="N51" s="4">
         <v>9500</v>
       </c>
       <c r="O51" s="3">
         <v>300</v>
       </c>
-      <c r="P51" s="3">
+      <c r="P51" s="58">
         <v>180000</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="Q51" s="58">
         <v>16000</v>
       </c>
-      <c r="R51" s="3">
+      <c r="R51" s="58">
         <v>15000</v>
       </c>
-      <c r="S51" s="3">
+      <c r="S51" s="58">
         <v>16008</v>
       </c>
-      <c r="T51" s="43">
+      <c r="T51" s="50">
         <v>20</v>
       </c>
-      <c r="U51" s="43">
+      <c r="U51" s="50">
         <v>0</v>
       </c>
       <c r="V51" t="s">
         <v>61</v>
       </c>
-      <c r="W51" s="4" t="s">
+      <c r="W51" s="8" t="s">
         <v>102</v>
       </c>
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="49"/>
+      <c r="Y51" s="57"/>
     </row>
-    <row r="52" spans="1:25" s="3" customFormat="1">
-      <c r="A52" s="43">
+    <row r="52" s="3" customFormat="1" spans="1:25">
+      <c r="A52" s="50">
         <v>20060012</v>
       </c>
       <c r="B52" s="3">
@@ -5262,19 +5869,19 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="52" t="s">
+      <c r="F52" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="45" t="s">
+      <c r="G52" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H52" s="44">
-        <v>12</v>
-      </c>
-      <c r="I52" s="44">
+      <c r="H52" s="3">
+        <v>3</v>
+      </c>
+      <c r="I52" s="51">
         <v>1980000</v>
       </c>
-      <c r="J52" s="31" t="s">
+      <c r="J52" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K52" s="3">
@@ -5283,10 +5890,10 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="46" t="s">
+      <c r="M52" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="N52" s="2">
+      <c r="N52" s="4">
         <v>9500</v>
       </c>
       <c r="O52" s="3">
@@ -5304,25 +5911,25 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="43">
+      <c r="T52" s="50">
         <v>20</v>
       </c>
-      <c r="U52" s="43">
+      <c r="U52" s="50">
         <v>0</v>
       </c>
       <c r="V52" t="s">
         <v>65</v>
       </c>
-      <c r="W52" s="4" t="s">
+      <c r="W52" s="8" t="s">
         <v>103</v>
       </c>
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="49"/>
+      <c r="Y52" s="57"/>
     </row>
-    <row r="53" spans="1:25" s="3" customFormat="1">
-      <c r="A53" s="43">
+    <row r="53" s="3" customFormat="1" spans="1:25">
+      <c r="A53" s="50">
         <v>20070010</v>
       </c>
       <c r="B53" s="3">
@@ -5337,19 +5944,19 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="52" t="s">
+      <c r="F53" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="45" t="s">
+      <c r="G53" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H53" s="44">
-        <v>10</v>
-      </c>
-      <c r="I53" s="44">
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="51">
         <v>1980000</v>
       </c>
-      <c r="J53" s="31" t="s">
+      <c r="J53" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K53" s="3">
@@ -5358,10 +5965,10 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="46" t="s">
+      <c r="M53" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="N53" s="2">
+      <c r="N53" s="4">
         <v>9500</v>
       </c>
       <c r="O53" s="3">
@@ -5379,25 +5986,25 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="43">
+      <c r="T53" s="50">
         <v>30</v>
       </c>
-      <c r="U53" s="43">
+      <c r="U53" s="50">
         <v>1</v>
       </c>
       <c r="V53" t="s">
         <v>57</v>
       </c>
-      <c r="W53" s="4" t="s">
+      <c r="W53" s="8" t="s">
         <v>104</v>
       </c>
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="49"/>
+      <c r="Y53" s="57"/>
     </row>
-    <row r="54" spans="1:25" s="3" customFormat="1">
-      <c r="A54" s="43">
+    <row r="54" s="3" customFormat="1" spans="1:25">
+      <c r="A54" s="50">
         <v>20070011</v>
       </c>
       <c r="B54" s="3">
@@ -5412,19 +6019,19 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="52" t="s">
+      <c r="F54" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="45" t="s">
+      <c r="G54" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H54" s="44">
-        <v>11</v>
-      </c>
-      <c r="I54" s="44">
+      <c r="H54" s="3">
+        <v>2</v>
+      </c>
+      <c r="I54" s="51">
         <v>1980000</v>
       </c>
-      <c r="J54" s="36" t="s">
+      <c r="J54" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K54" s="3">
@@ -5433,10 +6040,10 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="46" t="s">
+      <c r="M54" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="N54" s="2">
+      <c r="N54" s="4">
         <v>9500</v>
       </c>
       <c r="O54" s="3">
@@ -5454,25 +6061,25 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="43">
+      <c r="T54" s="50">
         <v>30</v>
       </c>
-      <c r="U54" s="43">
+      <c r="U54" s="50">
         <v>1</v>
       </c>
       <c r="V54" t="s">
         <v>61</v>
       </c>
-      <c r="W54" s="4" t="s">
+      <c r="W54" s="8" t="s">
         <v>105</v>
       </c>
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="49"/>
+      <c r="Y54" s="57"/>
     </row>
-    <row r="55" spans="1:25" s="3" customFormat="1">
-      <c r="A55" s="43">
+    <row r="55" s="3" customFormat="1" spans="1:25">
+      <c r="A55" s="50">
         <v>20070012</v>
       </c>
       <c r="B55" s="3">
@@ -5487,19 +6094,19 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="52" t="s">
+      <c r="F55" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="45" t="s">
+      <c r="G55" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H55" s="44">
-        <v>12</v>
-      </c>
-      <c r="I55" s="44">
+      <c r="H55" s="3">
+        <v>3</v>
+      </c>
+      <c r="I55" s="51">
         <v>1980000</v>
       </c>
-      <c r="J55" s="31" t="s">
+      <c r="J55" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K55" s="3">
@@ -5508,10 +6115,10 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="46" t="s">
+      <c r="M55" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="N55" s="2">
+      <c r="N55" s="4">
         <v>9500</v>
       </c>
       <c r="O55" s="3">
@@ -5529,25 +6136,25 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="43">
+      <c r="T55" s="50">
         <v>30</v>
       </c>
-      <c r="U55" s="43">
+      <c r="U55" s="50">
         <v>1</v>
       </c>
       <c r="V55" t="s">
         <v>65</v>
       </c>
-      <c r="W55" s="4" t="s">
+      <c r="W55" s="8" t="s">
         <v>106</v>
       </c>
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="49"/>
+      <c r="Y55" s="57"/>
     </row>
-    <row r="56" spans="1:25" s="3" customFormat="1">
-      <c r="A56" s="43">
+    <row r="56" s="3" customFormat="1" spans="1:25">
+      <c r="A56" s="50">
         <v>20080010</v>
       </c>
       <c r="B56" s="3">
@@ -5562,19 +6169,19 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="52" t="s">
+      <c r="F56" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="45" t="s">
+      <c r="G56" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H56" s="44">
-        <v>10</v>
-      </c>
-      <c r="I56" s="44">
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" s="51">
         <v>1980000</v>
       </c>
-      <c r="J56" s="31" t="s">
+      <c r="J56" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K56" s="3">
@@ -5583,10 +6190,10 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="46" t="s">
+      <c r="M56" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N56" s="2">
+      <c r="N56" s="4">
         <v>9500</v>
       </c>
       <c r="O56" s="3">
@@ -5604,25 +6211,25 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="43">
+      <c r="T56" s="50">
         <v>20</v>
       </c>
-      <c r="U56" s="43">
+      <c r="U56" s="50">
         <v>0</v>
       </c>
       <c r="V56" t="s">
         <v>57</v>
       </c>
-      <c r="W56" s="4" t="s">
+      <c r="W56" s="8" t="s">
         <v>107</v>
       </c>
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="49"/>
+      <c r="Y56" s="57"/>
     </row>
-    <row r="57" spans="1:25" s="3" customFormat="1">
-      <c r="A57" s="43">
+    <row r="57" s="3" customFormat="1" spans="1:25">
+      <c r="A57" s="50">
         <v>20080011</v>
       </c>
       <c r="B57" s="3">
@@ -5637,19 +6244,19 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="52" t="s">
+      <c r="F57" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="45" t="s">
+      <c r="G57" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H57" s="44">
-        <v>11</v>
-      </c>
-      <c r="I57" s="44">
+      <c r="H57" s="3">
+        <v>2</v>
+      </c>
+      <c r="I57" s="51">
         <v>1980000</v>
       </c>
-      <c r="J57" s="36" t="s">
+      <c r="J57" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K57" s="3">
@@ -5658,10 +6265,10 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="46" t="s">
+      <c r="M57" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N57" s="2">
+      <c r="N57" s="4">
         <v>9500</v>
       </c>
       <c r="O57" s="3">
@@ -5679,25 +6286,25 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="43">
+      <c r="T57" s="50">
         <v>20</v>
       </c>
-      <c r="U57" s="43">
+      <c r="U57" s="50">
         <v>0</v>
       </c>
       <c r="V57" t="s">
         <v>61</v>
       </c>
-      <c r="W57" s="4" t="s">
+      <c r="W57" s="8" t="s">
         <v>86</v>
       </c>
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="49"/>
+      <c r="Y57" s="57"/>
     </row>
-    <row r="58" spans="1:25" s="3" customFormat="1">
-      <c r="A58" s="43">
+    <row r="58" s="3" customFormat="1" spans="1:25">
+      <c r="A58" s="50">
         <v>20080012</v>
       </c>
       <c r="B58" s="3">
@@ -5712,19 +6319,19 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="52" t="s">
+      <c r="F58" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="45" t="s">
+      <c r="G58" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H58" s="44">
-        <v>12</v>
-      </c>
-      <c r="I58" s="44">
+      <c r="H58" s="3">
+        <v>3</v>
+      </c>
+      <c r="I58" s="51">
         <v>1980000</v>
       </c>
-      <c r="J58" s="31" t="s">
+      <c r="J58" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K58" s="3">
@@ -5733,10 +6340,10 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="46" t="s">
+      <c r="M58" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N58" s="2">
+      <c r="N58" s="4">
         <v>9500</v>
       </c>
       <c r="O58" s="3">
@@ -5754,25 +6361,25 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="43">
+      <c r="T58" s="50">
         <v>20</v>
       </c>
-      <c r="U58" s="43">
+      <c r="U58" s="50">
         <v>0</v>
       </c>
       <c r="V58" t="s">
         <v>65</v>
       </c>
-      <c r="W58" s="4" t="s">
+      <c r="W58" s="8" t="s">
         <v>87</v>
       </c>
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="49"/>
+      <c r="Y58" s="57"/>
     </row>
-    <row r="59" spans="1:25" s="3" customFormat="1">
-      <c r="A59" s="43">
+    <row r="59" s="3" customFormat="1" spans="1:25">
+      <c r="A59" s="50">
         <v>20090010</v>
       </c>
       <c r="B59" s="3">
@@ -5787,19 +6394,19 @@
       <c r="E59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="52" t="s">
+      <c r="F59" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G59" s="45" t="s">
+      <c r="G59" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H59" s="44">
-        <v>10</v>
-      </c>
-      <c r="I59" s="44">
+      <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="I59" s="51">
         <v>1980000</v>
       </c>
-      <c r="J59" s="31" t="s">
+      <c r="J59" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K59" s="3">
@@ -5808,10 +6415,10 @@
       <c r="L59" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M59" s="46" t="s">
+      <c r="M59" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N59" s="2">
+      <c r="N59" s="4">
         <v>9500</v>
       </c>
       <c r="O59" s="3">
@@ -5829,25 +6436,25 @@
       <c r="S59" s="3">
         <v>16008</v>
       </c>
-      <c r="T59" s="43">
+      <c r="T59" s="50">
         <v>20</v>
       </c>
-      <c r="U59" s="43">
+      <c r="U59" s="50">
         <v>0</v>
       </c>
       <c r="V59" t="s">
         <v>57</v>
       </c>
-      <c r="W59" s="4" t="s">
+      <c r="W59" s="8" t="s">
         <v>108</v>
       </c>
       <c r="X59" s="3">
         <v>1</v>
       </c>
-      <c r="Y59" s="49"/>
+      <c r="Y59" s="57"/>
     </row>
-    <row r="60" spans="1:25" s="3" customFormat="1">
-      <c r="A60" s="43">
+    <row r="60" s="3" customFormat="1" spans="1:25">
+      <c r="A60" s="50">
         <v>20090011</v>
       </c>
       <c r="B60" s="3">
@@ -5862,19 +6469,19 @@
       <c r="E60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F60" s="52" t="s">
+      <c r="F60" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G60" s="45" t="s">
+      <c r="G60" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H60" s="44">
-        <v>11</v>
-      </c>
-      <c r="I60" s="44">
+      <c r="H60" s="3">
+        <v>2</v>
+      </c>
+      <c r="I60" s="51">
         <v>1980000</v>
       </c>
-      <c r="J60" s="36" t="s">
+      <c r="J60" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K60" s="3">
@@ -5883,10 +6490,10 @@
       <c r="L60" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M60" s="46" t="s">
+      <c r="M60" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N60" s="2">
+      <c r="N60" s="4">
         <v>9500</v>
       </c>
       <c r="O60" s="3">
@@ -5904,25 +6511,25 @@
       <c r="S60" s="3">
         <v>16008</v>
       </c>
-      <c r="T60" s="43">
+      <c r="T60" s="50">
         <v>20</v>
       </c>
-      <c r="U60" s="43">
+      <c r="U60" s="50">
         <v>0</v>
       </c>
       <c r="V60" t="s">
         <v>61</v>
       </c>
-      <c r="W60" s="4" t="s">
+      <c r="W60" s="8" t="s">
         <v>109</v>
       </c>
       <c r="X60" s="3">
         <v>1</v>
       </c>
-      <c r="Y60" s="49"/>
+      <c r="Y60" s="57"/>
     </row>
-    <row r="61" spans="1:25" s="3" customFormat="1">
-      <c r="A61" s="43">
+    <row r="61" s="3" customFormat="1" spans="1:25">
+      <c r="A61" s="50">
         <v>20090012</v>
       </c>
       <c r="B61" s="3">
@@ -5937,19 +6544,19 @@
       <c r="E61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G61" s="45" t="s">
+      <c r="G61" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H61" s="44">
-        <v>12</v>
-      </c>
-      <c r="I61" s="44">
+      <c r="H61" s="3">
+        <v>3</v>
+      </c>
+      <c r="I61" s="51">
         <v>1980000</v>
       </c>
-      <c r="J61" s="31" t="s">
+      <c r="J61" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K61" s="3">
@@ -5958,10 +6565,10 @@
       <c r="L61" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M61" s="46" t="s">
+      <c r="M61" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N61" s="2">
+      <c r="N61" s="4">
         <v>9500</v>
       </c>
       <c r="O61" s="3">
@@ -5979,28 +6586,28 @@
       <c r="S61" s="3">
         <v>16008</v>
       </c>
-      <c r="T61" s="43">
+      <c r="T61" s="50">
         <v>20</v>
       </c>
-      <c r="U61" s="43">
+      <c r="U61" s="50">
         <v>0</v>
       </c>
       <c r="V61" t="s">
         <v>65</v>
       </c>
-      <c r="W61" s="4" t="s">
+      <c r="W61" s="8" t="s">
         <v>110</v>
       </c>
       <c r="X61" s="3">
         <v>1</v>
       </c>
-      <c r="Y61" s="49"/>
+      <c r="Y61" s="57"/>
     </row>
-    <row r="62" spans="1:25" s="3" customFormat="1">
-      <c r="A62" s="43">
+    <row r="62" s="3" customFormat="1" spans="1:25">
+      <c r="A62" s="50">
         <v>20120010</v>
       </c>
-      <c r="B62" s="42">
+      <c r="B62" s="49">
         <v>201200</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -6012,19 +6619,19 @@
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="52" t="s">
+      <c r="F62" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G62" s="45" t="s">
+      <c r="G62" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H62" s="44">
-        <v>10</v>
-      </c>
-      <c r="I62" s="44">
+      <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="I62" s="51">
         <v>1980000</v>
       </c>
-      <c r="J62" s="31" t="s">
+      <c r="J62" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K62" s="3">
@@ -6033,10 +6640,10 @@
       <c r="L62" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M62" s="46" t="s">
+      <c r="M62" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="N62" s="2">
+      <c r="N62" s="4">
         <v>9500</v>
       </c>
       <c r="O62" s="3">
@@ -6054,28 +6661,28 @@
       <c r="S62" s="3">
         <v>16008</v>
       </c>
-      <c r="T62" s="43">
+      <c r="T62" s="50">
         <v>12</v>
       </c>
-      <c r="U62" s="43">
+      <c r="U62" s="50">
         <v>0</v>
       </c>
       <c r="V62" t="s">
         <v>57</v>
       </c>
-      <c r="W62" s="4" t="s">
+      <c r="W62" s="8" t="s">
         <v>108</v>
       </c>
       <c r="X62" s="3">
         <v>1</v>
       </c>
-      <c r="Y62" s="49"/>
+      <c r="Y62" s="57"/>
     </row>
-    <row r="63" spans="1:25" s="3" customFormat="1">
-      <c r="A63" s="43">
+    <row r="63" s="3" customFormat="1" spans="1:25">
+      <c r="A63" s="50">
         <v>20120011</v>
       </c>
-      <c r="B63" s="42">
+      <c r="B63" s="49">
         <v>201200</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -6087,19 +6694,19 @@
       <c r="E63" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="52" t="s">
+      <c r="F63" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G63" s="45" t="s">
+      <c r="G63" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H63" s="44">
-        <v>11</v>
-      </c>
-      <c r="I63" s="44">
+      <c r="H63" s="3">
+        <v>2</v>
+      </c>
+      <c r="I63" s="51">
         <v>1980000</v>
       </c>
-      <c r="J63" s="36" t="s">
+      <c r="J63" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K63" s="3">
@@ -6108,10 +6715,10 @@
       <c r="L63" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M63" s="46" t="s">
+      <c r="M63" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="N63" s="2">
+      <c r="N63" s="4">
         <v>9500</v>
       </c>
       <c r="O63" s="3">
@@ -6129,28 +6736,28 @@
       <c r="S63" s="3">
         <v>16008</v>
       </c>
-      <c r="T63" s="43">
+      <c r="T63" s="50">
         <v>12</v>
       </c>
-      <c r="U63" s="43">
+      <c r="U63" s="50">
         <v>0</v>
       </c>
       <c r="V63" t="s">
         <v>61</v>
       </c>
-      <c r="W63" s="4" t="s">
+      <c r="W63" s="8" t="s">
         <v>109</v>
       </c>
       <c r="X63" s="3">
         <v>1</v>
       </c>
-      <c r="Y63" s="49"/>
+      <c r="Y63" s="57"/>
     </row>
-    <row r="64" spans="1:25" s="3" customFormat="1">
-      <c r="A64" s="43">
+    <row r="64" s="3" customFormat="1" spans="1:25">
+      <c r="A64" s="50">
         <v>20120012</v>
       </c>
-      <c r="B64" s="42">
+      <c r="B64" s="49">
         <v>201200</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -6162,19 +6769,19 @@
       <c r="E64" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G64" s="45" t="s">
+      <c r="G64" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="H64" s="44">
-        <v>12</v>
-      </c>
-      <c r="I64" s="44">
+      <c r="H64" s="3">
+        <v>3</v>
+      </c>
+      <c r="I64" s="51">
         <v>1980000</v>
       </c>
-      <c r="J64" s="31" t="s">
+      <c r="J64" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K64" s="3">
@@ -6183,10 +6790,10 @@
       <c r="L64" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M64" s="46" t="s">
+      <c r="M64" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="N64" s="2">
+      <c r="N64" s="4">
         <v>9500</v>
       </c>
       <c r="O64" s="3">
@@ -6204,2398 +6811,30 @@
       <c r="S64" s="3">
         <v>16008</v>
       </c>
-      <c r="T64" s="43">
+      <c r="T64" s="50">
         <v>12</v>
       </c>
-      <c r="U64" s="43">
+      <c r="U64" s="50">
         <v>0</v>
       </c>
       <c r="V64" t="s">
         <v>65</v>
       </c>
-      <c r="W64" s="4" t="s">
+      <c r="W64" s="8" t="s">
         <v>110</v>
       </c>
       <c r="X64" s="3">
         <v>1</v>
       </c>
-      <c r="Y64" s="49"/>
-    </row>
-    <row r="65" spans="1:25">
-      <c r="A65" s="2">
-        <f>B65*100+H65</f>
-        <v>20010021</v>
-      </c>
-      <c r="B65" s="28">
-        <v>200100</v>
-      </c>
-      <c r="C65" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" s="28">
-        <v>200100038</v>
-      </c>
-      <c r="E65" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F65" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G65" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H65" s="28">
-        <v>21</v>
-      </c>
-      <c r="I65" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J65" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K65" s="2">
-        <v>1</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M65" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="N65" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O65" s="2">
-        <v>0</v>
-      </c>
-      <c r="P65" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q65" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R65" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S65" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T65" s="5">
-        <v>48</v>
-      </c>
-      <c r="U65" s="34">
-        <v>0</v>
-      </c>
-      <c r="V65" t="s">
-        <v>57</v>
-      </c>
-      <c r="W65" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X65" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25">
-      <c r="A66" s="2">
-        <f t="shared" ref="A66:A94" si="6">B66*100+H66</f>
-        <v>20010022</v>
-      </c>
-      <c r="B66" s="35">
-        <v>200100</v>
-      </c>
-      <c r="C66" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="D66" s="35">
-        <v>200100038</v>
-      </c>
-      <c r="E66" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F66" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G66" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H66" s="28">
-        <v>22</v>
-      </c>
-      <c r="I66" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J66" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K66" s="2">
-        <v>1</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M66" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="N66" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O66" s="2">
-        <v>0</v>
-      </c>
-      <c r="P66" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q66" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R66" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S66" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T66" s="5">
-        <v>48</v>
-      </c>
-      <c r="U66" s="34">
-        <v>0</v>
-      </c>
-      <c r="V66" t="s">
-        <v>61</v>
-      </c>
-      <c r="W66" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X66" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="4">
-        <f t="shared" ref="Y66:Y70" si="7">Y65*10</f>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" s="2" customFormat="1">
-      <c r="A67" s="2">
-        <f t="shared" si="6"/>
-        <v>20010023</v>
-      </c>
-      <c r="B67" s="28">
-        <v>200100</v>
-      </c>
-      <c r="C67" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="D67" s="28">
-        <v>200100038</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F67" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G67" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H67" s="28">
-        <v>23</v>
-      </c>
-      <c r="I67" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J67" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K67" s="2">
-        <v>1</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M67" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="N67" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O67" s="2">
-        <v>0</v>
-      </c>
-      <c r="P67" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q67" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R67" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S67" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T67" s="5">
-        <v>48</v>
-      </c>
-      <c r="U67" s="34">
-        <v>0</v>
-      </c>
-      <c r="V67" t="s">
-        <v>65</v>
-      </c>
-      <c r="W67" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X67" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y67" s="4">
-        <f t="shared" si="7"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" s="2" customFormat="1">
-      <c r="A68" s="2">
-        <f t="shared" si="6"/>
-        <v>20010121</v>
-      </c>
-      <c r="B68" s="28">
-        <v>200101</v>
-      </c>
-      <c r="C68" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="D68" s="28">
-        <v>200101001</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F68" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G68" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H68" s="28">
-        <v>21</v>
-      </c>
-      <c r="I68" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J68" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K68" s="2">
-        <v>0</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M68" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="N68" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O68" s="2">
-        <v>0</v>
-      </c>
-      <c r="P68" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q68" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R68" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S68" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T68" s="5">
-        <v>48</v>
-      </c>
-      <c r="U68" s="34">
-        <v>0</v>
-      </c>
-      <c r="V68" t="s">
-        <v>57</v>
-      </c>
-      <c r="W68" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X68" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25">
-      <c r="A69" s="2">
-        <f t="shared" si="6"/>
-        <v>20010122</v>
-      </c>
-      <c r="B69" s="35">
-        <v>200101</v>
-      </c>
-      <c r="C69" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="D69" s="35">
-        <v>200101001</v>
-      </c>
-      <c r="E69" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F69" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G69" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H69" s="28">
-        <v>22</v>
-      </c>
-      <c r="I69" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J69" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K69" s="2">
-        <v>0</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M69" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="N69" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O69" s="2">
-        <v>0</v>
-      </c>
-      <c r="P69" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q69" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R69" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S69" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T69" s="5">
-        <v>48</v>
-      </c>
-      <c r="U69" s="34">
-        <v>0</v>
-      </c>
-      <c r="V69" t="s">
-        <v>61</v>
-      </c>
-      <c r="W69" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X69" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="4">
-        <f t="shared" si="7"/>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25">
-      <c r="A70" s="2">
-        <f t="shared" si="6"/>
-        <v>20010123</v>
-      </c>
-      <c r="B70" s="28">
-        <v>200101</v>
-      </c>
-      <c r="C70" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="D70" s="28">
-        <v>200101001</v>
-      </c>
-      <c r="E70" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F70" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G70" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H70" s="28">
-        <v>23</v>
-      </c>
-      <c r="I70" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J70" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K70" s="2">
-        <v>0</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M70" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="N70" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O70" s="2">
-        <v>0</v>
-      </c>
-      <c r="P70" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q70" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R70" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S70" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T70" s="5">
-        <v>48</v>
-      </c>
-      <c r="U70" s="34">
-        <v>0</v>
-      </c>
-      <c r="V70" t="s">
-        <v>65</v>
-      </c>
-      <c r="W70" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X70" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="4">
-        <f t="shared" si="7"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25">
-      <c r="A71" s="2">
-        <f t="shared" si="6"/>
-        <v>20030021</v>
-      </c>
-      <c r="B71" s="28">
-        <v>200300</v>
-      </c>
-      <c r="C71" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="D71" s="28">
-        <v>200300001</v>
-      </c>
-      <c r="E71" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="F71" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G71" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H71" s="28">
-        <v>21</v>
-      </c>
-      <c r="I71" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J71" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K71" s="2">
-        <v>0</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M71" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="N71" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O71" s="2">
-        <v>0</v>
-      </c>
-      <c r="P71" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q71" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R71" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S71" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T71" s="5">
-        <v>50</v>
-      </c>
-      <c r="U71" s="34">
-        <v>0</v>
-      </c>
-      <c r="V71" t="s">
-        <v>57</v>
-      </c>
-      <c r="W71" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X71" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" s="2" customFormat="1">
-      <c r="A72" s="2">
-        <f t="shared" si="6"/>
-        <v>20030022</v>
-      </c>
-      <c r="B72" s="35">
-        <v>200300</v>
-      </c>
-      <c r="C72" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D72" s="35">
-        <v>200300001</v>
-      </c>
-      <c r="E72" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F72" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G72" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H72" s="28">
-        <v>22</v>
-      </c>
-      <c r="I72" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J72" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K72" s="2">
-        <v>0</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M72" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="N72" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O72" s="2">
-        <v>0</v>
-      </c>
-      <c r="P72" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q72" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R72" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S72" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T72" s="5">
-        <v>50</v>
-      </c>
-      <c r="U72" s="34">
-        <v>0</v>
-      </c>
-      <c r="V72" t="s">
-        <v>61</v>
-      </c>
-      <c r="W72" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X72" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="4">
-        <f t="shared" ref="Y72:Y76" si="8">Y71*10</f>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25">
-      <c r="A73" s="2">
-        <f t="shared" si="6"/>
-        <v>20030023</v>
-      </c>
-      <c r="B73" s="28">
-        <v>200300</v>
-      </c>
-      <c r="C73" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="D73" s="28">
-        <v>200300001</v>
-      </c>
-      <c r="E73" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F73" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G73" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H73" s="28">
-        <v>23</v>
-      </c>
-      <c r="I73" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J73" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K73" s="2">
-        <v>0</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M73" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="N73" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O73" s="2">
-        <v>0</v>
-      </c>
-      <c r="P73" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q73" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R73" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S73" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T73" s="5">
-        <v>50</v>
-      </c>
-      <c r="U73" s="34">
-        <v>0</v>
-      </c>
-      <c r="V73" t="s">
-        <v>65</v>
-      </c>
-      <c r="W73" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X73" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="4">
-        <f t="shared" si="8"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25">
-      <c r="A74" s="2">
-        <f t="shared" si="6"/>
-        <v>20040021</v>
-      </c>
-      <c r="B74" s="28">
-        <v>200400</v>
-      </c>
-      <c r="C74" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="D74" s="28">
-        <v>200400009</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F74" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G74" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H74" s="28">
-        <v>21</v>
-      </c>
-      <c r="I74" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J74" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K74" s="2">
-        <v>0</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M74" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="N74" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O74" s="2">
-        <v>0</v>
-      </c>
-      <c r="P74" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q74" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R74" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S74" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T74" s="5">
-        <v>50</v>
-      </c>
-      <c r="U74" s="34">
-        <v>0</v>
-      </c>
-      <c r="V74" t="s">
-        <v>57</v>
-      </c>
-      <c r="W74" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X74" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25">
-      <c r="A75" s="2">
-        <f t="shared" si="6"/>
-        <v>20040022</v>
-      </c>
-      <c r="B75" s="35">
-        <v>200400</v>
-      </c>
-      <c r="C75" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="D75" s="35">
-        <v>200400009</v>
-      </c>
-      <c r="E75" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F75" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G75" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H75" s="28">
-        <v>22</v>
-      </c>
-      <c r="I75" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J75" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K75" s="2">
-        <v>0</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M75" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="N75" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O75" s="2">
-        <v>0</v>
-      </c>
-      <c r="P75" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q75" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R75" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S75" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T75" s="5">
-        <v>50</v>
-      </c>
-      <c r="U75" s="34">
-        <v>0</v>
-      </c>
-      <c r="V75" t="s">
-        <v>61</v>
-      </c>
-      <c r="W75" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X75" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="4">
-        <f t="shared" si="8"/>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25" s="2" customFormat="1">
-      <c r="A76" s="2">
-        <f t="shared" si="6"/>
-        <v>20040023</v>
-      </c>
-      <c r="B76" s="28">
-        <v>200400</v>
-      </c>
-      <c r="C76" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="D76" s="28">
-        <v>200400009</v>
-      </c>
-      <c r="E76" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F76" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G76" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H76" s="28">
-        <v>23</v>
-      </c>
-      <c r="I76" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J76" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K76" s="2">
-        <v>0</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M76" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="N76" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O76" s="2">
-        <v>0</v>
-      </c>
-      <c r="P76" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q76" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R76" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S76" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T76" s="5">
-        <v>50</v>
-      </c>
-      <c r="U76" s="34">
-        <v>0</v>
-      </c>
-      <c r="V76" t="s">
-        <v>65</v>
-      </c>
-      <c r="W76" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X76" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="4">
-        <f t="shared" si="8"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:25" s="2" customFormat="1">
-      <c r="A77" s="2">
-        <f t="shared" si="6"/>
-        <v>20050021</v>
-      </c>
-      <c r="B77" s="28">
-        <v>200500</v>
-      </c>
-      <c r="C77" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D77" s="28">
-        <v>200500025</v>
-      </c>
-      <c r="E77" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F77" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G77" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H77" s="28">
-        <v>21</v>
-      </c>
-      <c r="I77" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J77" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K77" s="2">
-        <v>1</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M77" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="N77" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O77" s="2">
-        <v>0</v>
-      </c>
-      <c r="P77" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q77" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R77" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S77" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T77" s="5">
-        <v>48</v>
-      </c>
-      <c r="U77" s="34">
-        <v>0</v>
-      </c>
-      <c r="V77" t="s">
-        <v>57</v>
-      </c>
-      <c r="W77" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X77" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25">
-      <c r="A78" s="2">
-        <f t="shared" si="6"/>
-        <v>20050022</v>
-      </c>
-      <c r="B78" s="35">
-        <v>200500</v>
-      </c>
-      <c r="C78" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="D78" s="35">
-        <v>200500025</v>
-      </c>
-      <c r="E78" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F78" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G78" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H78" s="28">
-        <v>22</v>
-      </c>
-      <c r="I78" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J78" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K78" s="2">
-        <v>1</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M78" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="N78" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O78" s="2">
-        <v>0</v>
-      </c>
-      <c r="P78" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q78" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R78" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S78" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T78" s="5">
-        <v>48</v>
-      </c>
-      <c r="U78" s="34">
-        <v>0</v>
-      </c>
-      <c r="V78" t="s">
-        <v>61</v>
-      </c>
-      <c r="W78" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X78" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="4">
-        <f t="shared" ref="Y78:Y82" si="9">Y77*10</f>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25">
-      <c r="A79" s="2">
-        <f t="shared" si="6"/>
-        <v>20050023</v>
-      </c>
-      <c r="B79" s="28">
-        <v>200500</v>
-      </c>
-      <c r="C79" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D79" s="28">
-        <v>200500025</v>
-      </c>
-      <c r="E79" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F79" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G79" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H79" s="28">
-        <v>23</v>
-      </c>
-      <c r="I79" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J79" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K79" s="2">
-        <v>1</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M79" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="N79" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O79" s="2">
-        <v>0</v>
-      </c>
-      <c r="P79" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q79" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R79" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S79" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T79" s="5">
-        <v>48</v>
-      </c>
-      <c r="U79" s="34">
-        <v>0</v>
-      </c>
-      <c r="V79" t="s">
-        <v>65</v>
-      </c>
-      <c r="W79" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X79" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y79" s="4">
-        <f t="shared" si="9"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25">
-      <c r="A80" s="2">
-        <f t="shared" si="6"/>
-        <v>20060021</v>
-      </c>
-      <c r="B80" s="28">
-        <v>200600</v>
-      </c>
-      <c r="C80" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D80" s="28">
-        <v>200600001</v>
-      </c>
-      <c r="E80" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="F80" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G80" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H80" s="28">
-        <v>21</v>
-      </c>
-      <c r="I80" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J80" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K80" s="2">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M80" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="N80" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O80" s="2">
-        <v>0</v>
-      </c>
-      <c r="P80" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q80" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R80" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S80" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T80" s="5">
-        <v>20</v>
-      </c>
-      <c r="U80" s="34">
-        <v>0</v>
-      </c>
-      <c r="V80" t="s">
-        <v>57</v>
-      </c>
-      <c r="W80" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X80" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:25" s="2" customFormat="1">
-      <c r="A81" s="2">
-        <f t="shared" si="6"/>
-        <v>20060022</v>
-      </c>
-      <c r="B81" s="35">
-        <v>200600</v>
-      </c>
-      <c r="C81" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="D81" s="35">
-        <v>200600001</v>
-      </c>
-      <c r="E81" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F81" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G81" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H81" s="28">
-        <v>22</v>
-      </c>
-      <c r="I81" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J81" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K81" s="2">
-        <v>0</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M81" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="N81" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O81" s="2">
-        <v>0</v>
-      </c>
-      <c r="P81" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q81" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R81" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S81" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T81" s="5">
-        <v>20</v>
-      </c>
-      <c r="U81" s="34">
-        <v>0</v>
-      </c>
-      <c r="V81" t="s">
-        <v>61</v>
-      </c>
-      <c r="W81" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X81" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="4">
-        <f t="shared" si="9"/>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25">
-      <c r="A82" s="2">
-        <f t="shared" si="6"/>
-        <v>20060023</v>
-      </c>
-      <c r="B82" s="28">
-        <v>200600</v>
-      </c>
-      <c r="C82" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D82" s="28">
-        <v>200600001</v>
-      </c>
-      <c r="E82" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F82" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G82" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H82" s="28">
-        <v>23</v>
-      </c>
-      <c r="I82" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J82" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K82" s="2">
-        <v>0</v>
-      </c>
-      <c r="L82" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M82" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="N82" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O82" s="2">
-        <v>0</v>
-      </c>
-      <c r="P82" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q82" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R82" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S82" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T82" s="5">
-        <v>20</v>
-      </c>
-      <c r="U82" s="34">
-        <v>0</v>
-      </c>
-      <c r="V82" t="s">
-        <v>65</v>
-      </c>
-      <c r="W82" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X82" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="4">
-        <f t="shared" si="9"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:25">
-      <c r="A83" s="2">
-        <f t="shared" si="6"/>
-        <v>20070021</v>
-      </c>
-      <c r="B83" s="28">
-        <v>200700</v>
-      </c>
-      <c r="C83" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D83" s="28">
-        <v>200700001</v>
-      </c>
-      <c r="E83" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F83" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G83" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H83" s="28">
-        <v>21</v>
-      </c>
-      <c r="I83" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J83" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K83" s="2">
-        <v>1</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M83" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="N83" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O83" s="2">
-        <v>0</v>
-      </c>
-      <c r="P83" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q83" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R83" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S83" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T83" s="5">
-        <v>30</v>
-      </c>
-      <c r="U83" s="34">
-        <v>1</v>
-      </c>
-      <c r="V83" t="s">
-        <v>57</v>
-      </c>
-      <c r="W83" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X83" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:25">
-      <c r="A84" s="2">
-        <f t="shared" si="6"/>
-        <v>20070022</v>
-      </c>
-      <c r="B84" s="35">
-        <v>200700</v>
-      </c>
-      <c r="C84" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D84" s="35">
-        <v>200700001</v>
-      </c>
-      <c r="E84" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F84" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G84" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H84" s="28">
-        <v>22</v>
-      </c>
-      <c r="I84" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J84" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K84" s="2">
-        <v>1</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M84" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="N84" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O84" s="2">
-        <v>0</v>
-      </c>
-      <c r="P84" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q84" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R84" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S84" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T84" s="5">
-        <v>30</v>
-      </c>
-      <c r="U84" s="34">
-        <v>1</v>
-      </c>
-      <c r="V84" t="s">
-        <v>61</v>
-      </c>
-      <c r="W84" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X84" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="4">
-        <f t="shared" ref="Y84:Y88" si="10">Y83*10</f>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:25" s="2" customFormat="1">
-      <c r="A85" s="2">
-        <f t="shared" si="6"/>
-        <v>20070023</v>
-      </c>
-      <c r="B85" s="28">
-        <v>200700</v>
-      </c>
-      <c r="C85" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D85" s="28">
-        <v>200700001</v>
-      </c>
-      <c r="E85" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F85" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G85" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H85" s="28">
-        <v>23</v>
-      </c>
-      <c r="I85" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J85" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K85" s="2">
-        <v>1</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M85" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="N85" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O85" s="2">
-        <v>0</v>
-      </c>
-      <c r="P85" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q85" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R85" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S85" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T85" s="5">
-        <v>30</v>
-      </c>
-      <c r="U85" s="34">
-        <v>1</v>
-      </c>
-      <c r="V85" t="s">
-        <v>65</v>
-      </c>
-      <c r="W85" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X85" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y85" s="4">
-        <f t="shared" si="10"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:25" s="2" customFormat="1">
-      <c r="A86" s="2">
-        <f t="shared" si="6"/>
-        <v>20080021</v>
-      </c>
-      <c r="B86" s="28">
-        <v>200800</v>
-      </c>
-      <c r="C86" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="D86" s="28">
-        <v>200800001</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="F86" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G86" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H86" s="28">
-        <v>21</v>
-      </c>
-      <c r="I86" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J86" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K86" s="2">
-        <v>0</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M86" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N86" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O86" s="2">
-        <v>0</v>
-      </c>
-      <c r="P86" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q86" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R86" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S86" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T86" s="5">
-        <v>20</v>
-      </c>
-      <c r="U86" s="34">
-        <v>0</v>
-      </c>
-      <c r="V86" t="s">
-        <v>57</v>
-      </c>
-      <c r="W86" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X86" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y86" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="87" spans="1:25" s="2" customFormat="1">
-      <c r="A87" s="2">
-        <f t="shared" si="6"/>
-        <v>20080022</v>
-      </c>
-      <c r="B87" s="28">
-        <v>200800</v>
-      </c>
-      <c r="C87" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="D87" s="28">
-        <v>200800001</v>
-      </c>
-      <c r="E87" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F87" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G87" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H87" s="28">
-        <v>22</v>
-      </c>
-      <c r="I87" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J87" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K87" s="2">
-        <v>0</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M87" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N87" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O87" s="2">
-        <v>0</v>
-      </c>
-      <c r="P87" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q87" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R87" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S87" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T87" s="5">
-        <v>20</v>
-      </c>
-      <c r="U87" s="34">
-        <v>0</v>
-      </c>
-      <c r="V87" t="s">
-        <v>61</v>
-      </c>
-      <c r="W87" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X87" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y87" s="4">
-        <f t="shared" si="10"/>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="88" spans="1:25" s="2" customFormat="1">
-      <c r="A88" s="2">
-        <f t="shared" si="6"/>
-        <v>20080023</v>
-      </c>
-      <c r="B88" s="28">
-        <v>200800</v>
-      </c>
-      <c r="C88" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="D88" s="28">
-        <v>200800001</v>
-      </c>
-      <c r="E88" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F88" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G88" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H88" s="28">
-        <v>23</v>
-      </c>
-      <c r="I88" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J88" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K88" s="2">
-        <v>0</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M88" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N88" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O88" s="2">
-        <v>0</v>
-      </c>
-      <c r="P88" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q88" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R88" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S88" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T88" s="5">
-        <v>20</v>
-      </c>
-      <c r="U88" s="34">
-        <v>0</v>
-      </c>
-      <c r="V88" t="s">
-        <v>65</v>
-      </c>
-      <c r="W88" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X88" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y88" s="4">
-        <f t="shared" si="10"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:25" s="2" customFormat="1">
-      <c r="A89" s="2">
-        <f t="shared" si="6"/>
-        <v>20090021</v>
-      </c>
-      <c r="B89" s="39">
-        <v>200900</v>
-      </c>
-      <c r="C89" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D89" s="28">
-        <v>200900001</v>
-      </c>
-      <c r="E89" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F89" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G89" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H89" s="28">
-        <v>21</v>
-      </c>
-      <c r="I89" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J89" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K89" s="40">
-        <v>0</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M89" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N89" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O89" s="2">
-        <v>0</v>
-      </c>
-      <c r="P89" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q89" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R89" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S89" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T89" s="5">
-        <v>20</v>
-      </c>
-      <c r="U89" s="34">
-        <v>0</v>
-      </c>
-      <c r="V89" t="s">
-        <v>57</v>
-      </c>
-      <c r="W89" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X89" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="90" spans="1:25">
-      <c r="A90" s="2">
-        <f t="shared" si="6"/>
-        <v>20090022</v>
-      </c>
-      <c r="B90" s="41">
-        <v>200900</v>
-      </c>
-      <c r="C90" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="D90" s="35">
-        <v>200900001</v>
-      </c>
-      <c r="E90" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F90" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G90" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H90" s="28">
-        <v>22</v>
-      </c>
-      <c r="I90" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J90" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K90" s="40">
-        <v>0</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M90" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N90" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O90" s="2">
-        <v>0</v>
-      </c>
-      <c r="P90" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q90" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R90" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S90" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T90" s="5">
-        <v>20</v>
-      </c>
-      <c r="U90" s="34">
-        <v>0</v>
-      </c>
-      <c r="V90" t="s">
-        <v>61</v>
-      </c>
-      <c r="W90" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X90" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y90" s="4">
-        <f t="shared" ref="Y90:Y94" si="11">Y89*10</f>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:25">
-      <c r="A91" s="2">
-        <f t="shared" si="6"/>
-        <v>20090023</v>
-      </c>
-      <c r="B91" s="39">
-        <v>200900</v>
-      </c>
-      <c r="C91" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D91" s="28">
-        <v>200900001</v>
-      </c>
-      <c r="E91" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F91" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G91" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H91" s="28">
-        <v>23</v>
-      </c>
-      <c r="I91" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J91" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K91" s="40">
-        <v>0</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M91" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N91" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O91" s="2">
-        <v>0</v>
-      </c>
-      <c r="P91" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q91" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R91" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S91" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T91" s="5">
-        <v>20</v>
-      </c>
-      <c r="U91" s="34">
-        <v>0</v>
-      </c>
-      <c r="V91" t="s">
-        <v>65</v>
-      </c>
-      <c r="W91" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X91" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="4">
-        <f t="shared" si="11"/>
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="92" spans="1:25" s="2" customFormat="1">
-      <c r="A92" s="2">
-        <f t="shared" si="6"/>
-        <v>20120021</v>
-      </c>
-      <c r="B92" s="42">
-        <v>201200</v>
-      </c>
-      <c r="C92" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D92" s="35">
-        <v>201200001</v>
-      </c>
-      <c r="E92" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F92" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G92" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H92" s="28">
-        <v>21</v>
-      </c>
-      <c r="I92" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J92" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K92" s="40">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M92" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="N92" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O92" s="2">
-        <v>0</v>
-      </c>
-      <c r="P92" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q92" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R92" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S92" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T92" s="5">
-        <v>12</v>
-      </c>
-      <c r="U92" s="34">
-        <v>0</v>
-      </c>
-      <c r="V92" t="s">
-        <v>57</v>
-      </c>
-      <c r="W92" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="X92" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y92" s="4">
-        <f>100*100000</f>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:25">
-      <c r="A93" s="2">
-        <f t="shared" si="6"/>
-        <v>20120022</v>
-      </c>
-      <c r="B93" s="42">
-        <v>201200</v>
-      </c>
-      <c r="C93" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D93" s="35">
-        <v>201200001</v>
-      </c>
-      <c r="E93" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F93" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G93" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H93" s="28">
-        <v>22</v>
-      </c>
-      <c r="I93" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J93" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K93" s="40">
-        <v>0</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M93" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="N93" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O93" s="2">
-        <v>0</v>
-      </c>
-      <c r="P93" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q93" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R93" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S93" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T93" s="5">
-        <v>12</v>
-      </c>
-      <c r="U93" s="34">
-        <v>0</v>
-      </c>
-      <c r="V93" t="s">
-        <v>61</v>
-      </c>
-      <c r="W93" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X93" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="4">
-        <f t="shared" si="11"/>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:25">
-      <c r="A94" s="2">
-        <f t="shared" si="6"/>
-        <v>20120023</v>
-      </c>
-      <c r="B94" s="42">
-        <v>201200</v>
-      </c>
-      <c r="C94" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D94" s="35">
-        <v>201200001</v>
-      </c>
-      <c r="E94" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F94" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G94" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H94" s="28">
-        <v>23</v>
-      </c>
-      <c r="I94" s="30">
-        <v>1990000</v>
-      </c>
-      <c r="J94" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K94" s="40">
-        <v>0</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M94" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="N94" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O94" s="2">
-        <v>0</v>
-      </c>
-      <c r="P94" s="2">
-        <v>180000</v>
-      </c>
-      <c r="Q94" s="2">
-        <v>16000</v>
-      </c>
-      <c r="R94" s="2">
-        <v>15000</v>
-      </c>
-      <c r="S94" s="33">
-        <v>16008</v>
-      </c>
-      <c r="T94" s="5">
-        <v>12</v>
-      </c>
-      <c r="U94" s="34">
-        <v>0</v>
-      </c>
-      <c r="V94" t="s">
-        <v>65</v>
-      </c>
-      <c r="W94" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="X94" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="4">
-        <f t="shared" si="11"/>
-        <v>1000000000</v>
-      </c>
+      <c r="Y64" s="57"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S64" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\特殊用户标记相关配置表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE37467-CAA5-4650-81E5-0D9A000FE32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,21 +30,20 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
     <author>C</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -59,7 +52,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -68,43 +60,41 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">普通场 1
+          <t>普通场 1
 中级场 2 
 高级场 3
-</t>
+10、11、12  创建房间功能
+21、22、23  SVIP体验场</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>押分筹码列表</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="K1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -113,7 +103,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -122,13 +111,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="M1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>阶段信息:[准备阶段时间-毫秒，押分阶段时间-毫秒，亮牌阶段时间-毫秒，结算阶段-毫秒]
@@ -137,13 +125,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>每笔投注进入房间水池比例
@@ -153,27 +140,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>净赢分*抽水比例</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="P1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -182,7 +167,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -191,14 +175,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="Q1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -207,7 +190,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -216,14 +198,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="R1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -232,7 +213,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -242,14 +222,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -258,7 +237,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -267,14 +245,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="U1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>C:</t>
@@ -283,7 +260,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -292,14 +268,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="V1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -308,7 +283,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -318,14 +292,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="W1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -334,7 +307,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -342,13 +314,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="Y1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最大押分值*10000</t>
@@ -698,11 +669,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -751,45 +726,173 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,54 +901,240 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7993408001953185"/>
+        <fgColor theme="7" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7993408001953185"/>
+        <fgColor theme="9" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993408001953185"/>
+        <fgColor theme="4" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7993408001953185"/>
+        <fgColor theme="5" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -853,30 +1142,272 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -896,19 +1427,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -947,11 +1478,11 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -968,6 +1499,10 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -996,11 +1531,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1015,7 +1550,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1025,6 +1560,10 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1040,40 +1579,84 @@
     <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="60">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="50"/>
+    <cellStyle name="常规 2 2 2" xfId="51"/>
+    <cellStyle name="常规 3" xfId="52"/>
+    <cellStyle name="常规 3 2" xfId="53"/>
+    <cellStyle name="常规 4" xfId="54"/>
+    <cellStyle name="常规 5" xfId="55"/>
+    <cellStyle name="常规 6" xfId="56"/>
+    <cellStyle name="常规 6 2" xfId="57"/>
+    <cellStyle name="常规 6 2 2" xfId="58"/>
+    <cellStyle name="常规 7" xfId="59"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1331,19 +1914,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="4" width="20.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
@@ -1365,7 +1947,7 @@
     <col min="25" max="25" width="20.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="41.1" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="41.1" customHeight="1" spans="1:25">
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1434,7 +2016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="1" customFormat="1">
+    <row r="2" s="1" customFormat="1" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1505,7 +2087,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="1" customFormat="1">
+    <row r="3" s="1" customFormat="1" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -1576,7 +2158,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="1" customFormat="1">
+    <row r="4" s="1" customFormat="1" spans="1:25">
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
@@ -1618,19 +2200,19 @@
       <c r="E5" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H5" s="28">
         <v>1</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <v>1990000</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="J5" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K5" s="2">
@@ -1639,11 +2221,11 @@
       <c r="L5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="M5" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O5" s="2">
         <v>300</v>
@@ -1657,13 +2239,13 @@
       <c r="R5" s="2">
         <v>15000</v>
       </c>
-      <c r="S5" s="33">
+      <c r="S5" s="34">
         <v>16008</v>
       </c>
       <c r="T5" s="5">
         <v>48</v>
       </c>
-      <c r="U5" s="34">
+      <c r="U5" s="35">
         <v>0</v>
       </c>
       <c r="V5" t="s">
@@ -1685,31 +2267,31 @@
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="36">
         <v>200100</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="36">
         <v>200100038</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="36">
         <v>2</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="31">
         <v>1990000</v>
       </c>
-      <c r="J6" s="36" t="s">
+      <c r="J6" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="2">
@@ -1718,11 +2300,11 @@
       <c r="L6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="M6" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N6" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O6" s="2">
         <v>300</v>
@@ -1736,13 +2318,13 @@
       <c r="R6" s="2">
         <v>15000</v>
       </c>
-      <c r="S6" s="33">
+      <c r="S6" s="34">
         <v>16008</v>
       </c>
       <c r="T6" s="5">
         <v>48</v>
       </c>
-      <c r="U6" s="34">
+      <c r="U6" s="35">
         <v>0</v>
       </c>
       <c r="V6" t="s">
@@ -1759,7 +2341,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="7" spans="1:25" s="2" customFormat="1">
+    <row r="7" s="2" customFormat="1" spans="1:25">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -1776,19 +2358,19 @@
       <c r="E7" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H7" s="28">
         <v>3</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <v>1990000</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K7" s="2">
@@ -1797,11 +2379,11 @@
       <c r="L7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="32" t="s">
+      <c r="M7" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N7" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O7" s="2">
         <v>300</v>
@@ -1815,13 +2397,13 @@
       <c r="R7" s="2">
         <v>15000</v>
       </c>
-      <c r="S7" s="33">
+      <c r="S7" s="34">
         <v>16008</v>
       </c>
       <c r="T7" s="5">
         <v>48</v>
       </c>
-      <c r="U7" s="34">
+      <c r="U7" s="35">
         <v>0</v>
       </c>
       <c r="V7" t="s">
@@ -1838,7 +2420,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="2" customFormat="1">
+    <row r="8" s="2" customFormat="1" spans="1:25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -1852,22 +2434,22 @@
       <c r="D8" s="28">
         <v>200101001</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H8" s="28">
         <v>1</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <v>1990000</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K8" s="2">
@@ -1876,11 +2458,11 @@
       <c r="L8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="32" t="s">
+      <c r="M8" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N8" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O8" s="2">
         <v>300</v>
@@ -1894,13 +2476,13 @@
       <c r="R8" s="2">
         <v>15000</v>
       </c>
-      <c r="S8" s="33">
+      <c r="S8" s="34">
         <v>16008</v>
       </c>
       <c r="T8" s="5">
         <v>48</v>
       </c>
-      <c r="U8" s="34">
+      <c r="U8" s="35">
         <v>0</v>
       </c>
       <c r="V8" t="s">
@@ -1922,31 +2504,31 @@
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <v>200101</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="36">
         <v>200101001</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="36">
         <v>2</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <v>1990000</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K9" s="2">
@@ -1955,11 +2537,11 @@
       <c r="L9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="M9" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N9" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O9" s="2">
         <v>300</v>
@@ -1973,13 +2555,13 @@
       <c r="R9" s="2">
         <v>15000</v>
       </c>
-      <c r="S9" s="33">
+      <c r="S9" s="34">
         <v>16008</v>
       </c>
       <c r="T9" s="5">
         <v>48</v>
       </c>
-      <c r="U9" s="34">
+      <c r="U9" s="35">
         <v>0</v>
       </c>
       <c r="V9" t="s">
@@ -2013,19 +2595,19 @@
       <c r="E10" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H10" s="28">
         <v>3</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="31">
         <v>1990000</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K10" s="2">
@@ -2034,11 +2616,11 @@
       <c r="L10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="32" t="s">
+      <c r="M10" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N10" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O10" s="2">
         <v>300</v>
@@ -2052,13 +2634,13 @@
       <c r="R10" s="2">
         <v>15000</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10" s="34">
         <v>16008</v>
       </c>
       <c r="T10" s="5">
         <v>48</v>
       </c>
-      <c r="U10" s="34">
+      <c r="U10" s="35">
         <v>0</v>
       </c>
       <c r="V10" t="s">
@@ -2089,22 +2671,22 @@
       <c r="D11" s="28">
         <v>200300001</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H11" s="28">
         <v>1</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <v>1990000</v>
       </c>
-      <c r="J11" s="31" t="s">
+      <c r="J11" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K11" s="2">
@@ -2113,11 +2695,11 @@
       <c r="L11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="32" t="s">
+      <c r="M11" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N11" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O11" s="2">
         <v>300</v>
@@ -2131,13 +2713,13 @@
       <c r="R11" s="2">
         <v>15000</v>
       </c>
-      <c r="S11" s="33">
+      <c r="S11" s="34">
         <v>16008</v>
       </c>
       <c r="T11" s="5">
         <v>50</v>
       </c>
-      <c r="U11" s="34">
+      <c r="U11" s="35">
         <v>0</v>
       </c>
       <c r="V11" t="s">
@@ -2154,36 +2736,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="2" customFormat="1">
+    <row r="12" s="2" customFormat="1" spans="1:25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <v>200300</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="36">
         <v>200300001</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="36">
         <v>2</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <v>1990000</v>
       </c>
-      <c r="J12" s="36" t="s">
+      <c r="J12" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K12" s="2">
@@ -2192,11 +2774,11 @@
       <c r="L12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N12" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O12" s="2">
         <v>300</v>
@@ -2210,13 +2792,13 @@
       <c r="R12" s="2">
         <v>15000</v>
       </c>
-      <c r="S12" s="33">
+      <c r="S12" s="34">
         <v>16008</v>
       </c>
       <c r="T12" s="5">
         <v>50</v>
       </c>
-      <c r="U12" s="34">
+      <c r="U12" s="35">
         <v>0</v>
       </c>
       <c r="V12" t="s">
@@ -2250,19 +2832,19 @@
       <c r="E13" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H13" s="28">
         <v>3</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <v>1990000</v>
       </c>
-      <c r="J13" s="31" t="s">
+      <c r="J13" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K13" s="2">
@@ -2271,11 +2853,11 @@
       <c r="L13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="M13" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N13" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O13" s="2">
         <v>300</v>
@@ -2289,13 +2871,13 @@
       <c r="R13" s="2">
         <v>15000</v>
       </c>
-      <c r="S13" s="33">
+      <c r="S13" s="34">
         <v>16008</v>
       </c>
       <c r="T13" s="5">
         <v>50</v>
       </c>
-      <c r="U13" s="34">
+      <c r="U13" s="35">
         <v>0</v>
       </c>
       <c r="V13" t="s">
@@ -2326,22 +2908,22 @@
       <c r="D14" s="28">
         <v>200400009</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H14" s="28">
         <v>1</v>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <v>1990000</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="2">
@@ -2350,11 +2932,11 @@
       <c r="L14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="32" t="s">
+      <c r="M14" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N14" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O14" s="2">
         <v>300</v>
@@ -2368,13 +2950,13 @@
       <c r="R14" s="2">
         <v>15000</v>
       </c>
-      <c r="S14" s="33">
+      <c r="S14" s="34">
         <v>16008</v>
       </c>
       <c r="T14" s="5">
         <v>50</v>
       </c>
-      <c r="U14" s="34">
+      <c r="U14" s="35">
         <v>0</v>
       </c>
       <c r="V14" t="s">
@@ -2396,31 +2978,31 @@
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <v>200400</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <v>200400009</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="36">
         <v>2</v>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="31">
         <v>1990000</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K15" s="2">
@@ -2429,11 +3011,11 @@
       <c r="L15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="32" t="s">
+      <c r="M15" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N15" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O15" s="2">
         <v>300</v>
@@ -2447,13 +3029,13 @@
       <c r="R15" s="2">
         <v>15000</v>
       </c>
-      <c r="S15" s="33">
+      <c r="S15" s="34">
         <v>16008</v>
       </c>
       <c r="T15" s="5">
         <v>50</v>
       </c>
-      <c r="U15" s="34">
+      <c r="U15" s="35">
         <v>0</v>
       </c>
       <c r="V15" t="s">
@@ -2470,7 +3052,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" s="2" customFormat="1">
+    <row r="16" s="2" customFormat="1" spans="1:25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -2487,19 +3069,19 @@
       <c r="E16" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G16" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H16" s="28">
         <v>3</v>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="31">
         <v>1990000</v>
       </c>
-      <c r="J16" s="31" t="s">
+      <c r="J16" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K16" s="2">
@@ -2508,11 +3090,11 @@
       <c r="L16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M16" s="32" t="s">
+      <c r="M16" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N16" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O16" s="2">
         <v>300</v>
@@ -2526,13 +3108,13 @@
       <c r="R16" s="2">
         <v>15000</v>
       </c>
-      <c r="S16" s="33">
+      <c r="S16" s="34">
         <v>16008</v>
       </c>
       <c r="T16" s="5">
         <v>50</v>
       </c>
-      <c r="U16" s="34">
+      <c r="U16" s="35">
         <v>0</v>
       </c>
       <c r="V16" t="s">
@@ -2549,7 +3131,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="17" spans="1:25" s="2" customFormat="1">
+    <row r="17" s="2" customFormat="1" spans="1:25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -2566,19 +3148,19 @@
       <c r="E17" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H17" s="28">
         <v>1</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="31">
         <v>1990000</v>
       </c>
-      <c r="J17" s="31" t="s">
+      <c r="J17" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K17" s="2">
@@ -2587,11 +3169,11 @@
       <c r="L17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="32" t="s">
+      <c r="M17" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N17" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O17" s="2">
         <v>300</v>
@@ -2605,13 +3187,13 @@
       <c r="R17" s="2">
         <v>15000</v>
       </c>
-      <c r="S17" s="33">
+      <c r="S17" s="34">
         <v>16008</v>
       </c>
       <c r="T17" s="5">
         <v>48</v>
       </c>
-      <c r="U17" s="34">
+      <c r="U17" s="35">
         <v>0</v>
       </c>
       <c r="V17" t="s">
@@ -2633,31 +3215,31 @@
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="36">
         <v>200500</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="36">
         <v>200500025</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="36">
         <v>2</v>
       </c>
-      <c r="I18" s="30">
+      <c r="I18" s="31">
         <v>1990000</v>
       </c>
-      <c r="J18" s="36" t="s">
+      <c r="J18" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K18" s="2">
@@ -2666,11 +3248,11 @@
       <c r="L18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="32" t="s">
+      <c r="M18" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N18" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O18" s="2">
         <v>300</v>
@@ -2684,13 +3266,13 @@
       <c r="R18" s="2">
         <v>15000</v>
       </c>
-      <c r="S18" s="33">
+      <c r="S18" s="34">
         <v>16008</v>
       </c>
       <c r="T18" s="5">
         <v>48</v>
       </c>
-      <c r="U18" s="34">
+      <c r="U18" s="35">
         <v>0</v>
       </c>
       <c r="V18" t="s">
@@ -2724,19 +3306,19 @@
       <c r="E19" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="28">
         <v>3</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="31">
         <v>1990000</v>
       </c>
-      <c r="J19" s="31" t="s">
+      <c r="J19" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K19" s="2">
@@ -2745,11 +3327,11 @@
       <c r="L19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="32" t="s">
+      <c r="M19" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N19" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O19" s="2">
         <v>300</v>
@@ -2763,13 +3345,13 @@
       <c r="R19" s="2">
         <v>15000</v>
       </c>
-      <c r="S19" s="33">
+      <c r="S19" s="34">
         <v>16008</v>
       </c>
       <c r="T19" s="5">
         <v>48</v>
       </c>
-      <c r="U19" s="34">
+      <c r="U19" s="35">
         <v>0</v>
       </c>
       <c r="V19" t="s">
@@ -2800,22 +3382,22 @@
       <c r="D20" s="28">
         <v>200600001</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H20" s="28">
         <v>1</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="31">
         <v>1990000</v>
       </c>
-      <c r="J20" s="31" t="s">
+      <c r="J20" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K20" s="2">
@@ -2824,11 +3406,11 @@
       <c r="L20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="32" t="s">
+      <c r="M20" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N20" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O20" s="2">
         <v>300</v>
@@ -2842,13 +3424,13 @@
       <c r="R20" s="2">
         <v>15000</v>
       </c>
-      <c r="S20" s="33">
+      <c r="S20" s="34">
         <v>16008</v>
       </c>
       <c r="T20" s="5">
         <v>20</v>
       </c>
-      <c r="U20" s="34">
+      <c r="U20" s="35">
         <v>0</v>
       </c>
       <c r="V20" t="s">
@@ -2865,36 +3447,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="21" spans="1:25" s="2" customFormat="1">
+    <row r="21" s="2" customFormat="1" spans="1:25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="36">
         <v>200600</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="36">
         <v>200600001</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="36">
         <v>2</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>1990000</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K21" s="2">
@@ -2903,11 +3485,11 @@
       <c r="L21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="32" t="s">
+      <c r="M21" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N21" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O21" s="2">
         <v>300</v>
@@ -2921,13 +3503,13 @@
       <c r="R21" s="2">
         <v>15000</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="34">
         <v>16008</v>
       </c>
       <c r="T21" s="5">
         <v>20</v>
       </c>
-      <c r="U21" s="34">
+      <c r="U21" s="35">
         <v>0</v>
       </c>
       <c r="V21" t="s">
@@ -2961,19 +3543,19 @@
       <c r="E22" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G22" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H22" s="28">
         <v>3</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>1990000</v>
       </c>
-      <c r="J22" s="31" t="s">
+      <c r="J22" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K22" s="2">
@@ -2982,11 +3564,11 @@
       <c r="L22" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M22" s="32" t="s">
+      <c r="M22" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N22" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O22" s="2">
         <v>300</v>
@@ -3000,13 +3582,13 @@
       <c r="R22" s="2">
         <v>15000</v>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="34">
         <v>16008</v>
       </c>
       <c r="T22" s="5">
         <v>20</v>
       </c>
-      <c r="U22" s="34">
+      <c r="U22" s="35">
         <v>0</v>
       </c>
       <c r="V22" t="s">
@@ -3040,19 +3622,19 @@
       <c r="E23" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H23" s="28">
         <v>1</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="31">
         <v>1990000</v>
       </c>
-      <c r="J23" s="31" t="s">
+      <c r="J23" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K23" s="2">
@@ -3061,11 +3643,11 @@
       <c r="L23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="32" t="s">
+      <c r="M23" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N23" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O23" s="2">
         <v>300</v>
@@ -3079,13 +3661,13 @@
       <c r="R23" s="2">
         <v>15000</v>
       </c>
-      <c r="S23" s="33">
+      <c r="S23" s="34">
         <v>16008</v>
       </c>
       <c r="T23" s="5">
         <v>30</v>
       </c>
-      <c r="U23" s="34">
+      <c r="U23" s="35">
         <v>1</v>
       </c>
       <c r="V23" t="s">
@@ -3107,31 +3689,31 @@
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="36">
         <v>200700</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="36">
         <v>200700001</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="36">
         <v>2</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>1990000</v>
       </c>
-      <c r="J24" s="36" t="s">
+      <c r="J24" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K24" s="2">
@@ -3140,11 +3722,11 @@
       <c r="L24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N24" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O24" s="2">
         <v>300</v>
@@ -3158,13 +3740,13 @@
       <c r="R24" s="2">
         <v>15000</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="34">
         <v>16008</v>
       </c>
       <c r="T24" s="5">
         <v>30</v>
       </c>
-      <c r="U24" s="34">
+      <c r="U24" s="35">
         <v>1</v>
       </c>
       <c r="V24" t="s">
@@ -3181,7 +3763,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="25" spans="1:25" s="2" customFormat="1">
+    <row r="25" s="2" customFormat="1" spans="1:25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -3198,19 +3780,19 @@
       <c r="E25" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="29" t="s">
+      <c r="G25" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H25" s="28">
         <v>3</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>1990000</v>
       </c>
-      <c r="J25" s="31" t="s">
+      <c r="J25" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K25" s="2">
@@ -3219,11 +3801,11 @@
       <c r="L25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M25" s="32" t="s">
+      <c r="M25" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N25" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O25" s="2">
         <v>300</v>
@@ -3237,13 +3819,13 @@
       <c r="R25" s="2">
         <v>15000</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="34">
         <v>16008</v>
       </c>
       <c r="T25" s="5">
         <v>30</v>
       </c>
-      <c r="U25" s="34">
+      <c r="U25" s="35">
         <v>1</v>
       </c>
       <c r="V25" t="s">
@@ -3260,7 +3842,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="26" spans="1:25" s="2" customFormat="1">
+    <row r="26" s="2" customFormat="1" spans="1:25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -3274,22 +3856,22 @@
       <c r="D26" s="28">
         <v>200800001</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="29" t="s">
+      <c r="G26" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H26" s="28">
         <v>1</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="31">
         <v>1990000</v>
       </c>
-      <c r="J26" s="31" t="s">
+      <c r="J26" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K26" s="2">
@@ -3298,11 +3880,11 @@
       <c r="L26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="32" t="s">
+      <c r="M26" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N26" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O26" s="2">
         <v>300</v>
@@ -3316,13 +3898,13 @@
       <c r="R26" s="2">
         <v>15000</v>
       </c>
-      <c r="S26" s="33">
+      <c r="S26" s="34">
         <v>16008</v>
       </c>
       <c r="T26" s="5">
         <v>20</v>
       </c>
-      <c r="U26" s="34">
+      <c r="U26" s="35">
         <v>0</v>
       </c>
       <c r="V26" t="s">
@@ -3339,7 +3921,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="27" spans="1:25" s="2" customFormat="1">
+    <row r="27" s="2" customFormat="1" spans="1:25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -3353,22 +3935,22 @@
       <c r="D27" s="28">
         <v>200800001</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="36">
         <v>2</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="31">
         <v>1990000</v>
       </c>
-      <c r="J27" s="36" t="s">
+      <c r="J27" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K27" s="2">
@@ -3377,11 +3959,11 @@
       <c r="L27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="32" t="s">
+      <c r="M27" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N27" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O27" s="2">
         <v>300</v>
@@ -3395,13 +3977,13 @@
       <c r="R27" s="2">
         <v>15000</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>16008</v>
       </c>
       <c r="T27" s="5">
         <v>20</v>
       </c>
-      <c r="U27" s="34">
+      <c r="U27" s="35">
         <v>0</v>
       </c>
       <c r="V27" t="s">
@@ -3418,7 +4000,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="28" spans="1:25" s="2" customFormat="1">
+    <row r="28" s="2" customFormat="1" spans="1:25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -3435,19 +4017,19 @@
       <c r="E28" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G28" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H28" s="28">
         <v>3</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="31">
         <v>1990000</v>
       </c>
-      <c r="J28" s="31" t="s">
+      <c r="J28" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K28" s="2">
@@ -3456,11 +4038,11 @@
       <c r="L28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M28" s="32" t="s">
+      <c r="M28" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N28" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O28" s="2">
         <v>300</v>
@@ -3474,13 +4056,13 @@
       <c r="R28" s="2">
         <v>15000</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="34">
         <v>16008</v>
       </c>
       <c r="T28" s="5">
         <v>20</v>
       </c>
-      <c r="U28" s="34">
+      <c r="U28" s="35">
         <v>0</v>
       </c>
       <c r="V28" t="s">
@@ -3497,12 +4079,12 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="29" spans="1:25" s="2" customFormat="1">
+    <row r="29" s="2" customFormat="1" spans="1:25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="39">
+      <c r="B29" s="40">
         <v>200900</v>
       </c>
       <c r="C29" s="28" t="s">
@@ -3511,35 +4093,35 @@
       <c r="D29" s="28">
         <v>200900001</v>
       </c>
-      <c r="E29" s="37" t="s">
+      <c r="E29" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="29" t="s">
+      <c r="G29" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H29" s="28">
         <v>1</v>
       </c>
-      <c r="I29" s="30">
+      <c r="I29" s="31">
         <v>1990000</v>
       </c>
-      <c r="J29" s="31" t="s">
+      <c r="J29" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="40">
+      <c r="K29" s="41">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M29" s="32" t="s">
+      <c r="M29" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N29" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O29" s="2">
         <v>300</v>
@@ -3553,13 +4135,13 @@
       <c r="R29" s="2">
         <v>15000</v>
       </c>
-      <c r="S29" s="33">
+      <c r="S29" s="34">
         <v>16008</v>
       </c>
       <c r="T29" s="5">
         <v>20</v>
       </c>
-      <c r="U29" s="34">
+      <c r="U29" s="35">
         <v>0</v>
       </c>
       <c r="V29" t="s">
@@ -3581,44 +4163,44 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="42">
         <v>200900</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>200900001</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="29" t="s">
+      <c r="G30" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>2</v>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="31">
         <v>1990000</v>
       </c>
-      <c r="J30" s="36" t="s">
+      <c r="J30" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="40">
+      <c r="K30" s="41">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M30" s="32" t="s">
+      <c r="M30" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N30" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O30" s="2">
         <v>300</v>
@@ -3632,13 +4214,13 @@
       <c r="R30" s="2">
         <v>15000</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="34">
         <v>16008</v>
       </c>
       <c r="T30" s="5">
         <v>20</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="35">
         <v>0</v>
       </c>
       <c r="V30" t="s">
@@ -3660,7 +4242,7 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="39">
+      <c r="B31" s="40">
         <v>200900</v>
       </c>
       <c r="C31" s="28" t="s">
@@ -3672,32 +4254,32 @@
       <c r="E31" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="G31" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H31" s="28">
         <v>3</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="31">
         <v>1990000</v>
       </c>
-      <c r="J31" s="31" t="s">
+      <c r="J31" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="40">
+      <c r="K31" s="41">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M31" s="32" t="s">
+      <c r="M31" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N31" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O31" s="2">
         <v>300</v>
@@ -3711,13 +4293,13 @@
       <c r="R31" s="2">
         <v>15000</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="34">
         <v>16008</v>
       </c>
       <c r="T31" s="5">
         <v>20</v>
       </c>
-      <c r="U31" s="34">
+      <c r="U31" s="35">
         <v>0</v>
       </c>
       <c r="V31" t="s">
@@ -3734,49 +4316,49 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="32" spans="1:25" s="2" customFormat="1">
+    <row r="32" s="2" customFormat="1" spans="1:25">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>2012001</v>
       </c>
-      <c r="B32" s="42">
+      <c r="B32" s="43">
         <v>201200</v>
       </c>
       <c r="C32" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="36">
         <v>201200001</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="E32" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="G32" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H32" s="28">
         <v>1</v>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="31">
         <v>1990000</v>
       </c>
-      <c r="J32" s="31" t="s">
+      <c r="J32" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="40">
+      <c r="K32" s="41">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M32" s="32" t="s">
+      <c r="M32" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N32" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O32" s="2">
         <v>300</v>
@@ -3790,13 +4372,13 @@
       <c r="R32" s="2">
         <v>15000</v>
       </c>
-      <c r="S32" s="33">
+      <c r="S32" s="34">
         <v>16008</v>
       </c>
       <c r="T32" s="5">
         <v>12</v>
       </c>
-      <c r="U32" s="34">
+      <c r="U32" s="35">
         <v>0</v>
       </c>
       <c r="V32" t="s">
@@ -3818,44 +4400,44 @@
         <f t="shared" si="0"/>
         <v>2012002</v>
       </c>
-      <c r="B33" s="42">
+      <c r="B33" s="43">
         <v>201200</v>
       </c>
       <c r="C33" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>201200001</v>
       </c>
-      <c r="E33" s="35" t="s">
+      <c r="E33" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="50" t="s">
+      <c r="F33" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="29" t="s">
+      <c r="G33" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>2</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="31">
         <v>1990000</v>
       </c>
-      <c r="J33" s="36" t="s">
+      <c r="J33" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="40">
+      <c r="K33" s="41">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="32" t="s">
+      <c r="M33" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N33" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O33" s="2">
         <v>300</v>
@@ -3869,13 +4451,13 @@
       <c r="R33" s="2">
         <v>15000</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="34">
         <v>16008</v>
       </c>
       <c r="T33" s="5">
         <v>12</v>
       </c>
-      <c r="U33" s="34">
+      <c r="U33" s="35">
         <v>0</v>
       </c>
       <c r="V33" t="s">
@@ -3897,44 +4479,44 @@
         <f t="shared" si="0"/>
         <v>2012003</v>
       </c>
-      <c r="B34" s="42">
+      <c r="B34" s="43">
         <v>201200</v>
       </c>
       <c r="C34" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>201200001</v>
       </c>
       <c r="E34" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H34" s="28">
         <v>3</v>
       </c>
-      <c r="I34" s="30">
+      <c r="I34" s="31">
         <v>1990000</v>
       </c>
-      <c r="J34" s="31" t="s">
+      <c r="J34" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="40">
+      <c r="K34" s="41">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M34" s="32" t="s">
+      <c r="M34" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N34" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O34" s="2">
         <v>300</v>
@@ -3948,13 +4530,13 @@
       <c r="R34" s="2">
         <v>15000</v>
       </c>
-      <c r="S34" s="33">
+      <c r="S34" s="34">
         <v>16008</v>
       </c>
       <c r="T34" s="5">
         <v>12</v>
       </c>
-      <c r="U34" s="34">
+      <c r="U34" s="35">
         <v>0</v>
       </c>
       <c r="V34" t="s">
@@ -3971,35 +4553,35 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="35" spans="1:25" s="3" customFormat="1">
-      <c r="A35" s="43">
+    <row r="35" s="3" customFormat="1" spans="1:25">
+      <c r="A35" s="44">
         <v>20010010</v>
       </c>
       <c r="B35" s="3">
         <v>200100</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="C35" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="45">
         <v>200100038</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="45" t="s">
+      <c r="G35" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="44">
+      <c r="H35" s="45">
         <v>10</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="45">
         <v>1980000</v>
       </c>
-      <c r="J35" s="31" t="s">
+      <c r="J35" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K35" s="3">
@@ -4008,11 +4590,11 @@
       <c r="L35" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M35" s="46" t="s">
+      <c r="M35" s="48" t="s">
         <v>56</v>
       </c>
       <c r="N35" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O35" s="3">
         <v>300</v>
@@ -4026,13 +4608,13 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="47">
+      <c r="S35" s="49">
         <v>16008</v>
       </c>
-      <c r="T35" s="43">
+      <c r="T35" s="44">
         <v>48</v>
       </c>
-      <c r="U35" s="48">
+      <c r="U35" s="50">
         <v>0</v>
       </c>
       <c r="V35" t="s">
@@ -4044,37 +4626,37 @@
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="49"/>
-    </row>
-    <row r="36" spans="1:25" s="3" customFormat="1">
-      <c r="A36" s="43">
+      <c r="Y35" s="51"/>
+    </row>
+    <row r="36" s="3" customFormat="1" spans="1:25">
+      <c r="A36" s="44">
         <v>20010011</v>
       </c>
       <c r="B36" s="3">
         <v>200100</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="C36" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="45">
         <v>200100038</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="51" t="s">
+      <c r="F36" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="45" t="s">
+      <c r="G36" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H36" s="44">
+      <c r="H36" s="45">
         <v>11</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="45">
         <v>1980000</v>
       </c>
-      <c r="J36" s="36" t="s">
+      <c r="J36" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K36" s="3">
@@ -4083,11 +4665,11 @@
       <c r="L36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M36" s="46" t="s">
+      <c r="M36" s="48" t="s">
         <v>56</v>
       </c>
       <c r="N36" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O36" s="3">
         <v>300</v>
@@ -4101,13 +4683,13 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="47">
+      <c r="S36" s="49">
         <v>16008</v>
       </c>
-      <c r="T36" s="43">
+      <c r="T36" s="44">
         <v>48</v>
       </c>
-      <c r="U36" s="48">
+      <c r="U36" s="50">
         <v>0</v>
       </c>
       <c r="V36" t="s">
@@ -4119,37 +4701,37 @@
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="49"/>
-    </row>
-    <row r="37" spans="1:25" s="3" customFormat="1">
-      <c r="A37" s="43">
+      <c r="Y36" s="51"/>
+    </row>
+    <row r="37" s="3" customFormat="1" spans="1:25">
+      <c r="A37" s="44">
         <v>20010012</v>
       </c>
       <c r="B37" s="3">
         <v>200100</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="C37" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="45">
         <v>200100038</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E37" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="51" t="s">
+      <c r="F37" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="45" t="s">
+      <c r="G37" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H37" s="44">
+      <c r="H37" s="45">
         <v>12</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="45">
         <v>1980000</v>
       </c>
-      <c r="J37" s="31" t="s">
+      <c r="J37" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K37" s="3">
@@ -4158,11 +4740,11 @@
       <c r="L37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M37" s="46" t="s">
+      <c r="M37" s="48" t="s">
         <v>56</v>
       </c>
       <c r="N37" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O37" s="3">
         <v>300</v>
@@ -4176,13 +4758,13 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="47">
+      <c r="S37" s="49">
         <v>16008</v>
       </c>
-      <c r="T37" s="43">
+      <c r="T37" s="44">
         <v>48</v>
       </c>
-      <c r="U37" s="48">
+      <c r="U37" s="50">
         <v>0</v>
       </c>
       <c r="V37" t="s">
@@ -4194,10 +4776,10 @@
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="49"/>
-    </row>
-    <row r="38" spans="1:25" s="3" customFormat="1">
-      <c r="A38" s="43">
+      <c r="Y37" s="51"/>
+    </row>
+    <row r="38" s="3" customFormat="1" spans="1:25">
+      <c r="A38" s="44">
         <v>20010110</v>
       </c>
       <c r="B38" s="3">
@@ -4212,19 +4794,19 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="52" t="s">
+      <c r="F38" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G38" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H38" s="44">
+      <c r="H38" s="45">
         <v>10</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="45">
         <v>1980000</v>
       </c>
-      <c r="J38" s="31" t="s">
+      <c r="J38" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K38" s="3">
@@ -4233,11 +4815,11 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="46" t="s">
+      <c r="M38" s="48" t="s">
         <v>69</v>
       </c>
       <c r="N38" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O38" s="3">
         <v>300</v>
@@ -4254,10 +4836,10 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="43">
+      <c r="T38" s="44">
         <v>48</v>
       </c>
-      <c r="U38" s="48">
+      <c r="U38" s="50">
         <v>0</v>
       </c>
       <c r="V38" t="s">
@@ -4269,10 +4851,10 @@
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="49"/>
-    </row>
-    <row r="39" spans="1:25" s="3" customFormat="1">
-      <c r="A39" s="43">
+      <c r="Y38" s="51"/>
+    </row>
+    <row r="39" s="3" customFormat="1" spans="1:25">
+      <c r="A39" s="44">
         <v>20010111</v>
       </c>
       <c r="B39" s="3">
@@ -4287,19 +4869,19 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="52" t="s">
+      <c r="F39" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="45" t="s">
+      <c r="G39" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H39" s="44">
+      <c r="H39" s="45">
         <v>11</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="45">
         <v>1980000</v>
       </c>
-      <c r="J39" s="36" t="s">
+      <c r="J39" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K39" s="3">
@@ -4308,11 +4890,11 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="46" t="s">
+      <c r="M39" s="48" t="s">
         <v>69</v>
       </c>
       <c r="N39" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O39" s="3">
         <v>300</v>
@@ -4329,10 +4911,10 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="43">
+      <c r="T39" s="44">
         <v>48</v>
       </c>
-      <c r="U39" s="48">
+      <c r="U39" s="50">
         <v>0</v>
       </c>
       <c r="V39" t="s">
@@ -4344,10 +4926,10 @@
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="49"/>
-    </row>
-    <row r="40" spans="1:25" s="3" customFormat="1">
-      <c r="A40" s="43">
+      <c r="Y39" s="51"/>
+    </row>
+    <row r="40" s="3" customFormat="1" spans="1:25">
+      <c r="A40" s="44">
         <v>20010112</v>
       </c>
       <c r="B40" s="3">
@@ -4362,19 +4944,19 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="52" t="s">
+      <c r="F40" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="45" t="s">
+      <c r="G40" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H40" s="44">
+      <c r="H40" s="45">
         <v>12</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="45">
         <v>1980000</v>
       </c>
-      <c r="J40" s="31" t="s">
+      <c r="J40" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K40" s="3">
@@ -4383,11 +4965,11 @@
       <c r="L40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="46" t="s">
+      <c r="M40" s="48" t="s">
         <v>69</v>
       </c>
       <c r="N40" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O40" s="3">
         <v>300</v>
@@ -4404,10 +4986,10 @@
       <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="43">
+      <c r="T40" s="44">
         <v>48</v>
       </c>
-      <c r="U40" s="48">
+      <c r="U40" s="50">
         <v>0</v>
       </c>
       <c r="V40" t="s">
@@ -4419,10 +5001,10 @@
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="49"/>
-    </row>
-    <row r="41" spans="1:25" s="3" customFormat="1">
-      <c r="A41" s="43">
+      <c r="Y40" s="51"/>
+    </row>
+    <row r="41" s="3" customFormat="1" spans="1:25">
+      <c r="A41" s="44">
         <v>20030010</v>
       </c>
       <c r="B41" s="3">
@@ -4437,19 +5019,19 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="52" t="s">
+      <c r="F41" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="45" t="s">
+      <c r="G41" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H41" s="44">
+      <c r="H41" s="45">
         <v>10</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="45">
         <v>1980000</v>
       </c>
-      <c r="J41" s="31" t="s">
+      <c r="J41" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K41" s="3">
@@ -4458,11 +5040,11 @@
       <c r="L41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="46" t="s">
+      <c r="M41" s="48" t="s">
         <v>71</v>
       </c>
       <c r="N41" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
@@ -4479,10 +5061,10 @@
       <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="43">
+      <c r="T41" s="44">
         <v>50</v>
       </c>
-      <c r="U41" s="48">
+      <c r="U41" s="50">
         <v>0</v>
       </c>
       <c r="V41" t="s">
@@ -4494,10 +5076,10 @@
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="49"/>
-    </row>
-    <row r="42" spans="1:25" s="3" customFormat="1">
-      <c r="A42" s="43">
+      <c r="Y41" s="51"/>
+    </row>
+    <row r="42" s="3" customFormat="1" spans="1:25">
+      <c r="A42" s="44">
         <v>20030011</v>
       </c>
       <c r="B42" s="3">
@@ -4512,19 +5094,19 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="52" t="s">
+      <c r="F42" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="45" t="s">
+      <c r="G42" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H42" s="44">
+      <c r="H42" s="45">
         <v>11</v>
       </c>
-      <c r="I42" s="44">
+      <c r="I42" s="45">
         <v>1980000</v>
       </c>
-      <c r="J42" s="36" t="s">
+      <c r="J42" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K42" s="3">
@@ -4533,11 +5115,11 @@
       <c r="L42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="46" t="s">
+      <c r="M42" s="48" t="s">
         <v>71</v>
       </c>
       <c r="N42" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O42" s="3">
         <v>300</v>
@@ -4554,10 +5136,10 @@
       <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="43">
+      <c r="T42" s="44">
         <v>50</v>
       </c>
-      <c r="U42" s="48">
+      <c r="U42" s="50">
         <v>0</v>
       </c>
       <c r="V42" t="s">
@@ -4569,10 +5151,10 @@
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="49"/>
-    </row>
-    <row r="43" spans="1:25" s="3" customFormat="1">
-      <c r="A43" s="43">
+      <c r="Y42" s="51"/>
+    </row>
+    <row r="43" s="3" customFormat="1" spans="1:25">
+      <c r="A43" s="44">
         <v>20030012</v>
       </c>
       <c r="B43" s="3">
@@ -4587,19 +5169,19 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="52" t="s">
+      <c r="F43" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="45" t="s">
+      <c r="G43" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H43" s="44">
+      <c r="H43" s="45">
         <v>12</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="45">
         <v>1980000</v>
       </c>
-      <c r="J43" s="31" t="s">
+      <c r="J43" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K43" s="3">
@@ -4608,11 +5190,11 @@
       <c r="L43" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="46" t="s">
+      <c r="M43" s="48" t="s">
         <v>71</v>
       </c>
       <c r="N43" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
@@ -4629,10 +5211,10 @@
       <c r="S43" s="3">
         <v>16008</v>
       </c>
-      <c r="T43" s="43">
+      <c r="T43" s="44">
         <v>50</v>
       </c>
-      <c r="U43" s="48">
+      <c r="U43" s="50">
         <v>0</v>
       </c>
       <c r="V43" t="s">
@@ -4644,10 +5226,10 @@
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="49"/>
-    </row>
-    <row r="44" spans="1:25" s="3" customFormat="1">
-      <c r="A44" s="43">
+      <c r="Y43" s="51"/>
+    </row>
+    <row r="44" s="3" customFormat="1" spans="1:25">
+      <c r="A44" s="44">
         <v>20040010</v>
       </c>
       <c r="B44" s="3">
@@ -4662,19 +5244,19 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="52" t="s">
+      <c r="F44" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H44" s="44">
+      <c r="H44" s="45">
         <v>10</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="45">
         <v>1980000</v>
       </c>
-      <c r="J44" s="31" t="s">
+      <c r="J44" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K44" s="3">
@@ -4683,11 +5265,11 @@
       <c r="L44" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M44" s="46" t="s">
+      <c r="M44" s="48" t="s">
         <v>73</v>
       </c>
       <c r="N44" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
@@ -4704,10 +5286,10 @@
       <c r="S44" s="3">
         <v>16008</v>
       </c>
-      <c r="T44" s="43">
+      <c r="T44" s="44">
         <v>50</v>
       </c>
-      <c r="U44" s="48">
+      <c r="U44" s="50">
         <v>0</v>
       </c>
       <c r="V44" t="s">
@@ -4719,10 +5301,10 @@
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="49"/>
-    </row>
-    <row r="45" spans="1:25" s="3" customFormat="1">
-      <c r="A45" s="43">
+      <c r="Y44" s="51"/>
+    </row>
+    <row r="45" s="3" customFormat="1" spans="1:25">
+      <c r="A45" s="44">
         <v>20040011</v>
       </c>
       <c r="B45" s="3">
@@ -4737,19 +5319,19 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="52" t="s">
+      <c r="F45" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="45" t="s">
+      <c r="G45" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H45" s="44">
+      <c r="H45" s="45">
         <v>11</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="45">
         <v>1980000</v>
       </c>
-      <c r="J45" s="36" t="s">
+      <c r="J45" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K45" s="3">
@@ -4758,11 +5340,11 @@
       <c r="L45" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M45" s="46" t="s">
+      <c r="M45" s="48" t="s">
         <v>73</v>
       </c>
       <c r="N45" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
@@ -4779,10 +5361,10 @@
       <c r="S45" s="3">
         <v>16008</v>
       </c>
-      <c r="T45" s="43">
+      <c r="T45" s="44">
         <v>50</v>
       </c>
-      <c r="U45" s="48">
+      <c r="U45" s="50">
         <v>0</v>
       </c>
       <c r="V45" t="s">
@@ -4794,10 +5376,10 @@
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="49"/>
-    </row>
-    <row r="46" spans="1:25" s="3" customFormat="1">
-      <c r="A46" s="43">
+      <c r="Y45" s="51"/>
+    </row>
+    <row r="46" s="3" customFormat="1" spans="1:25">
+      <c r="A46" s="44">
         <v>20040012</v>
       </c>
       <c r="B46" s="3">
@@ -4812,19 +5394,19 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="52" t="s">
+      <c r="F46" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="45" t="s">
+      <c r="G46" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H46" s="44">
+      <c r="H46" s="45">
         <v>12</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="45">
         <v>1980000</v>
       </c>
-      <c r="J46" s="31" t="s">
+      <c r="J46" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K46" s="3">
@@ -4833,11 +5415,11 @@
       <c r="L46" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M46" s="46" t="s">
+      <c r="M46" s="48" t="s">
         <v>73</v>
       </c>
       <c r="N46" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O46" s="3">
         <v>300</v>
@@ -4854,10 +5436,10 @@
       <c r="S46" s="3">
         <v>16008</v>
       </c>
-      <c r="T46" s="43">
+      <c r="T46" s="44">
         <v>50</v>
       </c>
-      <c r="U46" s="48">
+      <c r="U46" s="50">
         <v>0</v>
       </c>
       <c r="V46" t="s">
@@ -4869,10 +5451,10 @@
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="49"/>
-    </row>
-    <row r="47" spans="1:25" s="3" customFormat="1">
-      <c r="A47" s="43">
+      <c r="Y46" s="51"/>
+    </row>
+    <row r="47" s="3" customFormat="1" spans="1:25">
+      <c r="A47" s="44">
         <v>20050010</v>
       </c>
       <c r="B47" s="3">
@@ -4887,19 +5469,19 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="52" t="s">
+      <c r="F47" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="45" t="s">
+      <c r="G47" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H47" s="44">
+      <c r="H47" s="45">
         <v>10</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="45">
         <v>1980000</v>
       </c>
-      <c r="J47" s="31" t="s">
+      <c r="J47" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K47" s="3">
@@ -4908,11 +5490,11 @@
       <c r="L47" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M47" s="46" t="s">
+      <c r="M47" s="48" t="s">
         <v>75</v>
       </c>
       <c r="N47" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
@@ -4929,10 +5511,10 @@
       <c r="S47" s="3">
         <v>16008</v>
       </c>
-      <c r="T47" s="43">
+      <c r="T47" s="44">
         <v>48</v>
       </c>
-      <c r="U47" s="43">
+      <c r="U47" s="44">
         <v>0</v>
       </c>
       <c r="V47" t="s">
@@ -4944,10 +5526,10 @@
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="49"/>
-    </row>
-    <row r="48" spans="1:25" s="3" customFormat="1">
-      <c r="A48" s="43">
+      <c r="Y47" s="51"/>
+    </row>
+    <row r="48" s="3" customFormat="1" spans="1:25">
+      <c r="A48" s="44">
         <v>20050011</v>
       </c>
       <c r="B48" s="3">
@@ -4962,19 +5544,19 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="52" t="s">
+      <c r="F48" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="45" t="s">
+      <c r="G48" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H48" s="44">
+      <c r="H48" s="45">
         <v>11</v>
       </c>
-      <c r="I48" s="44">
+      <c r="I48" s="45">
         <v>1980000</v>
       </c>
-      <c r="J48" s="36" t="s">
+      <c r="J48" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K48" s="3">
@@ -4983,11 +5565,11 @@
       <c r="L48" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M48" s="46" t="s">
+      <c r="M48" s="48" t="s">
         <v>75</v>
       </c>
       <c r="N48" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -5004,10 +5586,10 @@
       <c r="S48" s="3">
         <v>16008</v>
       </c>
-      <c r="T48" s="43">
+      <c r="T48" s="44">
         <v>48</v>
       </c>
-      <c r="U48" s="43">
+      <c r="U48" s="44">
         <v>0</v>
       </c>
       <c r="V48" t="s">
@@ -5019,10 +5601,10 @@
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="49"/>
-    </row>
-    <row r="49" spans="1:25" s="3" customFormat="1">
-      <c r="A49" s="43">
+      <c r="Y48" s="51"/>
+    </row>
+    <row r="49" s="3" customFormat="1" spans="1:25">
+      <c r="A49" s="44">
         <v>20050012</v>
       </c>
       <c r="B49" s="3">
@@ -5037,19 +5619,19 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="52" t="s">
+      <c r="F49" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="45" t="s">
+      <c r="G49" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H49" s="44">
+      <c r="H49" s="45">
         <v>12</v>
       </c>
-      <c r="I49" s="44">
+      <c r="I49" s="45">
         <v>1980000</v>
       </c>
-      <c r="J49" s="31" t="s">
+      <c r="J49" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K49" s="3">
@@ -5058,11 +5640,11 @@
       <c r="L49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M49" s="46" t="s">
+      <c r="M49" s="48" t="s">
         <v>75</v>
       </c>
       <c r="N49" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
@@ -5079,10 +5661,10 @@
       <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="43">
+      <c r="T49" s="44">
         <v>48</v>
       </c>
-      <c r="U49" s="43">
+      <c r="U49" s="44">
         <v>0</v>
       </c>
       <c r="V49" t="s">
@@ -5094,10 +5676,10 @@
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="49"/>
-    </row>
-    <row r="50" spans="1:25" s="3" customFormat="1">
-      <c r="A50" s="43">
+      <c r="Y49" s="51"/>
+    </row>
+    <row r="50" s="3" customFormat="1" spans="1:25">
+      <c r="A50" s="44">
         <v>20060010</v>
       </c>
       <c r="B50" s="3">
@@ -5112,19 +5694,19 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="52" t="s">
+      <c r="F50" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="45" t="s">
+      <c r="G50" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H50" s="44">
+      <c r="H50" s="45">
         <v>10</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="45">
         <v>1980000</v>
       </c>
-      <c r="J50" s="31" t="s">
+      <c r="J50" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K50" s="3">
@@ -5133,11 +5715,11 @@
       <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="46" t="s">
+      <c r="M50" s="48" t="s">
         <v>77</v>
       </c>
       <c r="N50" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O50" s="3">
         <v>300</v>
@@ -5154,10 +5736,10 @@
       <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="43">
+      <c r="T50" s="44">
         <v>20</v>
       </c>
-      <c r="U50" s="43">
+      <c r="U50" s="44">
         <v>0</v>
       </c>
       <c r="V50" t="s">
@@ -5169,10 +5751,10 @@
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="49"/>
-    </row>
-    <row r="51" spans="1:25" s="3" customFormat="1">
-      <c r="A51" s="43">
+      <c r="Y50" s="51"/>
+    </row>
+    <row r="51" s="3" customFormat="1" spans="1:25">
+      <c r="A51" s="44">
         <v>20060011</v>
       </c>
       <c r="B51" s="3">
@@ -5187,19 +5769,19 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="52" t="s">
+      <c r="F51" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="45" t="s">
+      <c r="G51" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H51" s="44">
+      <c r="H51" s="45">
         <v>11</v>
       </c>
-      <c r="I51" s="44">
+      <c r="I51" s="45">
         <v>1980000</v>
       </c>
-      <c r="J51" s="36" t="s">
+      <c r="J51" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K51" s="3">
@@ -5208,11 +5790,11 @@
       <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="46" t="s">
+      <c r="M51" s="48" t="s">
         <v>77</v>
       </c>
       <c r="N51" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O51" s="3">
         <v>300</v>
@@ -5229,10 +5811,10 @@
       <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="43">
+      <c r="T51" s="44">
         <v>20</v>
       </c>
-      <c r="U51" s="43">
+      <c r="U51" s="44">
         <v>0</v>
       </c>
       <c r="V51" t="s">
@@ -5244,10 +5826,10 @@
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="49"/>
-    </row>
-    <row r="52" spans="1:25" s="3" customFormat="1">
-      <c r="A52" s="43">
+      <c r="Y51" s="51"/>
+    </row>
+    <row r="52" s="3" customFormat="1" spans="1:25">
+      <c r="A52" s="44">
         <v>20060012</v>
       </c>
       <c r="B52" s="3">
@@ -5262,19 +5844,19 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="52" t="s">
+      <c r="F52" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="45" t="s">
+      <c r="G52" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H52" s="44">
+      <c r="H52" s="45">
         <v>12</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="45">
         <v>1980000</v>
       </c>
-      <c r="J52" s="31" t="s">
+      <c r="J52" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K52" s="3">
@@ -5283,11 +5865,11 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="46" t="s">
+      <c r="M52" s="48" t="s">
         <v>77</v>
       </c>
       <c r="N52" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
@@ -5304,10 +5886,10 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="43">
+      <c r="T52" s="44">
         <v>20</v>
       </c>
-      <c r="U52" s="43">
+      <c r="U52" s="44">
         <v>0</v>
       </c>
       <c r="V52" t="s">
@@ -5319,10 +5901,10 @@
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="49"/>
-    </row>
-    <row r="53" spans="1:25" s="3" customFormat="1">
-      <c r="A53" s="43">
+      <c r="Y52" s="51"/>
+    </row>
+    <row r="53" s="3" customFormat="1" spans="1:25">
+      <c r="A53" s="44">
         <v>20070010</v>
       </c>
       <c r="B53" s="3">
@@ -5337,19 +5919,19 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="52" t="s">
+      <c r="F53" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="45" t="s">
+      <c r="G53" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H53" s="44">
+      <c r="H53" s="45">
         <v>10</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="45">
         <v>1980000</v>
       </c>
-      <c r="J53" s="31" t="s">
+      <c r="J53" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K53" s="3">
@@ -5358,11 +5940,11 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="46" t="s">
+      <c r="M53" s="48" t="s">
         <v>79</v>
       </c>
       <c r="N53" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O53" s="3">
         <v>300</v>
@@ -5379,10 +5961,10 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="43">
+      <c r="T53" s="44">
         <v>30</v>
       </c>
-      <c r="U53" s="43">
+      <c r="U53" s="44">
         <v>1</v>
       </c>
       <c r="V53" t="s">
@@ -5394,10 +5976,10 @@
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="49"/>
-    </row>
-    <row r="54" spans="1:25" s="3" customFormat="1">
-      <c r="A54" s="43">
+      <c r="Y53" s="51"/>
+    </row>
+    <row r="54" s="3" customFormat="1" spans="1:25">
+      <c r="A54" s="44">
         <v>20070011</v>
       </c>
       <c r="B54" s="3">
@@ -5412,19 +5994,19 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="52" t="s">
+      <c r="F54" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="45" t="s">
+      <c r="G54" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H54" s="44">
+      <c r="H54" s="45">
         <v>11</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="45">
         <v>1980000</v>
       </c>
-      <c r="J54" s="36" t="s">
+      <c r="J54" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K54" s="3">
@@ -5433,11 +6015,11 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="46" t="s">
+      <c r="M54" s="48" t="s">
         <v>79</v>
       </c>
       <c r="N54" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O54" s="3">
         <v>300</v>
@@ -5454,10 +6036,10 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="43">
+      <c r="T54" s="44">
         <v>30</v>
       </c>
-      <c r="U54" s="43">
+      <c r="U54" s="44">
         <v>1</v>
       </c>
       <c r="V54" t="s">
@@ -5469,10 +6051,10 @@
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="49"/>
-    </row>
-    <row r="55" spans="1:25" s="3" customFormat="1">
-      <c r="A55" s="43">
+      <c r="Y54" s="51"/>
+    </row>
+    <row r="55" s="3" customFormat="1" spans="1:25">
+      <c r="A55" s="44">
         <v>20070012</v>
       </c>
       <c r="B55" s="3">
@@ -5487,19 +6069,19 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="52" t="s">
+      <c r="F55" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="45" t="s">
+      <c r="G55" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H55" s="44">
+      <c r="H55" s="45">
         <v>12</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="45">
         <v>1980000</v>
       </c>
-      <c r="J55" s="31" t="s">
+      <c r="J55" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K55" s="3">
@@ -5508,11 +6090,11 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="46" t="s">
+      <c r="M55" s="48" t="s">
         <v>79</v>
       </c>
       <c r="N55" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O55" s="3">
         <v>300</v>
@@ -5529,10 +6111,10 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="43">
+      <c r="T55" s="44">
         <v>30</v>
       </c>
-      <c r="U55" s="43">
+      <c r="U55" s="44">
         <v>1</v>
       </c>
       <c r="V55" t="s">
@@ -5544,10 +6126,10 @@
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="49"/>
-    </row>
-    <row r="56" spans="1:25" s="3" customFormat="1">
-      <c r="A56" s="43">
+      <c r="Y55" s="51"/>
+    </row>
+    <row r="56" s="3" customFormat="1" spans="1:25">
+      <c r="A56" s="44">
         <v>20080010</v>
       </c>
       <c r="B56" s="3">
@@ -5562,19 +6144,19 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="52" t="s">
+      <c r="F56" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="45" t="s">
+      <c r="G56" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H56" s="44">
+      <c r="H56" s="45">
         <v>10</v>
       </c>
-      <c r="I56" s="44">
+      <c r="I56" s="45">
         <v>1980000</v>
       </c>
-      <c r="J56" s="31" t="s">
+      <c r="J56" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K56" s="3">
@@ -5583,11 +6165,11 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="46" t="s">
+      <c r="M56" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N56" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O56" s="3">
         <v>300</v>
@@ -5604,10 +6186,10 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="43">
+      <c r="T56" s="44">
         <v>20</v>
       </c>
-      <c r="U56" s="43">
+      <c r="U56" s="44">
         <v>0</v>
       </c>
       <c r="V56" t="s">
@@ -5619,10 +6201,10 @@
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="49"/>
-    </row>
-    <row r="57" spans="1:25" s="3" customFormat="1">
-      <c r="A57" s="43">
+      <c r="Y56" s="51"/>
+    </row>
+    <row r="57" s="3" customFormat="1" spans="1:25">
+      <c r="A57" s="44">
         <v>20080011</v>
       </c>
       <c r="B57" s="3">
@@ -5637,19 +6219,19 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="52" t="s">
+      <c r="F57" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="45" t="s">
+      <c r="G57" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H57" s="44">
+      <c r="H57" s="45">
         <v>11</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="45">
         <v>1980000</v>
       </c>
-      <c r="J57" s="36" t="s">
+      <c r="J57" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K57" s="3">
@@ -5658,11 +6240,11 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="46" t="s">
+      <c r="M57" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O57" s="3">
         <v>300</v>
@@ -5679,10 +6261,10 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="43">
+      <c r="T57" s="44">
         <v>20</v>
       </c>
-      <c r="U57" s="43">
+      <c r="U57" s="44">
         <v>0</v>
       </c>
       <c r="V57" t="s">
@@ -5694,10 +6276,10 @@
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="49"/>
-    </row>
-    <row r="58" spans="1:25" s="3" customFormat="1">
-      <c r="A58" s="43">
+      <c r="Y57" s="51"/>
+    </row>
+    <row r="58" s="3" customFormat="1" spans="1:25">
+      <c r="A58" s="44">
         <v>20080012</v>
       </c>
       <c r="B58" s="3">
@@ -5712,19 +6294,19 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="52" t="s">
+      <c r="F58" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="45" t="s">
+      <c r="G58" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H58" s="44">
+      <c r="H58" s="45">
         <v>12</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="45">
         <v>1980000</v>
       </c>
-      <c r="J58" s="31" t="s">
+      <c r="J58" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K58" s="3">
@@ -5733,11 +6315,11 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="46" t="s">
+      <c r="M58" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N58" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -5754,10 +6336,10 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="43">
+      <c r="T58" s="44">
         <v>20</v>
       </c>
-      <c r="U58" s="43">
+      <c r="U58" s="44">
         <v>0</v>
       </c>
       <c r="V58" t="s">
@@ -5769,10 +6351,10 @@
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="49"/>
-    </row>
-    <row r="59" spans="1:25" s="3" customFormat="1">
-      <c r="A59" s="43">
+      <c r="Y58" s="51"/>
+    </row>
+    <row r="59" s="3" customFormat="1" spans="1:25">
+      <c r="A59" s="44">
         <v>20090010</v>
       </c>
       <c r="B59" s="3">
@@ -5787,19 +6369,19 @@
       <c r="E59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="52" t="s">
+      <c r="F59" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G59" s="45" t="s">
+      <c r="G59" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H59" s="44">
+      <c r="H59" s="45">
         <v>10</v>
       </c>
-      <c r="I59" s="44">
+      <c r="I59" s="45">
         <v>1980000</v>
       </c>
-      <c r="J59" s="31" t="s">
+      <c r="J59" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K59" s="3">
@@ -5808,11 +6390,11 @@
       <c r="L59" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M59" s="46" t="s">
+      <c r="M59" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N59" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
@@ -5829,10 +6411,10 @@
       <c r="S59" s="3">
         <v>16008</v>
       </c>
-      <c r="T59" s="43">
+      <c r="T59" s="44">
         <v>20</v>
       </c>
-      <c r="U59" s="43">
+      <c r="U59" s="44">
         <v>0</v>
       </c>
       <c r="V59" t="s">
@@ -5844,10 +6426,10 @@
       <c r="X59" s="3">
         <v>1</v>
       </c>
-      <c r="Y59" s="49"/>
-    </row>
-    <row r="60" spans="1:25" s="3" customFormat="1">
-      <c r="A60" s="43">
+      <c r="Y59" s="51"/>
+    </row>
+    <row r="60" s="3" customFormat="1" spans="1:25">
+      <c r="A60" s="44">
         <v>20090011</v>
       </c>
       <c r="B60" s="3">
@@ -5862,19 +6444,19 @@
       <c r="E60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F60" s="52" t="s">
+      <c r="F60" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G60" s="45" t="s">
+      <c r="G60" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H60" s="44">
+      <c r="H60" s="45">
         <v>11</v>
       </c>
-      <c r="I60" s="44">
+      <c r="I60" s="45">
         <v>1980000</v>
       </c>
-      <c r="J60" s="36" t="s">
+      <c r="J60" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K60" s="3">
@@ -5883,11 +6465,11 @@
       <c r="L60" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M60" s="46" t="s">
+      <c r="M60" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N60" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O60" s="3">
         <v>300</v>
@@ -5904,10 +6486,10 @@
       <c r="S60" s="3">
         <v>16008</v>
       </c>
-      <c r="T60" s="43">
+      <c r="T60" s="44">
         <v>20</v>
       </c>
-      <c r="U60" s="43">
+      <c r="U60" s="44">
         <v>0</v>
       </c>
       <c r="V60" t="s">
@@ -5919,10 +6501,10 @@
       <c r="X60" s="3">
         <v>1</v>
       </c>
-      <c r="Y60" s="49"/>
-    </row>
-    <row r="61" spans="1:25" s="3" customFormat="1">
-      <c r="A61" s="43">
+      <c r="Y60" s="51"/>
+    </row>
+    <row r="61" s="3" customFormat="1" spans="1:25">
+      <c r="A61" s="44">
         <v>20090012</v>
       </c>
       <c r="B61" s="3">
@@ -5937,19 +6519,19 @@
       <c r="E61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G61" s="45" t="s">
+      <c r="G61" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H61" s="44">
+      <c r="H61" s="45">
         <v>12</v>
       </c>
-      <c r="I61" s="44">
+      <c r="I61" s="45">
         <v>1980000</v>
       </c>
-      <c r="J61" s="31" t="s">
+      <c r="J61" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K61" s="3">
@@ -5958,11 +6540,11 @@
       <c r="L61" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M61" s="46" t="s">
+      <c r="M61" s="48" t="s">
         <v>81</v>
       </c>
       <c r="N61" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>
@@ -5979,10 +6561,10 @@
       <c r="S61" s="3">
         <v>16008</v>
       </c>
-      <c r="T61" s="43">
+      <c r="T61" s="44">
         <v>20</v>
       </c>
-      <c r="U61" s="43">
+      <c r="U61" s="44">
         <v>0</v>
       </c>
       <c r="V61" t="s">
@@ -5994,13 +6576,13 @@
       <c r="X61" s="3">
         <v>1</v>
       </c>
-      <c r="Y61" s="49"/>
-    </row>
-    <row r="62" spans="1:25" s="3" customFormat="1">
-      <c r="A62" s="43">
+      <c r="Y61" s="51"/>
+    </row>
+    <row r="62" s="3" customFormat="1" spans="1:25">
+      <c r="A62" s="44">
         <v>20120010</v>
       </c>
-      <c r="B62" s="42">
+      <c r="B62" s="43">
         <v>201200</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -6012,19 +6594,19 @@
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="52" t="s">
+      <c r="F62" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G62" s="45" t="s">
+      <c r="G62" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H62" s="44">
+      <c r="H62" s="45">
         <v>10</v>
       </c>
-      <c r="I62" s="44">
+      <c r="I62" s="45">
         <v>1980000</v>
       </c>
-      <c r="J62" s="31" t="s">
+      <c r="J62" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K62" s="3">
@@ -6033,11 +6615,11 @@
       <c r="L62" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M62" s="46" t="s">
+      <c r="M62" s="48" t="s">
         <v>84</v>
       </c>
       <c r="N62" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O62" s="3">
         <v>300</v>
@@ -6054,10 +6636,10 @@
       <c r="S62" s="3">
         <v>16008</v>
       </c>
-      <c r="T62" s="43">
+      <c r="T62" s="44">
         <v>12</v>
       </c>
-      <c r="U62" s="43">
+      <c r="U62" s="44">
         <v>0</v>
       </c>
       <c r="V62" t="s">
@@ -6069,13 +6651,13 @@
       <c r="X62" s="3">
         <v>1</v>
       </c>
-      <c r="Y62" s="49"/>
-    </row>
-    <row r="63" spans="1:25" s="3" customFormat="1">
-      <c r="A63" s="43">
+      <c r="Y62" s="51"/>
+    </row>
+    <row r="63" s="3" customFormat="1" spans="1:25">
+      <c r="A63" s="44">
         <v>20120011</v>
       </c>
-      <c r="B63" s="42">
+      <c r="B63" s="43">
         <v>201200</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -6087,19 +6669,19 @@
       <c r="E63" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="52" t="s">
+      <c r="F63" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G63" s="45" t="s">
+      <c r="G63" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H63" s="44">
+      <c r="H63" s="45">
         <v>11</v>
       </c>
-      <c r="I63" s="44">
+      <c r="I63" s="45">
         <v>1980000</v>
       </c>
-      <c r="J63" s="36" t="s">
+      <c r="J63" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K63" s="3">
@@ -6108,11 +6690,11 @@
       <c r="L63" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M63" s="46" t="s">
+      <c r="M63" s="48" t="s">
         <v>84</v>
       </c>
       <c r="N63" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O63" s="3">
         <v>300</v>
@@ -6129,10 +6711,10 @@
       <c r="S63" s="3">
         <v>16008</v>
       </c>
-      <c r="T63" s="43">
+      <c r="T63" s="44">
         <v>12</v>
       </c>
-      <c r="U63" s="43">
+      <c r="U63" s="44">
         <v>0</v>
       </c>
       <c r="V63" t="s">
@@ -6144,13 +6726,13 @@
       <c r="X63" s="3">
         <v>1</v>
       </c>
-      <c r="Y63" s="49"/>
-    </row>
-    <row r="64" spans="1:25" s="3" customFormat="1">
-      <c r="A64" s="43">
+      <c r="Y63" s="51"/>
+    </row>
+    <row r="64" s="3" customFormat="1" spans="1:25">
+      <c r="A64" s="44">
         <v>20120012</v>
       </c>
-      <c r="B64" s="42">
+      <c r="B64" s="43">
         <v>201200</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -6162,19 +6744,19 @@
       <c r="E64" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G64" s="45" t="s">
+      <c r="G64" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H64" s="44">
+      <c r="H64" s="45">
         <v>12</v>
       </c>
-      <c r="I64" s="44">
+      <c r="I64" s="45">
         <v>1980000</v>
       </c>
-      <c r="J64" s="31" t="s">
+      <c r="J64" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K64" s="3">
@@ -6183,11 +6765,11 @@
       <c r="L64" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M64" s="46" t="s">
+      <c r="M64" s="48" t="s">
         <v>84</v>
       </c>
       <c r="N64" s="2">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="O64" s="3">
         <v>300</v>
@@ -6204,10 +6786,10 @@
       <c r="S64" s="3">
         <v>16008</v>
       </c>
-      <c r="T64" s="43">
+      <c r="T64" s="44">
         <v>12</v>
       </c>
-      <c r="U64" s="43">
+      <c r="U64" s="44">
         <v>0</v>
       </c>
       <c r="V64" t="s">
@@ -6219,7 +6801,7 @@
       <c r="X64" s="3">
         <v>1</v>
       </c>
-      <c r="Y64" s="49"/>
+      <c r="Y64" s="51"/>
     </row>
     <row r="65" spans="1:25">
       <c r="A65" s="2">
@@ -6238,19 +6820,19 @@
       <c r="E65" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F65" s="50" t="s">
+      <c r="F65" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G65" s="29" t="s">
+      <c r="G65" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H65" s="28">
         <v>21</v>
       </c>
-      <c r="I65" s="30">
+      <c r="I65" s="31">
         <v>1990000</v>
       </c>
-      <c r="J65" s="31" t="s">
+      <c r="J65" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K65" s="2">
@@ -6259,13 +6841,13 @@
       <c r="L65" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M65" s="32" t="s">
+      <c r="M65" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N65" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O65" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O65" s="3">
         <v>0</v>
       </c>
       <c r="P65" s="2">
@@ -6277,13 +6859,13 @@
       <c r="R65" s="2">
         <v>15000</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>16008</v>
       </c>
       <c r="T65" s="5">
         <v>48</v>
       </c>
-      <c r="U65" s="34">
+      <c r="U65" s="35">
         <v>0</v>
       </c>
       <c r="V65" t="s">
@@ -6305,31 +6887,31 @@
         <f t="shared" ref="A66:A94" si="6">B66*100+H66</f>
         <v>20010022</v>
       </c>
-      <c r="B66" s="35">
+      <c r="B66" s="36">
         <v>200100</v>
       </c>
-      <c r="C66" s="35" t="s">
+      <c r="C66" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D66" s="35">
+      <c r="D66" s="36">
         <v>200100038</v>
       </c>
-      <c r="E66" s="35" t="s">
+      <c r="E66" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F66" s="50" t="s">
+      <c r="F66" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G66" s="29" t="s">
+      <c r="G66" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H66" s="28">
         <v>22</v>
       </c>
-      <c r="I66" s="30">
+      <c r="I66" s="31">
         <v>1990000</v>
       </c>
-      <c r="J66" s="36" t="s">
+      <c r="J66" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K66" s="2">
@@ -6338,13 +6920,13 @@
       <c r="L66" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M66" s="32" t="s">
+      <c r="M66" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N66" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O66" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O66" s="3">
         <v>0</v>
       </c>
       <c r="P66" s="2">
@@ -6356,13 +6938,13 @@
       <c r="R66" s="2">
         <v>15000</v>
       </c>
-      <c r="S66" s="33">
+      <c r="S66" s="34">
         <v>16008</v>
       </c>
       <c r="T66" s="5">
         <v>48</v>
       </c>
-      <c r="U66" s="34">
+      <c r="U66" s="35">
         <v>0</v>
       </c>
       <c r="V66" t="s">
@@ -6379,7 +6961,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="67" spans="1:25" s="2" customFormat="1">
+    <row r="67" s="2" customFormat="1" spans="1:25">
       <c r="A67" s="2">
         <f t="shared" si="6"/>
         <v>20010023</v>
@@ -6396,19 +6978,19 @@
       <c r="E67" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F67" s="50" t="s">
+      <c r="F67" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G67" s="29" t="s">
+      <c r="G67" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H67" s="28">
         <v>23</v>
       </c>
-      <c r="I67" s="30">
+      <c r="I67" s="31">
         <v>1990000</v>
       </c>
-      <c r="J67" s="31" t="s">
+      <c r="J67" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K67" s="2">
@@ -6417,13 +6999,13 @@
       <c r="L67" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M67" s="32" t="s">
+      <c r="M67" s="33" t="s">
         <v>56</v>
       </c>
       <c r="N67" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O67" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O67" s="3">
         <v>0</v>
       </c>
       <c r="P67" s="2">
@@ -6435,13 +7017,13 @@
       <c r="R67" s="2">
         <v>15000</v>
       </c>
-      <c r="S67" s="33">
+      <c r="S67" s="34">
         <v>16008</v>
       </c>
       <c r="T67" s="5">
         <v>48</v>
       </c>
-      <c r="U67" s="34">
+      <c r="U67" s="35">
         <v>0</v>
       </c>
       <c r="V67" t="s">
@@ -6458,7 +7040,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="68" spans="1:25" s="2" customFormat="1">
+    <row r="68" s="2" customFormat="1" spans="1:25">
       <c r="A68" s="2">
         <f t="shared" si="6"/>
         <v>20010121</v>
@@ -6472,22 +7054,22 @@
       <c r="D68" s="28">
         <v>200101001</v>
       </c>
-      <c r="E68" s="37" t="s">
+      <c r="E68" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F68" s="50" t="s">
+      <c r="F68" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G68" s="29" t="s">
+      <c r="G68" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H68" s="28">
         <v>21</v>
       </c>
-      <c r="I68" s="30">
+      <c r="I68" s="31">
         <v>1990000</v>
       </c>
-      <c r="J68" s="31" t="s">
+      <c r="J68" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K68" s="2">
@@ -6496,13 +7078,13 @@
       <c r="L68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M68" s="32" t="s">
+      <c r="M68" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N68" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O68" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O68" s="3">
         <v>0</v>
       </c>
       <c r="P68" s="2">
@@ -6514,13 +7096,13 @@
       <c r="R68" s="2">
         <v>15000</v>
       </c>
-      <c r="S68" s="33">
+      <c r="S68" s="34">
         <v>16008</v>
       </c>
       <c r="T68" s="5">
         <v>48</v>
       </c>
-      <c r="U68" s="34">
+      <c r="U68" s="35">
         <v>0</v>
       </c>
       <c r="V68" t="s">
@@ -6542,31 +7124,31 @@
         <f t="shared" si="6"/>
         <v>20010122</v>
       </c>
-      <c r="B69" s="35">
+      <c r="B69" s="36">
         <v>200101</v>
       </c>
-      <c r="C69" s="35" t="s">
+      <c r="C69" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D69" s="35">
+      <c r="D69" s="36">
         <v>200101001</v>
       </c>
-      <c r="E69" s="35" t="s">
+      <c r="E69" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F69" s="50" t="s">
+      <c r="F69" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G69" s="29" t="s">
+      <c r="G69" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H69" s="28">
         <v>22</v>
       </c>
-      <c r="I69" s="30">
+      <c r="I69" s="31">
         <v>1990000</v>
       </c>
-      <c r="J69" s="36" t="s">
+      <c r="J69" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K69" s="2">
@@ -6575,13 +7157,13 @@
       <c r="L69" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M69" s="32" t="s">
+      <c r="M69" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N69" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O69" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O69" s="3">
         <v>0</v>
       </c>
       <c r="P69" s="2">
@@ -6593,13 +7175,13 @@
       <c r="R69" s="2">
         <v>15000</v>
       </c>
-      <c r="S69" s="33">
+      <c r="S69" s="34">
         <v>16008</v>
       </c>
       <c r="T69" s="5">
         <v>48</v>
       </c>
-      <c r="U69" s="34">
+      <c r="U69" s="35">
         <v>0</v>
       </c>
       <c r="V69" t="s">
@@ -6633,19 +7215,19 @@
       <c r="E70" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F70" s="50" t="s">
+      <c r="F70" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G70" s="29" t="s">
+      <c r="G70" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H70" s="28">
         <v>23</v>
       </c>
-      <c r="I70" s="30">
+      <c r="I70" s="31">
         <v>1990000</v>
       </c>
-      <c r="J70" s="31" t="s">
+      <c r="J70" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K70" s="2">
@@ -6654,13 +7236,13 @@
       <c r="L70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M70" s="32" t="s">
+      <c r="M70" s="33" t="s">
         <v>69</v>
       </c>
       <c r="N70" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O70" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O70" s="3">
         <v>0</v>
       </c>
       <c r="P70" s="2">
@@ -6672,13 +7254,13 @@
       <c r="R70" s="2">
         <v>15000</v>
       </c>
-      <c r="S70" s="33">
+      <c r="S70" s="34">
         <v>16008</v>
       </c>
       <c r="T70" s="5">
         <v>48</v>
       </c>
-      <c r="U70" s="34">
+      <c r="U70" s="35">
         <v>0</v>
       </c>
       <c r="V70" t="s">
@@ -6709,22 +7291,22 @@
       <c r="D71" s="28">
         <v>200300001</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="E71" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F71" s="50" t="s">
+      <c r="F71" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G71" s="29" t="s">
+      <c r="G71" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H71" s="28">
         <v>21</v>
       </c>
-      <c r="I71" s="30">
+      <c r="I71" s="31">
         <v>1990000</v>
       </c>
-      <c r="J71" s="31" t="s">
+      <c r="J71" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K71" s="2">
@@ -6733,13 +7315,13 @@
       <c r="L71" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M71" s="32" t="s">
+      <c r="M71" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N71" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O71" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O71" s="3">
         <v>0</v>
       </c>
       <c r="P71" s="2">
@@ -6751,13 +7333,13 @@
       <c r="R71" s="2">
         <v>15000</v>
       </c>
-      <c r="S71" s="33">
+      <c r="S71" s="34">
         <v>16008</v>
       </c>
       <c r="T71" s="5">
         <v>50</v>
       </c>
-      <c r="U71" s="34">
+      <c r="U71" s="35">
         <v>0</v>
       </c>
       <c r="V71" t="s">
@@ -6774,36 +7356,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="72" spans="1:25" s="2" customFormat="1">
+    <row r="72" s="2" customFormat="1" spans="1:25">
       <c r="A72" s="2">
         <f t="shared" si="6"/>
         <v>20030022</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B72" s="36">
         <v>200300</v>
       </c>
-      <c r="C72" s="35" t="s">
+      <c r="C72" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D72" s="35">
+      <c r="D72" s="36">
         <v>200300001</v>
       </c>
-      <c r="E72" s="35" t="s">
+      <c r="E72" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F72" s="50" t="s">
+      <c r="F72" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G72" s="29" t="s">
+      <c r="G72" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H72" s="28">
         <v>22</v>
       </c>
-      <c r="I72" s="30">
+      <c r="I72" s="31">
         <v>1990000</v>
       </c>
-      <c r="J72" s="36" t="s">
+      <c r="J72" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K72" s="2">
@@ -6812,13 +7394,13 @@
       <c r="L72" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M72" s="32" t="s">
+      <c r="M72" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N72" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O72" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O72" s="3">
         <v>0</v>
       </c>
       <c r="P72" s="2">
@@ -6830,13 +7412,13 @@
       <c r="R72" s="2">
         <v>15000</v>
       </c>
-      <c r="S72" s="33">
+      <c r="S72" s="34">
         <v>16008</v>
       </c>
       <c r="T72" s="5">
         <v>50</v>
       </c>
-      <c r="U72" s="34">
+      <c r="U72" s="35">
         <v>0</v>
       </c>
       <c r="V72" t="s">
@@ -6870,19 +7452,19 @@
       <c r="E73" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F73" s="50" t="s">
+      <c r="F73" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G73" s="29" t="s">
+      <c r="G73" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H73" s="28">
         <v>23</v>
       </c>
-      <c r="I73" s="30">
+      <c r="I73" s="31">
         <v>1990000</v>
       </c>
-      <c r="J73" s="31" t="s">
+      <c r="J73" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K73" s="2">
@@ -6891,13 +7473,13 @@
       <c r="L73" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M73" s="32" t="s">
+      <c r="M73" s="33" t="s">
         <v>71</v>
       </c>
       <c r="N73" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O73" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O73" s="3">
         <v>0</v>
       </c>
       <c r="P73" s="2">
@@ -6909,13 +7491,13 @@
       <c r="R73" s="2">
         <v>15000</v>
       </c>
-      <c r="S73" s="33">
+      <c r="S73" s="34">
         <v>16008</v>
       </c>
       <c r="T73" s="5">
         <v>50</v>
       </c>
-      <c r="U73" s="34">
+      <c r="U73" s="35">
         <v>0</v>
       </c>
       <c r="V73" t="s">
@@ -6946,22 +7528,22 @@
       <c r="D74" s="28">
         <v>200400009</v>
       </c>
-      <c r="E74" s="37" t="s">
+      <c r="E74" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F74" s="50" t="s">
+      <c r="F74" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G74" s="29" t="s">
+      <c r="G74" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H74" s="28">
         <v>21</v>
       </c>
-      <c r="I74" s="30">
+      <c r="I74" s="31">
         <v>1990000</v>
       </c>
-      <c r="J74" s="31" t="s">
+      <c r="J74" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K74" s="2">
@@ -6970,13 +7552,13 @@
       <c r="L74" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M74" s="32" t="s">
+      <c r="M74" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N74" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O74" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O74" s="3">
         <v>0</v>
       </c>
       <c r="P74" s="2">
@@ -6988,13 +7570,13 @@
       <c r="R74" s="2">
         <v>15000</v>
       </c>
-      <c r="S74" s="33">
+      <c r="S74" s="34">
         <v>16008</v>
       </c>
       <c r="T74" s="5">
         <v>50</v>
       </c>
-      <c r="U74" s="34">
+      <c r="U74" s="35">
         <v>0</v>
       </c>
       <c r="V74" t="s">
@@ -7016,31 +7598,31 @@
         <f t="shared" si="6"/>
         <v>20040022</v>
       </c>
-      <c r="B75" s="35">
+      <c r="B75" s="36">
         <v>200400</v>
       </c>
-      <c r="C75" s="35" t="s">
+      <c r="C75" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D75" s="35">
+      <c r="D75" s="36">
         <v>200400009</v>
       </c>
-      <c r="E75" s="35" t="s">
+      <c r="E75" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F75" s="50" t="s">
+      <c r="F75" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G75" s="29" t="s">
+      <c r="G75" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H75" s="28">
         <v>22</v>
       </c>
-      <c r="I75" s="30">
+      <c r="I75" s="31">
         <v>1990000</v>
       </c>
-      <c r="J75" s="36" t="s">
+      <c r="J75" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K75" s="2">
@@ -7049,13 +7631,13 @@
       <c r="L75" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M75" s="32" t="s">
+      <c r="M75" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N75" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O75" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O75" s="3">
         <v>0</v>
       </c>
       <c r="P75" s="2">
@@ -7067,13 +7649,13 @@
       <c r="R75" s="2">
         <v>15000</v>
       </c>
-      <c r="S75" s="33">
+      <c r="S75" s="34">
         <v>16008</v>
       </c>
       <c r="T75" s="5">
         <v>50</v>
       </c>
-      <c r="U75" s="34">
+      <c r="U75" s="35">
         <v>0</v>
       </c>
       <c r="V75" t="s">
@@ -7090,7 +7672,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="76" spans="1:25" s="2" customFormat="1">
+    <row r="76" s="2" customFormat="1" spans="1:25">
       <c r="A76" s="2">
         <f t="shared" si="6"/>
         <v>20040023</v>
@@ -7107,19 +7689,19 @@
       <c r="E76" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F76" s="50" t="s">
+      <c r="F76" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G76" s="29" t="s">
+      <c r="G76" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H76" s="28">
         <v>23</v>
       </c>
-      <c r="I76" s="30">
+      <c r="I76" s="31">
         <v>1990000</v>
       </c>
-      <c r="J76" s="31" t="s">
+      <c r="J76" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K76" s="2">
@@ -7128,13 +7710,13 @@
       <c r="L76" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M76" s="32" t="s">
+      <c r="M76" s="33" t="s">
         <v>73</v>
       </c>
       <c r="N76" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O76" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O76" s="3">
         <v>0</v>
       </c>
       <c r="P76" s="2">
@@ -7146,13 +7728,13 @@
       <c r="R76" s="2">
         <v>15000</v>
       </c>
-      <c r="S76" s="33">
+      <c r="S76" s="34">
         <v>16008</v>
       </c>
       <c r="T76" s="5">
         <v>50</v>
       </c>
-      <c r="U76" s="34">
+      <c r="U76" s="35">
         <v>0</v>
       </c>
       <c r="V76" t="s">
@@ -7169,7 +7751,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="77" spans="1:25" s="2" customFormat="1">
+    <row r="77" s="2" customFormat="1" spans="1:25">
       <c r="A77" s="2">
         <f t="shared" si="6"/>
         <v>20050021</v>
@@ -7186,19 +7768,19 @@
       <c r="E77" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F77" s="50" t="s">
+      <c r="F77" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G77" s="29" t="s">
+      <c r="G77" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H77" s="28">
         <v>21</v>
       </c>
-      <c r="I77" s="30">
+      <c r="I77" s="31">
         <v>1990000</v>
       </c>
-      <c r="J77" s="31" t="s">
+      <c r="J77" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K77" s="2">
@@ -7207,13 +7789,13 @@
       <c r="L77" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M77" s="32" t="s">
+      <c r="M77" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N77" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O77" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O77" s="3">
         <v>0</v>
       </c>
       <c r="P77" s="2">
@@ -7225,13 +7807,13 @@
       <c r="R77" s="2">
         <v>15000</v>
       </c>
-      <c r="S77" s="33">
+      <c r="S77" s="34">
         <v>16008</v>
       </c>
       <c r="T77" s="5">
         <v>48</v>
       </c>
-      <c r="U77" s="34">
+      <c r="U77" s="35">
         <v>0</v>
       </c>
       <c r="V77" t="s">
@@ -7253,31 +7835,31 @@
         <f t="shared" si="6"/>
         <v>20050022</v>
       </c>
-      <c r="B78" s="35">
+      <c r="B78" s="36">
         <v>200500</v>
       </c>
-      <c r="C78" s="35" t="s">
+      <c r="C78" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D78" s="35">
+      <c r="D78" s="36">
         <v>200500025</v>
       </c>
-      <c r="E78" s="35" t="s">
+      <c r="E78" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F78" s="50" t="s">
+      <c r="F78" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G78" s="29" t="s">
+      <c r="G78" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H78" s="28">
         <v>22</v>
       </c>
-      <c r="I78" s="30">
+      <c r="I78" s="31">
         <v>1990000</v>
       </c>
-      <c r="J78" s="36" t="s">
+      <c r="J78" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K78" s="2">
@@ -7286,13 +7868,13 @@
       <c r="L78" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M78" s="32" t="s">
+      <c r="M78" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N78" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O78" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O78" s="3">
         <v>0</v>
       </c>
       <c r="P78" s="2">
@@ -7304,13 +7886,13 @@
       <c r="R78" s="2">
         <v>15000</v>
       </c>
-      <c r="S78" s="33">
+      <c r="S78" s="34">
         <v>16008</v>
       </c>
       <c r="T78" s="5">
         <v>48</v>
       </c>
-      <c r="U78" s="34">
+      <c r="U78" s="35">
         <v>0</v>
       </c>
       <c r="V78" t="s">
@@ -7344,19 +7926,19 @@
       <c r="E79" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F79" s="50" t="s">
+      <c r="F79" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G79" s="29" t="s">
+      <c r="G79" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H79" s="28">
         <v>23</v>
       </c>
-      <c r="I79" s="30">
+      <c r="I79" s="31">
         <v>1990000</v>
       </c>
-      <c r="J79" s="31" t="s">
+      <c r="J79" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K79" s="2">
@@ -7365,13 +7947,13 @@
       <c r="L79" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M79" s="32" t="s">
+      <c r="M79" s="33" t="s">
         <v>75</v>
       </c>
       <c r="N79" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O79" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O79" s="3">
         <v>0</v>
       </c>
       <c r="P79" s="2">
@@ -7383,13 +7965,13 @@
       <c r="R79" s="2">
         <v>15000</v>
       </c>
-      <c r="S79" s="33">
+      <c r="S79" s="34">
         <v>16008</v>
       </c>
       <c r="T79" s="5">
         <v>48</v>
       </c>
-      <c r="U79" s="34">
+      <c r="U79" s="35">
         <v>0</v>
       </c>
       <c r="V79" t="s">
@@ -7420,22 +8002,22 @@
       <c r="D80" s="28">
         <v>200600001</v>
       </c>
-      <c r="E80" s="38" t="s">
+      <c r="E80" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F80" s="50" t="s">
+      <c r="F80" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G80" s="29" t="s">
+      <c r="G80" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H80" s="28">
         <v>21</v>
       </c>
-      <c r="I80" s="30">
+      <c r="I80" s="31">
         <v>1990000</v>
       </c>
-      <c r="J80" s="31" t="s">
+      <c r="J80" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K80" s="2">
@@ -7444,13 +8026,13 @@
       <c r="L80" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M80" s="32" t="s">
+      <c r="M80" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N80" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O80" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O80" s="3">
         <v>0</v>
       </c>
       <c r="P80" s="2">
@@ -7462,13 +8044,13 @@
       <c r="R80" s="2">
         <v>15000</v>
       </c>
-      <c r="S80" s="33">
+      <c r="S80" s="34">
         <v>16008</v>
       </c>
       <c r="T80" s="5">
         <v>20</v>
       </c>
-      <c r="U80" s="34">
+      <c r="U80" s="35">
         <v>0</v>
       </c>
       <c r="V80" t="s">
@@ -7485,36 +8067,36 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="81" spans="1:25" s="2" customFormat="1">
+    <row r="81" s="2" customFormat="1" spans="1:25">
       <c r="A81" s="2">
         <f t="shared" si="6"/>
         <v>20060022</v>
       </c>
-      <c r="B81" s="35">
+      <c r="B81" s="36">
         <v>200600</v>
       </c>
-      <c r="C81" s="35" t="s">
+      <c r="C81" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D81" s="35">
+      <c r="D81" s="36">
         <v>200600001</v>
       </c>
-      <c r="E81" s="35" t="s">
+      <c r="E81" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F81" s="50" t="s">
+      <c r="F81" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G81" s="29" t="s">
+      <c r="G81" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H81" s="28">
         <v>22</v>
       </c>
-      <c r="I81" s="30">
+      <c r="I81" s="31">
         <v>1990000</v>
       </c>
-      <c r="J81" s="36" t="s">
+      <c r="J81" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K81" s="2">
@@ -7523,13 +8105,13 @@
       <c r="L81" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M81" s="32" t="s">
+      <c r="M81" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N81" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O81" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O81" s="3">
         <v>0</v>
       </c>
       <c r="P81" s="2">
@@ -7541,13 +8123,13 @@
       <c r="R81" s="2">
         <v>15000</v>
       </c>
-      <c r="S81" s="33">
+      <c r="S81" s="34">
         <v>16008</v>
       </c>
       <c r="T81" s="5">
         <v>20</v>
       </c>
-      <c r="U81" s="34">
+      <c r="U81" s="35">
         <v>0</v>
       </c>
       <c r="V81" t="s">
@@ -7581,19 +8163,19 @@
       <c r="E82" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F82" s="50" t="s">
+      <c r="F82" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G82" s="29" t="s">
+      <c r="G82" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H82" s="28">
         <v>23</v>
       </c>
-      <c r="I82" s="30">
+      <c r="I82" s="31">
         <v>1990000</v>
       </c>
-      <c r="J82" s="31" t="s">
+      <c r="J82" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K82" s="2">
@@ -7602,13 +8184,13 @@
       <c r="L82" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M82" s="32" t="s">
+      <c r="M82" s="33" t="s">
         <v>77</v>
       </c>
       <c r="N82" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O82" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O82" s="3">
         <v>0</v>
       </c>
       <c r="P82" s="2">
@@ -7620,13 +8202,13 @@
       <c r="R82" s="2">
         <v>15000</v>
       </c>
-      <c r="S82" s="33">
+      <c r="S82" s="34">
         <v>16008</v>
       </c>
       <c r="T82" s="5">
         <v>20</v>
       </c>
-      <c r="U82" s="34">
+      <c r="U82" s="35">
         <v>0</v>
       </c>
       <c r="V82" t="s">
@@ -7660,19 +8242,19 @@
       <c r="E83" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F83" s="50" t="s">
+      <c r="F83" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G83" s="29" t="s">
+      <c r="G83" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H83" s="28">
         <v>21</v>
       </c>
-      <c r="I83" s="30">
+      <c r="I83" s="31">
         <v>1990000</v>
       </c>
-      <c r="J83" s="31" t="s">
+      <c r="J83" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K83" s="2">
@@ -7681,13 +8263,13 @@
       <c r="L83" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M83" s="32" t="s">
+      <c r="M83" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N83" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O83" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O83" s="3">
         <v>0</v>
       </c>
       <c r="P83" s="2">
@@ -7699,13 +8281,13 @@
       <c r="R83" s="2">
         <v>15000</v>
       </c>
-      <c r="S83" s="33">
+      <c r="S83" s="34">
         <v>16008</v>
       </c>
       <c r="T83" s="5">
         <v>30</v>
       </c>
-      <c r="U83" s="34">
+      <c r="U83" s="35">
         <v>1</v>
       </c>
       <c r="V83" t="s">
@@ -7727,31 +8309,31 @@
         <f t="shared" si="6"/>
         <v>20070022</v>
       </c>
-      <c r="B84" s="35">
+      <c r="B84" s="36">
         <v>200700</v>
       </c>
-      <c r="C84" s="35" t="s">
+      <c r="C84" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D84" s="35">
+      <c r="D84" s="36">
         <v>200700001</v>
       </c>
-      <c r="E84" s="35" t="s">
+      <c r="E84" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F84" s="50" t="s">
+      <c r="F84" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G84" s="29" t="s">
+      <c r="G84" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H84" s="28">
         <v>22</v>
       </c>
-      <c r="I84" s="30">
+      <c r="I84" s="31">
         <v>1990000</v>
       </c>
-      <c r="J84" s="36" t="s">
+      <c r="J84" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K84" s="2">
@@ -7760,13 +8342,13 @@
       <c r="L84" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M84" s="32" t="s">
+      <c r="M84" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N84" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O84" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O84" s="3">
         <v>0</v>
       </c>
       <c r="P84" s="2">
@@ -7778,13 +8360,13 @@
       <c r="R84" s="2">
         <v>15000</v>
       </c>
-      <c r="S84" s="33">
+      <c r="S84" s="34">
         <v>16008</v>
       </c>
       <c r="T84" s="5">
         <v>30</v>
       </c>
-      <c r="U84" s="34">
+      <c r="U84" s="35">
         <v>1</v>
       </c>
       <c r="V84" t="s">
@@ -7801,7 +8383,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="85" spans="1:25" s="2" customFormat="1">
+    <row r="85" s="2" customFormat="1" spans="1:25">
       <c r="A85" s="2">
         <f t="shared" si="6"/>
         <v>20070023</v>
@@ -7818,19 +8400,19 @@
       <c r="E85" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="50" t="s">
+      <c r="F85" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G85" s="29" t="s">
+      <c r="G85" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H85" s="28">
         <v>23</v>
       </c>
-      <c r="I85" s="30">
+      <c r="I85" s="31">
         <v>1990000</v>
       </c>
-      <c r="J85" s="31" t="s">
+      <c r="J85" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K85" s="2">
@@ -7839,13 +8421,13 @@
       <c r="L85" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M85" s="32" t="s">
+      <c r="M85" s="33" t="s">
         <v>79</v>
       </c>
       <c r="N85" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O85" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O85" s="3">
         <v>0</v>
       </c>
       <c r="P85" s="2">
@@ -7857,13 +8439,13 @@
       <c r="R85" s="2">
         <v>15000</v>
       </c>
-      <c r="S85" s="33">
+      <c r="S85" s="34">
         <v>16008</v>
       </c>
       <c r="T85" s="5">
         <v>30</v>
       </c>
-      <c r="U85" s="34">
+      <c r="U85" s="35">
         <v>1</v>
       </c>
       <c r="V85" t="s">
@@ -7880,7 +8462,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="86" spans="1:25" s="2" customFormat="1">
+    <row r="86" s="2" customFormat="1" spans="1:25">
       <c r="A86" s="2">
         <f t="shared" si="6"/>
         <v>20080021</v>
@@ -7894,22 +8476,22 @@
       <c r="D86" s="28">
         <v>200800001</v>
       </c>
-      <c r="E86" s="38" t="s">
+      <c r="E86" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F86" s="50" t="s">
+      <c r="F86" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G86" s="29" t="s">
+      <c r="G86" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H86" s="28">
         <v>21</v>
       </c>
-      <c r="I86" s="30">
+      <c r="I86" s="31">
         <v>1990000</v>
       </c>
-      <c r="J86" s="31" t="s">
+      <c r="J86" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K86" s="2">
@@ -7918,13 +8500,13 @@
       <c r="L86" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M86" s="32" t="s">
+      <c r="M86" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N86" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O86" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O86" s="3">
         <v>0</v>
       </c>
       <c r="P86" s="2">
@@ -7936,13 +8518,13 @@
       <c r="R86" s="2">
         <v>15000</v>
       </c>
-      <c r="S86" s="33">
+      <c r="S86" s="34">
         <v>16008</v>
       </c>
       <c r="T86" s="5">
         <v>20</v>
       </c>
-      <c r="U86" s="34">
+      <c r="U86" s="35">
         <v>0</v>
       </c>
       <c r="V86" t="s">
@@ -7959,7 +8541,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="87" spans="1:25" s="2" customFormat="1">
+    <row r="87" s="2" customFormat="1" spans="1:25">
       <c r="A87" s="2">
         <f t="shared" si="6"/>
         <v>20080022</v>
@@ -7973,22 +8555,22 @@
       <c r="D87" s="28">
         <v>200800001</v>
       </c>
-      <c r="E87" s="35" t="s">
+      <c r="E87" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F87" s="50" t="s">
+      <c r="F87" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G87" s="29" t="s">
+      <c r="G87" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H87" s="28">
         <v>22</v>
       </c>
-      <c r="I87" s="30">
+      <c r="I87" s="31">
         <v>1990000</v>
       </c>
-      <c r="J87" s="36" t="s">
+      <c r="J87" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K87" s="2">
@@ -7997,13 +8579,13 @@
       <c r="L87" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M87" s="32" t="s">
+      <c r="M87" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N87" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O87" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O87" s="3">
         <v>0</v>
       </c>
       <c r="P87" s="2">
@@ -8015,13 +8597,13 @@
       <c r="R87" s="2">
         <v>15000</v>
       </c>
-      <c r="S87" s="33">
+      <c r="S87" s="34">
         <v>16008</v>
       </c>
       <c r="T87" s="5">
         <v>20</v>
       </c>
-      <c r="U87" s="34">
+      <c r="U87" s="35">
         <v>0</v>
       </c>
       <c r="V87" t="s">
@@ -8038,7 +8620,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="88" spans="1:25" s="2" customFormat="1">
+    <row r="88" s="2" customFormat="1" spans="1:25">
       <c r="A88" s="2">
         <f t="shared" si="6"/>
         <v>20080023</v>
@@ -8055,19 +8637,19 @@
       <c r="E88" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F88" s="50" t="s">
+      <c r="F88" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G88" s="29" t="s">
+      <c r="G88" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H88" s="28">
         <v>23</v>
       </c>
-      <c r="I88" s="30">
+      <c r="I88" s="31">
         <v>1990000</v>
       </c>
-      <c r="J88" s="31" t="s">
+      <c r="J88" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K88" s="2">
@@ -8076,13 +8658,13 @@
       <c r="L88" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M88" s="32" t="s">
+      <c r="M88" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N88" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O88" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O88" s="3">
         <v>0</v>
       </c>
       <c r="P88" s="2">
@@ -8094,13 +8676,13 @@
       <c r="R88" s="2">
         <v>15000</v>
       </c>
-      <c r="S88" s="33">
+      <c r="S88" s="34">
         <v>16008</v>
       </c>
       <c r="T88" s="5">
         <v>20</v>
       </c>
-      <c r="U88" s="34">
+      <c r="U88" s="35">
         <v>0</v>
       </c>
       <c r="V88" t="s">
@@ -8117,12 +8699,12 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="89" spans="1:25" s="2" customFormat="1">
+    <row r="89" s="2" customFormat="1" spans="1:25">
       <c r="A89" s="2">
         <f t="shared" si="6"/>
         <v>20090021</v>
       </c>
-      <c r="B89" s="39">
+      <c r="B89" s="40">
         <v>200900</v>
       </c>
       <c r="C89" s="28" t="s">
@@ -8131,37 +8713,37 @@
       <c r="D89" s="28">
         <v>200900001</v>
       </c>
-      <c r="E89" s="37" t="s">
+      <c r="E89" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F89" s="50" t="s">
+      <c r="F89" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G89" s="29" t="s">
+      <c r="G89" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H89" s="28">
         <v>21</v>
       </c>
-      <c r="I89" s="30">
+      <c r="I89" s="31">
         <v>1990000</v>
       </c>
-      <c r="J89" s="31" t="s">
+      <c r="J89" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K89" s="40">
+      <c r="K89" s="41">
         <v>0</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M89" s="32" t="s">
+      <c r="M89" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N89" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O89" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O89" s="3">
         <v>0</v>
       </c>
       <c r="P89" s="2">
@@ -8173,13 +8755,13 @@
       <c r="R89" s="2">
         <v>15000</v>
       </c>
-      <c r="S89" s="33">
+      <c r="S89" s="34">
         <v>16008</v>
       </c>
       <c r="T89" s="5">
         <v>20</v>
       </c>
-      <c r="U89" s="34">
+      <c r="U89" s="35">
         <v>0</v>
       </c>
       <c r="V89" t="s">
@@ -8201,46 +8783,46 @@
         <f t="shared" si="6"/>
         <v>20090022</v>
       </c>
-      <c r="B90" s="41">
+      <c r="B90" s="42">
         <v>200900</v>
       </c>
-      <c r="C90" s="35" t="s">
+      <c r="C90" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="D90" s="35">
+      <c r="D90" s="36">
         <v>200900001</v>
       </c>
-      <c r="E90" s="35" t="s">
+      <c r="E90" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F90" s="50" t="s">
+      <c r="F90" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G90" s="29" t="s">
+      <c r="G90" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H90" s="28">
         <v>22</v>
       </c>
-      <c r="I90" s="30">
+      <c r="I90" s="31">
         <v>1990000</v>
       </c>
-      <c r="J90" s="36" t="s">
+      <c r="J90" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K90" s="40">
+      <c r="K90" s="41">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M90" s="32" t="s">
+      <c r="M90" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N90" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O90" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O90" s="3">
         <v>0</v>
       </c>
       <c r="P90" s="2">
@@ -8252,13 +8834,13 @@
       <c r="R90" s="2">
         <v>15000</v>
       </c>
-      <c r="S90" s="33">
+      <c r="S90" s="34">
         <v>16008</v>
       </c>
       <c r="T90" s="5">
         <v>20</v>
       </c>
-      <c r="U90" s="34">
+      <c r="U90" s="35">
         <v>0</v>
       </c>
       <c r="V90" t="s">
@@ -8280,7 +8862,7 @@
         <f t="shared" si="6"/>
         <v>20090023</v>
       </c>
-      <c r="B91" s="39">
+      <c r="B91" s="40">
         <v>200900</v>
       </c>
       <c r="C91" s="28" t="s">
@@ -8292,34 +8874,34 @@
       <c r="E91" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F91" s="50" t="s">
+      <c r="F91" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G91" s="29" t="s">
+      <c r="G91" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H91" s="28">
         <v>23</v>
       </c>
-      <c r="I91" s="30">
+      <c r="I91" s="31">
         <v>1990000</v>
       </c>
-      <c r="J91" s="31" t="s">
+      <c r="J91" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K91" s="40">
+      <c r="K91" s="41">
         <v>0</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M91" s="32" t="s">
+      <c r="M91" s="33" t="s">
         <v>81</v>
       </c>
       <c r="N91" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O91" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="2">
@@ -8331,13 +8913,13 @@
       <c r="R91" s="2">
         <v>15000</v>
       </c>
-      <c r="S91" s="33">
+      <c r="S91" s="34">
         <v>16008</v>
       </c>
       <c r="T91" s="5">
         <v>20</v>
       </c>
-      <c r="U91" s="34">
+      <c r="U91" s="35">
         <v>0</v>
       </c>
       <c r="V91" t="s">
@@ -8354,51 +8936,51 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="92" spans="1:25" s="2" customFormat="1">
+    <row r="92" s="2" customFormat="1" spans="1:25">
       <c r="A92" s="2">
         <f t="shared" si="6"/>
         <v>20120021</v>
       </c>
-      <c r="B92" s="42">
+      <c r="B92" s="43">
         <v>201200</v>
       </c>
       <c r="C92" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D92" s="35">
+      <c r="D92" s="36">
         <v>201200001</v>
       </c>
-      <c r="E92" s="37" t="s">
+      <c r="E92" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F92" s="50" t="s">
+      <c r="F92" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G92" s="29" t="s">
+      <c r="G92" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H92" s="28">
         <v>21</v>
       </c>
-      <c r="I92" s="30">
+      <c r="I92" s="31">
         <v>1990000</v>
       </c>
-      <c r="J92" s="31" t="s">
+      <c r="J92" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K92" s="40">
+      <c r="K92" s="41">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M92" s="32" t="s">
+      <c r="M92" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N92" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O92" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O92" s="3">
         <v>0</v>
       </c>
       <c r="P92" s="2">
@@ -8410,13 +8992,13 @@
       <c r="R92" s="2">
         <v>15000</v>
       </c>
-      <c r="S92" s="33">
+      <c r="S92" s="34">
         <v>16008</v>
       </c>
       <c r="T92" s="5">
         <v>12</v>
       </c>
-      <c r="U92" s="34">
+      <c r="U92" s="35">
         <v>0</v>
       </c>
       <c r="V92" t="s">
@@ -8438,46 +9020,46 @@
         <f t="shared" si="6"/>
         <v>20120022</v>
       </c>
-      <c r="B93" s="42">
+      <c r="B93" s="43">
         <v>201200</v>
       </c>
       <c r="C93" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D93" s="35">
+      <c r="D93" s="36">
         <v>201200001</v>
       </c>
-      <c r="E93" s="35" t="s">
+      <c r="E93" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F93" s="50" t="s">
+      <c r="F93" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G93" s="29" t="s">
+      <c r="G93" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H93" s="28">
         <v>22</v>
       </c>
-      <c r="I93" s="30">
+      <c r="I93" s="31">
         <v>1990000</v>
       </c>
-      <c r="J93" s="36" t="s">
+      <c r="J93" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K93" s="40">
+      <c r="K93" s="41">
         <v>0</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M93" s="32" t="s">
+      <c r="M93" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N93" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O93" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O93" s="3">
         <v>0</v>
       </c>
       <c r="P93" s="2">
@@ -8489,13 +9071,13 @@
       <c r="R93" s="2">
         <v>15000</v>
       </c>
-      <c r="S93" s="33">
+      <c r="S93" s="34">
         <v>16008</v>
       </c>
       <c r="T93" s="5">
         <v>12</v>
       </c>
-      <c r="U93" s="34">
+      <c r="U93" s="35">
         <v>0</v>
       </c>
       <c r="V93" t="s">
@@ -8517,46 +9099,46 @@
         <f t="shared" si="6"/>
         <v>20120023</v>
       </c>
-      <c r="B94" s="42">
+      <c r="B94" s="43">
         <v>201200</v>
       </c>
       <c r="C94" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="35">
+      <c r="D94" s="36">
         <v>201200001</v>
       </c>
       <c r="E94" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F94" s="50" t="s">
+      <c r="F94" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G94" s="29" t="s">
+      <c r="G94" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H94" s="28">
         <v>23</v>
       </c>
-      <c r="I94" s="30">
+      <c r="I94" s="31">
         <v>1990000</v>
       </c>
-      <c r="J94" s="31" t="s">
+      <c r="J94" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K94" s="40">
+      <c r="K94" s="41">
         <v>0</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M94" s="32" t="s">
+      <c r="M94" s="33" t="s">
         <v>84</v>
       </c>
       <c r="N94" s="2">
-        <v>9500</v>
-      </c>
-      <c r="O94" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="2">
@@ -8568,13 +9150,13 @@
       <c r="R94" s="2">
         <v>15000</v>
       </c>
-      <c r="S94" s="33">
+      <c r="S94" s="34">
         <v>16008</v>
       </c>
       <c r="T94" s="5">
         <v>12</v>
       </c>
-      <c r="U94" s="34">
+      <c r="U94" s="35">
         <v>0</v>
       </c>
       <c r="V94" t="s">
@@ -8592,10 +9174,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S94" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,10 +68,11 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">普通场 1
+          <t>普通场 1
 中级场 2 
 高级场 3
-</t>
+10、11、12  创建房间功能
+21、22、23  SVIP体验场</t>
         </r>
       </text>
     </comment>
@@ -330,7 +331,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="111">
   <si>
     <t>游戏ID</t>
   </si>
@@ -900,13 +901,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -936,13 +937,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1406,44 +1407,35 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1468,105 +1460,93 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1576,7 +1556,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1593,16 +1573,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1945,99 +1922,97 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:Y94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.375" style="4"/>
-    <col min="2" max="2" width="12" style="4" customWidth="1"/>
-    <col min="3" max="4" width="20.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.1416666666667" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.2333333333333" style="4" customWidth="1"/>
-    <col min="8" max="8" width="8.625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="21.025" style="4" customWidth="1"/>
-    <col min="10" max="10" width="65" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="5.125" style="4" customWidth="1"/>
-    <col min="13" max="13" width="24.75" style="5" customWidth="1"/>
-    <col min="14" max="14" width="19.2833333333333" style="4" customWidth="1"/>
-    <col min="15" max="15" width="18.75" style="4" customWidth="1"/>
-    <col min="16" max="19" width="9.81666666666667" style="4" customWidth="1"/>
-    <col min="20" max="20" width="17.2166666666667" style="6" customWidth="1"/>
-    <col min="21" max="22" width="19.5" style="7" customWidth="1"/>
-    <col min="23" max="23" width="19.125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="10.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12" style="2" customWidth="1"/>
+    <col min="3" max="4" width="20.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21" style="2" customWidth="1"/>
+    <col min="10" max="10" width="65" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="24.75" style="4" customWidth="1"/>
+    <col min="14" max="14" width="19.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="18.75" style="2" customWidth="1"/>
+    <col min="16" max="19" width="9.875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="17.25" style="5" customWidth="1"/>
+    <col min="21" max="22" width="19.5" style="6" customWidth="1"/>
+    <col min="23" max="23" width="19.125" style="4" customWidth="1"/>
     <col min="24" max="24" width="12.875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="20.125" style="8" customWidth="1"/>
+    <col min="25" max="25" width="20.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:25">
-      <c r="A1" s="9"/>
-      <c r="B1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="11" t="s">
+    <row r="1" s="1" customFormat="1" ht="41.1" customHeight="1" spans="1:25">
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="14" t="s">
+      <c r="L1" s="10"/>
+      <c r="M1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="Q1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="20" t="s">
+      <c r="W1" s="17" t="s">
         <v>19</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="21" t="s">
+      <c r="Y1" s="18" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2045,70 +2020,70 @@
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="22" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="5" t="s">
+      <c r="L2" s="2"/>
+      <c r="M2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="V2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="W2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="25" t="s">
+      <c r="Y2" s="22" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2116,2497 +2091,2497 @@
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5" t="s">
+      <c r="L3" s="2"/>
+      <c r="M3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="5" t="s">
         <v>45</v>
       </c>
       <c r="V3" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="20" t="s">
+      <c r="W3" s="17" t="s">
         <v>47</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Y3" s="25" t="s">
+      <c r="Y3" s="22" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:25">
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="20"/>
-      <c r="Y4" s="20"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="17"/>
+      <c r="Y4" s="17"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="28">
         <v>200100</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="28">
         <v>200100038</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="28">
         <v>1</v>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="31">
         <v>1990000</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="N5" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O5" s="4">
+      <c r="N5" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O5" s="2">
         <v>300</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="2">
         <v>180000</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="2">
         <v>16000</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="2">
         <v>15000</v>
       </c>
-      <c r="S5" s="38">
+      <c r="S5" s="34">
         <v>16008</v>
       </c>
-      <c r="T5" s="6">
+      <c r="T5" s="5">
         <v>48</v>
       </c>
-      <c r="U5" s="39">
+      <c r="U5" s="35">
         <v>0</v>
       </c>
       <c r="V5" t="s">
         <v>57</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="W5" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X5" s="2">
         <v>0</v>
       </c>
-      <c r="Y5" s="8">
+      <c r="Y5" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="36">
         <v>200100</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="36">
         <v>200100038</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="40">
+      <c r="H6" s="36">
         <v>2</v>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="31">
         <v>1990000</v>
       </c>
-      <c r="J6" s="41" t="s">
+      <c r="J6" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="N6" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O6" s="4">
+      <c r="N6" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O6" s="2">
         <v>300</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="2">
         <v>180000</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="2">
         <v>16000</v>
       </c>
-      <c r="R6" s="4">
+      <c r="R6" s="2">
         <v>15000</v>
       </c>
-      <c r="S6" s="38">
+      <c r="S6" s="34">
         <v>16008</v>
       </c>
-      <c r="T6" s="6">
+      <c r="T6" s="5">
         <v>48</v>
       </c>
-      <c r="U6" s="39">
+      <c r="U6" s="35">
         <v>0</v>
       </c>
       <c r="V6" t="s">
         <v>61</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="W6" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X6" s="2">
         <v>0</v>
       </c>
-      <c r="Y6" s="8">
+      <c r="Y6" s="4">
         <f t="shared" ref="Y6:Y10" si="1">Y5*10</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:25">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>2001003</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="28">
         <v>200100</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="28">
         <v>200100038</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="28">
         <v>3</v>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="31">
         <v>1990000</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="2">
         <v>1</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O7" s="4">
+      <c r="N7" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O7" s="2">
         <v>300</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="2">
         <v>180000</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="Q7" s="2">
         <v>16000</v>
       </c>
-      <c r="R7" s="4">
+      <c r="R7" s="2">
         <v>15000</v>
       </c>
-      <c r="S7" s="38">
+      <c r="S7" s="34">
         <v>16008</v>
       </c>
-      <c r="T7" s="6">
+      <c r="T7" s="5">
         <v>48</v>
       </c>
-      <c r="U7" s="39">
+      <c r="U7" s="35">
         <v>0</v>
       </c>
       <c r="V7" t="s">
         <v>65</v>
       </c>
-      <c r="W7" s="8" t="s">
+      <c r="W7" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="8">
+      <c r="Y7" s="4">
         <f t="shared" si="1"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:25">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>2001011</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="28">
         <v>200101</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="28">
         <v>200101001</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="28">
         <v>1</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="31">
         <v>1990000</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="s">
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="N8" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O8" s="4">
+      <c r="N8" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O8" s="2">
         <v>300</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="2">
         <v>180000</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="Q8" s="2">
         <v>16000</v>
       </c>
-      <c r="R8" s="4">
+      <c r="R8" s="2">
         <v>15000</v>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="34">
         <v>16008</v>
       </c>
-      <c r="T8" s="6">
+      <c r="T8" s="5">
         <v>48</v>
       </c>
-      <c r="U8" s="39">
+      <c r="U8" s="35">
         <v>0</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
-      <c r="W8" s="8" t="s">
+      <c r="W8" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X8" s="2">
         <v>0</v>
       </c>
-      <c r="Y8" s="8">
+      <c r="Y8" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="36">
         <v>200101</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="36">
         <v>200101001</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="36">
         <v>2</v>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="31">
         <v>1990000</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="4">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="s">
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="N9" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O9" s="4">
+      <c r="N9" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O9" s="2">
         <v>300</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="2">
         <v>180000</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="2">
         <v>16000</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9" s="2">
         <v>15000</v>
       </c>
-      <c r="S9" s="38">
+      <c r="S9" s="34">
         <v>16008</v>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="5">
         <v>48</v>
       </c>
-      <c r="U9" s="39">
+      <c r="U9" s="35">
         <v>0</v>
       </c>
       <c r="V9" t="s">
         <v>61</v>
       </c>
-      <c r="W9" s="8" t="s">
+      <c r="W9" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X9" s="2">
         <v>0</v>
       </c>
-      <c r="Y9" s="8">
+      <c r="Y9" s="4">
         <f t="shared" si="1"/>
         <v>100000000</v>
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>2001013</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="28">
         <v>200101</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="28">
         <v>200101001</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="28">
         <v>3</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="31">
         <v>1990000</v>
       </c>
-      <c r="J10" s="36" t="s">
+      <c r="J10" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="4">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="s">
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="M10" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="N10" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O10" s="4">
+      <c r="N10" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O10" s="2">
         <v>300</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="2">
         <v>180000</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="Q10" s="2">
         <v>16000</v>
       </c>
-      <c r="R10" s="4">
+      <c r="R10" s="2">
         <v>15000</v>
       </c>
-      <c r="S10" s="38">
+      <c r="S10" s="34">
         <v>16008</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="5">
         <v>48</v>
       </c>
-      <c r="U10" s="39">
+      <c r="U10" s="35">
         <v>0</v>
       </c>
       <c r="V10" t="s">
         <v>65</v>
       </c>
-      <c r="W10" s="8" t="s">
+      <c r="W10" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X10" s="2">
         <v>0</v>
       </c>
-      <c r="Y10" s="8">
+      <c r="Y10" s="4">
         <f t="shared" si="1"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>2003001</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="28">
         <v>200300</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="28">
         <v>200300001</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="28">
         <v>1</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="31">
         <v>1990000</v>
       </c>
-      <c r="J11" s="36" t="s">
+      <c r="J11" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="4">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="s">
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="N11" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O11" s="4">
+      <c r="N11" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O11" s="2">
         <v>300</v>
       </c>
-      <c r="P11" s="4">
+      <c r="P11" s="2">
         <v>180000</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="Q11" s="2">
         <v>16000</v>
       </c>
-      <c r="R11" s="4">
+      <c r="R11" s="2">
         <v>15000</v>
       </c>
-      <c r="S11" s="38">
+      <c r="S11" s="34">
         <v>16008</v>
       </c>
-      <c r="T11" s="6">
+      <c r="T11" s="5">
         <v>50</v>
       </c>
-      <c r="U11" s="39">
+      <c r="U11" s="35">
         <v>0</v>
       </c>
       <c r="V11" t="s">
         <v>57</v>
       </c>
-      <c r="W11" s="8" t="s">
+      <c r="W11" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X11" s="2">
         <v>0</v>
       </c>
-      <c r="Y11" s="8">
+      <c r="Y11" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:25">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="36">
         <v>200300</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="36">
         <v>200300001</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="36">
         <v>2</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="31">
         <v>1990000</v>
       </c>
-      <c r="J12" s="41" t="s">
+      <c r="J12" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="4">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="s">
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="N12" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O12" s="4">
+      <c r="N12" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O12" s="2">
         <v>300</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="2">
         <v>180000</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q12" s="2">
         <v>16000</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R12" s="2">
         <v>15000</v>
       </c>
-      <c r="S12" s="38">
+      <c r="S12" s="34">
         <v>16008</v>
       </c>
-      <c r="T12" s="6">
+      <c r="T12" s="5">
         <v>50</v>
       </c>
-      <c r="U12" s="39">
+      <c r="U12" s="35">
         <v>0</v>
       </c>
       <c r="V12" t="s">
         <v>61</v>
       </c>
-      <c r="W12" s="8" t="s">
+      <c r="W12" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X12" s="2">
         <v>0</v>
       </c>
-      <c r="Y12" s="8">
+      <c r="Y12" s="4">
         <f t="shared" ref="Y12:Y16" si="2">Y11*10</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>2003003</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="28">
         <v>200300</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="28">
         <v>200300001</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="28">
         <v>3</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="31">
         <v>1990000</v>
       </c>
-      <c r="J13" s="36" t="s">
+      <c r="J13" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="4">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="s">
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="N13" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O13" s="4">
+      <c r="N13" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O13" s="2">
         <v>300</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13" s="2">
         <v>180000</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="Q13" s="2">
         <v>16000</v>
       </c>
-      <c r="R13" s="4">
+      <c r="R13" s="2">
         <v>15000</v>
       </c>
-      <c r="S13" s="38">
+      <c r="S13" s="34">
         <v>16008</v>
       </c>
-      <c r="T13" s="6">
+      <c r="T13" s="5">
         <v>50</v>
       </c>
-      <c r="U13" s="39">
+      <c r="U13" s="35">
         <v>0</v>
       </c>
       <c r="V13" t="s">
         <v>65</v>
       </c>
-      <c r="W13" s="8" t="s">
+      <c r="W13" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X13" s="2">
         <v>0</v>
       </c>
-      <c r="Y13" s="8">
+      <c r="Y13" s="4">
         <f t="shared" si="2"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>2004001</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="28">
         <v>200400</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="28">
         <v>200400009</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="28">
         <v>1</v>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="31">
         <v>1990000</v>
       </c>
-      <c r="J14" s="36" t="s">
+      <c r="J14" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="s">
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="37" t="s">
+      <c r="M14" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="N14" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O14" s="4">
+      <c r="N14" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O14" s="2">
         <v>300</v>
       </c>
-      <c r="P14" s="4">
+      <c r="P14" s="2">
         <v>180000</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q14" s="2">
         <v>16000</v>
       </c>
-      <c r="R14" s="4">
+      <c r="R14" s="2">
         <v>15000</v>
       </c>
-      <c r="S14" s="38">
+      <c r="S14" s="34">
         <v>16008</v>
       </c>
-      <c r="T14" s="6">
+      <c r="T14" s="5">
         <v>50</v>
       </c>
-      <c r="U14" s="39">
+      <c r="U14" s="35">
         <v>0</v>
       </c>
       <c r="V14" t="s">
         <v>57</v>
       </c>
-      <c r="W14" s="8" t="s">
+      <c r="W14" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X14" s="2">
         <v>0</v>
       </c>
-      <c r="Y14" s="8">
+      <c r="Y14" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="4">
+      <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="36">
         <v>200400</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="36">
         <v>200400009</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="34" t="s">
+      <c r="G15" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="40">
+      <c r="H15" s="36">
         <v>2</v>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="31">
         <v>1990000</v>
       </c>
-      <c r="J15" s="41" t="s">
+      <c r="J15" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="4">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="s">
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="N15" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O15" s="4">
+      <c r="N15" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O15" s="2">
         <v>300</v>
       </c>
-      <c r="P15" s="4">
+      <c r="P15" s="2">
         <v>180000</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="Q15" s="2">
         <v>16000</v>
       </c>
-      <c r="R15" s="4">
+      <c r="R15" s="2">
         <v>15000</v>
       </c>
-      <c r="S15" s="38">
+      <c r="S15" s="34">
         <v>16008</v>
       </c>
-      <c r="T15" s="6">
+      <c r="T15" s="5">
         <v>50</v>
       </c>
-      <c r="U15" s="39">
+      <c r="U15" s="35">
         <v>0</v>
       </c>
       <c r="V15" t="s">
         <v>61</v>
       </c>
-      <c r="W15" s="8" t="s">
+      <c r="W15" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X15" s="2">
         <v>0</v>
       </c>
-      <c r="Y15" s="8">
+      <c r="Y15" s="4">
         <f t="shared" si="2"/>
         <v>100000000</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:25">
-      <c r="A16" s="4">
+      <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>2004003</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="28">
         <v>200400</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="28">
         <v>200400009</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="34" t="s">
+      <c r="G16" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="28">
         <v>3</v>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="31">
         <v>1990000</v>
       </c>
-      <c r="J16" s="36" t="s">
+      <c r="J16" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="4">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="s">
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="N16" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O16" s="4">
+      <c r="N16" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O16" s="2">
         <v>300</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P16" s="2">
         <v>180000</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="Q16" s="2">
         <v>16000</v>
       </c>
-      <c r="R16" s="4">
+      <c r="R16" s="2">
         <v>15000</v>
       </c>
-      <c r="S16" s="38">
+      <c r="S16" s="34">
         <v>16008</v>
       </c>
-      <c r="T16" s="6">
+      <c r="T16" s="5">
         <v>50</v>
       </c>
-      <c r="U16" s="39">
+      <c r="U16" s="35">
         <v>0</v>
       </c>
       <c r="V16" t="s">
         <v>65</v>
       </c>
-      <c r="W16" s="8" t="s">
+      <c r="W16" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X16" s="2">
         <v>0</v>
       </c>
-      <c r="Y16" s="8">
+      <c r="Y16" s="4">
         <f t="shared" si="2"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:25">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>2005001</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="28">
         <v>200500</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="28">
         <v>200500025</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="59" t="s">
+      <c r="F17" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="34" t="s">
+      <c r="G17" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="28">
         <v>1</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="31">
         <v>1990000</v>
       </c>
-      <c r="J17" s="36" t="s">
+      <c r="J17" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="2">
         <v>1</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="N17" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O17" s="4">
+      <c r="N17" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O17" s="2">
         <v>300</v>
       </c>
-      <c r="P17" s="4">
+      <c r="P17" s="2">
         <v>180000</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="Q17" s="2">
         <v>16000</v>
       </c>
-      <c r="R17" s="4">
+      <c r="R17" s="2">
         <v>15000</v>
       </c>
-      <c r="S17" s="38">
+      <c r="S17" s="34">
         <v>16008</v>
       </c>
-      <c r="T17" s="6">
+      <c r="T17" s="5">
         <v>48</v>
       </c>
-      <c r="U17" s="39">
+      <c r="U17" s="35">
         <v>0</v>
       </c>
       <c r="V17" t="s">
         <v>57</v>
       </c>
-      <c r="W17" s="8" t="s">
+      <c r="W17" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
       </c>
-      <c r="Y17" s="8">
+      <c r="Y17" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="36">
         <v>200500</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="36">
         <v>200500025</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="40">
+      <c r="H18" s="36">
         <v>2</v>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="31">
         <v>1990000</v>
       </c>
-      <c r="J18" s="41" t="s">
+      <c r="J18" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="2">
         <v>1</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="37" t="s">
+      <c r="M18" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="N18" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O18" s="4">
+      <c r="N18" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O18" s="2">
         <v>300</v>
       </c>
-      <c r="P18" s="4">
+      <c r="P18" s="2">
         <v>180000</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="Q18" s="2">
         <v>16000</v>
       </c>
-      <c r="R18" s="4">
+      <c r="R18" s="2">
         <v>15000</v>
       </c>
-      <c r="S18" s="38">
+      <c r="S18" s="34">
         <v>16008</v>
       </c>
-      <c r="T18" s="6">
+      <c r="T18" s="5">
         <v>48</v>
       </c>
-      <c r="U18" s="39">
+      <c r="U18" s="35">
         <v>0</v>
       </c>
       <c r="V18" t="s">
         <v>61</v>
       </c>
-      <c r="W18" s="8" t="s">
+      <c r="W18" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X18" s="2">
         <v>0</v>
       </c>
-      <c r="Y18" s="8">
+      <c r="Y18" s="4">
         <f t="shared" ref="Y18:Y22" si="3">Y17*10</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="4">
+      <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>2005003</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="28">
         <v>200500</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="28">
         <v>200500025</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="59" t="s">
+      <c r="F19" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="34" t="s">
+      <c r="G19" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="28">
         <v>3</v>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="31">
         <v>1990000</v>
       </c>
-      <c r="J19" s="36" t="s">
+      <c r="J19" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="2">
         <v>1</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="37" t="s">
+      <c r="M19" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="N19" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O19" s="4">
+      <c r="N19" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O19" s="2">
         <v>300</v>
       </c>
-      <c r="P19" s="4">
+      <c r="P19" s="2">
         <v>180000</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="Q19" s="2">
         <v>16000</v>
       </c>
-      <c r="R19" s="4">
+      <c r="R19" s="2">
         <v>15000</v>
       </c>
-      <c r="S19" s="38">
+      <c r="S19" s="34">
         <v>16008</v>
       </c>
-      <c r="T19" s="6">
+      <c r="T19" s="5">
         <v>48</v>
       </c>
-      <c r="U19" s="39">
+      <c r="U19" s="35">
         <v>0</v>
       </c>
       <c r="V19" t="s">
         <v>65</v>
       </c>
-      <c r="W19" s="8" t="s">
+      <c r="W19" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X19" s="2">
         <v>0</v>
       </c>
-      <c r="Y19" s="8">
+      <c r="Y19" s="4">
         <f t="shared" si="3"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>2006001</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="28">
         <v>200600</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="28">
         <v>200600001</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G20" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="28">
         <v>1</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="31">
         <v>1990000</v>
       </c>
-      <c r="J20" s="36" t="s">
+      <c r="J20" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K20" s="4">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="s">
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="37" t="s">
+      <c r="M20" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="N20" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O20" s="4">
+      <c r="N20" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O20" s="2">
         <v>300</v>
       </c>
-      <c r="P20" s="4">
+      <c r="P20" s="2">
         <v>180000</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="Q20" s="2">
         <v>16000</v>
       </c>
-      <c r="R20" s="4">
+      <c r="R20" s="2">
         <v>15000</v>
       </c>
-      <c r="S20" s="38">
+      <c r="S20" s="34">
         <v>16008</v>
       </c>
-      <c r="T20" s="6">
+      <c r="T20" s="5">
         <v>20</v>
       </c>
-      <c r="U20" s="39">
+      <c r="U20" s="35">
         <v>0</v>
       </c>
       <c r="V20" t="s">
         <v>57</v>
       </c>
-      <c r="W20" s="8" t="s">
+      <c r="W20" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X20" s="2">
         <v>0</v>
       </c>
-      <c r="Y20" s="8">
+      <c r="Y20" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:25">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="40">
+      <c r="B21" s="36">
         <v>200600</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="36">
         <v>200600001</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="G21" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="36">
         <v>2</v>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="31">
         <v>1990000</v>
       </c>
-      <c r="J21" s="41" t="s">
+      <c r="J21" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K21" s="4">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="s">
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="37" t="s">
+      <c r="M21" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="N21" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O21" s="4">
+      <c r="N21" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O21" s="2">
         <v>300</v>
       </c>
-      <c r="P21" s="4">
+      <c r="P21" s="2">
         <v>180000</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="Q21" s="2">
         <v>16000</v>
       </c>
-      <c r="R21" s="4">
+      <c r="R21" s="2">
         <v>15000</v>
       </c>
-      <c r="S21" s="38">
+      <c r="S21" s="34">
         <v>16008</v>
       </c>
-      <c r="T21" s="6">
+      <c r="T21" s="5">
         <v>20</v>
       </c>
-      <c r="U21" s="39">
+      <c r="U21" s="35">
         <v>0</v>
       </c>
       <c r="V21" t="s">
         <v>61</v>
       </c>
-      <c r="W21" s="8" t="s">
+      <c r="W21" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X21" s="2">
         <v>0</v>
       </c>
-      <c r="Y21" s="8">
+      <c r="Y21" s="4">
         <f t="shared" si="3"/>
         <v>100000000</v>
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>2006003</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="28">
         <v>200600</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="28">
         <v>200600001</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="34" t="s">
+      <c r="G22" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="28">
         <v>3</v>
       </c>
-      <c r="I22" s="35">
+      <c r="I22" s="31">
         <v>1990000</v>
       </c>
-      <c r="J22" s="36" t="s">
+      <c r="J22" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K22" s="4">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="s">
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M22" s="37" t="s">
+      <c r="M22" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="N22" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O22" s="4">
+      <c r="N22" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O22" s="2">
         <v>300</v>
       </c>
-      <c r="P22" s="4">
+      <c r="P22" s="2">
         <v>180000</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="Q22" s="2">
         <v>16000</v>
       </c>
-      <c r="R22" s="4">
+      <c r="R22" s="2">
         <v>15000</v>
       </c>
-      <c r="S22" s="38">
+      <c r="S22" s="34">
         <v>16008</v>
       </c>
-      <c r="T22" s="6">
+      <c r="T22" s="5">
         <v>20</v>
       </c>
-      <c r="U22" s="39">
+      <c r="U22" s="35">
         <v>0</v>
       </c>
       <c r="V22" t="s">
         <v>65</v>
       </c>
-      <c r="W22" s="8" t="s">
+      <c r="W22" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X22" s="2">
         <v>0</v>
       </c>
-      <c r="Y22" s="8">
+      <c r="Y22" s="4">
         <f t="shared" si="3"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="4">
+      <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>2007001</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="28">
         <v>200700</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="28">
         <v>200700001</v>
       </c>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="34" t="s">
+      <c r="G23" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="28">
         <v>1</v>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="31">
         <v>1990000</v>
       </c>
-      <c r="J23" s="36" t="s">
+      <c r="J23" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="2">
         <v>1</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="37" t="s">
+      <c r="M23" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="N23" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O23" s="4">
+      <c r="N23" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O23" s="2">
         <v>300</v>
       </c>
-      <c r="P23" s="4">
+      <c r="P23" s="2">
         <v>180000</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="Q23" s="2">
         <v>16000</v>
       </c>
-      <c r="R23" s="4">
+      <c r="R23" s="2">
         <v>15000</v>
       </c>
-      <c r="S23" s="38">
+      <c r="S23" s="34">
         <v>16008</v>
       </c>
-      <c r="T23" s="6">
+      <c r="T23" s="5">
         <v>30</v>
       </c>
-      <c r="U23" s="39">
+      <c r="U23" s="35">
         <v>1</v>
       </c>
       <c r="V23" t="s">
         <v>57</v>
       </c>
-      <c r="W23" s="8" t="s">
+      <c r="W23" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X23" s="2">
         <v>0</v>
       </c>
-      <c r="Y23" s="8">
+      <c r="Y23" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="4">
+      <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="36">
         <v>200700</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="36">
         <v>200700001</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="34" t="s">
+      <c r="G24" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="40">
+      <c r="H24" s="36">
         <v>2</v>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="31">
         <v>1990000</v>
       </c>
-      <c r="J24" s="41" t="s">
+      <c r="J24" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="2">
         <v>1</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M24" s="37" t="s">
+      <c r="M24" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="N24" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O24" s="4">
+      <c r="N24" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O24" s="2">
         <v>300</v>
       </c>
-      <c r="P24" s="4">
+      <c r="P24" s="2">
         <v>180000</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="Q24" s="2">
         <v>16000</v>
       </c>
-      <c r="R24" s="4">
+      <c r="R24" s="2">
         <v>15000</v>
       </c>
-      <c r="S24" s="38">
+      <c r="S24" s="34">
         <v>16008</v>
       </c>
-      <c r="T24" s="6">
+      <c r="T24" s="5">
         <v>30</v>
       </c>
-      <c r="U24" s="39">
+      <c r="U24" s="35">
         <v>1</v>
       </c>
       <c r="V24" t="s">
         <v>61</v>
       </c>
-      <c r="W24" s="8" t="s">
+      <c r="W24" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X24" s="2">
         <v>0</v>
       </c>
-      <c r="Y24" s="8">
+      <c r="Y24" s="4">
         <f t="shared" ref="Y24:Y28" si="4">Y23*10</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:25">
-      <c r="A25" s="4">
+      <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>2007003</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="28">
         <v>200700</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="28">
         <v>200700001</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G25" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="28">
         <v>3</v>
       </c>
-      <c r="I25" s="35">
+      <c r="I25" s="31">
         <v>1990000</v>
       </c>
-      <c r="J25" s="36" t="s">
+      <c r="J25" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25" s="2">
         <v>1</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M25" s="37" t="s">
+      <c r="M25" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="N25" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O25" s="4">
+      <c r="N25" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O25" s="2">
         <v>300</v>
       </c>
-      <c r="P25" s="4">
+      <c r="P25" s="2">
         <v>180000</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="Q25" s="2">
         <v>16000</v>
       </c>
-      <c r="R25" s="4">
+      <c r="R25" s="2">
         <v>15000</v>
       </c>
-      <c r="S25" s="38">
+      <c r="S25" s="34">
         <v>16008</v>
       </c>
-      <c r="T25" s="6">
+      <c r="T25" s="5">
         <v>30</v>
       </c>
-      <c r="U25" s="39">
+      <c r="U25" s="35">
         <v>1</v>
       </c>
       <c r="V25" t="s">
         <v>65</v>
       </c>
-      <c r="W25" s="8" t="s">
+      <c r="W25" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X25" s="2">
         <v>0</v>
       </c>
-      <c r="Y25" s="8">
+      <c r="Y25" s="4">
         <f t="shared" si="4"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:25">
-      <c r="A26" s="4">
+      <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>2008001</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="28">
         <v>200800</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="28">
         <v>200800001</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="34" t="s">
+      <c r="G26" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="28">
         <v>1</v>
       </c>
-      <c r="I26" s="35">
+      <c r="I26" s="31">
         <v>1990000</v>
       </c>
-      <c r="J26" s="36" t="s">
+      <c r="J26" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K26" s="4">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="s">
+      <c r="K26" s="2">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="37" t="s">
+      <c r="M26" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="N26" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O26" s="4">
+      <c r="N26" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O26" s="2">
         <v>300</v>
       </c>
-      <c r="P26" s="4">
+      <c r="P26" s="2">
         <v>180000</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="Q26" s="2">
         <v>16000</v>
       </c>
-      <c r="R26" s="4">
+      <c r="R26" s="2">
         <v>15000</v>
       </c>
-      <c r="S26" s="38">
+      <c r="S26" s="34">
         <v>16008</v>
       </c>
-      <c r="T26" s="6">
+      <c r="T26" s="5">
         <v>20</v>
       </c>
-      <c r="U26" s="39">
+      <c r="U26" s="35">
         <v>0</v>
       </c>
       <c r="V26" t="s">
         <v>57</v>
       </c>
-      <c r="W26" s="8" t="s">
+      <c r="W26" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X26" s="2">
         <v>0</v>
       </c>
-      <c r="Y26" s="8">
+      <c r="Y26" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:25">
-      <c r="A27" s="4">
+      <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>2008002</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="28">
         <v>200800</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="28">
         <v>200800001</v>
       </c>
-      <c r="E27" s="40" t="s">
+      <c r="E27" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="59" t="s">
+      <c r="F27" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="34" t="s">
+      <c r="G27" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="36">
         <v>2</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="31">
         <v>1990000</v>
       </c>
-      <c r="J27" s="41" t="s">
+      <c r="J27" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K27" s="4">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="s">
+      <c r="K27" s="2">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="37" t="s">
+      <c r="M27" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="N27" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O27" s="4">
+      <c r="N27" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O27" s="2">
         <v>300</v>
       </c>
-      <c r="P27" s="4">
+      <c r="P27" s="2">
         <v>180000</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="Q27" s="2">
         <v>16000</v>
       </c>
-      <c r="R27" s="4">
+      <c r="R27" s="2">
         <v>15000</v>
       </c>
-      <c r="S27" s="38">
+      <c r="S27" s="34">
         <v>16008</v>
       </c>
-      <c r="T27" s="6">
+      <c r="T27" s="5">
         <v>20</v>
       </c>
-      <c r="U27" s="39">
+      <c r="U27" s="35">
         <v>0</v>
       </c>
       <c r="V27" t="s">
         <v>61</v>
       </c>
-      <c r="W27" s="8" t="s">
+      <c r="W27" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X27" s="2">
         <v>0</v>
       </c>
-      <c r="Y27" s="8">
+      <c r="Y27" s="4">
         <f t="shared" si="4"/>
         <v>100000000</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="1:25">
-      <c r="A28" s="4">
+      <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>2008003</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="28">
         <v>200800</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="28">
         <v>200800001</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="34" t="s">
+      <c r="G28" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="28">
         <v>3</v>
       </c>
-      <c r="I28" s="35">
+      <c r="I28" s="31">
         <v>1990000</v>
       </c>
-      <c r="J28" s="36" t="s">
+      <c r="J28" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K28" s="4">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="s">
+      <c r="K28" s="2">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M28" s="37" t="s">
+      <c r="M28" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="N28" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O28" s="4">
+      <c r="N28" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O28" s="2">
         <v>300</v>
       </c>
-      <c r="P28" s="4">
+      <c r="P28" s="2">
         <v>180000</v>
       </c>
-      <c r="Q28" s="4">
+      <c r="Q28" s="2">
         <v>16000</v>
       </c>
-      <c r="R28" s="4">
+      <c r="R28" s="2">
         <v>15000</v>
       </c>
-      <c r="S28" s="38">
+      <c r="S28" s="34">
         <v>16008</v>
       </c>
-      <c r="T28" s="6">
+      <c r="T28" s="5">
         <v>20</v>
       </c>
-      <c r="U28" s="39">
+      <c r="U28" s="35">
         <v>0</v>
       </c>
       <c r="V28" t="s">
         <v>65</v>
       </c>
-      <c r="W28" s="8" t="s">
+      <c r="W28" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X28" s="2">
         <v>0</v>
       </c>
-      <c r="Y28" s="8">
+      <c r="Y28" s="4">
         <f t="shared" si="4"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:25">
-      <c r="A29" s="4">
+      <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="44">
+      <c r="B29" s="40">
         <v>200900</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="28">
         <v>200900001</v>
       </c>
-      <c r="E29" s="42" t="s">
+      <c r="E29" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="34" t="s">
+      <c r="G29" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="28">
         <v>1</v>
       </c>
-      <c r="I29" s="35">
+      <c r="I29" s="31">
         <v>1990000</v>
       </c>
-      <c r="J29" s="36" t="s">
+      <c r="J29" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="45">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="s">
+      <c r="K29" s="41">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M29" s="37" t="s">
+      <c r="M29" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="N29" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O29" s="4">
+      <c r="N29" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O29" s="2">
         <v>300</v>
       </c>
-      <c r="P29" s="4">
+      <c r="P29" s="2">
         <v>180000</v>
       </c>
-      <c r="Q29" s="4">
+      <c r="Q29" s="2">
         <v>16000</v>
       </c>
-      <c r="R29" s="4">
+      <c r="R29" s="2">
         <v>15000</v>
       </c>
-      <c r="S29" s="38">
+      <c r="S29" s="34">
         <v>16008</v>
       </c>
-      <c r="T29" s="6">
+      <c r="T29" s="5">
         <v>20</v>
       </c>
-      <c r="U29" s="39">
+      <c r="U29" s="35">
         <v>0</v>
       </c>
       <c r="V29" t="s">
         <v>57</v>
       </c>
-      <c r="W29" s="8" t="s">
+      <c r="W29" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X29" s="2">
         <v>0</v>
       </c>
-      <c r="Y29" s="8">
+      <c r="Y29" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="4">
+      <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="46">
+      <c r="B30" s="42">
         <v>200900</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="36">
         <v>200900001</v>
       </c>
-      <c r="E30" s="40" t="s">
+      <c r="E30" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="34" t="s">
+      <c r="G30" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="40">
+      <c r="H30" s="36">
         <v>2</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="31">
         <v>1990000</v>
       </c>
-      <c r="J30" s="41" t="s">
+      <c r="J30" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="45">
-        <v>0</v>
-      </c>
-      <c r="L30" s="4" t="s">
+      <c r="K30" s="41">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M30" s="37" t="s">
+      <c r="M30" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="N30" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O30" s="4">
+      <c r="N30" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O30" s="2">
         <v>300</v>
       </c>
-      <c r="P30" s="4">
+      <c r="P30" s="2">
         <v>180000</v>
       </c>
-      <c r="Q30" s="4">
+      <c r="Q30" s="2">
         <v>16000</v>
       </c>
-      <c r="R30" s="4">
+      <c r="R30" s="2">
         <v>15000</v>
       </c>
-      <c r="S30" s="38">
+      <c r="S30" s="34">
         <v>16008</v>
       </c>
-      <c r="T30" s="6">
+      <c r="T30" s="5">
         <v>20</v>
       </c>
-      <c r="U30" s="39">
+      <c r="U30" s="35">
         <v>0</v>
       </c>
       <c r="V30" t="s">
         <v>61</v>
       </c>
-      <c r="W30" s="8" t="s">
+      <c r="W30" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X30" s="2">
         <v>0</v>
       </c>
-      <c r="Y30" s="8">
+      <c r="Y30" s="4">
         <f t="shared" ref="Y30:Y34" si="5">Y29*10</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="4">
+      <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="47">
+      <c r="B31" s="40">
         <v>200900</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="48">
+      <c r="D31" s="28">
         <v>200900001</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="59" t="s">
+      <c r="F31" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="34" t="s">
+      <c r="G31" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="32">
+      <c r="H31" s="28">
         <v>3</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="31">
         <v>1990000</v>
       </c>
-      <c r="J31" s="36" t="s">
+      <c r="J31" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="45">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="s">
+      <c r="K31" s="41">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M31" s="37" t="s">
+      <c r="M31" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="N31" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O31" s="4">
+      <c r="N31" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O31" s="2">
         <v>300</v>
       </c>
-      <c r="P31" s="4">
+      <c r="P31" s="2">
         <v>180000</v>
       </c>
-      <c r="Q31" s="4">
+      <c r="Q31" s="2">
         <v>16000</v>
       </c>
-      <c r="R31" s="4">
+      <c r="R31" s="2">
         <v>15000</v>
       </c>
-      <c r="S31" s="38">
+      <c r="S31" s="34">
         <v>16008</v>
       </c>
-      <c r="T31" s="6">
+      <c r="T31" s="5">
         <v>20</v>
       </c>
-      <c r="U31" s="39">
+      <c r="U31" s="35">
         <v>0</v>
       </c>
       <c r="V31" t="s">
         <v>65</v>
       </c>
-      <c r="W31" s="8" t="s">
+      <c r="W31" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X31" s="2">
         <v>0</v>
       </c>
-      <c r="Y31" s="8">
+      <c r="Y31" s="4">
         <f t="shared" si="5"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:25">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>2012001</v>
       </c>
-      <c r="B32" s="49">
+      <c r="B32" s="43">
         <v>201200</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="36">
         <v>201200001</v>
       </c>
-      <c r="E32" s="42" t="s">
+      <c r="E32" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="34" t="s">
+      <c r="G32" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="28">
         <v>1</v>
       </c>
-      <c r="I32" s="35">
+      <c r="I32" s="31">
         <v>1990000</v>
       </c>
-      <c r="J32" s="36" t="s">
+      <c r="J32" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="45">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="s">
+      <c r="K32" s="41">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M32" s="37" t="s">
+      <c r="M32" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="N32" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O32" s="4">
+      <c r="N32" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O32" s="2">
         <v>300</v>
       </c>
-      <c r="P32" s="4">
+      <c r="P32" s="2">
         <v>180000</v>
       </c>
-      <c r="Q32" s="4">
+      <c r="Q32" s="2">
         <v>16000</v>
       </c>
-      <c r="R32" s="4">
+      <c r="R32" s="2">
         <v>15000</v>
       </c>
-      <c r="S32" s="38">
+      <c r="S32" s="34">
         <v>16008</v>
       </c>
-      <c r="T32" s="6">
+      <c r="T32" s="5">
         <v>12</v>
       </c>
-      <c r="U32" s="39">
+      <c r="U32" s="35">
         <v>0</v>
       </c>
       <c r="V32" t="s">
         <v>57</v>
       </c>
-      <c r="W32" s="8" t="s">
+      <c r="W32" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X32" s="2">
         <v>0</v>
       </c>
-      <c r="Y32" s="8">
+      <c r="Y32" s="4">
         <f>100*100000</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="33" customFormat="1" spans="1:25">
-      <c r="A33" s="4">
+    <row r="33" spans="1:25">
+      <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>2012002</v>
       </c>
-      <c r="B33" s="49">
+      <c r="B33" s="43">
         <v>201200</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="40">
+      <c r="D33" s="36">
         <v>201200001</v>
       </c>
-      <c r="E33" s="40" t="s">
+      <c r="E33" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="59" t="s">
+      <c r="F33" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="34" t="s">
+      <c r="G33" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="40">
+      <c r="H33" s="36">
         <v>2</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="31">
         <v>1990000</v>
       </c>
-      <c r="J33" s="41" t="s">
+      <c r="J33" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="45">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="s">
+      <c r="K33" s="41">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="37" t="s">
+      <c r="M33" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="N33" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O33" s="4">
+      <c r="N33" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O33" s="2">
         <v>300</v>
       </c>
-      <c r="P33" s="4">
+      <c r="P33" s="2">
         <v>180000</v>
       </c>
-      <c r="Q33" s="4">
+      <c r="Q33" s="2">
         <v>16000</v>
       </c>
-      <c r="R33" s="4">
+      <c r="R33" s="2">
         <v>15000</v>
       </c>
-      <c r="S33" s="38">
+      <c r="S33" s="34">
         <v>16008</v>
       </c>
-      <c r="T33" s="6">
+      <c r="T33" s="5">
         <v>12</v>
       </c>
-      <c r="U33" s="39">
+      <c r="U33" s="35">
         <v>0</v>
       </c>
       <c r="V33" t="s">
         <v>61</v>
       </c>
-      <c r="W33" s="8" t="s">
+      <c r="W33" s="4" t="s">
         <v>62</v>
       </c>
       <c r="X33" s="2">
         <v>0</v>
       </c>
-      <c r="Y33" s="8">
+      <c r="Y33" s="4">
         <f t="shared" si="5"/>
         <v>100000000</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:25">
-      <c r="A34" s="4">
+    <row r="34" spans="1:25">
+      <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>2012003</v>
       </c>
-      <c r="B34" s="49">
+      <c r="B34" s="43">
         <v>201200</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="40">
+      <c r="D34" s="36">
         <v>201200001</v>
       </c>
-      <c r="E34" s="48" t="s">
+      <c r="E34" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="34" t="s">
+      <c r="G34" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="28">
         <v>3</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="31">
         <v>1990000</v>
       </c>
-      <c r="J34" s="36" t="s">
+      <c r="J34" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="45">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="s">
+      <c r="K34" s="41">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M34" s="37" t="s">
+      <c r="M34" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="N34" s="4">
-        <v>9500</v>
-      </c>
-      <c r="O34" s="4">
+      <c r="N34" s="2">
+        <v>9700</v>
+      </c>
+      <c r="O34" s="2">
         <v>300</v>
       </c>
-      <c r="P34" s="4">
+      <c r="P34" s="2">
         <v>180000</v>
       </c>
-      <c r="Q34" s="4">
+      <c r="Q34" s="2">
         <v>16000</v>
       </c>
-      <c r="R34" s="4">
+      <c r="R34" s="2">
         <v>15000</v>
       </c>
-      <c r="S34" s="38">
+      <c r="S34" s="34">
         <v>16008</v>
       </c>
-      <c r="T34" s="6">
+      <c r="T34" s="5">
         <v>12</v>
       </c>
-      <c r="U34" s="39">
+      <c r="U34" s="35">
         <v>0</v>
       </c>
       <c r="V34" t="s">
         <v>65</v>
       </c>
-      <c r="W34" s="8" t="s">
+      <c r="W34" s="4" t="s">
         <v>66</v>
       </c>
       <c r="X34" s="2">
         <v>0</v>
       </c>
-      <c r="Y34" s="8">
+      <c r="Y34" s="4">
         <f t="shared" si="5"/>
         <v>1000000000</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="50">
+      <c r="A35" s="44">
         <v>20010010</v>
       </c>
       <c r="B35" s="3">
         <v>200100</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="45">
         <v>200100038</v>
       </c>
-      <c r="E35" s="51" t="s">
+      <c r="E35" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="60" t="s">
+      <c r="F35" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="53" t="s">
+      <c r="G35" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="51">
-        <v>1</v>
-      </c>
-      <c r="I35" s="51">
+      <c r="H35" s="45">
+        <v>10</v>
+      </c>
+      <c r="I35" s="45">
         <v>1980000</v>
       </c>
-      <c r="J35" s="36" t="s">
+      <c r="J35" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K35" s="3">
@@ -4615,11 +4590,11 @@
       <c r="L35" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M35" s="54" t="s">
+      <c r="M35" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="N35" s="4">
-        <v>9500</v>
+      <c r="N35" s="2">
+        <v>9700</v>
       </c>
       <c r="O35" s="3">
         <v>300</v>
@@ -4633,55 +4608,55 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="55">
+      <c r="S35" s="49">
         <v>16008</v>
       </c>
-      <c r="T35" s="50">
+      <c r="T35" s="44">
         <v>48</v>
       </c>
-      <c r="U35" s="56">
+      <c r="U35" s="50">
         <v>0</v>
       </c>
       <c r="V35" t="s">
         <v>57</v>
       </c>
-      <c r="W35" s="8" t="s">
+      <c r="W35" s="4" t="s">
         <v>86</v>
       </c>
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="57"/>
+      <c r="Y35" s="51"/>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="50">
+      <c r="A36" s="44">
         <v>20010011</v>
       </c>
       <c r="B36" s="3">
         <v>200100</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="45">
         <v>200100038</v>
       </c>
-      <c r="E36" s="51" t="s">
+      <c r="E36" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="60" t="s">
+      <c r="F36" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="53" t="s">
+      <c r="G36" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H36" s="51">
-        <v>2</v>
-      </c>
-      <c r="I36" s="51">
+      <c r="H36" s="45">
+        <v>11</v>
+      </c>
+      <c r="I36" s="45">
         <v>1980000</v>
       </c>
-      <c r="J36" s="41" t="s">
+      <c r="J36" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K36" s="3">
@@ -4690,11 +4665,11 @@
       <c r="L36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M36" s="54" t="s">
+      <c r="M36" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="N36" s="4">
-        <v>9500</v>
+      <c r="N36" s="2">
+        <v>9700</v>
       </c>
       <c r="O36" s="3">
         <v>300</v>
@@ -4708,55 +4683,55 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="55">
+      <c r="S36" s="49">
         <v>16008</v>
       </c>
-      <c r="T36" s="50">
+      <c r="T36" s="44">
         <v>48</v>
       </c>
-      <c r="U36" s="56">
+      <c r="U36" s="50">
         <v>0</v>
       </c>
       <c r="V36" t="s">
         <v>61</v>
       </c>
-      <c r="W36" s="8" t="s">
+      <c r="W36" s="4" t="s">
         <v>87</v>
       </c>
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="57"/>
+      <c r="Y36" s="51"/>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="50">
+      <c r="A37" s="44">
         <v>20010012</v>
       </c>
       <c r="B37" s="3">
         <v>200100</v>
       </c>
-      <c r="C37" s="51" t="s">
+      <c r="C37" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="45">
         <v>200100038</v>
       </c>
-      <c r="E37" s="51" t="s">
+      <c r="E37" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="60" t="s">
+      <c r="F37" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="53" t="s">
+      <c r="G37" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H37" s="51">
-        <v>3</v>
-      </c>
-      <c r="I37" s="51">
+      <c r="H37" s="45">
+        <v>12</v>
+      </c>
+      <c r="I37" s="45">
         <v>1980000</v>
       </c>
-      <c r="J37" s="36" t="s">
+      <c r="J37" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K37" s="3">
@@ -4765,11 +4740,11 @@
       <c r="L37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M37" s="54" t="s">
+      <c r="M37" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="N37" s="4">
-        <v>9500</v>
+      <c r="N37" s="2">
+        <v>9700</v>
       </c>
       <c r="O37" s="3">
         <v>300</v>
@@ -4783,28 +4758,28 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="55">
+      <c r="S37" s="49">
         <v>16008</v>
       </c>
-      <c r="T37" s="50">
+      <c r="T37" s="44">
         <v>48</v>
       </c>
-      <c r="U37" s="56">
+      <c r="U37" s="50">
         <v>0</v>
       </c>
       <c r="V37" t="s">
         <v>65</v>
       </c>
-      <c r="W37" s="8" t="s">
+      <c r="W37" s="4" t="s">
         <v>88</v>
       </c>
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="57"/>
+      <c r="Y37" s="51"/>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="50">
+      <c r="A38" s="44">
         <v>20010110</v>
       </c>
       <c r="B38" s="3">
@@ -4819,19 +4794,19 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="61" t="s">
+      <c r="F38" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="53" t="s">
+      <c r="G38" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H38" s="3">
-        <v>1</v>
-      </c>
-      <c r="I38" s="51">
+      <c r="H38" s="45">
+        <v>10</v>
+      </c>
+      <c r="I38" s="45">
         <v>1980000</v>
       </c>
-      <c r="J38" s="36" t="s">
+      <c r="J38" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K38" s="3">
@@ -4840,11 +4815,11 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="54" t="s">
+      <c r="M38" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="N38" s="4">
-        <v>9500</v>
+      <c r="N38" s="2">
+        <v>9700</v>
       </c>
       <c r="O38" s="3">
         <v>300</v>
@@ -4861,25 +4836,25 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="50">
+      <c r="T38" s="44">
         <v>48</v>
       </c>
-      <c r="U38" s="56">
+      <c r="U38" s="50">
         <v>0</v>
       </c>
       <c r="V38" t="s">
         <v>57</v>
       </c>
-      <c r="W38" s="8" t="s">
+      <c r="W38" s="4" t="s">
         <v>89</v>
       </c>
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="57"/>
+      <c r="Y38" s="51"/>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="50">
+      <c r="A39" s="44">
         <v>20010111</v>
       </c>
       <c r="B39" s="3">
@@ -4894,19 +4869,19 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="61" t="s">
+      <c r="F39" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="53" t="s">
+      <c r="G39" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H39" s="3">
-        <v>2</v>
-      </c>
-      <c r="I39" s="51">
+      <c r="H39" s="45">
+        <v>11</v>
+      </c>
+      <c r="I39" s="45">
         <v>1980000</v>
       </c>
-      <c r="J39" s="41" t="s">
+      <c r="J39" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K39" s="3">
@@ -4915,11 +4890,11 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="54" t="s">
+      <c r="M39" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="N39" s="4">
-        <v>9500</v>
+      <c r="N39" s="2">
+        <v>9700</v>
       </c>
       <c r="O39" s="3">
         <v>300</v>
@@ -4936,25 +4911,25 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="50">
+      <c r="T39" s="44">
         <v>48</v>
       </c>
-      <c r="U39" s="56">
+      <c r="U39" s="50">
         <v>0</v>
       </c>
       <c r="V39" t="s">
         <v>61</v>
       </c>
-      <c r="W39" s="8" t="s">
+      <c r="W39" s="4" t="s">
         <v>90</v>
       </c>
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="57"/>
+      <c r="Y39" s="51"/>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="50">
+      <c r="A40" s="44">
         <v>20010112</v>
       </c>
       <c r="B40" s="3">
@@ -4969,19 +4944,19 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="61" t="s">
+      <c r="F40" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="53" t="s">
+      <c r="G40" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H40" s="3">
-        <v>3</v>
-      </c>
-      <c r="I40" s="51">
+      <c r="H40" s="45">
+        <v>12</v>
+      </c>
+      <c r="I40" s="45">
         <v>1980000</v>
       </c>
-      <c r="J40" s="36" t="s">
+      <c r="J40" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K40" s="3">
@@ -4990,11 +4965,11 @@
       <c r="L40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="54" t="s">
+      <c r="M40" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="N40" s="4">
-        <v>9500</v>
+      <c r="N40" s="2">
+        <v>9700</v>
       </c>
       <c r="O40" s="3">
         <v>300</v>
@@ -5011,25 +4986,25 @@
       <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="50">
+      <c r="T40" s="44">
         <v>48</v>
       </c>
-      <c r="U40" s="56">
+      <c r="U40" s="50">
         <v>0</v>
       </c>
       <c r="V40" t="s">
         <v>65</v>
       </c>
-      <c r="W40" s="8" t="s">
+      <c r="W40" s="4" t="s">
         <v>91</v>
       </c>
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="57"/>
+      <c r="Y40" s="51"/>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="50">
+      <c r="A41" s="44">
         <v>20030010</v>
       </c>
       <c r="B41" s="3">
@@ -5044,19 +5019,19 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="61" t="s">
+      <c r="F41" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="53" t="s">
+      <c r="G41" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H41" s="3">
-        <v>1</v>
-      </c>
-      <c r="I41" s="51">
+      <c r="H41" s="45">
+        <v>10</v>
+      </c>
+      <c r="I41" s="45">
         <v>1980000</v>
       </c>
-      <c r="J41" s="36" t="s">
+      <c r="J41" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K41" s="3">
@@ -5065,11 +5040,11 @@
       <c r="L41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="54" t="s">
+      <c r="M41" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="N41" s="4">
-        <v>9500</v>
+      <c r="N41" s="2">
+        <v>9700</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
@@ -5086,25 +5061,25 @@
       <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="50">
+      <c r="T41" s="44">
         <v>50</v>
       </c>
-      <c r="U41" s="56">
+      <c r="U41" s="50">
         <v>0</v>
       </c>
       <c r="V41" t="s">
         <v>57</v>
       </c>
-      <c r="W41" s="8" t="s">
+      <c r="W41" s="4" t="s">
         <v>92</v>
       </c>
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="57"/>
+      <c r="Y41" s="51"/>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="50">
+      <c r="A42" s="44">
         <v>20030011</v>
       </c>
       <c r="B42" s="3">
@@ -5119,19 +5094,19 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="61" t="s">
+      <c r="F42" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="53" t="s">
+      <c r="G42" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H42" s="3">
-        <v>2</v>
-      </c>
-      <c r="I42" s="51">
+      <c r="H42" s="45">
+        <v>11</v>
+      </c>
+      <c r="I42" s="45">
         <v>1980000</v>
       </c>
-      <c r="J42" s="41" t="s">
+      <c r="J42" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K42" s="3">
@@ -5140,11 +5115,11 @@
       <c r="L42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="54" t="s">
+      <c r="M42" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="N42" s="4">
-        <v>9500</v>
+      <c r="N42" s="2">
+        <v>9700</v>
       </c>
       <c r="O42" s="3">
         <v>300</v>
@@ -5161,25 +5136,25 @@
       <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="50">
+      <c r="T42" s="44">
         <v>50</v>
       </c>
-      <c r="U42" s="56">
+      <c r="U42" s="50">
         <v>0</v>
       </c>
       <c r="V42" t="s">
         <v>61</v>
       </c>
-      <c r="W42" s="8" t="s">
+      <c r="W42" s="4" t="s">
         <v>93</v>
       </c>
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="57"/>
+      <c r="Y42" s="51"/>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="50">
+      <c r="A43" s="44">
         <v>20030012</v>
       </c>
       <c r="B43" s="3">
@@ -5194,67 +5169,67 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="61" t="s">
+      <c r="F43" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="53" t="s">
+      <c r="G43" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H43" s="3">
-        <v>3</v>
-      </c>
-      <c r="I43" s="51">
+      <c r="H43" s="45">
+        <v>12</v>
+      </c>
+      <c r="I43" s="45">
         <v>1980000</v>
       </c>
-      <c r="J43" s="36" t="s">
+      <c r="J43" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K43" s="58">
-        <v>0</v>
-      </c>
-      <c r="L43" s="58" t="s">
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="54" t="s">
+      <c r="M43" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="N43" s="4">
-        <v>9500</v>
+      <c r="N43" s="2">
+        <v>9700</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="58">
+      <c r="P43" s="3">
         <v>180000</v>
       </c>
-      <c r="Q43" s="58">
+      <c r="Q43" s="3">
         <v>16000</v>
       </c>
-      <c r="R43" s="58">
+      <c r="R43" s="3">
         <v>15000</v>
       </c>
-      <c r="S43" s="58">
+      <c r="S43" s="3">
         <v>16008</v>
       </c>
-      <c r="T43" s="50">
+      <c r="T43" s="44">
         <v>50</v>
       </c>
-      <c r="U43" s="56">
+      <c r="U43" s="50">
         <v>0</v>
       </c>
       <c r="V43" t="s">
         <v>65</v>
       </c>
-      <c r="W43" s="8" t="s">
+      <c r="W43" s="4" t="s">
         <v>94</v>
       </c>
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="57"/>
+      <c r="Y43" s="51"/>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="50">
+      <c r="A44" s="44">
         <v>20040010</v>
       </c>
       <c r="B44" s="3">
@@ -5269,67 +5244,67 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="53" t="s">
+      <c r="G44" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H44" s="3">
-        <v>1</v>
-      </c>
-      <c r="I44" s="51">
+      <c r="H44" s="45">
+        <v>10</v>
+      </c>
+      <c r="I44" s="45">
         <v>1980000</v>
       </c>
-      <c r="J44" s="36" t="s">
+      <c r="J44" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K44" s="58">
-        <v>0</v>
-      </c>
-      <c r="L44" s="58" t="s">
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M44" s="54" t="s">
+      <c r="M44" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="N44" s="4">
-        <v>9500</v>
+      <c r="N44" s="2">
+        <v>9700</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="58">
+      <c r="P44" s="3">
         <v>180000</v>
       </c>
-      <c r="Q44" s="58">
+      <c r="Q44" s="3">
         <v>16000</v>
       </c>
-      <c r="R44" s="58">
+      <c r="R44" s="3">
         <v>15000</v>
       </c>
-      <c r="S44" s="58">
+      <c r="S44" s="3">
         <v>16008</v>
       </c>
-      <c r="T44" s="50">
+      <c r="T44" s="44">
         <v>50</v>
       </c>
-      <c r="U44" s="56">
+      <c r="U44" s="50">
         <v>0</v>
       </c>
       <c r="V44" t="s">
         <v>57</v>
       </c>
-      <c r="W44" s="8" t="s">
+      <c r="W44" s="4" t="s">
         <v>95</v>
       </c>
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="57"/>
+      <c r="Y44" s="51"/>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="50">
+      <c r="A45" s="44">
         <v>20040011</v>
       </c>
       <c r="B45" s="3">
@@ -5344,67 +5319,67 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="61" t="s">
+      <c r="F45" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="53" t="s">
+      <c r="G45" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H45" s="3">
-        <v>2</v>
-      </c>
-      <c r="I45" s="51">
+      <c r="H45" s="45">
+        <v>11</v>
+      </c>
+      <c r="I45" s="45">
         <v>1980000</v>
       </c>
-      <c r="J45" s="41" t="s">
+      <c r="J45" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K45" s="58">
-        <v>0</v>
-      </c>
-      <c r="L45" s="58" t="s">
+      <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M45" s="54" t="s">
+      <c r="M45" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="N45" s="4">
-        <v>9500</v>
+      <c r="N45" s="2">
+        <v>9700</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="58">
+      <c r="P45" s="3">
         <v>180000</v>
       </c>
-      <c r="Q45" s="58">
+      <c r="Q45" s="3">
         <v>16000</v>
       </c>
-      <c r="R45" s="58">
+      <c r="R45" s="3">
         <v>15000</v>
       </c>
-      <c r="S45" s="58">
+      <c r="S45" s="3">
         <v>16008</v>
       </c>
-      <c r="T45" s="50">
+      <c r="T45" s="44">
         <v>50</v>
       </c>
-      <c r="U45" s="56">
+      <c r="U45" s="50">
         <v>0</v>
       </c>
       <c r="V45" t="s">
         <v>61</v>
       </c>
-      <c r="W45" s="8" t="s">
+      <c r="W45" s="4" t="s">
         <v>96</v>
       </c>
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="57"/>
+      <c r="Y45" s="51"/>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="50">
+      <c r="A46" s="44">
         <v>20040012</v>
       </c>
       <c r="B46" s="3">
@@ -5419,67 +5394,67 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="61" t="s">
+      <c r="F46" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="53" t="s">
+      <c r="G46" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H46" s="3">
-        <v>3</v>
-      </c>
-      <c r="I46" s="51">
+      <c r="H46" s="45">
+        <v>12</v>
+      </c>
+      <c r="I46" s="45">
         <v>1980000</v>
       </c>
-      <c r="J46" s="36" t="s">
+      <c r="J46" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K46" s="58">
-        <v>0</v>
-      </c>
-      <c r="L46" s="58" t="s">
+      <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M46" s="54" t="s">
+      <c r="M46" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="N46" s="4">
-        <v>9500</v>
+      <c r="N46" s="2">
+        <v>9700</v>
       </c>
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="58">
+      <c r="P46" s="3">
         <v>180000</v>
       </c>
-      <c r="Q46" s="58">
+      <c r="Q46" s="3">
         <v>16000</v>
       </c>
-      <c r="R46" s="58">
+      <c r="R46" s="3">
         <v>15000</v>
       </c>
-      <c r="S46" s="58">
+      <c r="S46" s="3">
         <v>16008</v>
       </c>
-      <c r="T46" s="50">
+      <c r="T46" s="44">
         <v>50</v>
       </c>
-      <c r="U46" s="56">
+      <c r="U46" s="50">
         <v>0</v>
       </c>
       <c r="V46" t="s">
         <v>65</v>
       </c>
-      <c r="W46" s="8" t="s">
+      <c r="W46" s="4" t="s">
         <v>97</v>
       </c>
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="57"/>
+      <c r="Y46" s="51"/>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="50">
+      <c r="A47" s="44">
         <v>20050010</v>
       </c>
       <c r="B47" s="3">
@@ -5494,67 +5469,67 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="61" t="s">
+      <c r="F47" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="53" t="s">
+      <c r="G47" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="45">
+        <v>10</v>
+      </c>
+      <c r="I47" s="45">
+        <v>1980000</v>
+      </c>
+      <c r="J47" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="51">
-        <v>1980000</v>
-      </c>
-      <c r="J47" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="K47" s="58">
-        <v>1</v>
-      </c>
-      <c r="L47" s="58" t="s">
+      <c r="L47" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M47" s="54" t="s">
+      <c r="M47" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="N47" s="4">
-        <v>9500</v>
+      <c r="N47" s="2">
+        <v>9700</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="58">
+      <c r="P47" s="3">
         <v>180000</v>
       </c>
-      <c r="Q47" s="58">
+      <c r="Q47" s="3">
         <v>16000</v>
       </c>
-      <c r="R47" s="58">
+      <c r="R47" s="3">
         <v>15000</v>
       </c>
-      <c r="S47" s="58">
+      <c r="S47" s="3">
         <v>16008</v>
       </c>
-      <c r="T47" s="50">
+      <c r="T47" s="44">
         <v>48</v>
       </c>
-      <c r="U47" s="50">
+      <c r="U47" s="44">
         <v>0</v>
       </c>
       <c r="V47" t="s">
         <v>57</v>
       </c>
-      <c r="W47" s="8" t="s">
+      <c r="W47" s="4" t="s">
         <v>98</v>
       </c>
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="57"/>
+      <c r="Y47" s="51"/>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="50">
+      <c r="A48" s="44">
         <v>20050011</v>
       </c>
       <c r="B48" s="3">
@@ -5569,67 +5544,67 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="61" t="s">
+      <c r="F48" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="53" t="s">
+      <c r="G48" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H48" s="3">
-        <v>2</v>
-      </c>
-      <c r="I48" s="51">
+      <c r="H48" s="45">
+        <v>11</v>
+      </c>
+      <c r="I48" s="45">
         <v>1980000</v>
       </c>
-      <c r="J48" s="41" t="s">
+      <c r="J48" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K48" s="58">
+      <c r="K48" s="3">
         <v>1</v>
       </c>
-      <c r="L48" s="58" t="s">
+      <c r="L48" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M48" s="54" t="s">
+      <c r="M48" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="N48" s="4">
-        <v>9500</v>
+      <c r="N48" s="2">
+        <v>9700</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="58">
+      <c r="P48" s="3">
         <v>180000</v>
       </c>
-      <c r="Q48" s="58">
+      <c r="Q48" s="3">
         <v>16000</v>
       </c>
-      <c r="R48" s="58">
+      <c r="R48" s="3">
         <v>15000</v>
       </c>
-      <c r="S48" s="58">
+      <c r="S48" s="3">
         <v>16008</v>
       </c>
-      <c r="T48" s="50">
+      <c r="T48" s="44">
         <v>48</v>
       </c>
-      <c r="U48" s="50">
+      <c r="U48" s="44">
         <v>0</v>
       </c>
       <c r="V48" t="s">
         <v>61</v>
       </c>
-      <c r="W48" s="8" t="s">
+      <c r="W48" s="4" t="s">
         <v>99</v>
       </c>
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="57"/>
+      <c r="Y48" s="51"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="50">
+      <c r="A49" s="44">
         <v>20050012</v>
       </c>
       <c r="B49" s="3">
@@ -5644,67 +5619,67 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="61" t="s">
+      <c r="F49" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="53" t="s">
+      <c r="G49" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H49" s="3">
-        <v>3</v>
-      </c>
-      <c r="I49" s="51">
+      <c r="H49" s="45">
+        <v>12</v>
+      </c>
+      <c r="I49" s="45">
         <v>1980000</v>
       </c>
-      <c r="J49" s="36" t="s">
+      <c r="J49" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="K49" s="58">
+      <c r="K49" s="3">
         <v>1</v>
       </c>
-      <c r="L49" s="58" t="s">
+      <c r="L49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M49" s="54" t="s">
+      <c r="M49" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="N49" s="4">
-        <v>9500</v>
+      <c r="N49" s="2">
+        <v>9700</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="58">
+      <c r="P49" s="3">
         <v>180000</v>
       </c>
-      <c r="Q49" s="58">
+      <c r="Q49" s="3">
         <v>16000</v>
       </c>
-      <c r="R49" s="58">
+      <c r="R49" s="3">
         <v>15000</v>
       </c>
-      <c r="S49" s="58">
+      <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="50">
+      <c r="T49" s="44">
         <v>48</v>
       </c>
-      <c r="U49" s="50">
+      <c r="U49" s="44">
         <v>0</v>
       </c>
       <c r="V49" t="s">
         <v>65</v>
       </c>
-      <c r="W49" s="8" t="s">
+      <c r="W49" s="4" t="s">
         <v>100</v>
       </c>
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="57"/>
+      <c r="Y49" s="51"/>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="50">
+      <c r="A50" s="44">
         <v>20060010</v>
       </c>
       <c r="B50" s="3">
@@ -5719,67 +5694,67 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="61" t="s">
+      <c r="F50" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="53" t="s">
+      <c r="G50" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H50" s="3">
-        <v>1</v>
-      </c>
-      <c r="I50" s="51">
+      <c r="H50" s="45">
+        <v>10</v>
+      </c>
+      <c r="I50" s="45">
         <v>1980000</v>
       </c>
-      <c r="J50" s="36" t="s">
+      <c r="J50" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K50" s="58">
-        <v>0</v>
-      </c>
-      <c r="L50" s="58" t="s">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="54" t="s">
+      <c r="M50" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="N50" s="4">
-        <v>9500</v>
+      <c r="N50" s="2">
+        <v>9700</v>
       </c>
       <c r="O50" s="3">
         <v>300</v>
       </c>
-      <c r="P50" s="58">
+      <c r="P50" s="3">
         <v>180000</v>
       </c>
-      <c r="Q50" s="58">
+      <c r="Q50" s="3">
         <v>16000</v>
       </c>
-      <c r="R50" s="58">
+      <c r="R50" s="3">
         <v>15000</v>
       </c>
-      <c r="S50" s="58">
+      <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="50">
+      <c r="T50" s="44">
         <v>20</v>
       </c>
-      <c r="U50" s="50">
+      <c r="U50" s="44">
         <v>0</v>
       </c>
       <c r="V50" t="s">
         <v>57</v>
       </c>
-      <c r="W50" s="8" t="s">
+      <c r="W50" s="4" t="s">
         <v>101</v>
       </c>
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="57"/>
+      <c r="Y50" s="51"/>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="50">
+      <c r="A51" s="44">
         <v>20060011</v>
       </c>
       <c r="B51" s="3">
@@ -5794,67 +5769,67 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="61" t="s">
+      <c r="F51" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="53" t="s">
+      <c r="G51" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H51" s="3">
-        <v>2</v>
-      </c>
-      <c r="I51" s="51">
+      <c r="H51" s="45">
+        <v>11</v>
+      </c>
+      <c r="I51" s="45">
         <v>1980000</v>
       </c>
-      <c r="J51" s="41" t="s">
+      <c r="J51" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="K51" s="58">
-        <v>0</v>
-      </c>
-      <c r="L51" s="58" t="s">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="54" t="s">
+      <c r="M51" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="N51" s="4">
-        <v>9500</v>
+      <c r="N51" s="2">
+        <v>9700</v>
       </c>
       <c r="O51" s="3">
         <v>300</v>
       </c>
-      <c r="P51" s="58">
+      <c r="P51" s="3">
         <v>180000</v>
       </c>
-      <c r="Q51" s="58">
+      <c r="Q51" s="3">
         <v>16000</v>
       </c>
-      <c r="R51" s="58">
+      <c r="R51" s="3">
         <v>15000</v>
       </c>
-      <c r="S51" s="58">
+      <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="50">
+      <c r="T51" s="44">
         <v>20</v>
       </c>
-      <c r="U51" s="50">
+      <c r="U51" s="44">
         <v>0</v>
       </c>
       <c r="V51" t="s">
         <v>61</v>
       </c>
-      <c r="W51" s="8" t="s">
+      <c r="W51" s="4" t="s">
         <v>102</v>
       </c>
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="57"/>
+      <c r="Y51" s="51"/>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="50">
+      <c r="A52" s="44">
         <v>20060012</v>
       </c>
       <c r="B52" s="3">
@@ -5869,19 +5844,19 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="61" t="s">
+      <c r="F52" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="53" t="s">
+      <c r="G52" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H52" s="3">
-        <v>3</v>
-      </c>
-      <c r="I52" s="51">
+      <c r="H52" s="45">
+        <v>12</v>
+      </c>
+      <c r="I52" s="45">
         <v>1980000</v>
       </c>
-      <c r="J52" s="36" t="s">
+      <c r="J52" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K52" s="3">
@@ -5890,11 +5865,11 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="54" t="s">
+      <c r="M52" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="N52" s="4">
-        <v>9500</v>
+      <c r="N52" s="2">
+        <v>9700</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
@@ -5911,25 +5886,25 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="50">
+      <c r="T52" s="44">
         <v>20</v>
       </c>
-      <c r="U52" s="50">
+      <c r="U52" s="44">
         <v>0</v>
       </c>
       <c r="V52" t="s">
         <v>65</v>
       </c>
-      <c r="W52" s="8" t="s">
+      <c r="W52" s="4" t="s">
         <v>103</v>
       </c>
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="57"/>
+      <c r="Y52" s="51"/>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="50">
+      <c r="A53" s="44">
         <v>20070010</v>
       </c>
       <c r="B53" s="3">
@@ -5944,19 +5919,19 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="61" t="s">
+      <c r="F53" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="53" t="s">
+      <c r="G53" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H53" s="3">
-        <v>1</v>
-      </c>
-      <c r="I53" s="51">
+      <c r="H53" s="45">
+        <v>10</v>
+      </c>
+      <c r="I53" s="45">
         <v>1980000</v>
       </c>
-      <c r="J53" s="36" t="s">
+      <c r="J53" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K53" s="3">
@@ -5965,11 +5940,11 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="54" t="s">
+      <c r="M53" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="N53" s="4">
-        <v>9500</v>
+      <c r="N53" s="2">
+        <v>9700</v>
       </c>
       <c r="O53" s="3">
         <v>300</v>
@@ -5986,25 +5961,25 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="50">
+      <c r="T53" s="44">
         <v>30</v>
       </c>
-      <c r="U53" s="50">
+      <c r="U53" s="44">
         <v>1</v>
       </c>
       <c r="V53" t="s">
         <v>57</v>
       </c>
-      <c r="W53" s="8" t="s">
+      <c r="W53" s="4" t="s">
         <v>104</v>
       </c>
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="57"/>
+      <c r="Y53" s="51"/>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="50">
+      <c r="A54" s="44">
         <v>20070011</v>
       </c>
       <c r="B54" s="3">
@@ -6019,19 +5994,19 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="61" t="s">
+      <c r="F54" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="53" t="s">
+      <c r="G54" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H54" s="3">
-        <v>2</v>
-      </c>
-      <c r="I54" s="51">
+      <c r="H54" s="45">
+        <v>11</v>
+      </c>
+      <c r="I54" s="45">
         <v>1980000</v>
       </c>
-      <c r="J54" s="41" t="s">
+      <c r="J54" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K54" s="3">
@@ -6040,11 +6015,11 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="54" t="s">
+      <c r="M54" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="N54" s="4">
-        <v>9500</v>
+      <c r="N54" s="2">
+        <v>9700</v>
       </c>
       <c r="O54" s="3">
         <v>300</v>
@@ -6061,25 +6036,25 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="50">
+      <c r="T54" s="44">
         <v>30</v>
       </c>
-      <c r="U54" s="50">
+      <c r="U54" s="44">
         <v>1</v>
       </c>
       <c r="V54" t="s">
         <v>61</v>
       </c>
-      <c r="W54" s="8" t="s">
+      <c r="W54" s="4" t="s">
         <v>105</v>
       </c>
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="57"/>
+      <c r="Y54" s="51"/>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="50">
+      <c r="A55" s="44">
         <v>20070012</v>
       </c>
       <c r="B55" s="3">
@@ -6094,19 +6069,19 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="61" t="s">
+      <c r="F55" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="53" t="s">
+      <c r="G55" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H55" s="3">
-        <v>3</v>
-      </c>
-      <c r="I55" s="51">
+      <c r="H55" s="45">
+        <v>12</v>
+      </c>
+      <c r="I55" s="45">
         <v>1980000</v>
       </c>
-      <c r="J55" s="36" t="s">
+      <c r="J55" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K55" s="3">
@@ -6115,11 +6090,11 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="54" t="s">
+      <c r="M55" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="N55" s="4">
-        <v>9500</v>
+      <c r="N55" s="2">
+        <v>9700</v>
       </c>
       <c r="O55" s="3">
         <v>300</v>
@@ -6136,25 +6111,25 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="50">
+      <c r="T55" s="44">
         <v>30</v>
       </c>
-      <c r="U55" s="50">
+      <c r="U55" s="44">
         <v>1</v>
       </c>
       <c r="V55" t="s">
         <v>65</v>
       </c>
-      <c r="W55" s="8" t="s">
+      <c r="W55" s="4" t="s">
         <v>106</v>
       </c>
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="57"/>
+      <c r="Y55" s="51"/>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="50">
+      <c r="A56" s="44">
         <v>20080010</v>
       </c>
       <c r="B56" s="3">
@@ -6169,19 +6144,19 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="61" t="s">
+      <c r="F56" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="53" t="s">
+      <c r="G56" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H56" s="3">
-        <v>1</v>
-      </c>
-      <c r="I56" s="51">
+      <c r="H56" s="45">
+        <v>10</v>
+      </c>
+      <c r="I56" s="45">
         <v>1980000</v>
       </c>
-      <c r="J56" s="36" t="s">
+      <c r="J56" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K56" s="3">
@@ -6190,11 +6165,11 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="54" t="s">
+      <c r="M56" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="N56" s="4">
-        <v>9500</v>
+      <c r="N56" s="2">
+        <v>9700</v>
       </c>
       <c r="O56" s="3">
         <v>300</v>
@@ -6211,25 +6186,25 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="50">
+      <c r="T56" s="44">
         <v>20</v>
       </c>
-      <c r="U56" s="50">
+      <c r="U56" s="44">
         <v>0</v>
       </c>
       <c r="V56" t="s">
         <v>57</v>
       </c>
-      <c r="W56" s="8" t="s">
+      <c r="W56" s="4" t="s">
         <v>107</v>
       </c>
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="57"/>
+      <c r="Y56" s="51"/>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="50">
+      <c r="A57" s="44">
         <v>20080011</v>
       </c>
       <c r="B57" s="3">
@@ -6244,19 +6219,19 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="61" t="s">
+      <c r="F57" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="53" t="s">
+      <c r="G57" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H57" s="3">
-        <v>2</v>
-      </c>
-      <c r="I57" s="51">
+      <c r="H57" s="45">
+        <v>11</v>
+      </c>
+      <c r="I57" s="45">
         <v>1980000</v>
       </c>
-      <c r="J57" s="41" t="s">
+      <c r="J57" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K57" s="3">
@@ -6265,11 +6240,11 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="54" t="s">
+      <c r="M57" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="N57" s="4">
-        <v>9500</v>
+      <c r="N57" s="2">
+        <v>9700</v>
       </c>
       <c r="O57" s="3">
         <v>300</v>
@@ -6286,25 +6261,25 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="50">
+      <c r="T57" s="44">
         <v>20</v>
       </c>
-      <c r="U57" s="50">
+      <c r="U57" s="44">
         <v>0</v>
       </c>
       <c r="V57" t="s">
         <v>61</v>
       </c>
-      <c r="W57" s="8" t="s">
+      <c r="W57" s="4" t="s">
         <v>86</v>
       </c>
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="57"/>
+      <c r="Y57" s="51"/>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="50">
+      <c r="A58" s="44">
         <v>20080012</v>
       </c>
       <c r="B58" s="3">
@@ -6319,19 +6294,19 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="53" t="s">
+      <c r="G58" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H58" s="3">
-        <v>3</v>
-      </c>
-      <c r="I58" s="51">
+      <c r="H58" s="45">
+        <v>12</v>
+      </c>
+      <c r="I58" s="45">
         <v>1980000</v>
       </c>
-      <c r="J58" s="36" t="s">
+      <c r="J58" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K58" s="3">
@@ -6340,11 +6315,11 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="54" t="s">
+      <c r="M58" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="N58" s="4">
-        <v>9500</v>
+      <c r="N58" s="2">
+        <v>9700</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -6361,25 +6336,25 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="50">
+      <c r="T58" s="44">
         <v>20</v>
       </c>
-      <c r="U58" s="50">
+      <c r="U58" s="44">
         <v>0</v>
       </c>
       <c r="V58" t="s">
         <v>65</v>
       </c>
-      <c r="W58" s="8" t="s">
+      <c r="W58" s="4" t="s">
         <v>87</v>
       </c>
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="57"/>
+      <c r="Y58" s="51"/>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:25">
-      <c r="A59" s="50">
+      <c r="A59" s="44">
         <v>20090010</v>
       </c>
       <c r="B59" s="3">
@@ -6394,19 +6369,19 @@
       <c r="E59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="61" t="s">
+      <c r="F59" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G59" s="53" t="s">
+      <c r="G59" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H59" s="3">
-        <v>1</v>
-      </c>
-      <c r="I59" s="51">
+      <c r="H59" s="45">
+        <v>10</v>
+      </c>
+      <c r="I59" s="45">
         <v>1980000</v>
       </c>
-      <c r="J59" s="36" t="s">
+      <c r="J59" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K59" s="3">
@@ -6415,11 +6390,11 @@
       <c r="L59" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M59" s="54" t="s">
+      <c r="M59" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="N59" s="4">
-        <v>9500</v>
+      <c r="N59" s="2">
+        <v>9700</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
@@ -6436,25 +6411,25 @@
       <c r="S59" s="3">
         <v>16008</v>
       </c>
-      <c r="T59" s="50">
+      <c r="T59" s="44">
         <v>20</v>
       </c>
-      <c r="U59" s="50">
+      <c r="U59" s="44">
         <v>0</v>
       </c>
       <c r="V59" t="s">
         <v>57</v>
       </c>
-      <c r="W59" s="8" t="s">
+      <c r="W59" s="4" t="s">
         <v>108</v>
       </c>
       <c r="X59" s="3">
         <v>1</v>
       </c>
-      <c r="Y59" s="57"/>
+      <c r="Y59" s="51"/>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:25">
-      <c r="A60" s="50">
+      <c r="A60" s="44">
         <v>20090011</v>
       </c>
       <c r="B60" s="3">
@@ -6469,19 +6444,19 @@
       <c r="E60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F60" s="61" t="s">
+      <c r="F60" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G60" s="53" t="s">
+      <c r="G60" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H60" s="3">
-        <v>2</v>
-      </c>
-      <c r="I60" s="51">
+      <c r="H60" s="45">
+        <v>11</v>
+      </c>
+      <c r="I60" s="45">
         <v>1980000</v>
       </c>
-      <c r="J60" s="41" t="s">
+      <c r="J60" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K60" s="3">
@@ -6490,11 +6465,11 @@
       <c r="L60" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M60" s="54" t="s">
+      <c r="M60" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="N60" s="4">
-        <v>9500</v>
+      <c r="N60" s="2">
+        <v>9700</v>
       </c>
       <c r="O60" s="3">
         <v>300</v>
@@ -6511,25 +6486,25 @@
       <c r="S60" s="3">
         <v>16008</v>
       </c>
-      <c r="T60" s="50">
+      <c r="T60" s="44">
         <v>20</v>
       </c>
-      <c r="U60" s="50">
+      <c r="U60" s="44">
         <v>0</v>
       </c>
       <c r="V60" t="s">
         <v>61</v>
       </c>
-      <c r="W60" s="8" t="s">
+      <c r="W60" s="4" t="s">
         <v>109</v>
       </c>
       <c r="X60" s="3">
         <v>1</v>
       </c>
-      <c r="Y60" s="57"/>
+      <c r="Y60" s="51"/>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:25">
-      <c r="A61" s="50">
+      <c r="A61" s="44">
         <v>20090012</v>
       </c>
       <c r="B61" s="3">
@@ -6544,19 +6519,19 @@
       <c r="E61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="61" t="s">
+      <c r="F61" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G61" s="53" t="s">
+      <c r="G61" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H61" s="3">
-        <v>3</v>
-      </c>
-      <c r="I61" s="51">
+      <c r="H61" s="45">
+        <v>12</v>
+      </c>
+      <c r="I61" s="45">
         <v>1980000</v>
       </c>
-      <c r="J61" s="36" t="s">
+      <c r="J61" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K61" s="3">
@@ -6565,11 +6540,11 @@
       <c r="L61" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M61" s="54" t="s">
+      <c r="M61" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="N61" s="4">
-        <v>9500</v>
+      <c r="N61" s="2">
+        <v>9700</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>
@@ -6586,28 +6561,28 @@
       <c r="S61" s="3">
         <v>16008</v>
       </c>
-      <c r="T61" s="50">
+      <c r="T61" s="44">
         <v>20</v>
       </c>
-      <c r="U61" s="50">
+      <c r="U61" s="44">
         <v>0</v>
       </c>
       <c r="V61" t="s">
         <v>65</v>
       </c>
-      <c r="W61" s="8" t="s">
+      <c r="W61" s="4" t="s">
         <v>110</v>
       </c>
       <c r="X61" s="3">
         <v>1</v>
       </c>
-      <c r="Y61" s="57"/>
+      <c r="Y61" s="51"/>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:25">
-      <c r="A62" s="50">
+      <c r="A62" s="44">
         <v>20120010</v>
       </c>
-      <c r="B62" s="49">
+      <c r="B62" s="43">
         <v>201200</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -6619,19 +6594,19 @@
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="61" t="s">
+      <c r="F62" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G62" s="53" t="s">
+      <c r="G62" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H62" s="3">
-        <v>1</v>
-      </c>
-      <c r="I62" s="51">
+      <c r="H62" s="45">
+        <v>10</v>
+      </c>
+      <c r="I62" s="45">
         <v>1980000</v>
       </c>
-      <c r="J62" s="36" t="s">
+      <c r="J62" s="32" t="s">
         <v>54</v>
       </c>
       <c r="K62" s="3">
@@ -6640,11 +6615,11 @@
       <c r="L62" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M62" s="54" t="s">
+      <c r="M62" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="N62" s="4">
-        <v>9500</v>
+      <c r="N62" s="2">
+        <v>9700</v>
       </c>
       <c r="O62" s="3">
         <v>300</v>
@@ -6661,28 +6636,28 @@
       <c r="S62" s="3">
         <v>16008</v>
       </c>
-      <c r="T62" s="50">
+      <c r="T62" s="44">
         <v>12</v>
       </c>
-      <c r="U62" s="50">
+      <c r="U62" s="44">
         <v>0</v>
       </c>
       <c r="V62" t="s">
         <v>57</v>
       </c>
-      <c r="W62" s="8" t="s">
+      <c r="W62" s="4" t="s">
         <v>108</v>
       </c>
       <c r="X62" s="3">
         <v>1</v>
       </c>
-      <c r="Y62" s="57"/>
+      <c r="Y62" s="51"/>
     </row>
     <row r="63" s="3" customFormat="1" spans="1:25">
-      <c r="A63" s="50">
+      <c r="A63" s="44">
         <v>20120011</v>
       </c>
-      <c r="B63" s="49">
+      <c r="B63" s="43">
         <v>201200</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -6694,19 +6669,19 @@
       <c r="E63" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="61" t="s">
+      <c r="F63" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G63" s="53" t="s">
+      <c r="G63" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H63" s="3">
-        <v>2</v>
-      </c>
-      <c r="I63" s="51">
+      <c r="H63" s="45">
+        <v>11</v>
+      </c>
+      <c r="I63" s="45">
         <v>1980000</v>
       </c>
-      <c r="J63" s="41" t="s">
+      <c r="J63" s="37" t="s">
         <v>60</v>
       </c>
       <c r="K63" s="3">
@@ -6715,11 +6690,11 @@
       <c r="L63" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M63" s="54" t="s">
+      <c r="M63" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="N63" s="4">
-        <v>9500</v>
+      <c r="N63" s="2">
+        <v>9700</v>
       </c>
       <c r="O63" s="3">
         <v>300</v>
@@ -6736,28 +6711,28 @@
       <c r="S63" s="3">
         <v>16008</v>
       </c>
-      <c r="T63" s="50">
+      <c r="T63" s="44">
         <v>12</v>
       </c>
-      <c r="U63" s="50">
+      <c r="U63" s="44">
         <v>0</v>
       </c>
       <c r="V63" t="s">
         <v>61</v>
       </c>
-      <c r="W63" s="8" t="s">
+      <c r="W63" s="4" t="s">
         <v>109</v>
       </c>
       <c r="X63" s="3">
         <v>1</v>
       </c>
-      <c r="Y63" s="57"/>
+      <c r="Y63" s="51"/>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:25">
-      <c r="A64" s="50">
+      <c r="A64" s="44">
         <v>20120012</v>
       </c>
-      <c r="B64" s="49">
+      <c r="B64" s="43">
         <v>201200</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -6769,19 +6744,19 @@
       <c r="E64" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F64" s="61" t="s">
+      <c r="F64" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G64" s="53" t="s">
+      <c r="G64" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H64" s="3">
-        <v>3</v>
-      </c>
-      <c r="I64" s="51">
+      <c r="H64" s="45">
+        <v>12</v>
+      </c>
+      <c r="I64" s="45">
         <v>1980000</v>
       </c>
-      <c r="J64" s="36" t="s">
+      <c r="J64" s="32" t="s">
         <v>64</v>
       </c>
       <c r="K64" s="3">
@@ -6790,11 +6765,11 @@
       <c r="L64" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M64" s="54" t="s">
+      <c r="M64" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="N64" s="4">
-        <v>9500</v>
+      <c r="N64" s="2">
+        <v>9700</v>
       </c>
       <c r="O64" s="3">
         <v>300</v>
@@ -6811,25 +6786,2395 @@
       <c r="S64" s="3">
         <v>16008</v>
       </c>
-      <c r="T64" s="50">
+      <c r="T64" s="44">
         <v>12</v>
       </c>
-      <c r="U64" s="50">
+      <c r="U64" s="44">
         <v>0</v>
       </c>
       <c r="V64" t="s">
         <v>65</v>
       </c>
-      <c r="W64" s="8" t="s">
+      <c r="W64" s="4" t="s">
         <v>110</v>
       </c>
       <c r="X64" s="3">
         <v>1</v>
       </c>
-      <c r="Y64" s="57"/>
+      <c r="Y64" s="51"/>
+    </row>
+    <row r="65" spans="1:25">
+      <c r="A65" s="2">
+        <f>B65*100+H65</f>
+        <v>20010021</v>
+      </c>
+      <c r="B65" s="28">
+        <v>200100</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D65" s="28">
+        <v>200100038</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F65" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G65" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H65" s="28">
+        <v>21</v>
+      </c>
+      <c r="I65" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J65" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K65" s="2">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M65" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="N65" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R65" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S65" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T65" s="5">
+        <v>48</v>
+      </c>
+      <c r="U65" s="35">
+        <v>0</v>
+      </c>
+      <c r="V65" t="s">
+        <v>57</v>
+      </c>
+      <c r="W65" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X65" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25">
+      <c r="A66" s="2">
+        <f t="shared" ref="A66:A94" si="6">B66*100+H66</f>
+        <v>20010022</v>
+      </c>
+      <c r="B66" s="36">
+        <v>200100</v>
+      </c>
+      <c r="C66" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" s="36">
+        <v>200100038</v>
+      </c>
+      <c r="E66" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G66" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H66" s="28">
+        <v>22</v>
+      </c>
+      <c r="I66" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J66" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K66" s="2">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M66" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="N66" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O66" s="3">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R66" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S66" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T66" s="5">
+        <v>48</v>
+      </c>
+      <c r="U66" s="35">
+        <v>0</v>
+      </c>
+      <c r="V66" t="s">
+        <v>61</v>
+      </c>
+      <c r="W66" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X66" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="4">
+        <f t="shared" ref="Y66:Y70" si="7">Y65*10</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" spans="1:25">
+      <c r="A67" s="2">
+        <f t="shared" si="6"/>
+        <v>20010023</v>
+      </c>
+      <c r="B67" s="28">
+        <v>200100</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D67" s="28">
+        <v>200100038</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F67" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G67" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H67" s="28">
+        <v>23</v>
+      </c>
+      <c r="I67" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J67" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M67" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="N67" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O67" s="3">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R67" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S67" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T67" s="5">
+        <v>48</v>
+      </c>
+      <c r="U67" s="35">
+        <v>0</v>
+      </c>
+      <c r="V67" t="s">
+        <v>65</v>
+      </c>
+      <c r="W67" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X67" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="4">
+        <f t="shared" si="7"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" spans="1:25">
+      <c r="A68" s="2">
+        <f t="shared" si="6"/>
+        <v>20010121</v>
+      </c>
+      <c r="B68" s="28">
+        <v>200101</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D68" s="28">
+        <v>200101001</v>
+      </c>
+      <c r="E68" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="F68" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G68" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H68" s="28">
+        <v>21</v>
+      </c>
+      <c r="I68" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J68" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K68" s="2">
+        <v>0</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M68" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="N68" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R68" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S68" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T68" s="5">
+        <v>48</v>
+      </c>
+      <c r="U68" s="35">
+        <v>0</v>
+      </c>
+      <c r="V68" t="s">
+        <v>57</v>
+      </c>
+      <c r="W68" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X68" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25">
+      <c r="A69" s="2">
+        <f t="shared" si="6"/>
+        <v>20010122</v>
+      </c>
+      <c r="B69" s="36">
+        <v>200101</v>
+      </c>
+      <c r="C69" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D69" s="36">
+        <v>200101001</v>
+      </c>
+      <c r="E69" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F69" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H69" s="28">
+        <v>22</v>
+      </c>
+      <c r="I69" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J69" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K69" s="2">
+        <v>0</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M69" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="N69" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R69" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S69" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T69" s="5">
+        <v>48</v>
+      </c>
+      <c r="U69" s="35">
+        <v>0</v>
+      </c>
+      <c r="V69" t="s">
+        <v>61</v>
+      </c>
+      <c r="W69" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X69" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="4">
+        <f t="shared" si="7"/>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25">
+      <c r="A70" s="2">
+        <f t="shared" si="6"/>
+        <v>20010123</v>
+      </c>
+      <c r="B70" s="28">
+        <v>200101</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D70" s="28">
+        <v>200101001</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F70" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G70" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H70" s="28">
+        <v>23</v>
+      </c>
+      <c r="I70" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J70" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K70" s="2">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M70" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="N70" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R70" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S70" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T70" s="5">
+        <v>48</v>
+      </c>
+      <c r="U70" s="35">
+        <v>0</v>
+      </c>
+      <c r="V70" t="s">
+        <v>65</v>
+      </c>
+      <c r="W70" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X70" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="4">
+        <f t="shared" si="7"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25">
+      <c r="A71" s="2">
+        <f t="shared" si="6"/>
+        <v>20030021</v>
+      </c>
+      <c r="B71" s="28">
+        <v>200300</v>
+      </c>
+      <c r="C71" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="28">
+        <v>200300001</v>
+      </c>
+      <c r="E71" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F71" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G71" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71" s="28">
+        <v>21</v>
+      </c>
+      <c r="I71" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J71" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K71" s="2">
+        <v>0</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M71" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="N71" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R71" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S71" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T71" s="5">
+        <v>50</v>
+      </c>
+      <c r="U71" s="35">
+        <v>0</v>
+      </c>
+      <c r="V71" t="s">
+        <v>57</v>
+      </c>
+      <c r="W71" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X71" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:25">
+      <c r="A72" s="2">
+        <f t="shared" si="6"/>
+        <v>20030022</v>
+      </c>
+      <c r="B72" s="36">
+        <v>200300</v>
+      </c>
+      <c r="C72" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" s="36">
+        <v>200300001</v>
+      </c>
+      <c r="E72" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F72" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G72" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H72" s="28">
+        <v>22</v>
+      </c>
+      <c r="I72" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J72" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K72" s="2">
+        <v>0</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M72" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="N72" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R72" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S72" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T72" s="5">
+        <v>50</v>
+      </c>
+      <c r="U72" s="35">
+        <v>0</v>
+      </c>
+      <c r="V72" t="s">
+        <v>61</v>
+      </c>
+      <c r="W72" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X72" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="4">
+        <f t="shared" ref="Y72:Y76" si="8">Y71*10</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25">
+      <c r="A73" s="2">
+        <f t="shared" si="6"/>
+        <v>20030023</v>
+      </c>
+      <c r="B73" s="28">
+        <v>200300</v>
+      </c>
+      <c r="C73" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D73" s="28">
+        <v>200300001</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F73" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G73" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H73" s="28">
+        <v>23</v>
+      </c>
+      <c r="I73" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J73" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K73" s="2">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M73" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="N73" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R73" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S73" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T73" s="5">
+        <v>50</v>
+      </c>
+      <c r="U73" s="35">
+        <v>0</v>
+      </c>
+      <c r="V73" t="s">
+        <v>65</v>
+      </c>
+      <c r="W73" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X73" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="4">
+        <f t="shared" si="8"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25">
+      <c r="A74" s="2">
+        <f t="shared" si="6"/>
+        <v>20040021</v>
+      </c>
+      <c r="B74" s="28">
+        <v>200400</v>
+      </c>
+      <c r="C74" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D74" s="28">
+        <v>200400009</v>
+      </c>
+      <c r="E74" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="F74" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G74" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H74" s="28">
+        <v>21</v>
+      </c>
+      <c r="I74" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J74" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K74" s="2">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M74" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="N74" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R74" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S74" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T74" s="5">
+        <v>50</v>
+      </c>
+      <c r="U74" s="35">
+        <v>0</v>
+      </c>
+      <c r="V74" t="s">
+        <v>57</v>
+      </c>
+      <c r="W74" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X74" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25">
+      <c r="A75" s="2">
+        <f t="shared" si="6"/>
+        <v>20040022</v>
+      </c>
+      <c r="B75" s="36">
+        <v>200400</v>
+      </c>
+      <c r="C75" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D75" s="36">
+        <v>200400009</v>
+      </c>
+      <c r="E75" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F75" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G75" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H75" s="28">
+        <v>22</v>
+      </c>
+      <c r="I75" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J75" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K75" s="2">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M75" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="N75" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R75" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S75" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T75" s="5">
+        <v>50</v>
+      </c>
+      <c r="U75" s="35">
+        <v>0</v>
+      </c>
+      <c r="V75" t="s">
+        <v>61</v>
+      </c>
+      <c r="W75" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X75" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="4">
+        <f t="shared" si="8"/>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" spans="1:25">
+      <c r="A76" s="2">
+        <f t="shared" si="6"/>
+        <v>20040023</v>
+      </c>
+      <c r="B76" s="28">
+        <v>200400</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D76" s="28">
+        <v>200400009</v>
+      </c>
+      <c r="E76" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F76" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G76" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H76" s="28">
+        <v>23</v>
+      </c>
+      <c r="I76" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J76" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K76" s="2">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M76" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="N76" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O76" s="3">
+        <v>0</v>
+      </c>
+      <c r="P76" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R76" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S76" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T76" s="5">
+        <v>50</v>
+      </c>
+      <c r="U76" s="35">
+        <v>0</v>
+      </c>
+      <c r="V76" t="s">
+        <v>65</v>
+      </c>
+      <c r="W76" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X76" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="4">
+        <f t="shared" si="8"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" spans="1:25">
+      <c r="A77" s="2">
+        <f t="shared" si="6"/>
+        <v>20050021</v>
+      </c>
+      <c r="B77" s="28">
+        <v>200500</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D77" s="28">
+        <v>200500025</v>
+      </c>
+      <c r="E77" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F77" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G77" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H77" s="28">
+        <v>21</v>
+      </c>
+      <c r="I77" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J77" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K77" s="2">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M77" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="N77" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R77" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S77" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T77" s="5">
+        <v>48</v>
+      </c>
+      <c r="U77" s="35">
+        <v>0</v>
+      </c>
+      <c r="V77" t="s">
+        <v>57</v>
+      </c>
+      <c r="W77" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X77" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25">
+      <c r="A78" s="2">
+        <f t="shared" si="6"/>
+        <v>20050022</v>
+      </c>
+      <c r="B78" s="36">
+        <v>200500</v>
+      </c>
+      <c r="C78" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D78" s="36">
+        <v>200500025</v>
+      </c>
+      <c r="E78" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F78" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G78" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="28">
+        <v>22</v>
+      </c>
+      <c r="I78" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J78" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K78" s="2">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M78" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="N78" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O78" s="3">
+        <v>0</v>
+      </c>
+      <c r="P78" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R78" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S78" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T78" s="5">
+        <v>48</v>
+      </c>
+      <c r="U78" s="35">
+        <v>0</v>
+      </c>
+      <c r="V78" t="s">
+        <v>61</v>
+      </c>
+      <c r="W78" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X78" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="4">
+        <f t="shared" ref="Y78:Y82" si="9">Y77*10</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25">
+      <c r="A79" s="2">
+        <f t="shared" si="6"/>
+        <v>20050023</v>
+      </c>
+      <c r="B79" s="28">
+        <v>200500</v>
+      </c>
+      <c r="C79" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D79" s="28">
+        <v>200500025</v>
+      </c>
+      <c r="E79" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F79" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G79" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" s="28">
+        <v>23</v>
+      </c>
+      <c r="I79" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J79" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K79" s="2">
+        <v>1</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M79" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="N79" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O79" s="3">
+        <v>0</v>
+      </c>
+      <c r="P79" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R79" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S79" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T79" s="5">
+        <v>48</v>
+      </c>
+      <c r="U79" s="35">
+        <v>0</v>
+      </c>
+      <c r="V79" t="s">
+        <v>65</v>
+      </c>
+      <c r="W79" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X79" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="4">
+        <f t="shared" si="9"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25">
+      <c r="A80" s="2">
+        <f t="shared" si="6"/>
+        <v>20060021</v>
+      </c>
+      <c r="B80" s="28">
+        <v>200600</v>
+      </c>
+      <c r="C80" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D80" s="28">
+        <v>200600001</v>
+      </c>
+      <c r="E80" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F80" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G80" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" s="28">
+        <v>21</v>
+      </c>
+      <c r="I80" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J80" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K80" s="2">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M80" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="N80" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O80" s="3">
+        <v>0</v>
+      </c>
+      <c r="P80" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R80" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S80" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T80" s="5">
+        <v>20</v>
+      </c>
+      <c r="U80" s="35">
+        <v>0</v>
+      </c>
+      <c r="V80" t="s">
+        <v>57</v>
+      </c>
+      <c r="W80" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X80" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="81" s="2" customFormat="1" spans="1:25">
+      <c r="A81" s="2">
+        <f t="shared" si="6"/>
+        <v>20060022</v>
+      </c>
+      <c r="B81" s="36">
+        <v>200600</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D81" s="36">
+        <v>200600001</v>
+      </c>
+      <c r="E81" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F81" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G81" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="28">
+        <v>22</v>
+      </c>
+      <c r="I81" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J81" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K81" s="2">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M81" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="N81" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q81" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R81" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S81" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T81" s="5">
+        <v>20</v>
+      </c>
+      <c r="U81" s="35">
+        <v>0</v>
+      </c>
+      <c r="V81" t="s">
+        <v>61</v>
+      </c>
+      <c r="W81" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X81" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="4">
+        <f t="shared" si="9"/>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25">
+      <c r="A82" s="2">
+        <f t="shared" si="6"/>
+        <v>20060023</v>
+      </c>
+      <c r="B82" s="28">
+        <v>200600</v>
+      </c>
+      <c r="C82" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D82" s="28">
+        <v>200600001</v>
+      </c>
+      <c r="E82" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F82" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G82" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H82" s="28">
+        <v>23</v>
+      </c>
+      <c r="I82" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J82" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K82" s="2">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M82" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="N82" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O82" s="3">
+        <v>0</v>
+      </c>
+      <c r="P82" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q82" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R82" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S82" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T82" s="5">
+        <v>20</v>
+      </c>
+      <c r="U82" s="35">
+        <v>0</v>
+      </c>
+      <c r="V82" t="s">
+        <v>65</v>
+      </c>
+      <c r="W82" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X82" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="4">
+        <f t="shared" si="9"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25">
+      <c r="A83" s="2">
+        <f t="shared" si="6"/>
+        <v>20070021</v>
+      </c>
+      <c r="B83" s="28">
+        <v>200700</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D83" s="28">
+        <v>200700001</v>
+      </c>
+      <c r="E83" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F83" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G83" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H83" s="28">
+        <v>21</v>
+      </c>
+      <c r="I83" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J83" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K83" s="2">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M83" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="N83" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q83" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R83" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S83" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T83" s="5">
+        <v>30</v>
+      </c>
+      <c r="U83" s="35">
+        <v>1</v>
+      </c>
+      <c r="V83" t="s">
+        <v>57</v>
+      </c>
+      <c r="W83" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X83" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25">
+      <c r="A84" s="2">
+        <f t="shared" si="6"/>
+        <v>20070022</v>
+      </c>
+      <c r="B84" s="36">
+        <v>200700</v>
+      </c>
+      <c r="C84" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D84" s="36">
+        <v>200700001</v>
+      </c>
+      <c r="E84" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F84" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G84" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84" s="28">
+        <v>22</v>
+      </c>
+      <c r="I84" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J84" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K84" s="2">
+        <v>1</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M84" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="N84" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q84" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R84" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S84" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T84" s="5">
+        <v>30</v>
+      </c>
+      <c r="U84" s="35">
+        <v>1</v>
+      </c>
+      <c r="V84" t="s">
+        <v>61</v>
+      </c>
+      <c r="W84" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X84" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="4">
+        <f t="shared" ref="Y84:Y88" si="10">Y83*10</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" spans="1:25">
+      <c r="A85" s="2">
+        <f t="shared" si="6"/>
+        <v>20070023</v>
+      </c>
+      <c r="B85" s="28">
+        <v>200700</v>
+      </c>
+      <c r="C85" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D85" s="28">
+        <v>200700001</v>
+      </c>
+      <c r="E85" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F85" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G85" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" s="28">
+        <v>23</v>
+      </c>
+      <c r="I85" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J85" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K85" s="2">
+        <v>1</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M85" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="N85" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q85" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R85" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S85" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T85" s="5">
+        <v>30</v>
+      </c>
+      <c r="U85" s="35">
+        <v>1</v>
+      </c>
+      <c r="V85" t="s">
+        <v>65</v>
+      </c>
+      <c r="W85" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X85" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="4">
+        <f t="shared" si="10"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="86" s="2" customFormat="1" spans="1:25">
+      <c r="A86" s="2">
+        <f t="shared" si="6"/>
+        <v>20080021</v>
+      </c>
+      <c r="B86" s="28">
+        <v>200800</v>
+      </c>
+      <c r="C86" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D86" s="28">
+        <v>200800001</v>
+      </c>
+      <c r="E86" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F86" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G86" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86" s="28">
+        <v>21</v>
+      </c>
+      <c r="I86" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J86" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K86" s="2">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M86" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="N86" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R86" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S86" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T86" s="5">
+        <v>20</v>
+      </c>
+      <c r="U86" s="35">
+        <v>0</v>
+      </c>
+      <c r="V86" t="s">
+        <v>57</v>
+      </c>
+      <c r="W86" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X86" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" spans="1:25">
+      <c r="A87" s="2">
+        <f t="shared" si="6"/>
+        <v>20080022</v>
+      </c>
+      <c r="B87" s="28">
+        <v>200800</v>
+      </c>
+      <c r="C87" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D87" s="28">
+        <v>200800001</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F87" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G87" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" s="28">
+        <v>22</v>
+      </c>
+      <c r="I87" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J87" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K87" s="2">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M87" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="N87" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q87" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R87" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S87" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T87" s="5">
+        <v>20</v>
+      </c>
+      <c r="U87" s="35">
+        <v>0</v>
+      </c>
+      <c r="V87" t="s">
+        <v>61</v>
+      </c>
+      <c r="W87" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X87" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="4">
+        <f t="shared" si="10"/>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" spans="1:25">
+      <c r="A88" s="2">
+        <f t="shared" si="6"/>
+        <v>20080023</v>
+      </c>
+      <c r="B88" s="28">
+        <v>200800</v>
+      </c>
+      <c r="C88" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88" s="28">
+        <v>200800001</v>
+      </c>
+      <c r="E88" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F88" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G88" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H88" s="28">
+        <v>23</v>
+      </c>
+      <c r="I88" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J88" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K88" s="2">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M88" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="N88" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q88" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R88" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S88" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T88" s="5">
+        <v>20</v>
+      </c>
+      <c r="U88" s="35">
+        <v>0</v>
+      </c>
+      <c r="V88" t="s">
+        <v>65</v>
+      </c>
+      <c r="W88" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X88" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="4">
+        <f t="shared" si="10"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" spans="1:25">
+      <c r="A89" s="2">
+        <f t="shared" si="6"/>
+        <v>20090021</v>
+      </c>
+      <c r="B89" s="40">
+        <v>200900</v>
+      </c>
+      <c r="C89" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" s="28">
+        <v>200900001</v>
+      </c>
+      <c r="E89" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="F89" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G89" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H89" s="28">
+        <v>21</v>
+      </c>
+      <c r="I89" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J89" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K89" s="41">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M89" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="N89" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q89" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R89" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S89" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T89" s="5">
+        <v>20</v>
+      </c>
+      <c r="U89" s="35">
+        <v>0</v>
+      </c>
+      <c r="V89" t="s">
+        <v>57</v>
+      </c>
+      <c r="W89" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X89" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25">
+      <c r="A90" s="2">
+        <f t="shared" si="6"/>
+        <v>20090022</v>
+      </c>
+      <c r="B90" s="42">
+        <v>200900</v>
+      </c>
+      <c r="C90" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D90" s="36">
+        <v>200900001</v>
+      </c>
+      <c r="E90" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F90" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G90" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H90" s="28">
+        <v>22</v>
+      </c>
+      <c r="I90" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J90" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K90" s="41">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M90" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="N90" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O90" s="3">
+        <v>0</v>
+      </c>
+      <c r="P90" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q90" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R90" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S90" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T90" s="5">
+        <v>20</v>
+      </c>
+      <c r="U90" s="35">
+        <v>0</v>
+      </c>
+      <c r="V90" t="s">
+        <v>61</v>
+      </c>
+      <c r="W90" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X90" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="4">
+        <f t="shared" ref="Y90:Y94" si="11">Y89*10</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25">
+      <c r="A91" s="2">
+        <f t="shared" si="6"/>
+        <v>20090023</v>
+      </c>
+      <c r="B91" s="40">
+        <v>200900</v>
+      </c>
+      <c r="C91" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" s="28">
+        <v>200900001</v>
+      </c>
+      <c r="E91" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F91" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G91" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H91" s="28">
+        <v>23</v>
+      </c>
+      <c r="I91" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J91" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K91" s="41">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M91" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="N91" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q91" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R91" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S91" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T91" s="5">
+        <v>20</v>
+      </c>
+      <c r="U91" s="35">
+        <v>0</v>
+      </c>
+      <c r="V91" t="s">
+        <v>65</v>
+      </c>
+      <c r="W91" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X91" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="4">
+        <f t="shared" si="11"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" spans="1:25">
+      <c r="A92" s="2">
+        <f t="shared" si="6"/>
+        <v>20120021</v>
+      </c>
+      <c r="B92" s="43">
+        <v>201200</v>
+      </c>
+      <c r="C92" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D92" s="36">
+        <v>201200001</v>
+      </c>
+      <c r="E92" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="F92" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G92" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H92" s="28">
+        <v>21</v>
+      </c>
+      <c r="I92" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J92" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="K92" s="41">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M92" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="N92" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q92" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R92" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S92" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T92" s="5">
+        <v>12</v>
+      </c>
+      <c r="U92" s="35">
+        <v>0</v>
+      </c>
+      <c r="V92" t="s">
+        <v>57</v>
+      </c>
+      <c r="W92" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X92" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="4">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25">
+      <c r="A93" s="2">
+        <f t="shared" si="6"/>
+        <v>20120022</v>
+      </c>
+      <c r="B93" s="43">
+        <v>201200</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D93" s="36">
+        <v>201200001</v>
+      </c>
+      <c r="E93" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F93" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G93" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H93" s="28">
+        <v>22</v>
+      </c>
+      <c r="I93" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J93" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K93" s="41">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M93" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="N93" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q93" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R93" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S93" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T93" s="5">
+        <v>12</v>
+      </c>
+      <c r="U93" s="35">
+        <v>0</v>
+      </c>
+      <c r="V93" t="s">
+        <v>61</v>
+      </c>
+      <c r="W93" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X93" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="4">
+        <f t="shared" si="11"/>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25">
+      <c r="A94" s="2">
+        <f t="shared" si="6"/>
+        <v>20120023</v>
+      </c>
+      <c r="B94" s="43">
+        <v>201200</v>
+      </c>
+      <c r="C94" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D94" s="36">
+        <v>201200001</v>
+      </c>
+      <c r="E94" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G94" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H94" s="28">
+        <v>23</v>
+      </c>
+      <c r="I94" s="31">
+        <v>1990000</v>
+      </c>
+      <c r="J94" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K94" s="41">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M94" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="N94" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="2">
+        <v>180000</v>
+      </c>
+      <c r="Q94" s="2">
+        <v>16000</v>
+      </c>
+      <c r="R94" s="2">
+        <v>15000</v>
+      </c>
+      <c r="S94" s="34">
+        <v>16008</v>
+      </c>
+      <c r="T94" s="5">
+        <v>12</v>
+      </c>
+      <c r="U94" s="35">
+        <v>0</v>
+      </c>
+      <c r="V94" t="s">
+        <v>65</v>
+      </c>
+      <c r="W94" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="4">
+        <f t="shared" si="11"/>
+        <v>1000000000</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S64" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S94" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
